--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="826">
   <si>
     <t xml:space="preserve">Assumptions Drivers — Col A Baseline Yes/No. Col E/H = source page link. Cols I/J/K = plain Verbatim Ctrl+F strings. Converse pass: driver must match sourced figure or a justified gap; else driver was reset to the source.</t>
   </si>
@@ -1641,6 +1641,9 @@
   </si>
   <si>
     <t xml:space="preserve">Sponsor equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side note: Sponsor equity is the capital contributed by the private equity firm—totaling $1,871.3 million (or 1.88x EBITDA)—used to fund the acquisition alongside the various debt and cash sources.</t>
   </si>
   <si>
     <t xml:space="preserve">% of offer value</t>
@@ -6111,7 +6114,7 @@
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="84" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C2" s="85"/>
       <c r="D2" s="85"/>
@@ -6119,7 +6122,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="386" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6127,7 +6130,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="111" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E5" s="387" t="n">
         <f aca="false">LBO!H20</f>
@@ -6137,12 +6140,12 @@
         <v>5.0625</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="389" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E6" s="390" t="n">
         <f aca="false">LBO!D8</f>
@@ -6154,7 +6157,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="91" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E7" s="391" t="n">
         <f aca="false">LBO!H18</f>
@@ -6166,7 +6169,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="111" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E8" s="346" t="n">
         <v>0</v>
@@ -6174,7 +6177,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="111" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E9" s="332" t="n">
         <v>0</v>
@@ -6182,7 +6185,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="111" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E10" s="256" t="n">
         <v>0</v>
@@ -6190,7 +6193,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="111" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E11" s="256" t="n">
         <v>0</v>
@@ -6198,7 +6201,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="111" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E12" s="391" t="n">
         <v>0</v>
@@ -6210,7 +6213,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="392" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D14" s="116"/>
       <c r="E14" s="393" t="n">
@@ -6228,7 +6231,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="157" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C16" s="81"/>
       <c r="D16" s="133"/>
@@ -6236,7 +6239,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C17" s="209"/>
       <c r="D17" s="209"/>
@@ -6332,12 +6335,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="399" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B2" s="317"/>
       <c r="C2" s="317"/>
@@ -6347,7 +6350,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E4" s="400" t="n">
         <v>12.51</v>
@@ -6355,7 +6358,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E5" s="400" t="n">
         <v>2.54</v>
@@ -6363,27 +6366,27 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="329" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B7" s="329" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C7" s="329" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D7" s="329" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E7" s="329" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F7" s="329" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14230,7 +14233,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="9.18"/>
   </cols>
@@ -14785,7 +14788,7 @@
       <c r="P34" s="123"/>
       <c r="R34" s="124"/>
     </row>
-    <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="111" t="s">
         <v>536</v>
       </c>
@@ -14795,9 +14798,12 @@
       <c r="D35" s="133" t="n">
         <v>1871.3</v>
       </c>
+      <c r="E35" s="128" t="s">
+        <v>537</v>
+      </c>
       <c r="F35" s="111"/>
       <c r="G35" s="126" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H35" s="126" t="s">
         <v>522</v>
@@ -14807,7 +14813,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="137" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C36" s="138" t="n">
         <v>9.34910381783165</v>
@@ -14816,7 +14822,7 @@
         <v>2916.7</v>
       </c>
       <c r="F36" s="135" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G36" s="113" t="n">
         <v>0.02</v>
@@ -14827,10 +14833,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B38" s="89" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C38" s="139"/>
       <c r="D38" s="81"/>
@@ -14843,7 +14849,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C39" s="140" t="n">
         <v>2011</v>
@@ -14872,7 +14878,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="143" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C40" s="144" t="n">
         <v>40633</v>
@@ -14941,7 +14947,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C43" s="148" t="n">
         <v>-485.2</v>
@@ -14970,7 +14976,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="123" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C44" s="149" t="n">
         <v>1580.1</v>
@@ -14999,7 +15005,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C45" s="148" t="n">
         <v>-181.6</v>
@@ -15028,7 +15034,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C46" s="148" t="n">
         <v>-865.7</v>
@@ -15057,7 +15063,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C47" s="148"/>
       <c r="D47" s="148"/>
@@ -15080,7 +15086,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="123" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C48" s="149" t="n">
         <v>532.8</v>
@@ -15110,7 +15116,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C49" s="148" t="n">
         <v>15</v>
@@ -15139,7 +15145,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C50" s="148" t="n">
         <v>-19.8</v>
@@ -15168,7 +15174,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C51" s="148" t="n">
         <v>3.3</v>
@@ -15197,7 +15203,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="123" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C52" s="149" t="n">
         <v>531.3</v>
@@ -15226,7 +15232,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C53" s="148" t="n">
         <v>-75.1</v>
@@ -15294,7 +15300,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="150" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C56" s="103"/>
       <c r="D56" s="103"/>
@@ -15307,7 +15313,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="137" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C57" s="124" t="n">
         <v>532.8</v>
@@ -15336,7 +15342,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="111" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C58" s="148" t="n">
         <v>190</v>
@@ -15365,7 +15371,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="111" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C59" s="148"/>
       <c r="D59" s="148"/>
@@ -15388,7 +15394,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="111" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C60" s="148" t="n">
         <v>106.5</v>
@@ -15417,7 +15423,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="111" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C61" s="148" t="n">
         <v>14.3</v>
@@ -15478,11 +15484,11 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="150" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F64" s="116"/>
       <c r="K64" s="153" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15515,7 +15521,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="154" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C66" s="117" t="n">
         <v>0.765070449813586</v>
@@ -15547,7 +15553,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="154" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C67" s="117" t="n">
         <v>0.0879291144143708</v>
@@ -15579,7 +15585,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="154" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C68" s="117" t="n">
         <v>0.419164286060136</v>
@@ -15643,7 +15649,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="154" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C70" s="117" t="n">
         <v>0.0694942903752039</v>
@@ -15686,7 +15692,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="157" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C72" s="158"/>
       <c r="D72" s="158"/>
@@ -15699,7 +15705,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C73" s="156"/>
       <c r="D73" s="140" t="n">
@@ -15726,7 +15732,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="143" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C74" s="158"/>
       <c r="D74" s="145" t="n">
@@ -15764,7 +15770,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="152" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C76" s="159"/>
       <c r="D76" s="160" t="n">
@@ -15791,7 +15797,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="161" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C77" s="117"/>
       <c r="D77" s="117" t="n">
@@ -15818,7 +15824,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="152" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C78" s="159"/>
       <c r="D78" s="160" t="n">
@@ -15845,7 +15851,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="161" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C79" s="117"/>
       <c r="D79" s="117" t="n">
@@ -15872,7 +15878,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="152" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C80" s="159"/>
       <c r="D80" s="160" t="n">
@@ -15899,7 +15905,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="161" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C81" s="117"/>
       <c r="D81" s="117" t="n">
@@ -15926,7 +15932,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="152" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C82" s="162"/>
       <c r="D82" s="160" t="n">
@@ -15953,7 +15959,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="161" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C83" s="117"/>
       <c r="D83" s="117" t="n">
@@ -15986,7 +15992,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="136" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C85" s="93"/>
       <c r="D85" s="163" t="n">
@@ -16022,7 +16028,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B87" s="157" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C87" s="164"/>
       <c r="D87" s="164"/>
@@ -16035,7 +16041,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B88" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C88" s="140" t="n">
         <v>2011</v>
@@ -16064,7 +16070,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B89" s="143" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C89" s="145" t="n">
         <v>40633</v>
@@ -16096,7 +16102,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B91" s="152" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C91" s="123"/>
       <c r="D91" s="160" t="n">
@@ -16124,7 +16130,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B92" s="161" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C92" s="148" t="n">
         <v>22</v>
@@ -16154,7 +16160,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="161" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C93" s="148" t="n">
         <v>-39.1</v>
@@ -16181,13 +16187,13 @@
         <v>-31</v>
       </c>
       <c r="K93" s="153" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L93" s="116"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="166" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C94" s="155" t="n">
         <v>0.0106522054907277</v>
@@ -16214,12 +16220,12 @@
         <v>0.0110563932027424</v>
       </c>
       <c r="K94" s="167" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="166" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C95" s="168" t="n">
         <v>1.77727272727273</v>
@@ -16257,7 +16263,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B97" s="152" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C97" s="170"/>
       <c r="D97" s="160" t="n">
@@ -16284,7 +16290,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="161" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C98" s="148" t="n">
         <v>115.8</v>
@@ -16313,7 +16319,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="161" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C99" s="148" t="n">
         <v>-75.7</v>
@@ -16340,12 +16346,12 @@
         <v>-135</v>
       </c>
       <c r="K99" s="153" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B100" s="166" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C100" s="155" t="n">
         <v>0.0560693361739215</v>
@@ -16372,12 +16378,12 @@
         <v>0.0481488091087168</v>
       </c>
       <c r="K100" s="167" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="166" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C101" s="168" t="n">
         <v>0.653713298791019</v>
@@ -16415,7 +16421,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B103" s="152" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D103" s="160" t="n">
         <v>257.5</v>
@@ -16441,7 +16447,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="161" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C104" s="171" t="n">
         <v>0</v>
@@ -16470,7 +16476,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B105" s="161" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C105" s="148" t="n">
         <v>-79.1</v>
@@ -16505,7 +16511,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B107" s="152" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D107" s="160" t="n">
         <v>1940.3</v>
@@ -16541,7 +16547,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B109" s="152" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D109" s="160" t="n">
         <v>232.4</v>
@@ -16578,7 +16584,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B111" s="89" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C111" s="145"/>
       <c r="D111" s="145"/>
@@ -16591,7 +16597,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B112" s="88" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C112" s="172"/>
       <c r="D112" s="172"/>
@@ -16614,7 +16620,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B113" s="81" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C113" s="174"/>
       <c r="D113" s="174"/>
@@ -16660,7 +16666,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B116" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C116" s="175"/>
       <c r="D116" s="175"/>
@@ -16683,7 +16689,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B117" s="154" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C117" s="175"/>
       <c r="D117" s="175"/>
@@ -16706,7 +16712,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B118" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C118" s="175"/>
       <c r="D118" s="175"/>
@@ -16729,7 +16735,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B119" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C119" s="103"/>
       <c r="D119" s="103"/>
@@ -16752,7 +16758,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B120" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C120" s="103"/>
       <c r="D120" s="103"/>
@@ -16775,7 +16781,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B121" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C121" s="103"/>
       <c r="D121" s="103"/>
@@ -16798,7 +16804,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B122" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C122" s="103"/>
       <c r="D122" s="103"/>
@@ -16821,7 +16827,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B123" s="123" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F123" s="124" t="n">
         <v>637.922161164797</v>
@@ -16841,7 +16847,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B125" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F125" s="116" t="n">
         <v>-26</v>
@@ -16861,7 +16867,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B126" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F126" s="116" t="n">
         <v>-201</v>
@@ -16881,7 +16887,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B127" s="123" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F127" s="124" t="n">
         <v>-227</v>
@@ -16901,7 +16907,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B129" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F129" s="116" t="n">
         <v>-322.1855</v>
@@ -16921,7 +16927,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B130" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F130" s="116" t="n">
         <v>0</v>
@@ -16941,7 +16947,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B131" s="177" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C131" s="123"/>
       <c r="D131" s="123"/>
@@ -16984,7 +16990,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B133" s="177" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C133" s="123"/>
       <c r="D133" s="123"/>
@@ -17007,7 +17013,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B134" s="154" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F134" s="116" t="n">
         <v>-88.7366611647973</v>
@@ -17027,7 +17033,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B135" s="154" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F135" s="116" t="n">
         <v>0</v>
@@ -17047,7 +17053,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B136" s="123" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F136" s="124" t="n">
         <v>0</v>
@@ -17075,7 +17081,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B138" s="157" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C138" s="81"/>
       <c r="D138" s="81"/>
@@ -17088,7 +17094,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B139" s="88" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C139" s="172" t="n">
         <v>2011</v>
@@ -17117,7 +17123,7 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B140" s="81" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C140" s="174" t="n">
         <v>40633</v>
@@ -17149,7 +17155,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B142" s="111" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F142" s="178" t="n">
         <v>180</v>
@@ -17169,7 +17175,7 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B143" s="111" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F143" s="116" t="n">
         <v>0</v>
@@ -17189,7 +17195,7 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B144" s="152" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C144" s="123"/>
       <c r="D144" s="160" t="n">
@@ -17216,7 +17222,7 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B145" s="111" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D145" s="179" t="n">
         <v>0.00648080215211543</v>
@@ -17242,7 +17248,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B146" s="111" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C146" s="103"/>
       <c r="D146" s="116" t="n">
@@ -17292,7 +17298,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B149" s="161" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F149" s="116" t="n">
         <v>180</v>
@@ -17312,7 +17318,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B150" s="161" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F150" s="108" t="n">
         <v>-180</v>
@@ -17332,7 +17338,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B151" s="161" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F151" s="116" t="n">
         <v>0</v>
@@ -17352,7 +17358,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B152" s="181" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C152" s="150"/>
       <c r="D152" s="150"/>
@@ -17375,7 +17381,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B153" s="183" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C153" s="93"/>
       <c r="D153" s="93"/>
@@ -17398,7 +17404,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B155" s="111" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F155" s="178" t="n">
         <v>0</v>
@@ -17418,7 +17424,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B156" s="111" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F156" s="116" t="n">
         <v>0</v>
@@ -17438,13 +17444,13 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B157" s="152" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D157" s="150" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E157" s="150" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F157" s="124" t="n">
         <v>0</v>
@@ -17464,7 +17470,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B158" s="183" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D158" s="184" t="n">
         <v>0.8</v>
@@ -17490,24 +17496,24 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B159" s="183" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D159" s="185"/>
       <c r="E159" s="185"/>
       <c r="F159" s="186" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G159" s="186" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H159" s="186" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="I159" s="186" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="J159" s="186" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17517,7 +17523,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B162" s="111" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F162" s="178" t="n">
         <v>2886.429</v>
@@ -17537,7 +17543,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B163" s="111" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F163" s="108" t="n">
         <v>288.6429</v>
@@ -17557,7 +17563,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B164" s="111" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F164" s="108" t="n">
         <v>88.7366611647973</v>
@@ -17577,7 +17583,7 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B165" s="152" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C165" s="123"/>
       <c r="D165" s="187"/>
@@ -17600,11 +17606,11 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B166" s="183" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C166" s="93"/>
       <c r="E166" s="153" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F166" s="188" t="n">
         <v>0.1</v>
@@ -17624,7 +17630,7 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B167" s="183" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C167" s="93"/>
       <c r="E167" s="189" t="n">
@@ -17662,7 +17668,7 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B170" s="111" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F170" s="178" t="n">
         <v>670.852</v>
@@ -17682,7 +17688,7 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B171" s="111" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F171" s="108" t="n">
         <v>33.5426</v>
@@ -17702,7 +17708,7 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B172" s="111" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F172" s="108" t="n">
         <v>0</v>
@@ -17722,7 +17728,7 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B173" s="152" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C173" s="123"/>
       <c r="F173" s="149" t="n">
@@ -17743,11 +17749,11 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B174" s="183" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C174" s="93"/>
       <c r="E174" s="153" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F174" s="188" t="n">
         <v>0.05</v>
@@ -17767,7 +17773,7 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B175" s="183" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C175" s="93"/>
       <c r="E175" s="189" t="n">
@@ -17808,7 +17814,7 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B178" s="111" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F178" s="178" t="n">
         <v>1632.995</v>
@@ -17828,7 +17834,7 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B179" s="111" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F179" s="108" t="n">
         <v>0</v>
@@ -17848,7 +17854,7 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B180" s="152" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C180" s="123"/>
       <c r="D180" s="123"/>
@@ -17871,7 +17877,7 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B181" s="183" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F181" s="188" t="n">
         <v>0</v>
@@ -17905,7 +17911,7 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B184" s="111" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F184" s="178" t="n">
         <v>0</v>
@@ -17925,13 +17931,13 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B185" s="111" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C185" s="153" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D185" s="153" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F185" s="108" t="n">
         <v>0</v>
@@ -17951,7 +17957,7 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B186" s="136" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C186" s="194" t="n">
         <v>0.04</v>
@@ -17977,7 +17983,7 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B187" s="152" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C187" s="123"/>
       <c r="D187" s="195"/>
@@ -18000,7 +18006,7 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B188" s="183" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F188" s="188" t="n">
         <v>0</v>
@@ -18040,7 +18046,7 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B191" s="111" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F191" s="197" t="n">
         <v>0</v>
@@ -18060,7 +18066,7 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B192" s="136" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F192" s="108" t="n">
         <v>0</v>
@@ -18080,13 +18086,13 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B193" s="123" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C193" s="153" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D193" s="153" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E193" s="123"/>
       <c r="F193" s="149" t="n">
@@ -18107,7 +18113,7 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B194" s="136" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C194" s="194" t="n">
         <v>0.04</v>
@@ -18137,13 +18143,13 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B196" s="198" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F196" s="103"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B197" s="111" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C197" s="116"/>
       <c r="D197" s="160"/>
@@ -18166,7 +18172,7 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B198" s="111" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C198" s="116"/>
       <c r="D198" s="116"/>
@@ -18189,7 +18195,7 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B199" s="123" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C199" s="116"/>
       <c r="D199" s="116"/>
@@ -18216,7 +18222,7 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B201" s="89" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C201" s="81"/>
       <c r="D201" s="81"/>
@@ -18229,7 +18235,7 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B202" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C202" s="140" t="n">
         <v>2011</v>
@@ -18258,7 +18264,7 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B203" s="143" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C203" s="145" t="n">
         <v>40633</v>
@@ -18290,7 +18296,7 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B205" s="136" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C205" s="199"/>
       <c r="D205" s="93"/>
@@ -18313,13 +18319,13 @@
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B206" s="111"/>
       <c r="C206" s="153" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D206" s="153" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E206" s="153" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F206" s="109"/>
       <c r="G206" s="109"/>
@@ -18431,7 +18437,7 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B211" s="111" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E211" s="204" t="n">
         <v>0.08</v>
@@ -18454,7 +18460,7 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B212" s="111" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C212" s="194"/>
       <c r="E212" s="204" t="n">
@@ -18489,7 +18495,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B214" s="89" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C214" s="81"/>
       <c r="D214" s="81"/>
@@ -18511,11 +18517,11 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B218" s="106" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C218" s="123"/>
       <c r="E218" s="153" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F218" s="206" t="n">
         <v>6.3</v>
@@ -18535,7 +18541,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B219" s="102" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E219" s="208" t="n">
         <v>0.5</v>
@@ -18578,7 +18584,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B221" s="209" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F221" s="103"/>
     </row>
@@ -18686,7 +18692,7 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B227" s="161" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E227" s="211"/>
       <c r="F227" s="116" t="n">
@@ -18727,16 +18733,16 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B229" s="137" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C229" s="212" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D229" s="213" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E229" s="214" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F229" s="124" t="n">
         <v>5695.63421862424</v>
@@ -18785,7 +18791,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B231" s="111" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C231" s="215" t="n">
         <v>0</v>
@@ -18814,7 +18820,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B232" s="111" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C232" s="218"/>
       <c r="D232" s="216"/>
@@ -18839,7 +18845,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B233" s="111" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C233" s="220"/>
       <c r="D233" s="221"/>
@@ -18874,7 +18880,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B235" s="157" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C235" s="137"/>
       <c r="D235" s="137"/>
@@ -18886,13 +18892,13 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C236" s="223" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D236" s="223" t="s">
         <v>234</v>
       </c>
       <c r="E236" s="224" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F236" s="225" t="n">
         <v>2014</v>
@@ -19028,7 +19034,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B241" s="154" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C241" s="228"/>
       <c r="D241" s="227"/>
@@ -19186,7 +19192,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B247" s="154" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C247" s="228"/>
       <c r="D247" s="227"/>
@@ -19344,7 +19350,7 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B253" s="154" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C253" s="230"/>
       <c r="D253" s="227"/>
@@ -19502,7 +19508,7 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B259" s="154" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C259" s="187"/>
       <c r="D259" s="231"/>
@@ -19660,7 +19666,7 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B266" s="89" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C266" s="81"/>
       <c r="D266" s="81"/>
@@ -19669,19 +19675,19 @@
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B267" s="123"/>
       <c r="F267" s="223" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G267" s="223" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H267" s="223" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="I267" s="223" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="J267" s="223" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19819,7 +19825,7 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B275" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F275" s="234" t="n">
         <v>1871.3</v>
@@ -19839,7 +19845,7 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B276" s="152" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F276" s="237" t="n">
         <v>6850.55394</v>
@@ -19859,7 +19865,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B277" s="152" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E277" s="239"/>
       <c r="G277" s="238"/>
@@ -19870,7 +19876,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B278" s="89" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C278" s="81"/>
       <c r="D278" s="240"/>
@@ -19893,10 +19899,10 @@
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B280" s="137"/>
       <c r="C280" s="245" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E280" s="246" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F280" s="246"/>
       <c r="G280" s="246"/>
@@ -19906,7 +19912,7 @@
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B281" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C281" s="247" t="n">
         <v>0.330505082844487</v>
@@ -20072,7 +20078,7 @@
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B288" s="136" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C288" s="270" t="n">
         <v>14.777039186237</v>
@@ -20102,7 +20108,7 @@
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D290" s="275" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E290" s="275"/>
       <c r="F290" s="275"/>
@@ -20113,10 +20119,10 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B291" s="276" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D291" s="277" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E291" s="277"/>
       <c r="F291" s="277"/>
@@ -20130,7 +20136,7 @@
         <v>0.3</v>
       </c>
       <c r="F292" s="279" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G292" s="279"/>
       <c r="H292" s="279"/>
@@ -20182,7 +20188,7 @@
     </row>
     <row r="295" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D295" s="283" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E295" s="284" t="n">
         <v>7.25</v>
@@ -20228,7 +20234,7 @@
     </row>
     <row r="297" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D297" s="283" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E297" s="284" t="n">
         <v>7.75</v>
@@ -20272,7 +20278,7 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D300" s="275" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E300" s="275"/>
       <c r="F300" s="275"/>
@@ -20283,7 +20289,7 @@
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D301" s="277" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E301" s="277"/>
       <c r="F301" s="277"/>
@@ -20294,7 +20300,7 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F302" s="279" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G302" s="279"/>
       <c r="H302" s="279"/>
@@ -20334,7 +20340,7 @@
     </row>
     <row r="305" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D305" s="283" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E305" s="285" t="n">
         <v>5</v>
@@ -20347,7 +20353,7 @@
     </row>
     <row r="306" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D306" s="283" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E306" s="285" t="n">
         <v>5.0625</v>
@@ -20360,7 +20366,7 @@
     </row>
     <row r="307" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D307" s="283" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E307" s="285" t="n">
         <v>5.25</v>
@@ -20384,7 +20390,7 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D310" s="275" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E310" s="275"/>
       <c r="F310" s="275"/>
@@ -20395,7 +20401,7 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F311" s="279" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G311" s="279"/>
       <c r="H311" s="279"/>
@@ -20445,7 +20451,7 @@
     </row>
     <row r="314" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D314" s="283" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E314" s="288" t="n">
         <v>0.02</v>
@@ -20468,7 +20474,7 @@
     </row>
     <row r="315" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D315" s="283" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E315" s="288" t="n">
         <v>0.04</v>
@@ -20491,7 +20497,7 @@
     </row>
     <row r="316" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D316" s="283" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E316" s="288" t="n">
         <v>0.06</v>
@@ -20535,7 +20541,7 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B319" s="89" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C319" s="81"/>
       <c r="D319" s="81"/>
@@ -20549,7 +20555,7 @@
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H320" s="125"/>
       <c r="J320" s="289" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20560,7 +20566,7 @@
         <v>2013</v>
       </c>
       <c r="G321" s="290" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H321" s="290"/>
       <c r="I321" s="290"/>
@@ -20579,13 +20585,13 @@
         <v>41364</v>
       </c>
       <c r="G322" s="292" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H322" s="292" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="I322" s="292" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J322" s="291" t="n">
         <v>41364</v>
@@ -20614,7 +20620,7 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B324" s="111" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E324" s="116" t="n">
         <v>484.8</v>
@@ -20631,7 +20637,7 @@
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B325" s="111" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E325" s="116" t="n">
         <v>195.1</v>
@@ -20648,7 +20654,7 @@
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B326" s="111" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E326" s="116" t="n">
         <v>87.8</v>
@@ -20667,7 +20673,7 @@
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B327" s="111" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E327" s="116" t="n">
         <v>244.7</v>
@@ -20684,7 +20690,7 @@
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B328" s="111" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E328" s="116" t="n">
         <v>257.5</v>
@@ -20705,7 +20711,7 @@
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B329" s="111" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E329" s="133" t="n">
         <v>1940.3</v>
@@ -20724,7 +20730,7 @@
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B330" s="123" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E330" s="124" t="n">
         <v>4845.8</v>
@@ -20748,7 +20754,7 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B332" s="111" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E332" s="116" t="n">
         <v>32.7</v>
@@ -20765,7 +20771,7 @@
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B333" s="111" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E333" s="116" t="n">
         <v>2313.3</v>
@@ -20782,7 +20788,7 @@
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B334" s="111" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E334" s="116" t="n">
         <v>232.4</v>
@@ -20801,7 +20807,7 @@
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B335" s="111" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E335" s="296" t="n">
         <v>821.6</v>
@@ -20822,7 +20828,7 @@
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B336" s="123" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E336" s="124" t="n">
         <v>3400</v>
@@ -20846,7 +20852,7 @@
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B338" s="111" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E338" s="298" t="s">
         <v>533</v>
@@ -20865,7 +20871,7 @@
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B339" s="111" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E339" s="148" t="n">
         <v>1445.8</v>
@@ -20888,7 +20894,7 @@
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B340" s="123" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E340" s="170" t="n">
         <v>1445.8</v>
@@ -20902,7 +20908,7 @@
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B341" s="136" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E341" s="163" t="n">
         <v>0</v>
@@ -20927,7 +20933,7 @@
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B343" s="89" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D343" s="143"/>
       <c r="E343" s="299"/>
@@ -20940,7 +20946,7 @@
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B344" s="88" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C344" s="300"/>
       <c r="D344" s="172" t="n">
@@ -20970,7 +20976,7 @@
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B345" s="81" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C345" s="81"/>
       <c r="D345" s="174" t="n">
@@ -21029,7 +21035,7 @@
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B347" s="111" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D347" s="116" t="n">
         <v>484.8</v>
@@ -21058,7 +21064,7 @@
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B348" s="111" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D348" s="116" t="n">
         <v>195.1</v>
@@ -21087,7 +21093,7 @@
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B349" s="111" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D349" s="116" t="n">
         <v>87.8</v>
@@ -21116,7 +21122,7 @@
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B350" s="111" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D350" s="116" t="n">
         <v>244.7</v>
@@ -21145,7 +21151,7 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B351" s="111" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D351" s="116" t="n">
         <v>257.5</v>
@@ -21174,7 +21180,7 @@
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B352" s="111" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D352" s="133" t="n">
         <v>1940.3</v>
@@ -21203,7 +21209,7 @@
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B353" s="152" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D353" s="124" t="n">
         <v>4845.8</v>
@@ -21243,7 +21249,7 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B355" s="111" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D355" s="116" t="n">
         <v>32.7</v>
@@ -21272,7 +21278,7 @@
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B356" s="111" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D356" s="116" t="n">
         <v>2313.3</v>
@@ -21301,7 +21307,7 @@
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B357" s="111" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D357" s="116" t="n">
         <v>232.4</v>
@@ -21330,7 +21336,7 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B358" s="111" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D358" s="116" t="n">
         <v>821.6</v>
@@ -21359,7 +21365,7 @@
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B359" s="111" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D359" s="124" t="n">
         <v>3400</v>
@@ -21399,7 +21405,7 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B361" s="111" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D361" s="303" t="s">
         <v>533</v>
@@ -21428,7 +21434,7 @@
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B362" s="111" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D362" s="303" t="n">
         <v>1445.8</v>
@@ -21457,7 +21463,7 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B363" s="111" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D363" s="124" t="n">
         <v>1445.8</v>
@@ -21486,7 +21492,7 @@
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B364" s="111" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D364" s="116" t="n">
         <v>0</v>
@@ -21521,7 +21527,7 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B366" s="123" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C366" s="123"/>
       <c r="D366" s="123"/>
@@ -21545,7 +21551,7 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B367" s="111" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="G367" s="116" t="n">
         <v>152.904923766934</v>
@@ -21565,7 +21571,7 @@
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B368" s="111" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="G368" s="116" t="n">
         <v>0</v>
@@ -21585,7 +21591,7 @@
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B369" s="111" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="G369" s="116" t="n">
         <v>161.054736827472</v>
@@ -21605,7 +21611,7 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B370" s="152" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C370" s="123"/>
       <c r="D370" s="123"/>
@@ -21629,7 +21635,7 @@
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B372" s="157" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C372" s="81"/>
       <c r="D372" s="81"/>
@@ -21646,15 +21652,15 @@
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B374" s="154" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C374" s="304" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B375" s="154" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C375" s="304" t="s">
         <v>384</v>
@@ -21662,29 +21668,29 @@
     </row>
     <row r="377" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B377" s="305" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C377" s="306"/>
       <c r="E377" s="302"/>
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B378" s="154" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C378" s="116" t="n">
         <v>818.5</v>
       </c>
       <c r="D378" s="126" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E378" s="126" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G378" s="103"/>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B379" s="111" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C379" s="307" t="n">
         <v>300</v>
@@ -21698,7 +21704,7 @@
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B380" s="111" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C380" s="310" t="n">
         <v>200</v>
@@ -21712,7 +21718,7 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B381" s="111" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C381" s="176" t="n">
         <v>500</v>
@@ -21721,7 +21727,7 @@
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B382" s="111" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C382" s="182" t="n">
         <v>113.227389577004</v>
@@ -21729,7 +21735,7 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B383" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C383" s="116" t="n">
         <v>1205.272610423</v>
@@ -21737,7 +21743,7 @@
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B385" s="123" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C385" s="170" t="n">
         <v>6741.92625</v>
@@ -21745,7 +21751,7 @@
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B386" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C386" s="103" t="n">
         <v>5536.653639577</v>
@@ -21753,7 +21759,7 @@
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B388" s="89" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C388" s="81"/>
       <c r="D388" s="81"/>
@@ -21806,10 +21812,10 @@
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B391" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D391" s="312" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E391" s="313" t="n">
         <v>30</v>
@@ -21832,10 +21838,10 @@
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B392" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D392" s="312" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E392" s="313" t="n">
         <v>13.3333333333333</v>
@@ -21858,10 +21864,10 @@
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B393" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D393" s="312" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E393" s="314" t="n">
         <v>9.81304043000701</v>
@@ -21927,7 +21933,7 @@
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="84" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C2" s="85"/>
       <c r="D2" s="85"/>
@@ -21940,23 +21946,23 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="315" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="315" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="316" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C5" s="317"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C6" s="318" t="n">
         <f aca="false">LBO!D8</f>
@@ -21966,12 +21972,12 @@
         <v>4.05</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="315" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C7" s="319" t="n">
         <f aca="false">LBO!D9</f>
@@ -21980,7 +21986,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="315" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C8" s="320" t="n">
         <f aca="false">Shares!E14</f>
@@ -21992,7 +21998,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="315" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C9" s="180" t="n">
         <f aca="false">C59</f>
@@ -22004,7 +22010,7 @@
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="322" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C11" s="317"/>
       <c r="D11" s="317"/>
@@ -22017,7 +22023,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C12" s="140" t="n">
         <v>2024</v>
@@ -22042,7 +22048,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="143" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C13" s="323" t="n">
         <v>45657</v>
@@ -22168,7 +22174,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="123" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C18" s="328" t="n">
         <f aca="false">C16*(1-C17)</f>
@@ -22202,7 +22208,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="154" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D20" s="110" t="n">
         <f aca="false">AI_Operating!D15</f>
@@ -22229,7 +22235,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="154" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D21" s="110" t="n">
         <v>0</v>
@@ -22251,7 +22257,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D22" s="110" t="n">
         <f aca="false">AI_Operating!D20</f>
@@ -22278,7 +22284,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D23" s="110" t="n">
         <v>0</v>
@@ -22300,7 +22306,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="123" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D24" s="110" t="n">
         <f aca="false">D18+D20+D21-D22+D23</f>
@@ -22327,7 +22333,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="111" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D25" s="110" t="n">
         <f aca="false">-AI_Operating!D19</f>
@@ -22354,7 +22360,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="111" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D26" s="110" t="n">
         <v>0</v>
@@ -22376,7 +22382,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="329" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D27" s="330" t="n">
         <f aca="false">D24+D25+D26</f>
@@ -22403,7 +22409,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="136" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E28" s="331" t="n">
         <f aca="false">IF(D27=0,0,E27/D27-1)</f>
@@ -22433,7 +22439,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="154" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D30" s="332" t="n">
         <v>0.5</v>
@@ -22455,10 +22461,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C31" s="333" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="G31" s="122"/>
       <c r="H31" s="122"/>
@@ -22467,7 +22473,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C32" s="334" t="n">
         <f aca="false">(1+$C$9)^0.5</f>
@@ -22476,7 +22482,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="154" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D33" s="110" t="n">
         <f aca="false">D27/(1+$C$9)^D30</f>
@@ -22507,11 +22513,11 @@
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="316" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C35" s="317"/>
       <c r="E35" s="316" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F35" s="317"/>
       <c r="G35" s="317"/>
@@ -22521,14 +22527,14 @@
     </row>
     <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C36" s="337" t="n">
         <f aca="false">H27*(1+C37)</f>
         <v>269.439805935893</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H36" s="110" t="n">
         <f aca="false">H15</f>
@@ -22538,14 +22544,14 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C37" s="338" t="n">
         <f aca="false">Assumptions_Drivers!C10</f>
         <v>0.02</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H37" s="339" t="n">
         <f aca="false">Assumptions_Drivers!C20</f>
@@ -22556,14 +22562,14 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C38" s="110" t="n">
         <f aca="false">IF(($C$9-C37)&lt;=0,"NM",C36/($C$9-C37))</f>
         <v>3695.94187683077</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H38" s="110" t="n">
         <f aca="false">H36*H37</f>
@@ -22573,14 +22579,14 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C39" s="110" t="n">
         <f aca="false">IF(ISNUMBER(C38),C38/(1+$C$9)^H30,0)</f>
         <v>2478.05240056564</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H39" s="110" t="n">
         <f aca="false">H38/(1+$C$9)^H30</f>
@@ -22590,14 +22596,14 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C40" s="110" t="n">
         <f aca="false">SUM(D33:H33)</f>
         <v>886.646971093705</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H40" s="110" t="n">
         <f aca="false">C40</f>
@@ -22627,14 +22633,14 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="93" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C42" s="341" t="n">
         <f aca="false">IF(H15=0,0,C38/H15)</f>
         <v>11.6028524177675</v>
       </c>
       <c r="E42" s="93" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F42" s="93"/>
       <c r="G42" s="93"/>
@@ -22651,11 +22657,11 @@
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="316" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C44" s="317"/>
       <c r="E44" s="316" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="F44" s="317"/>
       <c r="G44" s="317"/>
@@ -22665,25 +22671,25 @@
     </row>
     <row r="45" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C45" s="343" t="n">
         <f aca="false">LBO!D15</f>
         <v>179.9</v>
       </c>
       <c r="H45" s="150" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="I45" s="150" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="J45" s="150" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C46" s="343" t="n">
         <f aca="false">ABS(LBO!D14)</f>
@@ -22707,14 +22713,14 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="123" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C47" s="328" t="n">
         <f aca="false">C46-C45</f>
         <v>1150</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H47" s="110" t="n">
         <f aca="false">-C47</f>
@@ -22732,7 +22738,7 @@
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C48" s="109"/>
       <c r="E48" s="123" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F48" s="123"/>
       <c r="G48" s="123"/>
@@ -22751,11 +22757,11 @@
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="316" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C49" s="317"/>
       <c r="E49" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H49" s="345" t="n">
         <f aca="false">$C$8</f>
@@ -22772,14 +22778,14 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="347" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C50" s="348" t="n">
         <f aca="false">(Debt_Sweep_AI!G12*Assumptions_Drivers!C27+Debt_Sweep_AI!G13*Assumptions_Drivers!C28+Debt_Sweep_AI!G14*(Assumptions_Drivers!C14+0.035))/Debt_Sweep_AI!G15</f>
         <v>0.085</v>
       </c>
       <c r="E50" s="123" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H50" s="349" t="n">
         <f aca="false">LBO!H20</f>
@@ -22797,7 +22803,7 @@
         <v>8.10863430429332</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22809,7 +22815,7 @@
         <v>0.21</v>
       </c>
       <c r="E51" s="93" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H51" s="350" t="s">
         <v>533</v>
@@ -22825,7 +22831,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C52" s="110" t="n">
         <f aca="false">Debt_Sweep_AI!G15</f>
@@ -22834,7 +22840,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C53" s="351" t="n">
         <f aca="false">C52/(C52+C54)</f>
@@ -22843,7 +22849,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C54" s="110" t="n">
         <f aca="false">Strategy_Summary!C20</f>
@@ -22852,7 +22858,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C55" s="352" t="n">
         <f aca="false">Assumptions_Drivers!C14</f>
@@ -22861,7 +22867,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C56" s="353" t="n">
         <v>1.25</v>
@@ -22869,7 +22875,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C57" s="338" t="n">
         <v>0.05</v>
@@ -22877,7 +22883,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C58" s="331" t="n">
         <f aca="false">1-C53</f>
@@ -22886,7 +22892,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="329" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C59" s="354" t="n">
         <f aca="false">C58*(C55+C56*C57)+C53*C50*(1-C51)</f>
@@ -23132,7 +23138,7 @@
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="316" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C93" s="317"/>
       <c r="D93" s="317"/>
@@ -23141,18 +23147,18 @@
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B114" s="381"/>
       <c r="C114" s="382" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D114" s="382" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E114" s="383" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B115" s="384" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C115" s="104" t="n">
         <v>8.10863430429332</v>
@@ -23166,7 +23172,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B116" s="384" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C116" s="104" t="n">
         <v>7.20710255214664</v>
@@ -23180,7 +23186,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B117" s="384" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C117" s="104" t="n">
         <f aca="false">LBO!H20</f>
@@ -23196,7 +23202,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B118" s="385" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C118" s="272" t="n">
         <f aca="false">52wkHL!E5</f>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">Sponsor equity</t>
   </si>
   <si>
-    <t xml:space="preserve">Side note: Sponsor equity is the capital contributed by the private equity firm—totaling $1,871.3 million (or 1.88x EBITDA)—used to fund the acquisition alongside the various debt and cash sources.</t>
+    <t xml:space="preserve">Side note: Sponsor equity is the capital contributed by the private equity firm—totaling $1,871.3 million (≈10.22x LTM/entry EBITDA of $183.1m, not exit EBITDA)—used to fund the acquisition alongside the various debt and cash sources.</t>
   </si>
   <si>
     <t xml:space="preserve">% of offer value</t>
@@ -3787,7 +3787,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="183" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3831,7 +3831,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="183" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="179" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14605,7 +14605,7 @@
         <v>525</v>
       </c>
       <c r="C27" s="127" t="n">
-        <v>1.58819530984479</v>
+        <v>0.7094</v>
       </c>
       <c r="D27" s="116" t="n">
         <v>129.9</v>
@@ -14788,12 +14788,12 @@
       <c r="P34" s="123"/>
       <c r="R34" s="124"/>
     </row>
-    <row r="35" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="111" t="s">
         <v>536</v>
       </c>
       <c r="C35" s="127" t="n">
-        <v>1.88090850798686</v>
+        <v>10.2201</v>
       </c>
       <c r="D35" s="133" t="n">
         <v>1871.3</v>
@@ -14816,7 +14816,7 @@
         <v>539</v>
       </c>
       <c r="C36" s="138" t="n">
-        <v>9.34910381783165</v>
+        <v>15.9295</v>
       </c>
       <c r="D36" s="124" t="n">
         <v>2916.7</v>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -14654,13 +14654,13 @@
         </is>
       </c>
       <c r="C39" s="552" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D39" s="552" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="E39" s="553" t="n">
-        <v>2027</v>
+        <v>2024</v>
       </c>
       <c r="F39" s="554" t="n">
         <v>2025</v>
@@ -15576,7 +15576,9 @@
           <t xml:space="preserve">Fiscal year  </t>
         </is>
       </c>
-      <c r="C73" s="569" t="n"/>
+      <c r="C73" s="569" t="n">
+        <v>2022</v>
+      </c>
       <c r="D73" s="552" t="n">
         <v>2023</v>
       </c>
@@ -16536,9 +16538,15 @@
           <t xml:space="preserve">Fiscal year  </t>
         </is>
       </c>
-      <c r="C112" s="586" t="n"/>
-      <c r="D112" s="586" t="n"/>
-      <c r="E112" s="586" t="n"/>
+      <c r="C112" s="586" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D112" s="586" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E112" s="586" t="n">
+        <v>2024</v>
+      </c>
       <c r="F112" s="587" t="n">
         <v>2025</v>
       </c>
@@ -21343,27 +21351,29 @@
           <t xml:space="preserve">Fiscal year  </t>
         </is>
       </c>
-      <c r="C344" s="719" t="n"/>
+      <c r="C344" s="719" t="n">
+        <v>2022</v>
+      </c>
       <c r="D344" s="586" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E344" s="586" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F344" s="586" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G344" s="587" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H344" s="587" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="I344" s="587" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="J344" s="587" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="K344" s="587" t="n">
         <v>2029</v>
@@ -21377,25 +21387,25 @@
       </c>
       <c r="C345" s="490" t="n"/>
       <c r="D345" s="589" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="E345" s="589" t="n">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="F345" s="589" t="n">
-        <v>45657</v>
+        <v>46022</v>
       </c>
       <c r="G345" s="589" t="n">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="H345" s="589" t="n">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="I345" s="589" t="n">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="J345" s="589" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="K345" s="589" t="n">
         <v>47483</v>
@@ -22276,19 +22286,19 @@
       <c r="E390" s="490" t="n"/>
       <c r="F390" s="490" t="n"/>
       <c r="G390" s="709" t="n">
-        <v>41729</v>
+        <v>46022</v>
       </c>
       <c r="H390" s="709" t="n">
-        <v>42094</v>
+        <v>46387</v>
       </c>
       <c r="I390" s="709" t="n">
-        <v>42460</v>
+        <v>46752</v>
       </c>
       <c r="J390" s="709" t="n">
-        <v>42825</v>
+        <v>47118</v>
       </c>
       <c r="K390" s="709" t="n">
-        <v>43190</v>
+        <v>47483</v>
       </c>
     </row>
     <row r="391" ht="15" customHeight="1" s="410">

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -60,7 +60,7 @@
     <numFmt numFmtId="194" formatCode="#,##0.0_);\(#,##0.0\);&quot;- _)&quot;;@_)"/>
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
   </numFmts>
-  <fonts count="63">
+  <fonts count="66">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -479,8 +479,21 @@
     <font>
       <sz val="9"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -578,6 +591,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -778,7 +801,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="799">
+  <cellXfs count="809">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3168,6 +3191,22 @@
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3352,7 +3391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A2:K35"/>
+  <dimension ref="A2:K36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="408" min="1" max="1"/>
@@ -4619,85 +4658,134 @@
       <c r="J28" s="425" t="n"/>
       <c r="K28" s="425" t="n"/>
     </row>
-    <row r="29" ht="72" customHeight="1" s="409">
-      <c r="B29" s="440" t="inlineStr">
-        <is>
-          <t>AI $24.5m IN-EQ sources + Ctrl+F:</t>
-        </is>
-      </c>
-      <c r="C29" s="441" t="inlineStr">
-        <is>
-          <t>White Space Ctrl+F $5,000-10,000+ | Miniloop Ctrl+F $10,000-$15,000+ | SEC Ctrl+F 1,513 in sales | roles=18% of HC (same 18% as payroll cut)</t>
+    <row r="29" ht="48" customHeight="1" s="409">
+      <c r="A29" s="799" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="B29" s="408" t="inlineStr">
+        <is>
+          <t>SBC as % of operating expenses</t>
+        </is>
+      </c>
+      <c r="C29" s="800" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="D29" s="801" t="inlineStr">
+        <is>
+          <t>FY25 ZI: equity-based comp $116.2m ÷ total operating expenses $824.2m = 14.1%. Replaces prior 9.3% BMC hist trend. Not in AI_Operating FCF (no SBC add-back).</t>
+        </is>
+      </c>
+      <c r="E29" s="802">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm","IN EQ: FY25 SBC $116.2 ÷ opex $824.2 = 14.1% → C29")</f>
+        <v/>
+      </c>
+      <c r="F29" s="801" t="inlineStr">
+        <is>
+          <t>10-K: FY25 SBC $116.2m and opex $824.2m. 116.2÷824.2=14.1% enters LBO SBC $ via C29.</t>
+        </is>
+      </c>
+      <c r="G29" s="408" t="inlineStr">
+        <is>
+          <t>Go to LBO!F70 (SBC %) and LBO!F60 (SBC $); DCF!D21 stays 0 (no add-back).</t>
+        </is>
+      </c>
+      <c r="I29" s="803" t="inlineStr">
+        <is>
+          <t>Ctrl+F: Total equity-based compensation expense $ 116.2</t>
+        </is>
+      </c>
+      <c r="J29" s="803" t="inlineStr">
+        <is>
+          <t>Ctrl+F: Total operating expenses $ 824.2</t>
+        </is>
+      </c>
+      <c r="K29" s="408" t="inlineStr">
+        <is>
+          <t>EQ: 116.2÷824.2=14.1%. LBO F60=F70×(|COS|+|R&amp;D|+|SG&amp;A|).</t>
         </is>
       </c>
     </row>
     <row r="30" ht="84" customHeight="1" s="409">
       <c r="B30" s="440" t="inlineStr">
         <is>
+          <t>AI $24.5m IN-EQ sources + Ctrl+F:</t>
+        </is>
+      </c>
+      <c r="C30" s="441" t="inlineStr">
+        <is>
+          <t>White Space Ctrl+F $5,000-10,000+ | Miniloop Ctrl+F $10,000-$15,000+ | SEC Ctrl+F 1,513 in sales | roles=18% of HC (same 18% as payroll cut)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1" s="409">
+      <c r="B31" s="440" t="inlineStr">
+        <is>
           <t>ZI 10-K S&amp;M HC 1,513:</t>
         </is>
       </c>
-      <c r="C30" s="423" t="inlineStr">
+      <c r="C31" s="423" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="36" customHeight="1" s="409">
-      <c r="B31" s="442" t="inlineStr">
+    <row r="32" ht="132" customHeight="1" s="409">
+      <c r="B32" s="442" t="inlineStr">
         <is>
           <t>11x Growth $3,750 NOT in EQ:</t>
         </is>
       </c>
-      <c r="C31" s="443" t="inlineStr">
+      <c r="C32" s="443" t="inlineStr">
         <is>
           <t>https://www.11x.ai/products/alice/pricing</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="132" customHeight="1" s="409">
-      <c r="B32" s="408" t="inlineStr">
-        <is>
-          <t>PDF map:</t>
-        </is>
-      </c>
-      <c r="C32" s="443" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_DRIVER_SOURCES.pdf</t>
         </is>
       </c>
     </row>
     <row r="33" ht="216" customHeight="1" s="409">
       <c r="B33" s="408" t="inlineStr">
         <is>
-          <t>HOW TO USE VERBATIM (no auto-highlight):</t>
-        </is>
-      </c>
-      <c r="C33" s="444" t="inlineStr">
-        <is>
-          <t>1) Click Source link in column E (opens the page). 2) Copy the string from column I (or J/K). 3) Ctrl+F on the page and paste. Example row 9: I9 copy $5,000-10,000+ | J9 copy $10,000-$15,000+ | K9 copy 1,513 in sales and marketing</t>
+          <t>PDF map:</t>
+        </is>
+      </c>
+      <c r="C33" s="443" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_DRIVER_SOURCES.pdf</t>
         </is>
       </c>
     </row>
     <row r="34" ht="217.5" customHeight="1" s="409">
       <c r="B34" s="408" t="inlineStr">
         <is>
-          <t>AI $34m FIND example (row 9):</t>
-        </is>
-      </c>
-      <c r="C34" s="445" t="inlineStr">
-        <is>
-          <t>I → White Space $5,000-10,000+ highlighted | J → Miniloop $10,000-$15,000+ highlighted | K → SEC 1,513 in sales and marketing highlighted</t>
+          <t>HOW TO USE VERBATIM (no auto-highlight):</t>
+        </is>
+      </c>
+      <c r="C34" s="444" t="inlineStr">
+        <is>
+          <t>1) Click Source link in column E (opens the page). 2) Copy the string from column I (or J/K). 3) Ctrl+F on the page and paste. Example row 9: I9 copy $5,000-10,000+ | J9 copy $10,000-$15,000+ | K9 copy 1,513 in sales and marketing</t>
         </is>
       </c>
     </row>
     <row r="35" ht="231.75" customHeight="1" s="409">
       <c r="B35" s="408" t="inlineStr">
         <is>
+          <t>AI $34m FIND example (row 9):</t>
+        </is>
+      </c>
+      <c r="C35" s="445" t="inlineStr">
+        <is>
+          <t>I → White Space $5,000-10,000+ highlighted | J → Miniloop $10,000-$15,000+ highlighted | K → SEC 1,513 in sales and marketing highlighted</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="408" t="inlineStr">
+        <is>
           <t>Baseline legend (col A):</t>
         </is>
       </c>
-      <c r="C35" s="445" t="inlineStr">
+      <c r="C36" s="445" t="inlineStr">
         <is>
           <t>YES = yellow value derived from ZI past performance / FY24 S&amp;M pools. NO = external publication, market quote, MODEL CONST, or AI operating lever.</t>
         </is>
@@ -10679,7 +10767,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="13.8" customHeight="1" s="409"/>
+    <row r="47" ht="13.8" customHeight="1" s="409">
+      <c r="B47" s="808" t="inlineStr">
+        <is>
+          <t>SBC: Drivers C29=14.1% (FY25 $116.2÷$824.2) drives LBO SBC $/CF; DCF UFCF keeps SBC add-back at $0 (real cost).</t>
+        </is>
+      </c>
+    </row>
     <row r="48" ht="15" customHeight="1" s="409">
       <c r="B48" s="447" t="inlineStr">
         <is>
@@ -10795,7 +10889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:N43"/>
+  <dimension ref="B2:N44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="408" min="2" max="2"/>
@@ -11879,139 +11973,124 @@
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="409">
-      <c r="B22" s="440" t="inlineStr">
+      <c r="B22" s="408" t="n">
+        <v>16</v>
+      </c>
+      <c r="C22" s="408" t="inlineStr">
+        <is>
+          <t>SBC as % of operating expenses</t>
+        </is>
+      </c>
+      <c r="D22" s="408" t="inlineStr">
+        <is>
+          <t>14.1% (FY25 $116.2m÷$824.2m); LBO SBC$=%×opex; DCF add-back $0</t>
+        </is>
+      </c>
+      <c r="E22" s="408" t="inlineStr">
+        <is>
+          <t>LBO F60/F70 (DCF add-back off)</t>
+        </is>
+      </c>
+      <c r="F22" s="408" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G22" s="408" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="409">
+      <c r="B23" s="440" t="inlineStr">
         <is>
           <t>BASELINE POOLS (must match Assumptions_Drivers)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="409">
-      <c r="B23" s="447" t="n">
-        <v>16</v>
-      </c>
-      <c r="C23" s="408" t="inlineStr">
+    <row r="24" ht="15.75" customHeight="1" s="409">
+      <c r="B24" s="447" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" s="408" t="inlineStr">
         <is>
           <t>S&amp;M baseline ($m)</t>
         </is>
       </c>
-      <c r="D23" s="408" t="inlineStr">
+      <c r="D24" s="408" t="inlineStr">
         <is>
           <t>$414.1m</t>
         </is>
       </c>
-      <c r="E23" s="408" t="inlineStr">
+      <c r="E24" s="408" t="inlineStr">
         <is>
           <t>LBO (not DCF)</t>
         </is>
       </c>
-      <c r="F23" s="408" t="inlineStr">
+      <c r="F24" s="408" t="inlineStr">
         <is>
           <t>Assumptions_Drivers</t>
         </is>
       </c>
-      <c r="G23" s="408" t="inlineStr">
+      <c r="G24" s="408" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="H23" s="408" t="inlineStr">
+      <c r="H24" s="408" t="inlineStr">
         <is>
           <t>Go to Assumptions_Drivers!C21</t>
         </is>
       </c>
-      <c r="M23" s="408" t="inlineStr">
+      <c r="M24" s="408" t="inlineStr">
         <is>
           <t>ZI FY24-derived (~35%×$1,214.3m near filing $414.1m)</t>
         </is>
       </c>
-      <c r="N23" s="465" t="inlineStr">
+      <c r="N24" s="465" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="409">
-      <c r="B24" s="445" t="n">
-        <v>17</v>
-      </c>
-      <c r="C24" s="408" t="inlineStr">
+    <row r="25" ht="15" customHeight="1" s="409">
+      <c r="B25" s="445" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" s="408" t="inlineStr">
         <is>
           <t>Payroll baseline ($m)</t>
         </is>
       </c>
-      <c r="D24" s="408" t="inlineStr">
+      <c r="D25" s="408" t="inlineStr">
         <is>
           <t>$289.9m</t>
         </is>
       </c>
-      <c r="E24" s="408" t="inlineStr">
+      <c r="E25" s="408" t="inlineStr">
         <is>
           <t>LBO (not DCF)</t>
         </is>
       </c>
-      <c r="F24" s="408" t="inlineStr">
+      <c r="F25" s="408" t="inlineStr">
         <is>
           <t>Assumptions_Drivers</t>
         </is>
       </c>
-      <c r="G24" s="408" t="inlineStr">
+      <c r="G25" s="408" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="H24" s="408" t="inlineStr">
+      <c r="H25" s="408" t="inlineStr">
         <is>
           <t>Go to Assumptions_Drivers!C22</t>
         </is>
       </c>
-      <c r="M24" s="408" t="inlineStr">
+      <c r="M25" s="408" t="inlineStr">
         <is>
           <t>75% × $425m FY24 S&amp;M carve</t>
-        </is>
-      </c>
-      <c r="N24" s="465" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="409">
-      <c r="B25" s="408" t="n">
-        <v>18</v>
-      </c>
-      <c r="C25" s="408" t="inlineStr">
-        <is>
-          <t>Commission baseline ($m)</t>
-        </is>
-      </c>
-      <c r="D25" s="408" t="inlineStr">
-        <is>
-          <t>$124.2m</t>
-        </is>
-      </c>
-      <c r="E25" s="408" t="inlineStr">
-        <is>
-          <t>LBO (not DCF)</t>
-        </is>
-      </c>
-      <c r="F25" s="408" t="inlineStr">
-        <is>
-          <t>Assumptions_Drivers</t>
-        </is>
-      </c>
-      <c r="G25" s="408" t="inlineStr">
-        <is>
-          <t>C23</t>
-        </is>
-      </c>
-      <c r="H25" s="408" t="inlineStr">
-        <is>
-          <t>Go to Assumptions_Drivers!C23</t>
-        </is>
-      </c>
-      <c r="M25" s="408" t="inlineStr">
-        <is>
-          <t>25% × $425m FY24 S&amp;M carve</t>
         </is>
       </c>
       <c r="N25" s="465" t="inlineStr">
@@ -12026,187 +12105,232 @@
       </c>
       <c r="C26" s="408" t="inlineStr">
         <is>
+          <t>Commission baseline ($m)</t>
+        </is>
+      </c>
+      <c r="D26" s="408" t="inlineStr">
+        <is>
+          <t>$124.2m</t>
+        </is>
+      </c>
+      <c r="E26" s="408" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F26" s="408" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G26" s="408" t="inlineStr">
+        <is>
+          <t>C23</t>
+        </is>
+      </c>
+      <c r="H26" s="408" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C23</t>
+        </is>
+      </c>
+      <c r="M26" s="408" t="inlineStr">
+        <is>
+          <t>25% × $425m FY24 S&amp;M carve</t>
+        </is>
+      </c>
+      <c r="N26" s="465" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="409">
+      <c r="B27" s="408" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" s="408" t="inlineStr">
+        <is>
           <t>CapEx base % of rev</t>
         </is>
       </c>
-      <c r="D26" s="408" t="inlineStr">
+      <c r="D27" s="408" t="inlineStr">
         <is>
           <t>2.0%</t>
         </is>
       </c>
-      <c r="E26" s="408" t="inlineStr">
+      <c r="E27" s="408" t="inlineStr">
         <is>
           <t>LBO (not DCF)</t>
         </is>
       </c>
-      <c r="F26" s="408" t="inlineStr">
+      <c r="F27" s="408" t="inlineStr">
         <is>
           <t>Assumptions_Drivers</t>
         </is>
       </c>
-      <c r="G26" s="408" t="inlineStr">
+      <c r="G27" s="408" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="H26" s="408" t="inlineStr">
+      <c r="H27" s="408" t="inlineStr">
         <is>
           <t>Go to Assumptions_Drivers!C24</t>
         </is>
       </c>
-      <c r="M26" s="408" t="inlineStr">
+      <c r="M27" s="408" t="inlineStr">
         <is>
           <t>External SaaS CapEx 1–3% midpoint</t>
         </is>
       </c>
-      <c r="N26" s="466" t="inlineStr">
+      <c r="N27" s="466" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="409">
-      <c r="B27" s="447" t="n">
-        <v>20</v>
-      </c>
-      <c r="C27" s="408" t="inlineStr">
+    <row r="28" ht="90.75" customHeight="1" s="409">
+      <c r="B28" s="447" t="n">
+        <v>21</v>
+      </c>
+      <c r="C28" s="408" t="inlineStr">
         <is>
           <t>AR intensity + Deferred rev % (NWC)</t>
         </is>
       </c>
-      <c r="D27" s="408" t="inlineStr">
+      <c r="D28" s="408" t="inlineStr">
         <is>
           <t>AR 16.2% (C25) / Deferred 39.0% (C26); net ΔNWC rate ≈ −22.9% of Δrev</t>
         </is>
       </c>
-      <c r="E27" s="408" t="inlineStr">
+      <c r="E28" s="408" t="inlineStr">
         <is>
           <t>LBO (not DCF)</t>
         </is>
       </c>
-      <c r="F27" s="408" t="inlineStr">
+      <c r="F28" s="408" t="inlineStr">
         <is>
           <t>Assumptions_Drivers</t>
         </is>
       </c>
-      <c r="G27" s="408" t="inlineStr">
+      <c r="G28" s="408" t="inlineStr">
         <is>
           <t>C25 / C26</t>
         </is>
       </c>
-      <c r="H27" s="408" t="inlineStr">
+      <c r="H28" s="408" t="inlineStr">
         <is>
           <t>Go to Assumptions_Drivers!C25</t>
         </is>
       </c>
-      <c r="J27" s="408" t="inlineStr">
+      <c r="J28" s="408" t="inlineStr">
         <is>
           <t>AI_Operating!D20:H20 (ΔNWC)</t>
         </is>
       </c>
-      <c r="L27" s="408" t="inlineStr">
+      <c r="L28" s="408" t="inlineStr">
         <is>
           <t>ΔNWC_Base = ΔRev × (C25 − C26); ΔNWC_AI = ΔRev × (C25 × (1 − C13) − C26). C13 does not multiply the whole (C25−C26) net.</t>
         </is>
       </c>
-      <c r="M27" s="408" t="inlineStr">
+      <c r="M28" s="408" t="inlineStr">
         <is>
           <t>MODEL CONST plug</t>
         </is>
       </c>
-      <c r="N27" s="466" t="inlineStr">
+      <c r="N28" s="466" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="90.75" customHeight="1" s="409">
-      <c r="B28" s="467" t="inlineStr">
+    <row r="29" ht="25.5" customHeight="1" s="409">
+      <c r="B29" s="467" t="inlineStr">
         <is>
           <t>#'Assumptions_Drivers'!E9</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="25.5" customHeight="1" s="409">
-      <c r="B29" s="468" t="inlineStr">
+    <row r="30" ht="409.5" customHeight="1" s="409">
+      <c r="B30" s="468" t="inlineStr">
         <is>
           <t>NOTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="409.5" customHeight="1" s="409">
-      <c r="B30" s="467" t="inlineStr">
-        <is>
-          <t>NWC FIX: C13=10% cuts AR only (not entire NWC). ΔNWC≈ΔAR(C25)−ΔDeferred(C26). Old formula ΔRev×WCbase×(1−C13) removed from ops.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="409.5" customHeight="1" s="409">
       <c r="B31" s="467" t="inlineStr">
         <is>
+          <t>NWC FIX: C13=10% cuts AR only (not entire NWC). ΔNWC≈ΔAR(C25)−ΔDeferred(C26). Old formula ΔRev×WCbase×(1−C13) removed from ops.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="409">
+      <c r="B32" s="467" t="inlineStr">
+        <is>
           <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_AI_COST_SOURCES.pdf</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="409">
-      <c r="B32" s="440" t="inlineStr">
+    <row r="33" ht="409.5" customHeight="1" s="409">
+      <c r="B33" s="440" t="inlineStr">
         <is>
           <t>SOURCES / VERBATIM</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="409.5" customHeight="1" s="409">
-      <c r="B33" s="469" t="inlineStr">
+    <row r="34" ht="84" customHeight="1" s="409">
+      <c r="B34" s="469" t="inlineStr">
         <is>
           <t>Assumptions_Drivers: Col A Baseline Yes/No | Col E source | Cols I/J/K clickable Verbatim. PDF: https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_DRIVER_SOURCES.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="84" customHeight="1" s="409">
-      <c r="B34" s="423" t="inlineStr">
-        <is>
-          <t>#'Assumptions_Drivers'!E9</t>
         </is>
       </c>
     </row>
     <row r="35" ht="409.5" customHeight="1" s="409">
       <c r="B35" s="423" t="inlineStr">
         <is>
+          <t>#'Assumptions_Drivers'!E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="13.8" customHeight="1" s="409">
+      <c r="B36" s="423" t="inlineStr">
+        <is>
           <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_AI_COST_SOURCES.pdf</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="13.8" customHeight="1" s="409"/>
-    <row r="37" ht="15" customHeight="1" s="409">
-      <c r="B37" s="447" t="n"/>
-    </row>
+    <row r="37" ht="15" customHeight="1" s="409"/>
     <row r="38" ht="84" customHeight="1" s="409">
-      <c r="B38" s="423" t="inlineStr">
-        <is>
-          <t>#'Assumptions_Drivers'!E9</t>
-        </is>
-      </c>
+      <c r="B38" s="447" t="n"/>
     </row>
     <row r="39" ht="409.5" customHeight="1" s="409">
       <c r="B39" s="423" t="inlineStr">
         <is>
+          <t>#'Assumptions_Drivers'!E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="13.8" customHeight="1" s="409">
+      <c r="B40" s="423" t="inlineStr">
+        <is>
           <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_AI_COST_SOURCES.pdf</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="13.8" customHeight="1" s="409"/>
-    <row r="41" ht="15" customHeight="1" s="409">
-      <c r="B41" s="447" t="n"/>
-    </row>
+    <row r="41" ht="15" customHeight="1" s="409"/>
     <row r="42" ht="84" customHeight="1" s="409">
-      <c r="B42" s="423" t="inlineStr">
-        <is>
-          <t>#'Assumptions_Drivers'!E9</t>
-        </is>
-      </c>
+      <c r="B42" s="447" t="n"/>
     </row>
     <row r="43" ht="409.5" customHeight="1" s="409">
       <c r="B43" s="423" t="inlineStr">
+        <is>
+          <t>#'Assumptions_Drivers'!E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="423" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_AI_COST_SOURCES.pdf</t>
         </is>
@@ -15213,20 +15337,30 @@
       <c r="E60" s="553" t="n">
         <v>147.4</v>
       </c>
-      <c r="F60" s="515" t="n">
-        <v>161.054736827472</v>
-      </c>
-      <c r="G60" s="515" t="n">
-        <v>162.082091165166</v>
-      </c>
-      <c r="H60" s="515" t="n">
-        <v>163.697620289742</v>
-      </c>
-      <c r="I60" s="515" t="n">
-        <v>163.56828931607</v>
-      </c>
-      <c r="J60" s="515" t="n">
-        <v>162.916558614463</v>
+      <c r="F60" s="733">
+        <f>F70*(-F43-F45-F46)</f>
+        <v/>
+      </c>
+      <c r="G60" s="733">
+        <f>G70*(-G43-G45-G46)</f>
+        <v/>
+      </c>
+      <c r="H60" s="733">
+        <f>H70*(-H43-H45-H46)</f>
+        <v/>
+      </c>
+      <c r="I60" s="733">
+        <f>I70*(-I43-I45-I46)</f>
+        <v/>
+      </c>
+      <c r="J60" s="733">
+        <f>J70*(-J43-J45-J46)</f>
+        <v/>
+      </c>
+      <c r="L60" s="804" t="inlineStr">
+        <is>
+          <t>SBC $ now = F70 × (|COS|+|R&amp;D|+|SG&amp;A|). Driven by Assumptions_Drivers!C29 (14.1%).</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="409">
@@ -15622,38 +15756,43 @@
       <c r="E70" s="522" t="n">
         <v>0.0849078341013825</v>
       </c>
-      <c r="F70" s="519" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="G70" s="566" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="H70" s="566" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="I70" s="566" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="J70" s="566" t="n">
-        <v>0.141</v>
+      <c r="F70" s="519">
+        <f>Assumptions_Drivers!$C$29</f>
+        <v/>
+      </c>
+      <c r="G70" s="566">
+        <f>Assumptions_Drivers!$C$29</f>
+        <v/>
+      </c>
+      <c r="H70" s="566">
+        <f>Assumptions_Drivers!$C$29</f>
+        <v/>
+      </c>
+      <c r="I70" s="566">
+        <f>Assumptions_Drivers!$C$29</f>
+        <v/>
+      </c>
+      <c r="J70" s="566">
+        <f>Assumptions_Drivers!$C$29</f>
+        <v/>
       </c>
       <c r="K70" s="519" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="567">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm","CAUTION — not a Driver: FY25 SBC $116.2m ÷ opex $824.2m = 14.1% (replaced wrong 9.3% BMC trend)")</f>
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm","CAUTION — Drivers C29: FY25 SBC $116.2m ÷ opex $824.2m = 14.1%; LBO $ = %×opex")</f>
         <v/>
       </c>
       <c r="M70" s="568" t="inlineStr">
         <is>
           <t>Ctrl+F: Total equity-based compensation expense $ 116.2
 Ctrl+F: Total operating expenses $ 824.2
-EQ: 116.2 ÷ 824.2 = 14.1%. Forecast F70:J70 hardcoded 14.1% flat. (Prior 9.3% was only BMC hist step 6.9%→7.8%→8.5%→9.3%, not ZI.)</t>
+EQ: Drivers C29=116.2÷824.2=14.1%. LBO F70:J70=Assumptions_Drivers!$C$29. SBC $=F70×(|F43|+|F45|+|F46|); CF F118=F60.</t>
         </is>
       </c>
       <c r="N70" s="568" t="inlineStr">
         <is>
-          <t>14.1% = FY25 equity-based comp $116.2m ÷ total operating expenses $824.2m. Flat hold; not used in AI_Operating FCF.</t>
+          <t>Single source: Drivers C29. 14.1% from FY25 10-K; LBO $ and CF rows now formula-linked. DCF add-back stays 0.</t>
         </is>
       </c>
     </row>
@@ -16786,20 +16925,25 @@
       <c r="C118" s="585" t="n"/>
       <c r="D118" s="585" t="n"/>
       <c r="E118" s="585" t="n"/>
-      <c r="F118" s="515" t="n">
-        <v>161.054736827472</v>
-      </c>
-      <c r="G118" s="515" t="n">
-        <v>162.082091165166</v>
-      </c>
-      <c r="H118" s="515" t="n">
-        <v>163.697620289742</v>
-      </c>
-      <c r="I118" s="515" t="n">
-        <v>163.56828931607</v>
-      </c>
-      <c r="J118" s="515" t="n">
-        <v>162.916558614463</v>
+      <c r="F118" s="733">
+        <f>F60</f>
+        <v/>
+      </c>
+      <c r="G118" s="733">
+        <f>G60</f>
+        <v/>
+      </c>
+      <c r="H118" s="733">
+        <f>H60</f>
+        <v/>
+      </c>
+      <c r="I118" s="733">
+        <f>I60</f>
+        <v/>
+      </c>
+      <c r="J118" s="733">
+        <f>J60</f>
+        <v/>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="409">
@@ -22536,7 +22680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:L118"/>
+  <dimension ref="B2:M118"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="1.73" customWidth="1" style="408" min="1" max="1"/>
@@ -22545,7 +22689,7 @@
     <col width="11.18" customWidth="1" style="408" min="4" max="4"/>
     <col width="10.18" customWidth="1" style="408" min="5" max="5"/>
     <col width="11" customWidth="1" style="408" min="8" max="8"/>
-    <col width="12.18" customWidth="1" style="408" min="11" max="11"/>
+    <col width="40" customWidth="1" style="408" min="11" max="11"/>
     <col width="9.18" customWidth="1" style="408" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -22887,10 +23031,10 @@
       <c r="I20" s="556" t="n"/>
       <c r="J20" s="556" t="n"/>
     </row>
-    <row r="21" ht="15" customHeight="1" s="409">
+    <row r="21" ht="40" customHeight="1" s="409">
       <c r="B21" s="561" t="inlineStr">
         <is>
-          <t>Stock based compensation</t>
+          <t>Stock based compensation (add-back)</t>
         </is>
       </c>
       <c r="D21" s="517" t="n">
@@ -22910,6 +23054,20 @@
       </c>
       <c r="I21" s="556" t="n"/>
       <c r="J21" s="556" t="n"/>
+      <c r="K21" s="805" t="inlineStr">
+        <is>
+          <t>POLICY: add-back = $0 (SBC treated as real cost). Assumption lives at Assumptions_Drivers!C29=14.1% and drives LBO!F60/F70 only — changing C29 does NOT change DCF UFCF unless this row is switched on.</t>
+        </is>
+      </c>
+      <c r="L21" s="806">
+        <f>Assumptions_Drivers!$C$29</f>
+        <v/>
+      </c>
+      <c r="M21" s="807" t="inlineStr">
+        <is>
+          <t>Drivers SBC % (memo only — not in UFCF)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="409">
       <c r="B22" s="408" t="inlineStr">

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -60,7 +60,7 @@
     <numFmt numFmtId="194" formatCode="#,##0.0_);\(#,##0.0\);&quot;- _)&quot;;@_)"/>
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
   </numFmts>
-  <fonts count="66">
+  <fonts count="68">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -492,8 +492,17 @@
       <i val="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -601,6 +610,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -801,7 +815,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="809">
+  <cellXfs count="814">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3207,6 +3221,21 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="18" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="20" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="18" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10770,7 +10799,7 @@
     <row r="47" ht="13.8" customHeight="1" s="409">
       <c r="B47" s="808" t="inlineStr">
         <is>
-          <t>SBC: Drivers C29=14.1% (FY25 $116.2÷$824.2) drives LBO SBC $/CF; DCF UFCF keeps SBC add-back at $0 (real cost).</t>
+          <t>SBC: Drivers C29=14.1% (FY25 $116.2÷$824.2) drives LBO SBC $/CF; DCF UFCF keeps SBC add-back at $0 (real cost). WC Major Variables: AR (C25), Deferred (C26), AI DSO cut (C13) → AI_Operating ΔNWC → FCF/debt sweep (LBO col O).</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12276,27 @@
     <row r="29" ht="25.5" customHeight="1" s="409">
       <c r="B29" s="467" t="inlineStr">
         <is>
-          <t>#'Assumptions_Drivers'!E9</t>
+          <t>WC MAJOR</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>LBO Working Capital Major Variables (col O): AR% (C25), Deferred% (C26), AI AR cut (C13), EOP NWC, CF ΔNWC. AP/Other CA = not major.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>See LBO!O75:O86 and LBO!O119</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>O76:O86</t>
         </is>
       </c>
     </row>
@@ -13910,6 +13959,7 @@
     <col width="42" customWidth="1" style="408" min="12" max="12"/>
     <col width="55" customWidth="1" style="408" min="13" max="13"/>
     <col width="36" customWidth="1" style="408" min="14" max="14"/>
+    <col width="38" customWidth="1" style="409" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" s="409">
@@ -15821,6 +15871,11 @@
       <c r="H72" s="571" t="n"/>
       <c r="I72" s="571" t="n"/>
       <c r="J72" s="571" t="n"/>
+      <c r="L72" s="809" t="inlineStr">
+        <is>
+          <t>WORKING CAPITAL — forecast % linked to Drivers (same standard as IS margins). Core LBO FCF uses AI_Operating ΔNWC = ΔAR−ΔDeferred.</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="409">
       <c r="B73" s="408" t="inlineStr">
@@ -15882,7 +15937,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" s="409">
+    <row r="75" ht="28" customHeight="1" s="409">
       <c r="B75" s="500" t="n"/>
       <c r="C75" s="569" t="n"/>
       <c r="D75" s="569" t="n"/>
@@ -15892,8 +15947,28 @@
       <c r="H75" s="569" t="n"/>
       <c r="I75" s="569" t="n"/>
       <c r="J75" s="569" t="n"/>
-    </row>
-    <row r="76" ht="15" customHeight="1" s="409">
+      <c r="L75" s="558" t="inlineStr">
+        <is>
+          <t>SOURCE (click) — Assess + how number enters</t>
+        </is>
+      </c>
+      <c r="M75" s="558" t="inlineStr">
+        <is>
+          <t>VERBATIM Ctrl+F + EQ derivation</t>
+        </is>
+      </c>
+      <c r="N75" s="558" t="inlineStr">
+        <is>
+          <t>WHY REASONABLE (≤30 words)</t>
+        </is>
+      </c>
+      <c r="O75" s="558" t="inlineStr">
+        <is>
+          <t>Major Variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="70" customHeight="1" s="409">
       <c r="B76" s="557" t="inlineStr">
         <is>
           <t>Accounts receivable, EOP</t>
@@ -15906,26 +15981,51 @@
       <c r="E76" s="573" t="n">
         <v>443.7</v>
       </c>
-      <c r="F76" s="537" t="n">
-        <v>459.2295</v>
-      </c>
-      <c r="G76" s="537" t="n">
-        <v>484.4871225</v>
-      </c>
-      <c r="H76" s="537" t="n">
-        <v>513.5563498499999</v>
-      </c>
-      <c r="I76" s="537" t="n">
-        <v>539.2341673425</v>
-      </c>
-      <c r="J76" s="537" t="n">
-        <v>565.1174073749399</v>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="409">
+      <c r="F76" s="614">
+        <f>F77*F42</f>
+        <v/>
+      </c>
+      <c r="G76" s="614">
+        <f>G77*G42</f>
+        <v/>
+      </c>
+      <c r="H76" s="614">
+        <f>H77*H42</f>
+        <v/>
+      </c>
+      <c r="I76" s="614">
+        <f>I77*I42</f>
+        <v/>
+      </c>
+      <c r="J76" s="614">
+        <f>J77*J42</f>
+        <v/>
+      </c>
+      <c r="L76" s="563">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","REASONABLE: EOP AR = Drivers C25 × Revenue (stock from intensity)")</f>
+        <v/>
+      </c>
+      <c r="M76" s="564" t="inlineStr">
+        <is>
+          <t>Ctrl+F: Accounts receivable, net | 246.1
+EQ: F76=F77×F42. F77=Assumptions_Drivers!$C$25 (59/365). AI FCF uses ΔAR=ΔRev×C25×(1−C13), not this EOP alone.</t>
+        </is>
+      </c>
+      <c r="N76" s="564" t="inlineStr">
+        <is>
+          <t>EOP AR rebuilt as intensity×sales so the BS tracks Drivers. Live debt-sweep cash uses AI_Operating ΔAR, not BMC AR.</t>
+        </is>
+      </c>
+      <c r="O76" s="810" t="inlineStr">
+        <is>
+          <t>YES — AR drives ΔAR cash use in FCF → debt paydown / IRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="70" customHeight="1" s="409">
       <c r="B77" s="574" t="inlineStr">
         <is>
-          <t>AR as % of sales</t>
+          <t>AR as % of sales (Drivers C25 intensity)</t>
         </is>
       </c>
       <c r="C77" s="522" t="n"/>
@@ -15935,23 +16035,48 @@
       <c r="E77" s="522" t="n">
         <v>0.201553556827473</v>
       </c>
-      <c r="F77" s="534" t="n">
-        <v>0.201553556827473</v>
-      </c>
-      <c r="G77" s="534" t="n">
-        <v>0.201553556827473</v>
-      </c>
-      <c r="H77" s="534" t="n">
-        <v>0.201553556827473</v>
-      </c>
-      <c r="I77" s="534" t="n">
-        <v>0.201553556827473</v>
-      </c>
-      <c r="J77" s="534" t="n">
-        <v>0.201553556827473</v>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1" s="409">
+      <c r="F77" s="519">
+        <f>Assumptions_Drivers!$C$25</f>
+        <v/>
+      </c>
+      <c r="G77" s="519">
+        <f>Assumptions_Drivers!$C$25</f>
+        <v/>
+      </c>
+      <c r="H77" s="519">
+        <f>Assumptions_Drivers!$C$25</f>
+        <v/>
+      </c>
+      <c r="I77" s="519">
+        <f>Assumptions_Drivers!$C$25</f>
+        <v/>
+      </c>
+      <c r="J77" s="519">
+        <f>Assumptions_Drivers!$C$25</f>
+        <v/>
+      </c>
+      <c r="L77" s="563">
+        <f>HYPERLINK("https://getfairview.com/blog/working-capital-management-saas","REASONABLE: Fairview median DSO 59d → C25=59/365≈16.2%")</f>
+        <v/>
+      </c>
+      <c r="M77" s="564" t="inlineStr">
+        <is>
+          <t>Ctrl+F: Median B2B SaaS DSO is 59 days
+EQ: Assumptions_Drivers!C25=59/365≈16.164%. LBO F77:J77=Assumptions_Drivers!$C$25. AI also applies C13=10% cut on ΔAR only.</t>
+        </is>
+      </c>
+      <c r="N77" s="564" t="inlineStr">
+        <is>
+          <t>Fairview’s 59-day median becomes 16.2% AR intensity in Drivers C25; that cell feeds every forecast AR% here.</t>
+        </is>
+      </c>
+      <c r="O77" s="810" t="inlineStr">
+        <is>
+          <t>YES — primary AR/% assumption; pairs with C13 DSO cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="70" customHeight="1" s="409">
       <c r="B78" s="557" t="inlineStr">
         <is>
           <t>Other current assets, EOP</t>
@@ -15964,23 +16089,48 @@
       <c r="E78" s="573" t="n">
         <v>213.1</v>
       </c>
-      <c r="F78" s="537" t="n">
-        <v>220.5585</v>
-      </c>
-      <c r="G78" s="537" t="n">
-        <v>232.6892175</v>
-      </c>
-      <c r="H78" s="537" t="n">
-        <v>246.65057055</v>
-      </c>
-      <c r="I78" s="537" t="n">
-        <v>258.9830990775</v>
-      </c>
-      <c r="J78" s="537" t="n">
-        <v>271.41428783322</v>
-      </c>
-    </row>
-    <row r="79" ht="15" customHeight="1" s="409">
+      <c r="F78" s="614">
+        <f>F79*F42</f>
+        <v/>
+      </c>
+      <c r="G78" s="614">
+        <f>G79*G42</f>
+        <v/>
+      </c>
+      <c r="H78" s="614">
+        <f>H79*H42</f>
+        <v/>
+      </c>
+      <c r="I78" s="614">
+        <f>I79*I42</f>
+        <v/>
+      </c>
+      <c r="J78" s="614">
+        <f>J79*J42</f>
+        <v/>
+      </c>
+      <c r="L78" s="567">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","CAUTION — not a Driver: other CA held at FY24 % of sales")</f>
+        <v/>
+      </c>
+      <c r="M78" s="568" t="inlineStr">
+        <is>
+          <t>Ctrl+F: Prepaid expenses and other current assets (ZI BS)
+EQ: Hold E79≈9.7% of sales flat; F78=F79×F42. Not in AI_Operating ΔNWC math (ΔNWC≈ΔAR−ΔDeferred only).</t>
+        </is>
+      </c>
+      <c r="N78" s="568" t="inlineStr">
+        <is>
+          <t>No yellow Driver for other CA. Held flat vs last hist %. Excluded from core AI ΔNWC used in FCF.</t>
+        </is>
+      </c>
+      <c r="O78" s="811" t="inlineStr">
+        <is>
+          <t>NO — not in AI ΔNWC; immaterial to LBO FCF/IRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="70" customHeight="1" s="409">
       <c r="B79" s="574" t="inlineStr">
         <is>
           <t>Other current assets as % of sales</t>
@@ -15993,23 +16143,42 @@
       <c r="E79" s="522" t="n">
         <v>0.0968020350685927</v>
       </c>
-      <c r="F79" s="534" t="n">
+      <c r="F79" s="519" t="n">
         <v>0.0968020350685927</v>
       </c>
-      <c r="G79" s="534" t="n">
+      <c r="G79" s="519" t="n">
         <v>0.0968020350685927</v>
       </c>
-      <c r="H79" s="534" t="n">
+      <c r="H79" s="519" t="n">
         <v>0.0968020350685927</v>
       </c>
-      <c r="I79" s="534" t="n">
+      <c r="I79" s="519" t="n">
         <v>0.0968020350685927</v>
       </c>
-      <c r="J79" s="534" t="n">
+      <c r="J79" s="519" t="n">
         <v>0.0968020350685927</v>
       </c>
-    </row>
-    <row r="80" ht="15" customHeight="1" s="409">
+      <c r="L79" s="567">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","CAUTION — not a Driver: other CA % held flat")</f>
+        <v/>
+      </c>
+      <c r="M79" s="568" t="inlineStr">
+        <is>
+          <t>EQ: F79:J79 = E79 (last hist %). Not Assumptions_Drivers. Core model ignores other CA in ΔNWC.</t>
+        </is>
+      </c>
+      <c r="N79" s="568" t="inlineStr">
+        <is>
+          <t>Placeholder ratio only. Changing it does not move AI_Operating FCF or debt sweep.</t>
+        </is>
+      </c>
+      <c r="O79" s="811" t="inlineStr">
+        <is>
+          <t>NO — non-core; no Drivers link</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="70" customHeight="1" s="409">
       <c r="B80" s="557" t="inlineStr">
         <is>
           <t>Accounts payable, EOP</t>
@@ -16022,23 +16191,48 @@
       <c r="E80" s="573" t="n">
         <v>42.1</v>
       </c>
-      <c r="F80" s="537" t="n">
-        <v>41.3598506882921</v>
-      </c>
-      <c r="G80" s="537" t="n">
-        <v>42.7799258244632</v>
-      </c>
-      <c r="H80" s="537" t="n">
-        <v>44.440721723145</v>
-      </c>
-      <c r="I80" s="537" t="n">
-        <v>45.7114581759768</v>
-      </c>
-      <c r="J80" s="537" t="n">
-        <v>46.9086461526987</v>
-      </c>
-    </row>
-    <row r="81" ht="15" customHeight="1" s="409">
+      <c r="F80" s="614">
+        <f>F81*(-F43)</f>
+        <v/>
+      </c>
+      <c r="G80" s="614">
+        <f>G81*(-G43)</f>
+        <v/>
+      </c>
+      <c r="H80" s="614">
+        <f>H81*(-H43)</f>
+        <v/>
+      </c>
+      <c r="I80" s="614">
+        <f>I81*(-I43)</f>
+        <v/>
+      </c>
+      <c r="J80" s="614">
+        <f>J81*(-J43)</f>
+        <v/>
+      </c>
+      <c r="L80" s="567">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","CAUTION — ZI AP only $16.6m; hold hist AP/COGS %")</f>
+        <v/>
+      </c>
+      <c r="M80" s="568" t="inlineStr">
+        <is>
+          <t>Ctrl+F: Accounts payable | $16.6
+EQ: F81 held at E81; F80=F81×|COGS|. SaaS AP is tiny vs deferred revenue; not a Drivers lever.</t>
+        </is>
+      </c>
+      <c r="N80" s="568" t="inlineStr">
+        <is>
+          <t>ZI FY24 AP was $16.6m — small. Held hist AP/COGS %. Not a core LBO cash lever vs deferred/AR.</t>
+        </is>
+      </c>
+      <c r="O80" s="811" t="inlineStr">
+        <is>
+          <t>NO — small SaaS AP; weak FCF/IRR sensitivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="70" customHeight="1" s="409">
       <c r="B81" s="574" t="inlineStr">
         <is>
           <t>AP as % of COGS</t>
@@ -16051,23 +16245,43 @@
       <c r="E81" s="522" t="n">
         <v>0.0711148648648649</v>
       </c>
-      <c r="F81" s="534" t="n">
+      <c r="F81" s="519" t="n">
         <v>0.0711148648648649</v>
       </c>
-      <c r="G81" s="534" t="n">
+      <c r="G81" s="519" t="n">
         <v>0.0711148648648649</v>
       </c>
-      <c r="H81" s="534" t="n">
+      <c r="H81" s="519" t="n">
         <v>0.0711148648648649</v>
       </c>
-      <c r="I81" s="534" t="n">
+      <c r="I81" s="519" t="n">
         <v>0.0711148648648649</v>
       </c>
-      <c r="J81" s="534" t="n">
+      <c r="J81" s="519" t="n">
         <v>0.0711148648648649</v>
       </c>
-    </row>
-    <row r="82" ht="15" customHeight="1" s="409">
+      <c r="L81" s="567">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","CAUTION — not a Driver: AP/COGS % held flat")</f>
+        <v/>
+      </c>
+      <c r="M81" s="568" t="inlineStr">
+        <is>
+          <t>Ctrl+F: Accounts payable | $16.6
+EQ: F81:J81 = E81. No Assumptions_Drivers cell for DPO/AP%.</t>
+        </is>
+      </c>
+      <c r="N81" s="568" t="inlineStr">
+        <is>
+          <t>AP% is residual hist, not a sourced Driver. Core NWC thesis is AR + deferred, not payables.</t>
+        </is>
+      </c>
+      <c r="O81" s="811" t="inlineStr">
+        <is>
+          <t>NO — not a Drivers assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="70" customHeight="1" s="409">
       <c r="B82" s="557" t="inlineStr">
         <is>
           <t>Accrued expenses &amp; def revenues, EOP</t>
@@ -16080,26 +16294,51 @@
       <c r="E82" s="573" t="n">
         <v>2301.7</v>
       </c>
-      <c r="F82" s="537" t="n">
-        <v>2382.2595</v>
-      </c>
-      <c r="G82" s="537" t="n">
-        <v>2513.2837725</v>
-      </c>
-      <c r="H82" s="537" t="n">
-        <v>2664.08079885</v>
-      </c>
-      <c r="I82" s="537" t="n">
-        <v>2797.2848387925</v>
-      </c>
-      <c r="J82" s="537" t="n">
-        <v>2931.55451105454</v>
-      </c>
-    </row>
-    <row r="83" ht="15" customHeight="1" s="409">
+      <c r="F82" s="614">
+        <f>F83*F42</f>
+        <v/>
+      </c>
+      <c r="G82" s="614">
+        <f>G83*G42</f>
+        <v/>
+      </c>
+      <c r="H82" s="614">
+        <f>H83*H42</f>
+        <v/>
+      </c>
+      <c r="I82" s="614">
+        <f>I83*I42</f>
+        <v/>
+      </c>
+      <c r="J82" s="614">
+        <f>J83*J42</f>
+        <v/>
+      </c>
+      <c r="L82" s="563">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","REASONABLE: EOP deferred/accrued ≈ Drivers C26 × Revenue")</f>
+        <v/>
+      </c>
+      <c r="M82" s="564" t="inlineStr">
+        <is>
+          <t>Ctrl+F: we had unearned revenue of $477.9 million, of which $473.8 million was recorded as a current liability
+EQ: F82=F83×F42; F83=Assumptions_Drivers!$C$26. ΔDeferred≈C26×ΔRev is the cash-source leg of AI ΔNWC.</t>
+        </is>
+      </c>
+      <c r="N82" s="564" t="inlineStr">
+        <is>
+          <t>EOP deferred rebuilt from Drivers 39% so BS matches the unearned-revenue cash source in FCF math.</t>
+        </is>
+      </c>
+      <c r="O82" s="810" t="inlineStr">
+        <is>
+          <t>YES — deferred revenue is the largest SaaS NWC cash source</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="70" customHeight="1" s="409">
       <c r="B83" s="574" t="inlineStr">
         <is>
-          <t>As % of sales</t>
+          <t>Deferred/accrued as % of sales (Drivers C26)</t>
         </is>
       </c>
       <c r="C83" s="522" t="n"/>
@@ -16109,20 +16348,46 @@
       <c r="E83" s="522" t="n">
         <v>1.04556191514491</v>
       </c>
-      <c r="F83" s="519" t="n">
-        <v>1.04556191514491</v>
-      </c>
-      <c r="G83" s="519" t="n">
-        <v>1.04556191514491</v>
-      </c>
-      <c r="H83" s="519" t="n">
-        <v>1.04556191514491</v>
-      </c>
-      <c r="I83" s="519" t="n">
-        <v>1.04556191514491</v>
-      </c>
-      <c r="J83" s="519" t="n">
-        <v>1.04556191514491</v>
+      <c r="F83" s="519">
+        <f>Assumptions_Drivers!$C$26</f>
+        <v/>
+      </c>
+      <c r="G83" s="519">
+        <f>Assumptions_Drivers!$C$26</f>
+        <v/>
+      </c>
+      <c r="H83" s="519">
+        <f>Assumptions_Drivers!$C$26</f>
+        <v/>
+      </c>
+      <c r="I83" s="519">
+        <f>Assumptions_Drivers!$C$26</f>
+        <v/>
+      </c>
+      <c r="J83" s="519">
+        <f>Assumptions_Drivers!$C$26</f>
+        <v/>
+      </c>
+      <c r="L83" s="563">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","REASONABLE: ZI FY24 unearned $473.8m / sales $1,214.3m → C26≈39%")</f>
+        <v/>
+      </c>
+      <c r="M83" s="564" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 473.8
+Ctrl+F: Unearned revenue, current portion
+EQ: Assumptions_Drivers!C26=473.8/1,214.3≈39.02%. LBO F83:J83=Assumptions_Drivers!$C$26.</t>
+        </is>
+      </c>
+      <c r="N83" s="564" t="inlineStr">
+        <is>
+          <t>10-K current unearned $473.8m ÷ FY24 sales $1,214.3m = 39%. That exact ratio is Drivers C26.</t>
+        </is>
+      </c>
+      <c r="O83" s="810" t="inlineStr">
+        <is>
+          <t>YES — sets ΔDeferred in ΔNWC ≈ ΔAR − ΔDeferred</t>
+        </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="409">
@@ -16131,10 +16396,10 @@
       <c r="D84" s="522" t="n"/>
       <c r="E84" s="522" t="n"/>
     </row>
-    <row r="85" ht="15" customHeight="1" s="409">
+    <row r="85" ht="70" customHeight="1" s="409">
       <c r="B85" s="525" t="inlineStr">
         <is>
-          <t>Net Working Capital</t>
+          <t>Net Working Capital (EOP)</t>
         </is>
       </c>
       <c r="C85" s="500" t="n"/>
@@ -16144,23 +16409,52 @@
       <c r="E85" s="576" t="n">
         <v>-1687</v>
       </c>
-      <c r="F85" s="515" t="n">
-        <v>-1743.83135068829</v>
-      </c>
-      <c r="G85" s="515" t="n">
-        <v>-1838.88735832446</v>
-      </c>
-      <c r="H85" s="515" t="n">
-        <v>-1948.31460017315</v>
-      </c>
-      <c r="I85" s="515" t="n">
-        <v>-2044.77903054848</v>
-      </c>
-      <c r="J85" s="515" t="n">
-        <v>-2141.93146199908</v>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1" s="409">
+      <c r="F85" s="733">
+        <f>F76+F78-F80-F82</f>
+        <v/>
+      </c>
+      <c r="G85" s="733">
+        <f>G76+G78-G80-G82</f>
+        <v/>
+      </c>
+      <c r="H85" s="733">
+        <f>H76+H78-H80-H82</f>
+        <v/>
+      </c>
+      <c r="I85" s="733">
+        <f>I76+I78-I80-I82</f>
+        <v/>
+      </c>
+      <c r="J85" s="733">
+        <f>J76+J78-J80-J82</f>
+        <v/>
+      </c>
+      <c r="L85" s="563">
+        <f>HYPERLINK("https://getfairview.com/blog/working-capital-management-saas","REASONABLE: EOP NWC = AR+OCA−AP−Deferred; FCF uses AI ΔNWC")</f>
+        <v/>
+      </c>
+      <c r="M85" s="564" t="inlineStr">
+        <is>
+          <t>EQ: F85=F76+F78−F80−F82. Core LBO/DCF cash: AI_Operating ΔNWC≈ΔAR−ΔDeferred with ΔAR=ΔRev×C25×(1−C13), ΔDef=ΔRev×C26. CF row F119=AI_Operating ΔNWC.</t>
+        </is>
+      </c>
+      <c r="N85" s="564" t="inlineStr">
+        <is>
+          <t>EOP NWC is the BS rollup. Deal cash and debt sweep follow AI_Operating ΔNWC from Drivers C13/C25/C26.</t>
+        </is>
+      </c>
+      <c r="O85" s="810" t="inlineStr">
+        <is>
+          <t>YES — ΔNWC hits FCF, debt sweep, MOIC/IRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="55" customHeight="1" s="409">
+      <c r="B86" s="408" t="inlineStr">
+        <is>
+          <t>AI AR improvement (Drivers C13) — applies in AI_Operating ΔNWC</t>
+        </is>
+      </c>
       <c r="D86" s="516" t="n"/>
       <c r="E86" s="516" t="n"/>
       <c r="F86" s="510" t="n"/>
@@ -16168,6 +16462,26 @@
       <c r="H86" s="510" t="n"/>
       <c r="I86" s="510" t="n"/>
       <c r="J86" s="510" t="n"/>
+      <c r="L86" s="563">
+        <f>HYPERLINK("https://getfairview.com/blog/working-capital-management-saas","RELATED Drivers C13: 10% AR/DSO improvement — MAJOR AI lever")</f>
+        <v/>
+      </c>
+      <c r="M86" s="564" t="inlineStr">
+        <is>
+          <t>Ctrl+F: Median B2B SaaS DSO is 59 days
+EQ: Drivers C13=10%. Model story: ~6/59≈10% DSO cut → ΔAR_AI=ΔRev×C25×(1−0.10). Applies to AI_Operating only (not Base).</t>
+        </is>
+      </c>
+      <c r="N86" s="564" t="inlineStr">
+        <is>
+          <t>10% cuts ΔAR only (not whole NWC). With deferred still at 39%, net ΔNWC stays a cash source.</t>
+        </is>
+      </c>
+      <c r="O86" s="812" t="inlineStr">
+        <is>
+          <t>YES — AI case lever vs Base; lifts FCF/debt paydown</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="409">
       <c r="B87" s="570" t="inlineStr">
@@ -16955,20 +17269,35 @@
       <c r="C119" s="510" t="n"/>
       <c r="D119" s="510" t="n"/>
       <c r="E119" s="510" t="n"/>
-      <c r="F119" s="515" t="n">
-        <v>56.8313506882919</v>
-      </c>
-      <c r="G119" s="515" t="n">
-        <v>95.0560076361708</v>
-      </c>
-      <c r="H119" s="515" t="n">
-        <v>109.427241848682</v>
-      </c>
-      <c r="I119" s="515" t="n">
-        <v>96.4644303753319</v>
-      </c>
-      <c r="J119" s="515" t="n">
-        <v>97.1524314506019</v>
+      <c r="F119" s="733">
+        <f>AI_Operating!D20</f>
+        <v/>
+      </c>
+      <c r="G119" s="733">
+        <f>AI_Operating!E20</f>
+        <v/>
+      </c>
+      <c r="H119" s="733">
+        <f>AI_Operating!F20</f>
+        <v/>
+      </c>
+      <c r="I119" s="733">
+        <f>AI_Operating!G20</f>
+        <v/>
+      </c>
+      <c r="J119" s="733">
+        <f>AI_Operating!H20</f>
+        <v/>
+      </c>
+      <c r="L119" s="805" t="inlineStr">
+        <is>
+          <t>ΔNWC in CF now = AI_Operating (Drivers C13/C25/C26). This is the cash line that feeds debt sweep — not the old BMC WC delta.</t>
+        </is>
+      </c>
+      <c r="O119" s="813" t="inlineStr">
+        <is>
+          <t>YES — CF ΔNWC is a core LBO cash variable</t>
+        </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" s="409">

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -502,7 +502,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -615,6 +615,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -815,7 +820,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="814">
+  <cellXfs count="815">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3234,6 +3239,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="21" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12279,22 +12287,22 @@
           <t>WC MAJOR</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="408" t="inlineStr">
         <is>
           <t>LBO Working Capital Major Variables (col O): AR% (C25), Deferred% (C26), AI AR cut (C13), EOP NWC, CF ΔNWC. AP/Other CA = not major.</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="408" t="inlineStr">
         <is>
           <t>See LBO!O75:O86 and LBO!O119</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="408" t="inlineStr">
         <is>
           <t>LBO</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="408" t="inlineStr">
         <is>
           <t>O76:O86</t>
         </is>
@@ -13956,10 +13964,11 @@
     <col width="15.73" customWidth="1" style="408" min="3" max="3"/>
     <col width="48" customWidth="1" style="408" min="5" max="5"/>
     <col width="12.82" customWidth="1" style="408" min="11" max="11"/>
-    <col width="42" customWidth="1" style="408" min="12" max="12"/>
-    <col width="55" customWidth="1" style="408" min="13" max="13"/>
-    <col width="36" customWidth="1" style="408" min="14" max="14"/>
-    <col width="38" customWidth="1" style="409" min="15" max="15"/>
+    <col width="40" customWidth="1" style="408" min="12" max="12"/>
+    <col width="42" customWidth="1" style="408" min="13" max="13"/>
+    <col width="52" customWidth="1" style="408" min="14" max="14"/>
+    <col width="34" customWidth="1" style="409" min="15" max="15"/>
+    <col width="38" customWidth="1" style="409" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" s="409">
@@ -15873,6 +15882,11 @@
       <c r="J72" s="571" t="n"/>
       <c r="L72" s="809" t="inlineStr">
         <is>
+          <t>How each WC line grows (or stays flat) in the forecast.</t>
+        </is>
+      </c>
+      <c r="M72" s="809" t="inlineStr">
+        <is>
           <t>WORKING CAPITAL — forecast % linked to Drivers (same standard as IS margins). Core LBO FCF uses AI_Operating ΔNWC = ΔAR−ΔDeferred.</t>
         </is>
       </c>
@@ -15937,7 +15951,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="75" ht="28" customHeight="1" s="409">
+    <row r="75" ht="30" customHeight="1" s="409">
       <c r="B75" s="500" t="n"/>
       <c r="C75" s="569" t="n"/>
       <c r="D75" s="569" t="n"/>
@@ -15949,26 +15963,31 @@
       <c r="J75" s="569" t="n"/>
       <c r="L75" s="558" t="inlineStr">
         <is>
+          <t>Growth trajectory</t>
+        </is>
+      </c>
+      <c r="M75" s="558" t="inlineStr">
+        <is>
           <t>SOURCE (click) — Assess + how number enters</t>
         </is>
       </c>
-      <c r="M75" s="558" t="inlineStr">
+      <c r="N75" s="558" t="inlineStr">
         <is>
           <t>VERBATIM Ctrl+F + EQ derivation</t>
         </is>
       </c>
-      <c r="N75" s="558" t="inlineStr">
+      <c r="O75" s="558" t="inlineStr">
         <is>
           <t>WHY REASONABLE (≤30 words)</t>
         </is>
       </c>
-      <c r="O75" s="558" t="inlineStr">
+      <c r="P75" s="558" t="inlineStr">
         <is>
           <t>Major Variable</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="70" customHeight="1" s="409">
+    <row r="76" ht="78" customHeight="1" s="409">
       <c r="B76" s="557" t="inlineStr">
         <is>
           <t>Accounts receivable, EOP</t>
@@ -16001,28 +16020,33 @@
         <f>J77*J42</f>
         <v/>
       </c>
-      <c r="L76" s="563">
+      <c r="L76" s="814" t="inlineStr">
+        <is>
+          <t>Grows with revenue at +5%/yr (Drivers C5). EOP AR = 16.2% × Sales each year → $AR rises ~5% as sales rise; ratio flat. AI FCF: ΔAR = ΔRev×16.2%×(1−10%).</t>
+        </is>
+      </c>
+      <c r="M76" s="563">
         <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","REASONABLE: EOP AR = Drivers C25 × Revenue (stock from intensity)")</f>
         <v/>
       </c>
-      <c r="M76" s="564" t="inlineStr">
+      <c r="N76" s="564" t="inlineStr">
         <is>
           <t>Ctrl+F: Accounts receivable, net | 246.1
 EQ: F76=F77×F42. F77=Assumptions_Drivers!$C$25 (59/365). AI FCF uses ΔAR=ΔRev×C25×(1−C13), not this EOP alone.</t>
         </is>
       </c>
-      <c r="N76" s="564" t="inlineStr">
+      <c r="O76" s="564" t="inlineStr">
         <is>
           <t>EOP AR rebuilt as intensity×sales so the BS tracks Drivers. Live debt-sweep cash uses AI_Operating ΔAR, not BMC AR.</t>
         </is>
       </c>
-      <c r="O76" s="810" t="inlineStr">
+      <c r="P76" s="810" t="inlineStr">
         <is>
           <t>YES — AR drives ΔAR cash use in FCF → debt paydown / IRR</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="70" customHeight="1" s="409">
+    <row r="77" ht="78" customHeight="1" s="409">
       <c r="B77" s="574" t="inlineStr">
         <is>
           <t>AR as % of sales (Drivers C25 intensity)</t>
@@ -16055,28 +16079,33 @@
         <f>Assumptions_Drivers!$C$25</f>
         <v/>
       </c>
-      <c r="L77" s="563">
+      <c r="L77" s="814" t="inlineStr">
+        <is>
+          <t>Ratio FLAT at 16.2% every forecast year (no step-up). Does not grow as a %. Dollar AR grows only because sales grow +5%. AI case: effective ΔAR intensity = 16.2%×90% = 14.55%.</t>
+        </is>
+      </c>
+      <c r="M77" s="563">
         <f>HYPERLINK("https://getfairview.com/blog/working-capital-management-saas","REASONABLE: Fairview median DSO 59d → C25=59/365≈16.2%")</f>
         <v/>
       </c>
-      <c r="M77" s="564" t="inlineStr">
+      <c r="N77" s="564" t="inlineStr">
         <is>
           <t>Ctrl+F: Median B2B SaaS DSO is 59 days
 EQ: Assumptions_Drivers!C25=59/365≈16.164%. LBO F77:J77=Assumptions_Drivers!$C$25. AI also applies C13=10% cut on ΔAR only.</t>
         </is>
       </c>
-      <c r="N77" s="564" t="inlineStr">
+      <c r="O77" s="564" t="inlineStr">
         <is>
           <t>Fairview’s 59-day median becomes 16.2% AR intensity in Drivers C25; that cell feeds every forecast AR% here.</t>
         </is>
       </c>
-      <c r="O77" s="810" t="inlineStr">
+      <c r="P77" s="810" t="inlineStr">
         <is>
           <t>YES — primary AR/% assumption; pairs with C13 DSO cut</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="70" customHeight="1" s="409">
+    <row r="78" ht="78" customHeight="1" s="409">
       <c r="B78" s="557" t="inlineStr">
         <is>
           <t>Other current assets, EOP</t>
@@ -16109,28 +16138,33 @@
         <f>J79*J42</f>
         <v/>
       </c>
-      <c r="L78" s="567">
+      <c r="L78" s="814" t="inlineStr">
+        <is>
+          <t>Grows with revenue at +5%/yr. EOP = flat 9.7% × Sales → dollars track sales; % does not trend.</t>
+        </is>
+      </c>
+      <c r="M78" s="567">
         <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","CAUTION — not a Driver: other CA held at FY24 % of sales")</f>
         <v/>
       </c>
-      <c r="M78" s="568" t="inlineStr">
+      <c r="N78" s="568" t="inlineStr">
         <is>
           <t>Ctrl+F: Prepaid expenses and other current assets (ZI BS)
 EQ: Hold E79≈9.7% of sales flat; F78=F79×F42. Not in AI_Operating ΔNWC math (ΔNWC≈ΔAR−ΔDeferred only).</t>
         </is>
       </c>
-      <c r="N78" s="568" t="inlineStr">
+      <c r="O78" s="568" t="inlineStr">
         <is>
           <t>No yellow Driver for other CA. Held flat vs last hist %. Excluded from core AI ΔNWC used in FCF.</t>
         </is>
       </c>
-      <c r="O78" s="811" t="inlineStr">
+      <c r="P78" s="811" t="inlineStr">
         <is>
           <t>NO — not in AI ΔNWC; immaterial to LBO FCF/IRR</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="70" customHeight="1" s="409">
+    <row r="79" ht="78" customHeight="1" s="409">
       <c r="B79" s="574" t="inlineStr">
         <is>
           <t>Other current assets as % of sales</t>
@@ -16158,27 +16192,32 @@
       <c r="J79" s="519" t="n">
         <v>0.0968020350685927</v>
       </c>
-      <c r="L79" s="567">
+      <c r="L79" s="814" t="inlineStr">
+        <is>
+          <t>FLAT — held at last hist ~9.7% of sales for all F–J. No growth in the ratio; no Drivers path.</t>
+        </is>
+      </c>
+      <c r="M79" s="567">
         <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","CAUTION — not a Driver: other CA % held flat")</f>
         <v/>
       </c>
-      <c r="M79" s="568" t="inlineStr">
+      <c r="N79" s="568" t="inlineStr">
         <is>
           <t>EQ: F79:J79 = E79 (last hist %). Not Assumptions_Drivers. Core model ignores other CA in ΔNWC.</t>
         </is>
       </c>
-      <c r="N79" s="568" t="inlineStr">
+      <c r="O79" s="568" t="inlineStr">
         <is>
           <t>Placeholder ratio only. Changing it does not move AI_Operating FCF or debt sweep.</t>
         </is>
       </c>
-      <c r="O79" s="811" t="inlineStr">
+      <c r="P79" s="811" t="inlineStr">
         <is>
           <t>NO — non-core; no Drivers link</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="70" customHeight="1" s="409">
+    <row r="80" ht="78" customHeight="1" s="409">
       <c r="B80" s="557" t="inlineStr">
         <is>
           <t>Accounts payable, EOP</t>
@@ -16211,28 +16250,33 @@
         <f>J81*(-J43)</f>
         <v/>
       </c>
-      <c r="L80" s="567">
+      <c r="L80" s="814" t="inlineStr">
+        <is>
+          <t>Grows with COGS (COGS = (1−80% GM)×Sales → COGS also +5%/yr). EOP AP = flat 7.1% × |COGS|; ratio flat, dollars ≈+5%.</t>
+        </is>
+      </c>
+      <c r="M80" s="567">
         <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","CAUTION — ZI AP only $16.6m; hold hist AP/COGS %")</f>
         <v/>
       </c>
-      <c r="M80" s="568" t="inlineStr">
+      <c r="N80" s="568" t="inlineStr">
         <is>
           <t>Ctrl+F: Accounts payable | $16.6
 EQ: F81 held at E81; F80=F81×|COGS|. SaaS AP is tiny vs deferred revenue; not a Drivers lever.</t>
         </is>
       </c>
-      <c r="N80" s="568" t="inlineStr">
+      <c r="O80" s="568" t="inlineStr">
         <is>
           <t>ZI FY24 AP was $16.6m — small. Held hist AP/COGS %. Not a core LBO cash lever vs deferred/AR.</t>
         </is>
       </c>
-      <c r="O80" s="811" t="inlineStr">
+      <c r="P80" s="811" t="inlineStr">
         <is>
           <t>NO — small SaaS AP; weak FCF/IRR sensitivity</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="70" customHeight="1" s="409">
+    <row r="81" ht="78" customHeight="1" s="409">
       <c r="B81" s="574" t="inlineStr">
         <is>
           <t>AP as % of COGS</t>
@@ -16260,28 +16304,33 @@
       <c r="J81" s="519" t="n">
         <v>0.0711148648648649</v>
       </c>
-      <c r="L81" s="567">
+      <c r="L81" s="814" t="inlineStr">
+        <is>
+          <t>FLAT — AP/COGS held at last hist ~7.1% every year. No DPO improvement assumed.</t>
+        </is>
+      </c>
+      <c r="M81" s="567">
         <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","CAUTION — not a Driver: AP/COGS % held flat")</f>
         <v/>
       </c>
-      <c r="M81" s="568" t="inlineStr">
+      <c r="N81" s="568" t="inlineStr">
         <is>
           <t>Ctrl+F: Accounts payable | $16.6
 EQ: F81:J81 = E81. No Assumptions_Drivers cell for DPO/AP%.</t>
         </is>
       </c>
-      <c r="N81" s="568" t="inlineStr">
+      <c r="O81" s="568" t="inlineStr">
         <is>
           <t>AP% is residual hist, not a sourced Driver. Core NWC thesis is AR + deferred, not payables.</t>
         </is>
       </c>
-      <c r="O81" s="811" t="inlineStr">
+      <c r="P81" s="811" t="inlineStr">
         <is>
           <t>NO — not a Drivers assumption</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="70" customHeight="1" s="409">
+    <row r="82" ht="78" customHeight="1" s="409">
       <c r="B82" s="557" t="inlineStr">
         <is>
           <t>Accrued expenses &amp; def revenues, EOP</t>
@@ -16314,28 +16363,33 @@
         <f>J83*J42</f>
         <v/>
       </c>
-      <c r="L82" s="563">
+      <c r="L82" s="814" t="inlineStr">
+        <is>
+          <t>Grows with revenue at +5%/yr. EOP deferred/accrued = 39.0% × Sales → $ balance rises ~5% with sales; ratio flat. ΔDeferred = 39%×ΔRev each year (cash source).</t>
+        </is>
+      </c>
+      <c r="M82" s="563">
         <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","REASONABLE: EOP deferred/accrued ≈ Drivers C26 × Revenue")</f>
         <v/>
       </c>
-      <c r="M82" s="564" t="inlineStr">
+      <c r="N82" s="564" t="inlineStr">
         <is>
           <t>Ctrl+F: we had unearned revenue of $477.9 million, of which $473.8 million was recorded as a current liability
 EQ: F82=F83×F42; F83=Assumptions_Drivers!$C$26. ΔDeferred≈C26×ΔRev is the cash-source leg of AI ΔNWC.</t>
         </is>
       </c>
-      <c r="N82" s="564" t="inlineStr">
+      <c r="O82" s="564" t="inlineStr">
         <is>
           <t>EOP deferred rebuilt from Drivers 39% so BS matches the unearned-revenue cash source in FCF math.</t>
         </is>
       </c>
-      <c r="O82" s="810" t="inlineStr">
+      <c r="P82" s="810" t="inlineStr">
         <is>
           <t>YES — deferred revenue is the largest SaaS NWC cash source</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="70" customHeight="1" s="409">
+    <row r="83" ht="78" customHeight="1" s="409">
       <c r="B83" s="574" t="inlineStr">
         <is>
           <t>Deferred/accrued as % of sales (Drivers C26)</t>
@@ -16368,23 +16422,28 @@
         <f>Assumptions_Drivers!$C$26</f>
         <v/>
       </c>
-      <c r="L83" s="563">
+      <c r="L83" s="814" t="inlineStr">
+        <is>
+          <t>Ratio FLAT at ~39% of sales all years (Drivers C26). Dollars grow only via +5% revenue. No fade or step-up in deferred attach.</t>
+        </is>
+      </c>
+      <c r="M83" s="563">
         <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","REASONABLE: ZI FY24 unearned $473.8m / sales $1,214.3m → C26≈39%")</f>
         <v/>
       </c>
-      <c r="M83" s="564" t="inlineStr">
+      <c r="N83" s="564" t="inlineStr">
         <is>
           <t>Ctrl+F: 473.8
 Ctrl+F: Unearned revenue, current portion
 EQ: Assumptions_Drivers!C26=473.8/1,214.3≈39.02%. LBO F83:J83=Assumptions_Drivers!$C$26.</t>
         </is>
       </c>
-      <c r="N83" s="564" t="inlineStr">
+      <c r="O83" s="564" t="inlineStr">
         <is>
           <t>10-K current unearned $473.8m ÷ FY24 sales $1,214.3m = 39%. That exact ratio is Drivers C26.</t>
         </is>
       </c>
-      <c r="O83" s="810" t="inlineStr">
+      <c r="P83" s="810" t="inlineStr">
         <is>
           <t>YES — sets ΔDeferred in ΔNWC ≈ ΔAR − ΔDeferred</t>
         </is>
@@ -16396,7 +16455,7 @@
       <c r="D84" s="522" t="n"/>
       <c r="E84" s="522" t="n"/>
     </row>
-    <row r="85" ht="70" customHeight="1" s="409">
+    <row r="85" ht="78" customHeight="1" s="409">
       <c r="B85" s="525" t="inlineStr">
         <is>
           <t>Net Working Capital (EOP)</t>
@@ -16429,27 +16488,32 @@
         <f>J76+J78-J80-J82</f>
         <v/>
       </c>
-      <c r="L85" s="563">
+      <c r="L85" s="814" t="inlineStr">
+        <is>
+          <t>More negative ~in line with +5% sales: deferred (39%) &gt; AR (16.2%), so NWC stays a cash source. ΔNWC ≈ ΔRev×[16.2%×(1−10%)−39%] ≈ −24.45% of ΔRev each year (AI).</t>
+        </is>
+      </c>
+      <c r="M85" s="563">
         <f>HYPERLINK("https://getfairview.com/blog/working-capital-management-saas","REASONABLE: EOP NWC = AR+OCA−AP−Deferred; FCF uses AI ΔNWC")</f>
         <v/>
       </c>
-      <c r="M85" s="564" t="inlineStr">
+      <c r="N85" s="564" t="inlineStr">
         <is>
           <t>EQ: F85=F76+F78−F80−F82. Core LBO/DCF cash: AI_Operating ΔNWC≈ΔAR−ΔDeferred with ΔAR=ΔRev×C25×(1−C13), ΔDef=ΔRev×C26. CF row F119=AI_Operating ΔNWC.</t>
         </is>
       </c>
-      <c r="N85" s="564" t="inlineStr">
+      <c r="O85" s="564" t="inlineStr">
         <is>
           <t>EOP NWC is the BS rollup. Deal cash and debt sweep follow AI_Operating ΔNWC from Drivers C13/C25/C26.</t>
         </is>
       </c>
-      <c r="O85" s="810" t="inlineStr">
+      <c r="P85" s="810" t="inlineStr">
         <is>
           <t>YES — ΔNWC hits FCF, debt sweep, MOIC/IRR</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="55" customHeight="1" s="409">
+    <row r="86" ht="78" customHeight="1" s="409">
       <c r="B86" s="408" t="inlineStr">
         <is>
           <t>AI AR improvement (Drivers C13) — applies in AI_Operating ΔNWC</t>
@@ -16462,22 +16526,27 @@
       <c r="H86" s="510" t="n"/>
       <c r="I86" s="510" t="n"/>
       <c r="J86" s="510" t="n"/>
-      <c r="L86" s="563">
+      <c r="L86" s="814" t="inlineStr">
+        <is>
+          <t>ONE-TIME structural cut: AI ΔAR intensity permanently 10% lower than Base from Y1 on (not a further −10% each year). Base ΔAR=16.2%×ΔRev; AI=14.55%×ΔRev.</t>
+        </is>
+      </c>
+      <c r="M86" s="563">
         <f>HYPERLINK("https://getfairview.com/blog/working-capital-management-saas","RELATED Drivers C13: 10% AR/DSO improvement — MAJOR AI lever")</f>
         <v/>
       </c>
-      <c r="M86" s="564" t="inlineStr">
+      <c r="N86" s="564" t="inlineStr">
         <is>
           <t>Ctrl+F: Median B2B SaaS DSO is 59 days
 EQ: Drivers C13=10%. Model story: ~6/59≈10% DSO cut → ΔAR_AI=ΔRev×C25×(1−0.10). Applies to AI_Operating only (not Base).</t>
         </is>
       </c>
-      <c r="N86" s="564" t="inlineStr">
+      <c r="O86" s="564" t="inlineStr">
         <is>
           <t>10% cuts ΔAR only (not whole NWC). With deferred still at 39%, net ΔNWC stays a cash source.</t>
         </is>
       </c>
-      <c r="O86" s="812" t="inlineStr">
+      <c r="P86" s="810" t="inlineStr">
         <is>
           <t>YES — AI case lever vs Base; lifts FCF/debt paydown</t>
         </is>
@@ -17289,12 +17358,18 @@
         <f>AI_Operating!H20</f>
         <v/>
       </c>
-      <c r="L119" s="805" t="inlineStr">
-        <is>
-          <t>ΔNWC in CF now = AI_Operating (Drivers C13/C25/C26). This is the cash line that feeds debt sweep — not the old BMC WC delta.</t>
-        </is>
-      </c>
-      <c r="O119" s="813" t="inlineStr">
+      <c r="L119" s="814" t="inlineStr">
+        <is>
+          <t>Each year ΔNWC ≈ ΔRev × (14.55% − 39.0%) ≈ −24.5% of ΔRev (AI). Grows in $ with +5% revenue (larger ΔRev → larger cash release). Not a flat $.</t>
+        </is>
+      </c>
+      <c r="M119" s="805" t="inlineStr">
+        <is>
+          <t>ΔNWC in CF = AI_Operating (Drivers C13/C25/C26). Cash line that feeds debt sweep — not the old BMC WC delta.</t>
+        </is>
+      </c>
+      <c r="O119" s="813" t="n"/>
+      <c r="P119" s="810" t="inlineStr">
         <is>
           <t>YES — CF ΔNWC is a core LBO cash variable</t>
         </is>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -16140,7 +16140,7 @@
       </c>
       <c r="L78" s="814" t="inlineStr">
         <is>
-          <t>Grows with revenue at +5%/yr. EOP = flat 9.7% × Sales → dollars track sales; % does not trend.</t>
+          <t>“Flat” = the 9.7% of-sales ratio stays unchanged each year (no step-up/fade). Dollars still grow ~+5% with revenue: EOP = 9.7% × Sales.</t>
         </is>
       </c>
       <c r="M78" s="567">
@@ -16155,7 +16155,7 @@
       </c>
       <c r="O78" s="568" t="inlineStr">
         <is>
-          <t>No yellow Driver for other CA. Held flat vs last hist %. Excluded from core AI ΔNWC used in FCF.</t>
+          <t>Flat means the % does not trend. Only the dollar balance rises because sales rise +5%; ratio locked at ~9.7%.</t>
         </is>
       </c>
       <c r="P78" s="811" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="L79" s="814" t="inlineStr">
         <is>
-          <t>FLAT — held at last hist ~9.7% of sales for all F–J. No growth in the ratio; no Drivers path.</t>
+          <t>“Flat” = same ~9.7% every forecast year. Not growing as a percentage; only $ Other CA grow when sales grow.</t>
         </is>
       </c>
       <c r="M79" s="567">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="O79" s="568" t="inlineStr">
         <is>
-          <t>Placeholder ratio only. Changing it does not move AI_Operating FCF or debt sweep.</t>
+          <t>Flat ratio = no YoY change in %. Placeholder hist hold; dollars move only with +5% sales.</t>
         </is>
       </c>
       <c r="P79" s="811" t="inlineStr">
@@ -16306,7 +16306,7 @@
       </c>
       <c r="L81" s="814" t="inlineStr">
         <is>
-          <t>FLAT — AP/COGS held at last hist ~7.1% every year. No DPO improvement assumed.</t>
+          <t>“Flat” = AP/COGS stays ~7.1% every year (no DPO improvement). Dollars grow only as COGS grows ~+5% with sales.</t>
         </is>
       </c>
       <c r="M81" s="567">

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -15963,7 +15963,7 @@
       <c r="J75" s="569" t="n"/>
       <c r="L75" s="558" t="inlineStr">
         <is>
-          <t>Growth trajectory</t>
+          <t>Growth trajectory (figure FIRST)</t>
         </is>
       </c>
       <c r="M75" s="558" t="inlineStr">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="L76" s="814" t="inlineStr">
         <is>
-          <t>Grows with revenue at +5%/yr (Drivers C5). EOP AR = 16.2% × Sales each year → $AR rises ~5% as sales rise; ratio flat. AI FCF: ΔAR = ΔRev×16.2%×(1−10%).</t>
+          <t>+5%/yr. EOP AR = flat 16.2% × Sales; dollars track revenue growth; AR% does not trend. AI FCF: ΔAR = ΔRev×16.2%×(1−10%).</t>
         </is>
       </c>
       <c r="M76" s="563">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="L77" s="814" t="inlineStr">
         <is>
-          <t>Ratio FLAT at 16.2% every forecast year (no step-up). Does not grow as a %. Dollar AR grows only because sales grow +5%. AI case: effective ΔAR intensity = 16.2%×90% = 14.55%.</t>
+          <t>16.2% flat every year (Drivers C25). Ratio does not grow; dollar AR grows only because sales grow +5%. AI ΔAR intensity = 16.2%×90% = 14.55%.</t>
         </is>
       </c>
       <c r="M77" s="563">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="L78" s="814" t="inlineStr">
         <is>
-          <t>“Flat” = the 9.7% of-sales ratio stays unchanged each year (no step-up/fade). Dollars still grow ~+5% with revenue: EOP = 9.7% × Sales.</t>
+          <t>+5%/yr. EOP = flat 9.7% × Sales → dollars track sales. “Flat” = the 9.7% ratio stays unchanged (no step-up/fade).</t>
         </is>
       </c>
       <c r="M78" s="567">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="L79" s="814" t="inlineStr">
         <is>
-          <t>“Flat” = same ~9.7% every forecast year. Not growing as a percentage; only $ Other CA grow when sales grow.</t>
+          <t>9.7% flat every forecast year. Not growing as a percentage; only $ Other CA grow when sales grow +5%.</t>
         </is>
       </c>
       <c r="M79" s="567">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="L80" s="814" t="inlineStr">
         <is>
-          <t>Grows with COGS (COGS = (1−80% GM)×Sales → COGS also +5%/yr). EOP AP = flat 7.1% × |COGS|; ratio flat, dollars ≈+5%.</t>
+          <t>+5%/yr. EOP AP = flat 7.1% × |COGS|; COGS also rises ~+5% with sales. Ratio flat; dollars ≈+5%.</t>
         </is>
       </c>
       <c r="M80" s="567">
@@ -16306,7 +16306,7 @@
       </c>
       <c r="L81" s="814" t="inlineStr">
         <is>
-          <t>“Flat” = AP/COGS stays ~7.1% every year (no DPO improvement). Dollars grow only as COGS grows ~+5% with sales.</t>
+          <t>7.1% flat every year (AP/COGS). No DPO improvement. Dollars grow only as COGS grows ~+5% with sales.</t>
         </is>
       </c>
       <c r="M81" s="567">
@@ -16365,7 +16365,7 @@
       </c>
       <c r="L82" s="814" t="inlineStr">
         <is>
-          <t>Grows with revenue at +5%/yr. EOP deferred/accrued = 39.0% × Sales → $ balance rises ~5% with sales; ratio flat. ΔDeferred = 39%×ΔRev each year (cash source).</t>
+          <t>+5%/yr. EOP deferred/accrued = flat 39.0% × Sales; $ balance rises with sales. ΔDeferred = 39%×ΔRev each year (cash source).</t>
         </is>
       </c>
       <c r="M82" s="563">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="L83" s="814" t="inlineStr">
         <is>
-          <t>Ratio FLAT at ~39% of sales all years (Drivers C26). Dollars grow only via +5% revenue. No fade or step-up in deferred attach.</t>
+          <t>39% flat of sales all years (Drivers C26). Dollars grow only via +5% revenue. No fade or step-up in deferred attach.</t>
         </is>
       </c>
       <c r="M83" s="563">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="L85" s="814" t="inlineStr">
         <is>
-          <t>More negative ~in line with +5% sales: deferred (39%) &gt; AR (16.2%), so NWC stays a cash source. ΔNWC ≈ ΔRev×[16.2%×(1−10%)−39%] ≈ −24.45% of ΔRev each year (AI).</t>
+          <t>−24.45% of ΔRev/yr (AI). NWC more negative as sales grow +5%: deferred 39% &gt; AR 16.2%×(1−10%). ΔNWC ≈ ΔRev×[14.55%−39%].</t>
         </is>
       </c>
       <c r="M85" s="563">
@@ -16528,7 +16528,7 @@
       <c r="J86" s="510" t="n"/>
       <c r="L86" s="814" t="inlineStr">
         <is>
-          <t>ONE-TIME structural cut: AI ΔAR intensity permanently 10% lower than Base from Y1 on (not a further −10% each year). Base ΔAR=16.2%×ΔRev; AI=14.55%×ΔRev.</t>
+          <t>−10% once (Drivers C13). Permanent lower ΔAR intensity from Y1 — not another −10% each year. Base 16.2%×ΔRev; AI 14.55%×ΔRev.</t>
         </is>
       </c>
       <c r="M86" s="563">
@@ -17360,7 +17360,7 @@
       </c>
       <c r="L119" s="814" t="inlineStr">
         <is>
-          <t>Each year ΔNWC ≈ ΔRev × (14.55% − 39.0%) ≈ −24.5% of ΔRev (AI). Grows in $ with +5% revenue (larger ΔRev → larger cash release). Not a flat $.</t>
+          <t>−24.5% of ΔRev/yr (AI). ΔNWC ≈ ΔRev×(14.55%−39%). Cash release grows in $ as +5% sales widens ΔRev; not a flat dollar.</t>
         </is>
       </c>
       <c r="M119" s="805" t="inlineStr">

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -15498,15 +15498,20 @@
       <c r="B63" s="557" t="n"/>
       <c r="L63" s="558" t="inlineStr">
         <is>
+          <t>Growth trajectory (figure FIRST)</t>
+        </is>
+      </c>
+      <c r="M63" s="558" t="inlineStr">
+        <is>
           <t>SOURCE (click) — Assess + how number enters</t>
         </is>
       </c>
-      <c r="M63" s="558" t="inlineStr">
+      <c r="N63" s="558" t="inlineStr">
         <is>
           <t>VERBATIM Ctrl+F + EQ derivation (how the % was calculated)</t>
         </is>
       </c>
-      <c r="N63" s="558" t="inlineStr">
+      <c r="O63" s="558" t="inlineStr">
         <is>
           <t>WHY REASONABLE (≤30 words) — where the number came from</t>
         </is>
@@ -15524,13 +15529,18 @@
           <t>Step</t>
         </is>
       </c>
-      <c r="L64" s="560" t="inlineStr">
+      <c r="L64" s="809" t="inlineStr">
+        <is>
+          <t>Figure first: +5%, 80% flat, etc.</t>
+        </is>
+      </c>
+      <c r="M64" s="804" t="inlineStr">
         <is>
           <t>Growth rates &amp; margins — each forecast % must show source quote + arithmetic (EQ)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="75" customHeight="1" s="409">
+    <row r="65" ht="72" customHeight="1" s="409">
       <c r="B65" s="561" t="inlineStr">
         <is>
           <t>Revenue growth</t>
@@ -15566,23 +15576,28 @@
       <c r="K65" s="519" t="n">
         <v>0</v>
       </c>
-      <c r="L65" s="563">
+      <c r="L65" s="814" t="inlineStr">
+        <is>
+          <t>+5%/yr flat (Drivers C5). Same growth rate every forecast year — not the FY25 +3% print; rounded 2022–25 CAGR ~4.4% → +5%.</t>
+        </is>
+      </c>
+      <c r="M65" s="563">
         <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm","REASONABLE: ZI FY25 10-K — Drivers C5=+5% (rounded CAGR, not raw +3%)")</f>
         <v/>
       </c>
-      <c r="M65" s="564" t="inlineStr">
+      <c r="N65" s="564" t="inlineStr">
         <is>
           <t>Ctrl+F: Revenue was $1,249.5 million for the year ended December 31, 2025, an increase of $35.2 million, or 3%
 EQ: FY22 rev $1,098.0 → FY25 $1,249.5; CAGR=(1249.5/1098)^(1/3)−1≈4.4% → Drivers C5 rounds to +5%. LBO F65:J65 = Assumptions_Drivers!$C$5.</t>
         </is>
       </c>
-      <c r="N65" s="564" t="inlineStr">
-        <is>
-          <t>10-K shows FY25 +3% ($35.2m). Model uses +5% = rounded 2022–25 CAGR (~4.4%), via Drivers C5 linked here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="75" customHeight="1" s="409">
+      <c r="O65" s="564" t="inlineStr">
+        <is>
+          <t>+5% enters via Drivers C5. 10-K shows FY25 +3%; model uses rounded multi-year CAGR ~4.4%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="72" customHeight="1" s="409">
       <c r="B66" s="561" t="inlineStr">
         <is>
           <t>Gross profit as % of sales</t>
@@ -15620,23 +15635,28 @@
       <c r="K66" s="519" t="n">
         <v>0</v>
       </c>
-      <c r="L66" s="563">
+      <c r="L66" s="814" t="inlineStr">
+        <is>
+          <t>80% flat every year (Drivers C6). GM ratio does not trend up/down; dollars of GP grow ~+5% with sales at constant 80%.</t>
+        </is>
+      </c>
+      <c r="M66" s="563">
         <f>HYPERLINK("https://www.getaleph.com/answers/saas-gross-margin-2026","REASONABLE: Aleph × Benchmarkit — median GM 80% → Drivers C6")</f>
         <v/>
       </c>
-      <c r="M66" s="564" t="inlineStr">
+      <c r="N66" s="564" t="inlineStr">
         <is>
           <t>Ctrl+F: The 2025 median software gross margin is 80%
 EQ: Drivers C6 = 80% exactly from that median sentence. LBO F66:J66 = Assumptions_Drivers!$C$6. (ZI GAAP GM ~84% is NOT the driver.)</t>
         </is>
       </c>
-      <c r="N66" s="564" t="inlineStr">
-        <is>
-          <t>Aleph’s verbatim median is 80%. That 80% is Drivers C6 and feeds every forecast GM cell here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="75" customHeight="1" s="409">
+      <c r="O66" s="564" t="inlineStr">
+        <is>
+          <t>80% is Aleph’s median and Drivers C6; that flat 80% feeds every forecast GM cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="72" customHeight="1" s="409">
       <c r="B67" s="561" t="inlineStr">
         <is>
           <t>R&amp;D margin</t>
@@ -15674,24 +15694,29 @@
       <c r="K67" s="519" t="n">
         <v>0</v>
       </c>
-      <c r="L67" s="563">
+      <c r="L67" s="814" t="inlineStr">
+        <is>
+          <t>~16.15% flat (R&amp;D÷Sales). FY24 $196.1÷$1,214.3; both scale +5% in AI_Operating so the margin stays constant.</t>
+        </is>
+      </c>
+      <c r="M67" s="563">
         <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","REASONABLE: ZI FY24 10-K — R&amp;D $196.1m / Rev $1,214.3m ≈16.15%")</f>
         <v/>
       </c>
-      <c r="M67" s="564" t="inlineStr">
+      <c r="N67" s="564" t="inlineStr">
         <is>
           <t>Ctrl+F: Research and development for the year ended December 31, 2024 was $196.1 million
 Ctrl+F: Revenue was $1,214.3 million for the year ended December 31, 2024
 EQ: 196.1÷1,214.3≈16.15%. AI_Operating grows both at +5%, so R&amp;D% stays ~16.15%. LBO = AI_Operating!R&amp;D / AI_Operating!Revenue.</t>
         </is>
       </c>
-      <c r="N67" s="564" t="inlineStr">
-        <is>
-          <t>Ratio from FY24 R&amp;D $196.1m ÷ sales $1,214.3m. Forecast keeps that % by scaling R&amp;D with +5% revenue in AI_Operating.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="75" customHeight="1" s="409">
+      <c r="O67" s="564" t="inlineStr">
+        <is>
+          <t>16.15% from FY24 R&amp;D÷sales; held flat by growing R&amp;D with +5% revenue in AI_Operating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="72" customHeight="1" s="409">
       <c r="B68" s="561" t="inlineStr">
         <is>
           <t>SG&amp;A margin</t>
@@ -15729,24 +15754,29 @@
       <c r="K68" s="519" t="n">
         <v>0</v>
       </c>
-      <c r="L68" s="563">
+      <c r="L68" s="814" t="inlineStr">
+        <is>
+          <t>−18% S&amp;M cut in Y1, then S&amp;M +2%/yr (Fed); G&amp;A flat 18% of sales; +$24.5m AI each year. SG&amp;A% = (S&amp;M+AI+G&amp;A)/Sales from AI_Operating.</t>
+        </is>
+      </c>
+      <c r="M68" s="563">
         <f>HYPERLINK("https://www.digitalapplied.com/blog/ai-sdr-statistics-2026-outbound-sales-data-points","REASONABLE: Built %, not one page — 18% SDR cut (Digital Applied) + G&amp;A 18% (Blossom) + $24.5m AI")</f>
         <v/>
       </c>
-      <c r="M68" s="564" t="inlineStr">
+      <c r="N68" s="564" t="inlineStr">
         <is>
           <t>Ctrl+F (Digital Applied): Net SDR headcount in US B2B SaaS companies is down 18% YoY
 Ctrl+F (Blossom, Drivers E11): G&amp;A was 18%
 EQ: SG&amp;A% = (S&amp;M_human + AI_infra $24.5m + G&amp;A)/Revenue from AI_Operating. S&amp;M_human = FY24 $414.1m×(1−18%); G&amp;A = 18%×Revenue.</t>
         </is>
       </c>
-      <c r="N68" s="564" t="inlineStr">
-        <is>
-          <t>No single “SG&amp;A%” quote. % = AI_Operating (cut S&amp;M 18%, +$24.5m AI, G&amp;A 18% of sales) ÷ revenue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="75" customHeight="1" s="409">
+      <c r="O68" s="564" t="inlineStr">
+        <is>
+          <t>−18% is the Y1 S&amp;M lever; SG&amp;A% is built in AI_Operating, not a single page quote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="72" customHeight="1" s="409">
       <c r="B69" s="561" t="inlineStr">
         <is>
           <t>Tax rate</t>
@@ -15784,23 +15814,28 @@
       <c r="K69" s="519" t="n">
         <v>0</v>
       </c>
-      <c r="L69" s="563">
+      <c r="L69" s="814" t="inlineStr">
+        <is>
+          <t>21% flat every year (Drivers C19). Statutory rate — no glide path; tax $ grows with pretax income, rate unchanged.</t>
+        </is>
+      </c>
+      <c r="M69" s="563">
         <f>HYPERLINK("https://taxsummaries.pwc.com/united-states/corporate/taxes-on-corporate-income","REASONABLE: PwC — flat 21% → Drivers C19")</f>
         <v/>
       </c>
-      <c r="M69" s="564" t="inlineStr">
+      <c r="N69" s="564" t="inlineStr">
         <is>
           <t>Ctrl+F: The United States taxes resident corporations at a flat rate of 21%
 EQ: Drivers C19 = 21% from that sentence. LBO F69:J69 = Assumptions_Drivers!$C$19.</t>
         </is>
       </c>
-      <c r="N69" s="564" t="inlineStr">
-        <is>
-          <t>PwC’s flat 21% is copied into Drivers C19; this tax row is a direct link to that cell.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="75" customHeight="1" s="409">
+      <c r="O69" s="564" t="inlineStr">
+        <is>
+          <t>21% is PwC’s flat federal rate in Drivers C19; this row links straight to that cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="72" customHeight="1" s="409">
       <c r="B70" s="561" t="inlineStr">
         <is>
           <t>SBC as % of all operating expenses</t>
@@ -15838,20 +15873,25 @@
       <c r="K70" s="519" t="n">
         <v>0</v>
       </c>
-      <c r="L70" s="567">
+      <c r="L70" s="814" t="inlineStr">
+        <is>
+          <t>14.1% flat (Drivers C29). FY25 $116.2÷$824.2; SBC $ = 14.1%×opex each year. DCF add-back stays $0.</t>
+        </is>
+      </c>
+      <c r="M70" s="567">
         <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm","CAUTION — Drivers C29: FY25 SBC $116.2m ÷ opex $824.2m = 14.1%; LBO $ = %×opex")</f>
         <v/>
       </c>
-      <c r="M70" s="568" t="inlineStr">
+      <c r="N70" s="568" t="inlineStr">
         <is>
           <t>Ctrl+F: Total equity-based compensation expense $ 116.2
 Ctrl+F: Total operating expenses $ 824.2
 EQ: Drivers C29=116.2÷824.2=14.1%. LBO F70:J70=Assumptions_Drivers!$C$29. SBC $=F70×(|F43|+|F45|+|F46|); CF F118=F60.</t>
         </is>
       </c>
-      <c r="N70" s="568" t="inlineStr">
-        <is>
-          <t>Single source: Drivers C29. 14.1% from FY25 10-K; LBO $ and CF rows now formula-linked. DCF add-back stays 0.</t>
+      <c r="O70" s="568" t="inlineStr">
+        <is>
+          <t>14.1% from FY25 SBC÷opex in Drivers C29; LBO $ and CF linked. DCF add-back stays 0.</t>
         </is>
       </c>
     </row>
@@ -23058,7 +23098,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="F302:J302"/>
     <mergeCell ref="G321:I321"/>
     <mergeCell ref="D291:J291"/>
@@ -23068,7 +23108,6 @@
     <mergeCell ref="F292:J292"/>
     <mergeCell ref="F311:J311"/>
     <mergeCell ref="F216:J216"/>
-    <mergeCell ref="L64:N64"/>
     <mergeCell ref="D301:J301"/>
     <mergeCell ref="E280:J280"/>
   </mergeCells>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -820,7 +820,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="815">
+  <cellXfs count="819">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3243,6 +3243,18 @@
     </xf>
     <xf numFmtId="0" fontId="62" fillId="21" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="175" fontId="62" fillId="21" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -10901,9 +10913,9 @@
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="409">
-      <c r="B55" s="408" t="inlineStr">
-        <is>
-          <t>IRR (%)</t>
+      <c r="B55" s="815" t="inlineStr">
+        <is>
+          <t>ASSETS FIX: LBO CapEx→AI 1.84% of sales (C24×(1−C12)); D&amp;A→AI; software/intangible purchases→$0 (match DCF). See LBO!L90:P107.</t>
         </is>
       </c>
       <c r="C55" s="408" t="n">
@@ -10926,7 +10938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:N44"/>
+  <dimension ref="B2:N56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="408" min="2" max="2"/>
@@ -12390,6 +12402,23 @@
       <c r="B44" s="423" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel2-44dc/LBO/output/LBOMODEL2_AI_COST_SOURCES.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="408" t="inlineStr">
+        <is>
+          <t>ASSETS</t>
+        </is>
+      </c>
+      <c r="C56" s="408" t="inlineStr">
+        <is>
+          <t>CapEx Major Variable: Drivers C24=2%, C12=8% → 1.84%. LBO/DCF CapEx linked to AI_Operating. Intangible purchases $0.</t>
+        </is>
+      </c>
+      <c r="G56" s="408" t="inlineStr">
+        <is>
+          <t>LBO!F92 / DCF!D25</t>
         </is>
       </c>
     </row>
@@ -13067,20 +13096,25 @@
       <c r="C15" s="486" t="n">
         <v>85.7</v>
       </c>
-      <c r="D15" s="456" t="n">
-        <v>89.985</v>
-      </c>
-      <c r="E15" s="456" t="n">
-        <v>94.48425</v>
-      </c>
-      <c r="F15" s="456" t="n">
-        <v>99.2084625</v>
-      </c>
-      <c r="G15" s="456" t="n">
-        <v>104.168885625</v>
-      </c>
-      <c r="H15" s="456" t="n">
-        <v>109.37732990625</v>
+      <c r="D15" s="456">
+        <f>C15*(1+Assumptions_Drivers!$C$5)</f>
+        <v/>
+      </c>
+      <c r="E15" s="456">
+        <f>D15*(1+Assumptions_Drivers!$C$5)</f>
+        <v/>
+      </c>
+      <c r="F15" s="456">
+        <f>E15*(1+Assumptions_Drivers!$C$5)</f>
+        <v/>
+      </c>
+      <c r="G15" s="456">
+        <f>F15*(1+Assumptions_Drivers!$C$5)</f>
+        <v/>
+      </c>
+      <c r="H15" s="456">
+        <f>G15*(1+Assumptions_Drivers!$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="409">
@@ -13158,20 +13192,25 @@
           <t>CapEx</t>
         </is>
       </c>
-      <c r="D19" s="456" t="n">
-        <v>25.5003</v>
-      </c>
-      <c r="E19" s="456" t="n">
-        <v>26.775315</v>
-      </c>
-      <c r="F19" s="456" t="n">
-        <v>28.11408075</v>
-      </c>
-      <c r="G19" s="456" t="n">
-        <v>29.5197847875</v>
-      </c>
-      <c r="H19" s="456" t="n">
-        <v>30.995774026875</v>
+      <c r="D19" s="456">
+        <f>D5*Assumptions_Drivers!$C$24</f>
+        <v/>
+      </c>
+      <c r="E19" s="456">
+        <f>E5*Assumptions_Drivers!$C$24</f>
+        <v/>
+      </c>
+      <c r="F19" s="456">
+        <f>F5*Assumptions_Drivers!$C$24</f>
+        <v/>
+      </c>
+      <c r="G19" s="456">
+        <f>G5*Assumptions_Drivers!$C$24</f>
+        <v/>
+      </c>
+      <c r="H19" s="456">
+        <f>H5*Assumptions_Drivers!$C$24</f>
+        <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="409">
@@ -13618,20 +13657,25 @@
       <c r="C15" s="486" t="n">
         <v>85.7</v>
       </c>
-      <c r="D15" s="456" t="n">
-        <v>89.985</v>
-      </c>
-      <c r="E15" s="456" t="n">
-        <v>94.48425</v>
-      </c>
-      <c r="F15" s="456" t="n">
-        <v>99.2084625</v>
-      </c>
-      <c r="G15" s="456" t="n">
-        <v>104.168885625</v>
-      </c>
-      <c r="H15" s="456" t="n">
-        <v>109.37732990625</v>
+      <c r="D15" s="456">
+        <f>C15*(1+Assumptions_Drivers!$C$5)</f>
+        <v/>
+      </c>
+      <c r="E15" s="456">
+        <f>D15*(1+Assumptions_Drivers!$C$5)</f>
+        <v/>
+      </c>
+      <c r="F15" s="456">
+        <f>E15*(1+Assumptions_Drivers!$C$5)</f>
+        <v/>
+      </c>
+      <c r="G15" s="456">
+        <f>F15*(1+Assumptions_Drivers!$C$5)</f>
+        <v/>
+      </c>
+      <c r="H15" s="456">
+        <f>G15*(1+Assumptions_Drivers!$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="409">
@@ -13709,20 +13753,25 @@
           <t>CapEx</t>
         </is>
       </c>
-      <c r="D19" s="456" t="n">
-        <v>23.460276</v>
-      </c>
-      <c r="E19" s="456" t="n">
-        <v>24.6332898</v>
-      </c>
-      <c r="F19" s="456" t="n">
-        <v>25.86495429</v>
-      </c>
-      <c r="G19" s="456" t="n">
-        <v>27.1582020045</v>
-      </c>
-      <c r="H19" s="456" t="n">
-        <v>28.516112104725</v>
+      <c r="D19" s="456">
+        <f>D5*Assumptions_Drivers!$C$24*(1-Assumptions_Drivers!$C$12)</f>
+        <v/>
+      </c>
+      <c r="E19" s="456">
+        <f>E5*Assumptions_Drivers!$C$24*(1-Assumptions_Drivers!$C$12)</f>
+        <v/>
+      </c>
+      <c r="F19" s="456">
+        <f>F5*Assumptions_Drivers!$C$24*(1-Assumptions_Drivers!$C$12)</f>
+        <v/>
+      </c>
+      <c r="G19" s="456">
+        <f>G5*Assumptions_Drivers!$C$24*(1-Assumptions_Drivers!$C$12)</f>
+        <v/>
+      </c>
+      <c r="H19" s="456">
+        <f>H5*Assumptions_Drivers!$C$24*(1-Assumptions_Drivers!$C$12)</f>
+        <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="409">
@@ -15340,20 +15389,25 @@
       <c r="E58" s="553" t="n">
         <v>229</v>
       </c>
-      <c r="F58" s="515" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="G58" s="515" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="H58" s="515" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="I58" s="515" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="J58" s="515" t="n">
-        <v>101.3</v>
+      <c r="F58" s="733">
+        <f>AI_Operating!D15</f>
+        <v/>
+      </c>
+      <c r="G58" s="733">
+        <f>AI_Operating!E15</f>
+        <v/>
+      </c>
+      <c r="H58" s="733">
+        <f>AI_Operating!F15</f>
+        <v/>
+      </c>
+      <c r="I58" s="733">
+        <f>AI_Operating!G15</f>
+        <v/>
+      </c>
+      <c r="J58" s="733">
+        <f>AI_Operating!H15</f>
+        <v/>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="409">
@@ -16606,6 +16660,11 @@
       <c r="H87" s="578" t="n"/>
       <c r="I87" s="578" t="n"/>
       <c r="J87" s="578" t="n"/>
+      <c r="L87" s="809" t="inlineStr">
+        <is>
+          <t>Assets — CapEx/D&amp;A wired to Drivers/AI_Operating (was BMC). Intangible &amp; capitalized-software buys set to $0 to match DCF.</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="409">
       <c r="B88" s="408" t="inlineStr">
@@ -16671,8 +16730,33 @@
     </row>
     <row r="90" ht="15" customHeight="1" s="409">
       <c r="B90" s="579" t="n"/>
-    </row>
-    <row r="91" ht="15" customHeight="1" s="409">
+      <c r="L90" s="558" t="inlineStr">
+        <is>
+          <t>Growth trajectory (figure FIRST)</t>
+        </is>
+      </c>
+      <c r="M90" s="558" t="inlineStr">
+        <is>
+          <t>SOURCE (click) — Assess + how number enters</t>
+        </is>
+      </c>
+      <c r="N90" s="558" t="inlineStr">
+        <is>
+          <t>VERBATIM Ctrl+F + EQ derivation</t>
+        </is>
+      </c>
+      <c r="O90" s="558" t="inlineStr">
+        <is>
+          <t>WHY REASONABLE (≤30 words) — LBO impact</t>
+        </is>
+      </c>
+      <c r="P90" s="558" t="inlineStr">
+        <is>
+          <t>Major Variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="72" customHeight="1" s="409">
       <c r="B91" s="557" t="inlineStr">
         <is>
           <t>PP&amp;E</t>
@@ -16685,24 +16769,53 @@
       <c r="E91" s="573" t="n">
         <v>85.2</v>
       </c>
-      <c r="F91" s="537" t="n">
-        <v>73.1444897959184</v>
-      </c>
-      <c r="G91" s="537" t="n">
-        <v>63.4073469387755</v>
-      </c>
-      <c r="H91" s="537" t="n">
-        <v>56.4522448979592</v>
-      </c>
-      <c r="I91" s="537" t="n">
-        <v>53.090612244898</v>
-      </c>
-      <c r="J91" s="537" t="n">
-        <v>53.090612244898</v>
-      </c>
-      <c r="L91" s="537" t="n"/>
-    </row>
-    <row r="92" ht="15" customHeight="1" s="409">
+      <c r="F91" s="614">
+        <f>E91+F92+F93</f>
+        <v/>
+      </c>
+      <c r="G91" s="614">
+        <f>F91+G92+G93</f>
+        <v/>
+      </c>
+      <c r="H91" s="614">
+        <f>G91+H92+H93</f>
+        <v/>
+      </c>
+      <c r="I91" s="614">
+        <f>H91+I92+I93</f>
+        <v/>
+      </c>
+      <c r="J91" s="614">
+        <f>I91+J92+J93</f>
+        <v/>
+      </c>
+      <c r="L91" s="816" t="inlineStr">
+        <is>
+          <t>+5%/yr sales-linked. PP&amp;E rolls: prior + CapEx − D&amp;A. Net book often falls if D&amp;A &gt; CapEx (SaaS asset-light).</t>
+        </is>
+      </c>
+      <c r="M91" s="567">
+        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/","REASONABLE: PPE roll follows CapEx/D&amp;A; SaaS is asset-light")</f>
+        <v/>
+      </c>
+      <c r="N91" s="568" t="inlineStr">
+        <is>
+          <t>Ctrl+F: CapEx of 1–3% of revenue — primarily laptops, office equipment
+EQ: F91=E91+F92+F93 with F92=AI CapEx, F93=−AI D&amp;A.</t>
+        </is>
+      </c>
+      <c r="O91" s="568" t="inlineStr">
+        <is>
+          <t>PP&amp;E is the balance sheet roll of CapEx/D&amp;A. LBO cash cares about CapEx outlay, not PPE level.</t>
+        </is>
+      </c>
+      <c r="P91" s="811" t="inlineStr">
+        <is>
+          <t>NO — BS stock; cash impact is CapEx (row 92)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="72" customHeight="1" s="409">
       <c r="B92" s="574" t="inlineStr">
         <is>
           <t>Capital expenditures</t>
@@ -16717,24 +16830,54 @@
       <c r="E92" s="553" t="n">
         <v>24.5</v>
       </c>
-      <c r="F92" s="553" t="n">
-        <v>26</v>
-      </c>
-      <c r="G92" s="553" t="n">
-        <v>28</v>
-      </c>
-      <c r="H92" s="553" t="n">
-        <v>30</v>
-      </c>
-      <c r="I92" s="553" t="n">
-        <v>29</v>
-      </c>
-      <c r="J92" s="553" t="n">
-        <v>31</v>
-      </c>
-      <c r="L92" s="515" t="n"/>
-    </row>
-    <row r="93" ht="15" customHeight="1" s="409">
+      <c r="F92" s="583">
+        <f>AI_Operating!D19</f>
+        <v/>
+      </c>
+      <c r="G92" s="583">
+        <f>AI_Operating!E19</f>
+        <v/>
+      </c>
+      <c r="H92" s="583">
+        <f>AI_Operating!F19</f>
+        <v/>
+      </c>
+      <c r="I92" s="583">
+        <f>AI_Operating!G19</f>
+        <v/>
+      </c>
+      <c r="J92" s="583">
+        <f>AI_Operating!H19</f>
+        <v/>
+      </c>
+      <c r="L92" s="816" t="inlineStr">
+        <is>
+          <t>1.84% of sales/yr (=2%×(1−8%)). Dollars grow ~+5% with revenue. Was wrong BMC $26–31m — now AI_Operating CapEx.</t>
+        </is>
+      </c>
+      <c r="M92" s="563">
+        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/","REASONABLE: Drivers C24=2% mid of 1–3%; AI cut C12=8% → 1.84%")</f>
+        <v/>
+      </c>
+      <c r="N92" s="564" t="inlineStr">
+        <is>
+          <t>Ctrl+F: Most pure-play SaaS companies report CapEx of 1–3% of revenue
+Ctrl+F: primarily laptops, office equipment
+EQ: CapEx=Rev×C24×(1−C12)=Rev×1.84%. LBO F92=AI_Operating CapEx; DCF! CapEx same link.</t>
+        </is>
+      </c>
+      <c r="O92" s="564" t="inlineStr">
+        <is>
+          <t>1.84% CapEx directly reduces UFCF/FCF and cash for debt sweep — core LBO cash outflow.</t>
+        </is>
+      </c>
+      <c r="P92" s="810" t="inlineStr">
+        <is>
+          <t>YES — CapEx cuts FCF → less debt paydown / IRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="72" customHeight="1" s="409">
       <c r="B93" s="574" t="inlineStr">
         <is>
           <t>Depreciation</t>
@@ -16749,29 +16892,54 @@
       <c r="E93" s="553" t="n">
         <v>-38.7</v>
       </c>
-      <c r="F93" s="515" t="n">
-        <v>-38.0555102040816</v>
-      </c>
-      <c r="G93" s="515" t="n">
-        <v>-37.7371428571429</v>
-      </c>
-      <c r="H93" s="515" t="n">
-        <v>-36.9551020408163</v>
-      </c>
-      <c r="I93" s="515" t="n">
-        <v>-32.3616326530612</v>
-      </c>
-      <c r="J93" s="515" t="n">
-        <v>-31</v>
-      </c>
-      <c r="K93" s="559" t="inlineStr">
-        <is>
-          <t>Smoothing?</t>
-        </is>
-      </c>
-      <c r="L93" s="515" t="n"/>
-    </row>
-    <row r="94" ht="15" customHeight="1" s="409">
+      <c r="F93" s="733">
+        <f>-AI_Operating!D15</f>
+        <v/>
+      </c>
+      <c r="G93" s="733">
+        <f>-AI_Operating!E15</f>
+        <v/>
+      </c>
+      <c r="H93" s="733">
+        <f>-AI_Operating!F15</f>
+        <v/>
+      </c>
+      <c r="I93" s="733">
+        <f>-AI_Operating!G15</f>
+        <v/>
+      </c>
+      <c r="J93" s="733">
+        <f>-AI_Operating!H15</f>
+        <v/>
+      </c>
+      <c r="K93" s="559" t="n"/>
+      <c r="L93" s="816" t="inlineStr">
+        <is>
+          <t>+5%/yr. D&amp;A grows with revenue growth from FY24 $85.7m base (AI_Operating). Non-cash add-back in FCF.</t>
+        </is>
+      </c>
+      <c r="M93" s="563">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","REASONABLE: FY24 D&amp;A anchor $85.7m; grow at Drivers +5%")</f>
+        <v/>
+      </c>
+      <c r="N93" s="564" t="inlineStr">
+        <is>
+          <t>Ctrl+F: depreciation and amortization (ZI cash flow / notes)
+EQ: AI D15=C15×(1+C5); LBO F93=−AI_Operating D&amp;A; DCF adds back +D&amp;A.</t>
+        </is>
+      </c>
+      <c r="O93" s="564" t="inlineStr">
+        <is>
+          <t>D&amp;A is non-cash; added back in DCF/UFCF. Level must match CapEx thesis or FCF is wrong.</t>
+        </is>
+      </c>
+      <c r="P93" s="810" t="inlineStr">
+        <is>
+          <t>YES — D&amp;A add-back is a core UFCF bridge line</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="72" customHeight="1" s="409">
       <c r="B94" s="579" t="inlineStr">
         <is>
           <t>Capex as a % of revenue</t>
@@ -16786,28 +16954,54 @@
       <c r="E94" s="522" t="n">
         <v>0.0111292813664032</v>
       </c>
-      <c r="F94" s="522" t="n">
-        <v>0.0114112714394748</v>
-      </c>
-      <c r="G94" s="522" t="n">
-        <v>0.0116483995736528</v>
-      </c>
-      <c r="H94" s="522" t="n">
-        <v>0.0117739887873849</v>
-      </c>
-      <c r="I94" s="522" t="n">
-        <v>0.0108395452328305</v>
-      </c>
-      <c r="J94" s="522" t="n">
-        <v>0.0110563932027424</v>
-      </c>
-      <c r="K94" s="580" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1" s="409">
+      <c r="F94" s="590">
+        <f>Assumptions_Drivers!$C$24*(1-Assumptions_Drivers!$C$12)</f>
+        <v/>
+      </c>
+      <c r="G94" s="590">
+        <f>Assumptions_Drivers!$C$24*(1-Assumptions_Drivers!$C$12)</f>
+        <v/>
+      </c>
+      <c r="H94" s="590">
+        <f>Assumptions_Drivers!$C$24*(1-Assumptions_Drivers!$C$12)</f>
+        <v/>
+      </c>
+      <c r="I94" s="590">
+        <f>Assumptions_Drivers!$C$24*(1-Assumptions_Drivers!$C$12)</f>
+        <v/>
+      </c>
+      <c r="J94" s="590">
+        <f>Assumptions_Drivers!$C$24*(1-Assumptions_Drivers!$C$12)</f>
+        <v/>
+      </c>
+      <c r="K94" s="580" t="n"/>
+      <c r="L94" s="814" t="inlineStr">
+        <is>
+          <t>1.84% flat every year (Drivers C24×(1−C12)). Ratio does not trend; $ CapEx rises only with +5% sales.</t>
+        </is>
+      </c>
+      <c r="M94" s="563">
+        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/","REASONABLE: 2% midpoint × (1−8% AI cut) = 1.84% of sales")</f>
+        <v/>
+      </c>
+      <c r="N94" s="564" t="inlineStr">
+        <is>
+          <t>Ctrl+F: CapEx of 1–3% of revenue
+EQ: Assumptions_Drivers!C24=2%; C12=8%; net=1.84%. LBO F94:J94=C24*(1-C12).</t>
+        </is>
+      </c>
+      <c r="O94" s="564" t="inlineStr">
+        <is>
+          <t>1.84% is the CapEx intensity Driver. Fixing it removed BMC ~1.1% / $26–31m errors.</t>
+        </is>
+      </c>
+      <c r="P94" s="810" t="inlineStr">
+        <is>
+          <t>YES — sets CapEx $ used in LBO CF and DCF</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="72" customHeight="1" s="409">
       <c r="B95" s="579" t="inlineStr">
         <is>
           <t>Depreciation as a % of capex</t>
@@ -16822,23 +17016,50 @@
       <c r="E95" s="581" t="n">
         <v>1.57959183673469</v>
       </c>
-      <c r="F95" s="581" t="n">
-        <v>1.46367346938776</v>
-      </c>
-      <c r="G95" s="581" t="n">
-        <v>1.34775510204082</v>
-      </c>
-      <c r="H95" s="581" t="n">
-        <v>1.23183673469388</v>
-      </c>
-      <c r="I95" s="581" t="n">
-        <v>1.11591836734694</v>
-      </c>
-      <c r="J95" s="581" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" s="528" t="n">
-        <v>-0.115918367346939</v>
+      <c r="F95" s="670">
+        <f>IF(F92=0,0,ABS(F93)/F92)</f>
+        <v/>
+      </c>
+      <c r="G95" s="670">
+        <f>IF(G92=0,0,ABS(G93)/G92)</f>
+        <v/>
+      </c>
+      <c r="H95" s="670">
+        <f>IF(H92=0,0,ABS(H93)/H92)</f>
+        <v/>
+      </c>
+      <c r="I95" s="670">
+        <f>IF(I92=0,0,ABS(I93)/I92)</f>
+        <v/>
+      </c>
+      <c r="J95" s="670">
+        <f>IF(J92=0,0,ABS(J93)/J92)</f>
+        <v/>
+      </c>
+      <c r="K95" s="528" t="n"/>
+      <c r="L95" s="814" t="inlineStr">
+        <is>
+          <t>n/a — diagnostic |D&amp;A|÷CapEx each year (formula). Not a Driver; does not set cash.</t>
+        </is>
+      </c>
+      <c r="M95" s="567">
+        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/","CAUTION — diagnostic ratio only; not a yellow Driver")</f>
+        <v/>
+      </c>
+      <c r="N95" s="568" t="inlineStr">
+        <is>
+          <t>EQ: F95=ABS(F93)/F92. No Assumptions_Drivers cell. Watch if &gt;&gt;1 (depreciating faster than reinvesting).</t>
+        </is>
+      </c>
+      <c r="O95" s="568" t="inlineStr">
+        <is>
+          <t>Ratio is a check, not an input. Does not by itself change LBO IRR.</t>
+        </is>
+      </c>
+      <c r="P95" s="811" t="inlineStr">
+        <is>
+          <t>NO — diagnostic only</t>
+        </is>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="409">
@@ -16847,7 +17068,7 @@
       <c r="D96" s="581" t="n"/>
       <c r="E96" s="581" t="n"/>
     </row>
-    <row r="97" ht="15" customHeight="1" s="409">
+    <row r="97" ht="72" customHeight="1" s="409">
       <c r="B97" s="557" t="inlineStr">
         <is>
           <t>Software development costs</t>
@@ -16860,23 +17081,53 @@
       <c r="E97" s="573" t="n">
         <v>271.4</v>
       </c>
-      <c r="F97" s="537" t="n">
-        <v>286.508641975309</v>
-      </c>
-      <c r="G97" s="537" t="n">
-        <v>297.64475308642</v>
-      </c>
-      <c r="H97" s="537" t="n">
-        <v>305.199074074074</v>
-      </c>
-      <c r="I97" s="537" t="n">
-        <v>309.366975308642</v>
-      </c>
-      <c r="J97" s="537" t="n">
-        <v>309.366975308642</v>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1" s="409">
+      <c r="F97" s="614">
+        <f>E97</f>
+        <v/>
+      </c>
+      <c r="G97" s="614">
+        <f>E97</f>
+        <v/>
+      </c>
+      <c r="H97" s="614">
+        <f>E97</f>
+        <v/>
+      </c>
+      <c r="I97" s="614">
+        <f>E97</f>
+        <v/>
+      </c>
+      <c r="J97" s="614">
+        <f>E97</f>
+        <v/>
+      </c>
+      <c r="L97" s="814" t="inlineStr">
+        <is>
+          <t>0% new spend. Capitalized software EOP held flat at FY24. Cash CapEx already in 1.84% Drivers bucket.</t>
+        </is>
+      </c>
+      <c r="M97" s="567">
+        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/","CAUTION — capitalized software not separately modeled; CapEx in C24")</f>
+        <v/>
+      </c>
+      <c r="N97" s="568" t="inlineStr">
+        <is>
+          <t>Ctrl+F: Capitalized software development costs also affect this analysis
+EQ: F98:J98=0; F97=E97 flat. Avoids double-counting vs Drivers CapEx.</t>
+        </is>
+      </c>
+      <c r="O97" s="568" t="inlineStr">
+        <is>
+          <t>Separate software buys were BMC (~$115m+) and overstated investing cash use vs DCF $0.</t>
+        </is>
+      </c>
+      <c r="P97" s="811" t="inlineStr">
+        <is>
+          <t>NO — zeroed; would double-count CapEx if kept</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="72" customHeight="1" s="409">
       <c r="B98" s="574" t="inlineStr">
         <is>
           <t>Purchases</t>
@@ -16892,19 +17143,43 @@
         <v>129.6</v>
       </c>
       <c r="F98" s="553" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="G98" s="553" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="H98" s="553" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="I98" s="553" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="J98" s="553" t="n">
-        <v>135</v>
+        <v>0</v>
+      </c>
+      <c r="L98" s="814" t="inlineStr">
+        <is>
+          <t>0$/yr. Purchases set to $0 (was BMC $114–135m). Matches DCF intangible/software policy.</t>
+        </is>
+      </c>
+      <c r="M98" s="563">
+        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/","FIXED inaccuracy: BMC software purchases wiped; CapEx is Drivers 1.84%")</f>
+        <v/>
+      </c>
+      <c r="N98" s="564" t="inlineStr">
+        <is>
+          <t>EQ: F98:J98=0. Prior LBO CF subtracted ~$190m+/yr of software+intangibles — inconsistent with DCF row 26=0 and AI CapEx.</t>
+        </is>
+      </c>
+      <c r="O98" s="564" t="inlineStr">
+        <is>
+          <t>Zeroing stops fake ~$200m investing outflow that crushed LBO cash vs the DCF.</t>
+        </is>
+      </c>
+      <c r="P98" s="810" t="inlineStr">
+        <is>
+          <t>YES (as fix) — was a major false cash drain; now $0</t>
+        </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="409">
@@ -16923,25 +17198,21 @@
         <v>-108.5</v>
       </c>
       <c r="F99" s="515" t="n">
-        <v>-100.891358024691</v>
+        <v>0</v>
       </c>
       <c r="G99" s="515" t="n">
-        <v>-102.863888888889</v>
+        <v>0</v>
       </c>
       <c r="H99" s="515" t="n">
-        <v>-108.445679012346</v>
+        <v>0</v>
       </c>
       <c r="I99" s="515" t="n">
-        <v>-123.832098765432</v>
+        <v>0</v>
       </c>
       <c r="J99" s="515" t="n">
-        <v>-135</v>
-      </c>
-      <c r="K99" s="559" t="inlineStr">
-        <is>
-          <t>Smoothing?</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K99" s="559" t="n"/>
     </row>
     <row r="100" ht="15" customHeight="1" s="409">
       <c r="B100" s="579" t="inlineStr">
@@ -16958,26 +17229,22 @@
       <c r="E100" s="522" t="n">
         <v>0.0588716271463614</v>
       </c>
-      <c r="F100" s="522" t="n">
-        <v>0.0509118264222723</v>
-      </c>
-      <c r="G100" s="522" t="n">
-        <v>0.0474256268355863</v>
-      </c>
-      <c r="H100" s="522" t="n">
-        <v>0.0455260899778882</v>
-      </c>
-      <c r="I100" s="522" t="n">
-        <v>0.047843509993183</v>
-      </c>
-      <c r="J100" s="522" t="n">
-        <v>0.0481488091087168</v>
-      </c>
-      <c r="K100" s="580" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F100" s="566" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="566" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="566" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="566" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="566" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="580" t="n"/>
     </row>
     <row r="101" ht="15" customHeight="1" s="409">
       <c r="B101" s="579" t="inlineStr">
@@ -16995,23 +17262,21 @@
         <v>0.837191358024691</v>
       </c>
       <c r="F101" s="581" t="n">
-        <v>0.869753086419753</v>
+        <v>0</v>
       </c>
       <c r="G101" s="581" t="n">
-        <v>0.902314814814815</v>
+        <v>0</v>
       </c>
       <c r="H101" s="581" t="n">
-        <v>0.934876543209877</v>
+        <v>0</v>
       </c>
       <c r="I101" s="581" t="n">
-        <v>0.967438271604938</v>
+        <v>0</v>
       </c>
       <c r="J101" s="581" t="n">
-        <v>1</v>
-      </c>
-      <c r="K101" s="528" t="n">
-        <v>0.0325617283950617</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K101" s="528" t="n"/>
     </row>
     <row r="102" ht="15" customHeight="1" s="409">
       <c r="B102" s="579" t="n"/>
@@ -17019,7 +17284,7 @@
       <c r="D102" s="581" t="n"/>
       <c r="E102" s="581" t="n"/>
     </row>
-    <row r="103" ht="15" customHeight="1" s="409">
+    <row r="103" ht="72" customHeight="1" s="409">
       <c r="B103" s="557" t="inlineStr">
         <is>
           <t>Intangible assets</t>
@@ -17031,23 +17296,52 @@
       <c r="E103" s="573" t="n">
         <v>189.8</v>
       </c>
-      <c r="F103" s="537" t="n">
-        <v>189.8</v>
-      </c>
-      <c r="G103" s="537" t="n">
-        <v>189.8</v>
-      </c>
-      <c r="H103" s="537" t="n">
-        <v>189.8</v>
-      </c>
-      <c r="I103" s="537" t="n">
-        <v>189.8</v>
-      </c>
-      <c r="J103" s="537" t="n">
-        <v>189.8</v>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1" s="409">
+      <c r="F103" s="614">
+        <f>E103</f>
+        <v/>
+      </c>
+      <c r="G103" s="614">
+        <f>E103</f>
+        <v/>
+      </c>
+      <c r="H103" s="614">
+        <f>E103</f>
+        <v/>
+      </c>
+      <c r="I103" s="614">
+        <f>E103</f>
+        <v/>
+      </c>
+      <c r="J103" s="614">
+        <f>E103</f>
+        <v/>
+      </c>
+      <c r="L103" s="814" t="inlineStr">
+        <is>
+          <t>0% growth. Intangible EOP held flat; no new M&amp;A intangibles in forecast.</t>
+        </is>
+      </c>
+      <c r="M103" s="567">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","CAUTION — hold flat; no forecast M&amp;A")</f>
+        <v/>
+      </c>
+      <c r="N103" s="568" t="inlineStr">
+        <is>
+          <t>EQ: F103=E103; F104=0; F105=0. DCF “Purchases of intangible assets” = 0.</t>
+        </is>
+      </c>
+      <c r="O103" s="568" t="inlineStr">
+        <is>
+          <t>No modeled bolt-on M&amp;A. Flat intangibles avoid fake amortization cash stories.</t>
+        </is>
+      </c>
+      <c r="P103" s="811" t="inlineStr">
+        <is>
+          <t>NO — flat BS; not in AI FCF</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="72" customHeight="1" s="409">
       <c r="B104" s="574" t="inlineStr">
         <is>
           <t>Purchases</t>
@@ -17063,19 +17357,43 @@
         <v>0</v>
       </c>
       <c r="F104" s="553" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="G104" s="553" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H104" s="553" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="I104" s="553" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="J104" s="553" t="n">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="L104" s="814" t="inlineStr">
+        <is>
+          <t>0$/yr. Intangible purchases $0 (was BMC $57–85m). Aligned with DCF.</t>
+        </is>
+      </c>
+      <c r="M104" s="563">
+        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/","FIXED: intangible purchases → $0 to match DCF!D26:H26")</f>
+        <v/>
+      </c>
+      <c r="N104" s="564" t="inlineStr">
+        <is>
+          <t>EQ: F104:J104=0. DCF already had 0; LBO investing CF now matches.</t>
+        </is>
+      </c>
+      <c r="O104" s="564" t="inlineStr">
+        <is>
+          <t>Removes bogus purchase cash use so LBO investing CF matches DCF UFCF CapEx-only.</t>
+        </is>
+      </c>
+      <c r="P104" s="810" t="inlineStr">
+        <is>
+          <t>YES (as fix) — was false Uses of cash; now $0</t>
+        </is>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" s="409">
@@ -17094,19 +17412,19 @@
         <v>-86.90000000000001</v>
       </c>
       <c r="F105" s="553" t="n">
-        <v>-85</v>
+        <v>0</v>
       </c>
       <c r="G105" s="553" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="H105" s="553" t="n">
-        <v>-77</v>
+        <v>0</v>
       </c>
       <c r="I105" s="553" t="n">
-        <v>-68</v>
+        <v>0</v>
       </c>
       <c r="J105" s="553" t="n">
-        <v>-57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="409">
@@ -17115,7 +17433,7 @@
       <c r="D106" s="515" t="n"/>
       <c r="E106" s="515" t="n"/>
     </row>
-    <row r="107" ht="15" customHeight="1" s="409">
+    <row r="107" ht="72" customHeight="1" s="409">
       <c r="B107" s="557" t="inlineStr">
         <is>
           <t>Goodwill and other assets</t>
@@ -17127,20 +17445,49 @@
       <c r="E107" s="573" t="n">
         <v>1935.2</v>
       </c>
-      <c r="F107" s="573" t="n">
-        <v>1935.2</v>
-      </c>
-      <c r="G107" s="573" t="n">
-        <v>1935.2</v>
-      </c>
-      <c r="H107" s="573" t="n">
-        <v>1935.2</v>
-      </c>
-      <c r="I107" s="573" t="n">
-        <v>1935.2</v>
-      </c>
-      <c r="J107" s="573" t="n">
-        <v>1935.2</v>
+      <c r="F107" s="817">
+        <f>E107</f>
+        <v/>
+      </c>
+      <c r="G107" s="817">
+        <f>E107</f>
+        <v/>
+      </c>
+      <c r="H107" s="817">
+        <f>E107</f>
+        <v/>
+      </c>
+      <c r="I107" s="817">
+        <f>E107</f>
+        <v/>
+      </c>
+      <c r="J107" s="817">
+        <f>E107</f>
+        <v/>
+      </c>
+      <c r="L107" s="814" t="inlineStr">
+        <is>
+          <t>0% growth. Goodwill held flat — no impairment, no new deals in model.</t>
+        </is>
+      </c>
+      <c r="M107" s="567">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","CAUTION — flat goodwill; non-cash for FCF")</f>
+        <v/>
+      </c>
+      <c r="N107" s="568" t="inlineStr">
+        <is>
+          <t>EQ: F107:J107=E107. Goodwill does not enter AI_Operating FCF or DCF UFCF.</t>
+        </is>
+      </c>
+      <c r="O107" s="568" t="inlineStr">
+        <is>
+          <t>Goodwill is BS-only here. LBO IRR is cash/debt-driven, not goodwill-driven.</t>
+        </is>
+      </c>
+      <c r="P107" s="811" t="inlineStr">
+        <is>
+          <t>NO — non-cash; no FCF/debt-sweep impact</t>
+        </is>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1" s="409">
@@ -17298,20 +17645,25 @@
       <c r="C116" s="585" t="n"/>
       <c r="D116" s="585" t="n"/>
       <c r="E116" s="585" t="n"/>
-      <c r="F116" s="586" t="n">
-        <v>223.946868228773</v>
-      </c>
-      <c r="G116" s="586" t="n">
-        <v>220.601031746032</v>
-      </c>
-      <c r="H116" s="586" t="n">
-        <v>222.400781053162</v>
-      </c>
-      <c r="I116" s="586" t="n">
-        <v>224.193731418493</v>
-      </c>
-      <c r="J116" s="586" t="n">
-        <v>223</v>
+      <c r="F116" s="733">
+        <f>AI_Operating!D15</f>
+        <v/>
+      </c>
+      <c r="G116" s="733">
+        <f>AI_Operating!E15</f>
+        <v/>
+      </c>
+      <c r="H116" s="733">
+        <f>AI_Operating!F15</f>
+        <v/>
+      </c>
+      <c r="I116" s="733">
+        <f>AI_Operating!G15</f>
+        <v/>
+      </c>
+      <c r="J116" s="733">
+        <f>AI_Operating!H15</f>
+        <v/>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="409">
@@ -17519,20 +17871,35 @@
           <t>Capital expenditures</t>
         </is>
       </c>
-      <c r="F125" s="515" t="n">
-        <v>-26</v>
-      </c>
-      <c r="G125" s="515" t="n">
-        <v>-28</v>
-      </c>
-      <c r="H125" s="515" t="n">
-        <v>-30</v>
-      </c>
-      <c r="I125" s="515" t="n">
-        <v>-29</v>
-      </c>
-      <c r="J125" s="515" t="n">
-        <v>-31</v>
+      <c r="F125" s="733">
+        <f>-AI_Operating!D19</f>
+        <v/>
+      </c>
+      <c r="G125" s="733">
+        <f>-AI_Operating!E19</f>
+        <v/>
+      </c>
+      <c r="H125" s="733">
+        <f>-AI_Operating!F19</f>
+        <v/>
+      </c>
+      <c r="I125" s="733">
+        <f>-AI_Operating!G19</f>
+        <v/>
+      </c>
+      <c r="J125" s="733">
+        <f>-AI_Operating!H19</f>
+        <v/>
+      </c>
+      <c r="L125" s="814" t="inlineStr">
+        <is>
+          <t>1.84% of sales (via AI CapEx). CF CapEx now = −AI_Operating CapEx (was BMC −$26–31m).</t>
+        </is>
+      </c>
+      <c r="P125" s="813" t="inlineStr">
+        <is>
+          <t>YES — CF CapEx is a core LBO cash outflow</t>
+        </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="409">
@@ -17541,20 +17908,30 @@
           <t xml:space="preserve">Purchases of intangible assets and capitalized software development costs </t>
         </is>
       </c>
-      <c r="F126" s="515" t="n">
-        <v>-201</v>
-      </c>
-      <c r="G126" s="515" t="n">
-        <v>-194</v>
-      </c>
-      <c r="H126" s="515" t="n">
-        <v>-193</v>
-      </c>
-      <c r="I126" s="515" t="n">
-        <v>-196</v>
-      </c>
-      <c r="J126" s="515" t="n">
-        <v>-192</v>
+      <c r="F126" s="733" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="733" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="733" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="733" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="733" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="814" t="inlineStr">
+        <is>
+          <t>0$/yr. Was −$190m+ BMC software+intangibles — false cash drain vs DCF $0. Fixed.</t>
+        </is>
+      </c>
+      <c r="P126" s="813" t="inlineStr">
+        <is>
+          <t>YES (as fix) — zeroed fake investing drain</t>
+        </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" s="409">
@@ -23622,6 +23999,11 @@
       </c>
       <c r="I25" s="556" t="n"/>
       <c r="J25" s="556" t="n"/>
+      <c r="K25" s="818" t="inlineStr">
+        <is>
+          <t>CapEx = AI_Operating (Drivers C24=2% × (1−C12=8%) = 1.84% of sales). Intangible purchases = $0 (row 26).</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="409">
       <c r="B26" s="498" t="inlineStr">

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -502,7 +502,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -620,6 +620,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -820,7 +825,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="819">
+  <cellXfs count="821">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3255,6 +3260,12 @@
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="22" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="19" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -16077,7 +16088,7 @@
       </c>
       <c r="P75" s="558" t="inlineStr">
         <is>
-          <t>Major Variable</t>
+          <t>Major Variable — NET + or NET − for LBO</t>
         </is>
       </c>
     </row>
@@ -16134,9 +16145,9 @@
           <t>EOP AR rebuilt as intensity×sales so the BS tracks Drivers. Live debt-sweep cash uses AI_Operating ΔAR, not BMC AR.</t>
         </is>
       </c>
-      <c r="P76" s="810" t="inlineStr">
-        <is>
-          <t>YES — AR drives ΔAR cash use in FCF → debt paydown / IRR</t>
+      <c r="P76" s="819" t="inlineStr">
+        <is>
+          <t>YES — NET − for LBO. Higher AR ties cash; ΔAR is a cash use that slows debt paydown / IRR.</t>
         </is>
       </c>
     </row>
@@ -16193,9 +16204,9 @@
           <t>Fairview’s 59-day median becomes 16.2% AR intensity in Drivers C25; that cell feeds every forecast AR% here.</t>
         </is>
       </c>
-      <c r="P77" s="810" t="inlineStr">
-        <is>
-          <t>YES — primary AR/% assumption; pairs with C13 DSO cut</t>
+      <c r="P77" s="819" t="inlineStr">
+        <is>
+          <t>YES — NET − for LBO at 16.2% intensity (cash use on growth). AI C13 softens it; still an AR drag vs deferred.</t>
         </is>
       </c>
     </row>
@@ -16254,7 +16265,7 @@
       </c>
       <c r="P78" s="811" t="inlineStr">
         <is>
-          <t>NO — not in AI ΔNWC; immaterial to LBO FCF/IRR</t>
+          <t>NO — n/a sign. Not in AI ΔNWC; immaterial to LBO FCF/IRR.</t>
         </is>
       </c>
     </row>
@@ -16307,7 +16318,7 @@
       </c>
       <c r="P79" s="811" t="inlineStr">
         <is>
-          <t>NO — non-core; no Drivers link</t>
+          <t>NO — n/a sign. Non-core; no Drivers link.</t>
         </is>
       </c>
     </row>
@@ -16366,7 +16377,7 @@
       </c>
       <c r="P80" s="811" t="inlineStr">
         <is>
-          <t>NO — small SaaS AP; weak FCF/IRR sensitivity</t>
+          <t>NO — n/a sign. Small SaaS AP; weak FCF/IRR sensitivity.</t>
         </is>
       </c>
     </row>
@@ -16420,7 +16431,7 @@
       </c>
       <c r="P81" s="811" t="inlineStr">
         <is>
-          <t>NO — not a Drivers assumption</t>
+          <t>NO — n/a sign. Not a Drivers assumption.</t>
         </is>
       </c>
     </row>
@@ -16477,9 +16488,9 @@
           <t>EOP deferred rebuilt from Drivers 39% so BS matches the unearned-revenue cash source in FCF math.</t>
         </is>
       </c>
-      <c r="P82" s="810" t="inlineStr">
-        <is>
-          <t>YES — deferred revenue is the largest SaaS NWC cash source</t>
+      <c r="P82" s="820" t="inlineStr">
+        <is>
+          <t>YES — NET + for LBO. Deferred/unearned is the largest SaaS cash source; funds FCF and debt sweep.</t>
         </is>
       </c>
     </row>
@@ -16537,9 +16548,9 @@
           <t>10-K current unearned $473.8m ÷ FY24 sales $1,214.3m = 39%. That exact ratio is Drivers C26.</t>
         </is>
       </c>
-      <c r="P83" s="810" t="inlineStr">
-        <is>
-          <t>YES — sets ΔDeferred in ΔNWC ≈ ΔAR − ΔDeferred</t>
+      <c r="P83" s="820" t="inlineStr">
+        <is>
+          <t>YES — NET + for LBO. 39% deferred intensity → ΔDeferred cash inflow dominates ΔNWC.</t>
         </is>
       </c>
     </row>
@@ -16601,9 +16612,9 @@
           <t>EOP NWC is the BS rollup. Deal cash and debt sweep follow AI_Operating ΔNWC from Drivers C13/C25/C26.</t>
         </is>
       </c>
-      <c r="P85" s="810" t="inlineStr">
-        <is>
-          <t>YES — ΔNWC hits FCF, debt sweep, MOIC/IRR</t>
+      <c r="P85" s="820" t="inlineStr">
+        <is>
+          <t>YES — NET + for LBO. AI ΔNWC ≈ −24.5% of ΔRev (cash release) → more sweep / higher IRR.</t>
         </is>
       </c>
     </row>
@@ -16640,9 +16651,9 @@
           <t>10% cuts ΔAR only (not whole NWC). With deferred still at 39%, net ΔNWC stays a cash source.</t>
         </is>
       </c>
-      <c r="P86" s="810" t="inlineStr">
-        <is>
-          <t>YES — AI case lever vs Base; lifts FCF/debt paydown</t>
+      <c r="P86" s="820" t="inlineStr">
+        <is>
+          <t>YES — NET + for LBO. −10% ΔAR cut vs Base frees cash and lifts AI FCF / debt paydown.</t>
         </is>
       </c>
     </row>
@@ -16752,7 +16763,7 @@
       </c>
       <c r="P90" s="558" t="inlineStr">
         <is>
-          <t>Major Variable</t>
+          <t>Major Variable — NET + or NET − for LBO</t>
         </is>
       </c>
     </row>
@@ -16811,7 +16822,7 @@
       </c>
       <c r="P91" s="811" t="inlineStr">
         <is>
-          <t>NO — BS stock; cash impact is CapEx (row 92)</t>
+          <t>NO — n/a sign. BS stock; cash impact is CapEx (row 92).</t>
         </is>
       </c>
     </row>
@@ -16871,9 +16882,9 @@
           <t>1.84% CapEx directly reduces UFCF/FCF and cash for debt sweep — core LBO cash outflow.</t>
         </is>
       </c>
-      <c r="P92" s="810" t="inlineStr">
-        <is>
-          <t>YES — CapEx cuts FCF → less debt paydown / IRR</t>
+      <c r="P92" s="819" t="inlineStr">
+        <is>
+          <t>YES — NET − for LBO. CapEx is a cash outflow that reduces FCF available for debt paydown / IRR.</t>
         </is>
       </c>
     </row>
@@ -16933,9 +16944,9 @@
           <t>D&amp;A is non-cash; added back in DCF/UFCF. Level must match CapEx thesis or FCF is wrong.</t>
         </is>
       </c>
-      <c r="P93" s="810" t="inlineStr">
-        <is>
-          <t>YES — D&amp;A add-back is a core UFCF bridge line</t>
+      <c r="P93" s="820" t="inlineStr">
+        <is>
+          <t>YES — NET + for LBO. D&amp;A is non-cash; add-back raises UFCF vs pure earnings.</t>
         </is>
       </c>
     </row>
@@ -16995,9 +17006,9 @@
           <t>1.84% is the CapEx intensity Driver. Fixing it removed BMC ~1.1% / $26–31m errors.</t>
         </is>
       </c>
-      <c r="P94" s="810" t="inlineStr">
-        <is>
-          <t>YES — sets CapEx $ used in LBO CF and DCF</t>
+      <c r="P94" s="819" t="inlineStr">
+        <is>
+          <t>YES — NET − for LBO. 1.84% CapEx intensity sets the cash drag on FCF/DCF.</t>
         </is>
       </c>
     </row>
@@ -17058,7 +17069,7 @@
       </c>
       <c r="P95" s="811" t="inlineStr">
         <is>
-          <t>NO — diagnostic only</t>
+          <t>NO — n/a sign. Diagnostic only.</t>
         </is>
       </c>
     </row>
@@ -17123,7 +17134,7 @@
       </c>
       <c r="P97" s="811" t="inlineStr">
         <is>
-          <t>NO — zeroed; would double-count CapEx if kept</t>
+          <t>NO — n/a sign. Zeroed; would double-count CapEx if kept.</t>
         </is>
       </c>
     </row>
@@ -17176,9 +17187,9 @@
           <t>Zeroing stops fake ~$200m investing outflow that crushed LBO cash vs the DCF.</t>
         </is>
       </c>
-      <c r="P98" s="810" t="inlineStr">
-        <is>
-          <t>YES (as fix) — was a major false cash drain; now $0</t>
+      <c r="P98" s="820" t="inlineStr">
+        <is>
+          <t>YES — NET + for LBO (fix). Removing false ~$115m+ software buys stops a fake cash drain.</t>
         </is>
       </c>
     </row>
@@ -17337,7 +17348,7 @@
       </c>
       <c r="P103" s="811" t="inlineStr">
         <is>
-          <t>NO — flat BS; not in AI FCF</t>
+          <t>NO — n/a sign. Flat BS; not in AI FCF.</t>
         </is>
       </c>
     </row>
@@ -17390,9 +17401,9 @@
           <t>Removes bogus purchase cash use so LBO investing CF matches DCF UFCF CapEx-only.</t>
         </is>
       </c>
-      <c r="P104" s="810" t="inlineStr">
-        <is>
-          <t>YES (as fix) — was false Uses of cash; now $0</t>
+      <c r="P104" s="820" t="inlineStr">
+        <is>
+          <t>YES — NET + for LBO (fix). Zeroing BMC intangible buys removes false Uses of cash.</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17497,7 @@
       </c>
       <c r="P107" s="811" t="inlineStr">
         <is>
-          <t>NO — non-cash; no FCF/debt-sweep impact</t>
+          <t>NO — n/a sign. Non-cash; no FCF/debt-sweep impact.</t>
         </is>
       </c>
     </row>
@@ -17721,7 +17732,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" ht="15" customHeight="1" s="409">
+    <row r="119" ht="70" customHeight="1" s="409">
       <c r="B119" s="408" t="inlineStr">
         <is>
           <t>Changes in net working capital</t>
@@ -17761,9 +17772,9 @@
         </is>
       </c>
       <c r="O119" s="813" t="n"/>
-      <c r="P119" s="810" t="inlineStr">
-        <is>
-          <t>YES — CF ΔNWC is a core LBO cash variable</t>
+      <c r="P119" s="820" t="inlineStr">
+        <is>
+          <t>YES — NET + for LBO. CF ΔNWC cash release feeds debt sweep (core credit positive).</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17876,7 @@
       </c>
     </row>
     <row r="124" ht="13.8" customHeight="1" s="409"/>
-    <row r="125" ht="15" customHeight="1" s="409">
+    <row r="125" ht="70" customHeight="1" s="409">
       <c r="B125" s="408" t="inlineStr">
         <is>
           <t>Capital expenditures</t>
@@ -17896,13 +17907,13 @@
           <t>1.84% of sales (via AI CapEx). CF CapEx now = −AI_Operating CapEx (was BMC −$26–31m).</t>
         </is>
       </c>
-      <c r="P125" s="813" t="inlineStr">
-        <is>
-          <t>YES — CF CapEx is a core LBO cash outflow</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="15" customHeight="1" s="409">
+      <c r="P125" s="819" t="inlineStr">
+        <is>
+          <t>YES — NET − for LBO. CF CapEx outflow reduces cash for mandatory amort + sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="70" customHeight="1" s="409">
       <c r="B126" s="408" t="inlineStr">
         <is>
           <t xml:space="preserve">Purchases of intangible assets and capitalized software development costs </t>
@@ -17928,9 +17939,9 @@
           <t>0$/yr. Was −$190m+ BMC software+intangibles — false cash drain vs DCF $0. Fixed.</t>
         </is>
       </c>
-      <c r="P126" s="813" t="inlineStr">
-        <is>
-          <t>YES (as fix) — zeroed fake investing drain</t>
+      <c r="P126" s="820" t="inlineStr">
+        <is>
+          <t>YES — NET + for LBO (fix). Zeroing fake −$190m+ investing drain improves modeled cash.</t>
         </is>
       </c>
     </row>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -60,7 +60,7 @@
     <numFmt numFmtId="194" formatCode="#,##0.0_);\(#,##0.0\);&quot;- _)&quot;;@_)"/>
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
   </numFmts>
-  <fonts count="68">
+  <fonts count="69">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -501,6 +501,11 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="23">
     <fill>
@@ -825,7 +830,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="821">
+  <cellXfs count="822">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3266,6 +3271,9 @@
     </xf>
     <xf numFmtId="0" fontId="67" fillId="19" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -13350,7 +13358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:H24"/>
+  <dimension ref="B2:J24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="408" min="2" max="2"/>
@@ -13827,6 +13835,11 @@
       </c>
       <c r="H21" s="456" t="n">
         <v>247.663282589115</v>
+      </c>
+      <c r="J21" s="821" t="inlineStr">
+        <is>
+          <t>FCF≈NI+D&amp;A−CapEx−ΔNWC (D&amp;A IS added back; NI already deducted it).</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="409">
@@ -16926,7 +16939,7 @@
       <c r="K93" s="559" t="n"/>
       <c r="L93" s="816" t="inlineStr">
         <is>
-          <t>+5%/yr. D&amp;A grows with revenue growth from FY24 $85.7m base (AI_Operating). Non-cash add-back in FCF.</t>
+          <t>+5%/yr. D&amp;A grows with sales from $85.7m. IS added in FCF (add-back), not ignored.</t>
         </is>
       </c>
       <c r="M93" s="563">
@@ -16941,12 +16954,12 @@
       </c>
       <c r="O93" s="564" t="inlineStr">
         <is>
-          <t>D&amp;A is non-cash; added back in DCF/UFCF. Level must match CapEx thesis or FCF is wrong.</t>
+          <t>D&amp;A IS added to FCF: non-cash charge was deducted to get EBIT/NI, so UFCF adds it back (DCF EBIAT+D&amp;A; AI FCF≈NI+D&amp;A−CapEx−ΔNWC).</t>
         </is>
       </c>
       <c r="P93" s="820" t="inlineStr">
         <is>
-          <t>YES — NET + for LBO. D&amp;A is non-cash; add-back raises UFCF vs pure earnings.</t>
+          <t>YES — NET + for LBO. D&amp;A IS added back in FCF/UFCF; raises cash vs earnings that expensed it.</t>
         </is>
       </c>
     </row>
@@ -23861,6 +23874,11 @@
       </c>
       <c r="I20" s="556" t="n"/>
       <c r="J20" s="556" t="n"/>
+      <c r="K20" s="818" t="inlineStr">
+        <is>
+          <t>D&amp;A IS in UFCF: Unlevered CFO = EBIAT + D&amp;A + SBC − ΔNWC (row 24).</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="40" customHeight="1" s="409">
       <c r="B21" s="561" t="inlineStr">

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -16901,7 +16901,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="72" customHeight="1" s="409">
+    <row r="93" ht="95" customHeight="1" s="409">
       <c r="B93" s="574" t="inlineStr">
         <is>
           <t>Depreciation</t>
@@ -16939,7 +16939,7 @@
       <c r="K93" s="559" t="n"/>
       <c r="L93" s="816" t="inlineStr">
         <is>
-          <t>+5%/yr. D&amp;A grows with sales from $85.7m. IS added in FCF (add-back), not ignored.</t>
+          <t>+5%/yr. D&amp;A grows with sales from FY24 $85.7m. Major FCF point: IS deducts it; FCF adds it back (non-cash).</t>
         </is>
       </c>
       <c r="M93" s="563">
@@ -16949,17 +16949,17 @@
       <c r="N93" s="564" t="inlineStr">
         <is>
           <t>Ctrl+F: depreciation and amortization (ZI cash flow / notes)
-EQ: AI D15=C15×(1+C5); LBO F93=−AI_Operating D&amp;A; DCF adds back +D&amp;A.</t>
+EQ: AI D15=C15×(1+C5). DCF Unlevered CFO = EBIAT + D&amp;A (+SBC) − ΔNWC; then − CapEx → UFCF. AI FCF after interest ≈ NI + D&amp;A − CapEx − ΔNWC (D&amp;A explicitly added).</t>
         </is>
       </c>
       <c r="O93" s="564" t="inlineStr">
         <is>
-          <t>D&amp;A IS added to FCF: non-cash charge was deducted to get EBIT/NI, so UFCF adds it back (DCF EBIAT+D&amp;A; AI FCF≈NI+D&amp;A−CapEx−ΔNWC).</t>
+          <t>D&amp;A IS in FCF (add-back). Charged on IS to get EBIT/NI, then added in UFCF/AI FCF so cash isn’t understated.</t>
         </is>
       </c>
       <c r="P93" s="820" t="inlineStr">
         <is>
-          <t>YES — NET + for LBO. D&amp;A IS added back in FCF/UFCF; raises cash vs earnings that expensed it.</t>
+          <t>YES — NET + for LBO. D&amp;A IS added back in FCF: earnings (EBIT/NI) already deducted D&amp;A, but no cash left the firm. DCF UFCF = EBIAT + D&amp;A − ΔNWC − CapEx; AI FCF ≈ NI + D&amp;A − CapEx − ΔNWC. Higher D&amp;A add-back raises cash for debt sweep / IRR vs NI alone.</t>
         </is>
       </c>
     </row>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -830,7 +830,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="822">
+  <cellXfs count="824">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3274,6 +3274,12 @@
     </xf>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="21" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -16155,7 +16161,7 @@
       </c>
       <c r="O76" s="564" t="inlineStr">
         <is>
-          <t>EOP AR rebuilt as intensity×sales so the BS tracks Drivers. Live debt-sweep cash uses AI_Operating ΔAR, not BMC AR.</t>
+          <t>EOP AR rebuilt as intensity×sales so the BS tracks Drivers. Live debt-sweep cash uses AI_Operating ΔAR, not the old template AR path.</t>
         </is>
       </c>
       <c r="P76" s="819" t="inlineStr">
@@ -16684,9 +16690,9 @@
       <c r="H87" s="578" t="n"/>
       <c r="I87" s="578" t="n"/>
       <c r="J87" s="578" t="n"/>
-      <c r="L87" s="809" t="inlineStr">
-        <is>
-          <t>Assets — CapEx/D&amp;A wired to Drivers/AI_Operating (was BMC). Intangible &amp; capitalized-software buys set to $0 to match DCF.</t>
+      <c r="L87" s="822" t="inlineStr">
+        <is>
+          <t>Assets — CapEx/D&amp;A wired to Drivers/AI_Operating (replaced stale hardcodes). Intangible &amp; capitalized-software buys set to $0 to match DCF.</t>
         </is>
       </c>
     </row>
@@ -16876,7 +16882,7 @@
       </c>
       <c r="L92" s="816" t="inlineStr">
         <is>
-          <t>1.84% of sales/yr (=2%×(1−8%)). Dollars grow ~+5% with revenue. Was wrong BMC $26–31m — now AI_Operating CapEx.</t>
+          <t>1.84% of sales/yr (=2%×(1−8%)). Dollars grow ~+5% with revenue. Replaced stale $26–31m hardcodes with AI_Operating CapEx.</t>
         </is>
       </c>
       <c r="M92" s="563">
@@ -17016,7 +17022,7 @@
       </c>
       <c r="O94" s="564" t="inlineStr">
         <is>
-          <t>1.84% is the CapEx intensity Driver. Fixing it removed BMC ~1.1% / $26–31m errors.</t>
+          <t>1.84% is the CapEx intensity Driver. Fixing it removed stale ~1.1% / $26–31m hardcodes that disagreed with Drivers.</t>
         </is>
       </c>
       <c r="P94" s="819" t="inlineStr">
@@ -17142,7 +17148,7 @@
       </c>
       <c r="O97" s="568" t="inlineStr">
         <is>
-          <t>Separate software buys were BMC (~$115m+) and overstated investing cash use vs DCF $0.</t>
+          <t>Separate software buys were stale hardcodes (~$115m+) and overstated investing cash use vs DCF $0.</t>
         </is>
       </c>
       <c r="P97" s="811" t="inlineStr">
@@ -17183,11 +17189,11 @@
       </c>
       <c r="L98" s="814" t="inlineStr">
         <is>
-          <t>0$/yr. Purchases set to $0 (was BMC $114–135m). Matches DCF intangible/software policy.</t>
+          <t>0$/yr. Purchases set to $0 (was stale $114–135m hardcodes). Matches DCF intangible/software policy.</t>
         </is>
       </c>
       <c r="M98" s="563">
-        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/","FIXED inaccuracy: BMC software purchases wiped; CapEx is Drivers 1.84%")</f>
+        <f>HYPERLINK("https://saasdb.app/learn/financials/fcf-margin/","FIXED: software purchases → $0; CapEx is Drivers 1.84% only")</f>
         <v/>
       </c>
       <c r="N98" s="564" t="inlineStr">
@@ -17197,12 +17203,12 @@
       </c>
       <c r="O98" s="564" t="inlineStr">
         <is>
-          <t>Zeroing stops fake ~$200m investing outflow that crushed LBO cash vs the DCF.</t>
+          <t>Zeroing stops a false ~$200m investing outflow that understated LBO cash vs the DCF.</t>
         </is>
       </c>
       <c r="P98" s="820" t="inlineStr">
         <is>
-          <t>YES — NET + for LBO (fix). Removing false ~$115m+ software buys stops a fake cash drain.</t>
+          <t>YES — NET + for LBO. Software purchases = $0. Clearing old $114–135m hardcodes stops a false investing cash drain (CapEx is only Drivers 1.84%).</t>
         </is>
       </c>
     </row>
@@ -17397,7 +17403,7 @@
       </c>
       <c r="L104" s="814" t="inlineStr">
         <is>
-          <t>0$/yr. Intangible purchases $0 (was BMC $57–85m). Aligned with DCF.</t>
+          <t>0$/yr. Intangible purchases $0 (was stale $57–85m hardcodes). Aligned with DCF.</t>
         </is>
       </c>
       <c r="M104" s="563">
@@ -17406,17 +17412,17 @@
       </c>
       <c r="N104" s="564" t="inlineStr">
         <is>
-          <t>EQ: F104:J104=0. DCF already had 0; LBO investing CF now matches.</t>
+          <t>EQ: F104:J104=0. DCF “Purchases of intangible assets” = 0. LBO investing CF now matches; no separate intangible buy cash use.</t>
         </is>
       </c>
       <c r="O104" s="564" t="inlineStr">
         <is>
-          <t>Removes bogus purchase cash use so LBO investing CF matches DCF UFCF CapEx-only.</t>
+          <t>Intangible buys are $0 so LBO investing CF matches DCF CapEx-only UFCF (no false purchase outflow).</t>
         </is>
       </c>
       <c r="P104" s="820" t="inlineStr">
         <is>
-          <t>YES — NET + for LBO (fix). Zeroing BMC intangible buys removes false Uses of cash.</t>
+          <t>YES — NET + for LBO. Intangible purchases = $0 (Drivers/DCF policy). Clearing the old $57–85m hardcodes removes a false Use of cash.</t>
         </is>
       </c>
     </row>
@@ -17779,9 +17785,9 @@
           <t>−24.5% of ΔRev/yr (AI). ΔNWC ≈ ΔRev×(14.55%−39%). Cash release grows in $ as +5% sales widens ΔRev; not a flat dollar.</t>
         </is>
       </c>
-      <c r="M119" s="805" t="inlineStr">
-        <is>
-          <t>ΔNWC in CF = AI_Operating (Drivers C13/C25/C26). Cash line that feeds debt sweep — not the old BMC WC delta.</t>
+      <c r="M119" s="823" t="inlineStr">
+        <is>
+          <t>ΔNWC in CF = AI_Operating (Drivers C13/C25/C26). Cash line that feeds debt sweep — not the old template WC delta.</t>
         </is>
       </c>
       <c r="O119" s="813" t="n"/>
@@ -17917,7 +17923,7 @@
       </c>
       <c r="L125" s="814" t="inlineStr">
         <is>
-          <t>1.84% of sales (via AI CapEx). CF CapEx now = −AI_Operating CapEx (was BMC −$26–31m).</t>
+          <t>1.84% of sales (via AI CapEx). CF CapEx now = −AI_Operating CapEx (replaced stale −$26–31m hardcodes).</t>
         </is>
       </c>
       <c r="P125" s="819" t="inlineStr">
@@ -17949,12 +17955,12 @@
       </c>
       <c r="L126" s="814" t="inlineStr">
         <is>
-          <t>0$/yr. Was −$190m+ BMC software+intangibles — false cash drain vs DCF $0. Fixed.</t>
+          <t>0$/yr. Was −$190m+ stale software+intangible hardcodes — false cash drain vs DCF $0. Fixed.</t>
         </is>
       </c>
       <c r="P126" s="820" t="inlineStr">
         <is>
-          <t>YES — NET + for LBO (fix). Zeroing fake −$190m+ investing drain improves modeled cash.</t>
+          <t>YES — NET + for LBO. Investing purchases line = $0 to match DCF; removes the old −$190m+ hardcoded drain from LBO cash.</t>
         </is>
       </c>
     </row>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -830,7 +830,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="824">
+  <cellXfs count="829">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3279,6 +3279,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="185" fontId="61" fillId="16" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10297,7 +10312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:F55"/>
+  <dimension ref="B2:F56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="408" min="2" max="2"/>
@@ -10948,6 +10963,13 @@
       </c>
       <c r="D55" s="408" t="n">
         <v>27.1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="808" t="inlineStr">
+        <is>
+          <t>CASH &amp; DEBT FIX: LBO TLA/TLB/Notes now = Sources $457.8/$274.7/$183.1; mand=1%; sweep=100% of AI FCF after mand; rates=Drivers SOFR spreads. See LBO!L141:P210.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -10963,7 +10985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:N56"/>
+  <dimension ref="B2:N57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="408" min="2" max="2"/>
@@ -12444,6 +12466,23 @@
       <c r="G56" s="408" t="inlineStr">
         <is>
           <t>LBO!F92 / DCF!D25</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CASH/DEBT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Major: FCF inflow; 100% sweep &amp; 1% mand outflows (NET + delever); interest outflows (NET −). Stack=Sources; rates=C14–C18.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>LBO!F152 / F164 / F208</t>
         </is>
       </c>
     </row>
@@ -14047,7 +14086,7 @@
     <col width="42" customWidth="1" style="408" min="13" max="13"/>
     <col width="52" customWidth="1" style="408" min="14" max="14"/>
     <col width="34" customWidth="1" style="409" min="15" max="15"/>
-    <col width="38" customWidth="1" style="409" min="16" max="16"/>
+    <col width="42" customWidth="1" style="409" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" s="409">
@@ -15198,20 +15237,25 @@
       <c r="E50" s="553" t="n">
         <v>-47.8</v>
       </c>
-      <c r="F50" s="515" t="n">
-        <v>-68.7</v>
-      </c>
-      <c r="G50" s="515" t="n">
-        <v>-58.3</v>
-      </c>
-      <c r="H50" s="515" t="n">
-        <v>-46.4</v>
-      </c>
-      <c r="I50" s="515" t="n">
-        <v>-32.7</v>
-      </c>
-      <c r="J50" s="515" t="n">
-        <v>-17.3</v>
+      <c r="F50" s="733">
+        <f>-(F208+F209+F210)</f>
+        <v/>
+      </c>
+      <c r="G50" s="733">
+        <f>-(G208+G209+G210)</f>
+        <v/>
+      </c>
+      <c r="H50" s="733">
+        <f>-(H208+H209+H210)</f>
+        <v/>
+      </c>
+      <c r="I50" s="733">
+        <f>-(I208+I209+I210)</f>
+        <v/>
+      </c>
+      <c r="J50" s="733">
+        <f>-(J208+J209+J210)</f>
+        <v/>
       </c>
       <c r="L50" s="554" t="inlineStr">
         <is>
@@ -17970,20 +18014,25 @@
           <t>Cash from investing activities</t>
         </is>
       </c>
-      <c r="F127" s="537" t="n">
-        <v>-227</v>
-      </c>
-      <c r="G127" s="537" t="n">
-        <v>-222</v>
-      </c>
-      <c r="H127" s="537" t="n">
-        <v>-223</v>
-      </c>
-      <c r="I127" s="537" t="n">
-        <v>-225</v>
-      </c>
-      <c r="J127" s="537" t="n">
-        <v>-223</v>
+      <c r="F127" s="614">
+        <f>F125+F126</f>
+        <v/>
+      </c>
+      <c r="G127" s="614">
+        <f>G125+G126</f>
+        <v/>
+      </c>
+      <c r="H127" s="614">
+        <f>H125+H126</f>
+        <v/>
+      </c>
+      <c r="I127" s="614">
+        <f>I125+I126</f>
+        <v/>
+      </c>
+      <c r="J127" s="614">
+        <f>J125+J126</f>
+        <v/>
       </c>
     </row>
     <row r="128" ht="13.8" customHeight="1" s="409"/>
@@ -17993,20 +18042,25 @@
           <t>Required debt principal payments</t>
         </is>
       </c>
-      <c r="F129" s="515" t="n">
-        <v>-322.1855</v>
-      </c>
-      <c r="G129" s="515" t="n">
-        <v>-177.86405</v>
-      </c>
-      <c r="H129" s="515" t="n">
-        <v>-177.86405</v>
-      </c>
-      <c r="I129" s="515" t="n">
-        <v>-177.86405</v>
-      </c>
-      <c r="J129" s="515" t="n">
-        <v>-177.86405</v>
+      <c r="F129" s="733">
+        <f>-(F163+F171)</f>
+        <v/>
+      </c>
+      <c r="G129" s="733">
+        <f>-(G163+G171)</f>
+        <v/>
+      </c>
+      <c r="H129" s="733">
+        <f>-(H163+H171)</f>
+        <v/>
+      </c>
+      <c r="I129" s="733">
+        <f>-(I163+I171)</f>
+        <v/>
+      </c>
+      <c r="J129" s="733">
+        <f>-(J163+J171)</f>
+        <v/>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="409">
@@ -18040,20 +18094,25 @@
       <c r="C131" s="513" t="n"/>
       <c r="D131" s="513" t="n"/>
       <c r="E131" s="513" t="n"/>
-      <c r="F131" s="537" t="n">
-        <v>88.7366611647973</v>
-      </c>
-      <c r="G131" s="537" t="n">
-        <v>341.347888508174</v>
-      </c>
-      <c r="H131" s="537" t="n">
-        <v>430.874867157023</v>
-      </c>
-      <c r="I131" s="537" t="n">
-        <v>495.283971347461</v>
-      </c>
-      <c r="J131" s="537" t="n">
-        <v>586.718180731428</v>
+      <c r="F131" s="614">
+        <f>AI_Operating!D21</f>
+        <v/>
+      </c>
+      <c r="G131" s="614">
+        <f>AI_Operating!E21</f>
+        <v/>
+      </c>
+      <c r="H131" s="614">
+        <f>AI_Operating!F21</f>
+        <v/>
+      </c>
+      <c r="I131" s="614">
+        <f>AI_Operating!G21</f>
+        <v/>
+      </c>
+      <c r="J131" s="614">
+        <f>AI_Operating!H21</f>
+        <v/>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="409">
@@ -18087,20 +18146,25 @@
       <c r="C133" s="513" t="n"/>
       <c r="D133" s="513" t="n"/>
       <c r="E133" s="513" t="n"/>
-      <c r="F133" s="537" t="n">
-        <v>88.7366611647973</v>
-      </c>
-      <c r="G133" s="537" t="n">
-        <v>341.347888508174</v>
-      </c>
-      <c r="H133" s="537" t="n">
-        <v>430.874867157023</v>
-      </c>
-      <c r="I133" s="537" t="n">
-        <v>495.283971347461</v>
-      </c>
-      <c r="J133" s="537" t="n">
-        <v>586.718180731428</v>
+      <c r="F133" s="614">
+        <f>F131+F132</f>
+        <v/>
+      </c>
+      <c r="G133" s="614">
+        <f>G131+G132</f>
+        <v/>
+      </c>
+      <c r="H133" s="614">
+        <f>H131+H132</f>
+        <v/>
+      </c>
+      <c r="I133" s="614">
+        <f>I131+I132</f>
+        <v/>
+      </c>
+      <c r="J133" s="614">
+        <f>J131+J132</f>
+        <v/>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1" s="409">
@@ -18109,20 +18173,25 @@
           <t>Discretionary Term A paydown</t>
         </is>
       </c>
-      <c r="F134" s="515" t="n">
-        <v>-88.7366611647973</v>
-      </c>
-      <c r="G134" s="515" t="n">
-        <v>-341.347888508174</v>
-      </c>
-      <c r="H134" s="515" t="n">
-        <v>-430.874867157023</v>
-      </c>
-      <c r="I134" s="515" t="n">
-        <v>-495.283971347461</v>
-      </c>
-      <c r="J134" s="515" t="n">
-        <v>-586.718180731428</v>
+      <c r="F134" s="515">
+        <f>-F164</f>
+        <v/>
+      </c>
+      <c r="G134" s="515">
+        <f>-G164</f>
+        <v/>
+      </c>
+      <c r="H134" s="515">
+        <f>-H164</f>
+        <v/>
+      </c>
+      <c r="I134" s="515">
+        <f>-I164</f>
+        <v/>
+      </c>
+      <c r="J134" s="515">
+        <f>-J164</f>
+        <v/>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" s="409">
@@ -18131,20 +18200,25 @@
           <t>Discretionary Term B paydown</t>
         </is>
       </c>
-      <c r="F135" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" s="515" t="n">
-        <v>2.27373675443232e-13</v>
+      <c r="F135" s="515">
+        <f>-F172</f>
+        <v/>
+      </c>
+      <c r="G135" s="515">
+        <f>-G172</f>
+        <v/>
+      </c>
+      <c r="H135" s="515">
+        <f>-H172</f>
+        <v/>
+      </c>
+      <c r="I135" s="515">
+        <f>-I172</f>
+        <v/>
+      </c>
+      <c r="J135" s="515">
+        <f>-J172</f>
+        <v/>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" s="409">
@@ -18191,6 +18265,11 @@
       <c r="H138" s="489" t="n"/>
       <c r="I138" s="489" t="n"/>
       <c r="J138" s="489" t="n"/>
+      <c r="L138" s="809" t="inlineStr">
+        <is>
+          <t>CASH &amp; DEBT — wired to Sources debt stack ($915.5m), Drivers C14–C18, and AI_Operating FCF (replaced stale oversized loan hardcodes).</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="15" customHeight="1" s="409">
       <c r="B139" s="496" t="inlineStr">
@@ -18254,8 +18333,33 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="141" ht="15" customHeight="1" s="409">
+    <row r="141" ht="32" customHeight="1" s="409">
       <c r="B141" s="541" t="n"/>
+      <c r="L141" s="558" t="inlineStr">
+        <is>
+          <t>Growth trajectory (figure FIRST)</t>
+        </is>
+      </c>
+      <c r="M141" s="558" t="inlineStr">
+        <is>
+          <t>SOURCE (click) — Assess + how number enters</t>
+        </is>
+      </c>
+      <c r="N141" s="558" t="inlineStr">
+        <is>
+          <t>VERBATIM Ctrl+F + EQ derivation</t>
+        </is>
+      </c>
+      <c r="O141" s="558" t="inlineStr">
+        <is>
+          <t>WHY REASONABLE (≤30 words)</t>
+        </is>
+      </c>
+      <c r="P141" s="558" t="inlineStr">
+        <is>
+          <t>Major Variable — NET +/− ; INFLOW/OUTFLOW (plain English)</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="409">
       <c r="B142" s="498" t="inlineStr">
@@ -18263,20 +18367,25 @@
           <t>Cash, BOP</t>
         </is>
       </c>
-      <c r="F142" s="588" t="n">
-        <v>180</v>
-      </c>
-      <c r="G142" s="515" t="n">
-        <v>180</v>
-      </c>
-      <c r="H142" s="515" t="n">
-        <v>180</v>
-      </c>
-      <c r="I142" s="515" t="n">
-        <v>180</v>
-      </c>
-      <c r="J142" s="515" t="n">
-        <v>180</v>
+      <c r="F142" s="588">
+        <f>$D$16</f>
+        <v/>
+      </c>
+      <c r="G142" s="515">
+        <f>$D$16</f>
+        <v/>
+      </c>
+      <c r="H142" s="515">
+        <f>$D$16</f>
+        <v/>
+      </c>
+      <c r="I142" s="515">
+        <f>$D$16</f>
+        <v/>
+      </c>
+      <c r="J142" s="515">
+        <f>$D$16</f>
+        <v/>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" s="409">
@@ -18298,10 +18407,10 @@
         <v>0</v>
       </c>
       <c r="J143" s="515" t="n">
-        <v>2.27373675443232e-13</v>
-      </c>
-    </row>
-    <row r="144" ht="15" customHeight="1" s="409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" ht="88" customHeight="1" s="409">
       <c r="B144" s="557" t="inlineStr">
         <is>
           <t>Cash, EOP</t>
@@ -18314,20 +18423,49 @@
       <c r="E144" s="537" t="n">
         <v>1581.9</v>
       </c>
-      <c r="F144" s="537" t="n">
-        <v>180</v>
-      </c>
-      <c r="G144" s="537" t="n">
-        <v>180</v>
-      </c>
-      <c r="H144" s="537" t="n">
-        <v>180</v>
-      </c>
-      <c r="I144" s="537" t="n">
-        <v>180</v>
-      </c>
-      <c r="J144" s="537" t="n">
-        <v>180</v>
+      <c r="F144" s="537">
+        <f>$D$16</f>
+        <v/>
+      </c>
+      <c r="G144" s="537">
+        <f>$D$16</f>
+        <v/>
+      </c>
+      <c r="H144" s="537">
+        <f>$D$16</f>
+        <v/>
+      </c>
+      <c r="I144" s="537">
+        <f>$D$16</f>
+        <v/>
+      </c>
+      <c r="J144" s="537">
+        <f>$D$16</f>
+        <v/>
+      </c>
+      <c r="L144" s="814" t="inlineStr">
+        <is>
+          <t>0% excess. Cash EOP held at minimum $50m (Sources D16). Full sweep keeps cash flat; dollars do not pile up.</t>
+        </is>
+      </c>
+      <c r="M144" s="567">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","REASONABLE: hold operating cash at model minimum $50m")</f>
+        <v/>
+      </c>
+      <c r="N144" s="568" t="inlineStr">
+        <is>
+          <t>EQ: F144=$D$16 (Minimum cash desired). Filing cash was ~$179.9m at close; excess above $50m funded Sources (D27).</t>
+        </is>
+      </c>
+      <c r="O144" s="568" t="inlineStr">
+        <is>
+          <t>Keeping only $50m cash is normal in a full-sweep LBO so extra cash pays debt instead of sitting idle.</t>
+        </is>
+      </c>
+      <c r="P144" s="811" t="inlineStr">
+        <is>
+          <t>NO — cash stock stays flat. Not the main lever; the sweep of extra cash is.</t>
+        </is>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1" s="409">
@@ -18343,19 +18481,19 @@
         <v>0.00515928515928516</v>
       </c>
       <c r="F145" s="590" t="n">
-        <v>0.00515928515928516</v>
+        <v>0</v>
       </c>
       <c r="G145" s="590" t="n">
-        <v>0.00515928515928516</v>
+        <v>0</v>
       </c>
       <c r="H145" s="590" t="n">
-        <v>0.00515928515928516</v>
+        <v>0</v>
       </c>
       <c r="I145" s="590" t="n">
-        <v>0.00515928515928516</v>
+        <v>0</v>
       </c>
       <c r="J145" s="590" t="n">
-        <v>0.00515928515928516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1" s="409">
@@ -18372,19 +18510,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="F146" s="515" t="n">
-        <v>0.928671328671329</v>
+        <v>0</v>
       </c>
       <c r="G146" s="515" t="n">
-        <v>0.928671328671329</v>
+        <v>0</v>
       </c>
       <c r="H146" s="515" t="n">
-        <v>0.928671328671329</v>
+        <v>0</v>
       </c>
       <c r="I146" s="515" t="n">
-        <v>0.928671328671329</v>
+        <v>0</v>
       </c>
       <c r="J146" s="515" t="n">
-        <v>0.928671328671329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1" s="409">
@@ -18418,42 +18556,76 @@
           <t xml:space="preserve">Cash, BOP </t>
         </is>
       </c>
-      <c r="F149" s="515" t="n">
-        <v>180</v>
-      </c>
-      <c r="G149" s="515" t="n">
-        <v>180</v>
-      </c>
-      <c r="H149" s="515" t="n">
-        <v>180</v>
-      </c>
-      <c r="I149" s="515" t="n">
-        <v>180</v>
-      </c>
-      <c r="J149" s="515" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="150" ht="15" customHeight="1" s="409">
+      <c r="F149" s="515">
+        <f>F142</f>
+        <v/>
+      </c>
+      <c r="G149" s="515">
+        <f>G142</f>
+        <v/>
+      </c>
+      <c r="H149" s="515">
+        <f>H142</f>
+        <v/>
+      </c>
+      <c r="I149" s="515">
+        <f>I142</f>
+        <v/>
+      </c>
+      <c r="J149" s="515">
+        <f>J142</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" ht="88" customHeight="1" s="409">
       <c r="B150" s="574" t="inlineStr">
         <is>
           <t>Less: Minimum cash desired</t>
         </is>
       </c>
-      <c r="F150" s="515" t="n">
-        <v>-180</v>
-      </c>
-      <c r="G150" s="515" t="n">
-        <v>-180</v>
-      </c>
-      <c r="H150" s="515" t="n">
-        <v>-180</v>
-      </c>
-      <c r="I150" s="515" t="n">
-        <v>-180</v>
-      </c>
-      <c r="J150" s="515" t="n">
-        <v>-180</v>
+      <c r="F150" s="515">
+        <f>-$D$16</f>
+        <v/>
+      </c>
+      <c r="G150" s="515">
+        <f>-$D$16</f>
+        <v/>
+      </c>
+      <c r="H150" s="515">
+        <f>-$D$16</f>
+        <v/>
+      </c>
+      <c r="I150" s="515">
+        <f>-$D$16</f>
+        <v/>
+      </c>
+      <c r="J150" s="515">
+        <f>-$D$16</f>
+        <v/>
+      </c>
+      <c r="L150" s="814" t="inlineStr">
+        <is>
+          <t>$50m flat min cash every year (Sources D16). Same floor all periods.</t>
+        </is>
+      </c>
+      <c r="M150" s="563">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm","REASONABLE: Minimum cash desired = $50m in Sources")</f>
+        <v/>
+      </c>
+      <c r="N150" s="564" t="inlineStr">
+        <is>
+          <t>EQ: F150=−$D$16. Sources D16=50. Excess cash at close = filing cash − 50 → D27.</t>
+        </is>
+      </c>
+      <c r="O150" s="564" t="inlineStr">
+        <is>
+          <t>The $50m floor is the cash the business must keep to run day to day.</t>
+        </is>
+      </c>
+      <c r="P150" s="819" t="inlineStr">
+        <is>
+          <t>YES — OUTFLOW of usable cash (locked as minimum). NET − vs using that cash to cut debt, but needed so the company can operate.</t>
+        </is>
       </c>
     </row>
     <row r="151" ht="15" customHeight="1" s="409">
@@ -18462,23 +18634,28 @@
           <t>Equals: Excess cash at BOP</t>
         </is>
       </c>
-      <c r="F151" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G151" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H151" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I151" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" s="515" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" ht="15" customHeight="1" s="409">
+      <c r="F151" s="515">
+        <f>F149+F150</f>
+        <v/>
+      </c>
+      <c r="G151" s="515">
+        <f>G149+G150</f>
+        <v/>
+      </c>
+      <c r="H151" s="515">
+        <f>H149+H150</f>
+        <v/>
+      </c>
+      <c r="I151" s="515">
+        <f>I149+I150</f>
+        <v/>
+      </c>
+      <c r="J151" s="515">
+        <f>J149+J150</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152" ht="88" customHeight="1" s="409">
       <c r="B152" s="591" t="inlineStr">
         <is>
           <t>Plus: Free cash flows generated during period</t>
@@ -18487,20 +18664,50 @@
       <c r="C152" s="555" t="n"/>
       <c r="D152" s="555" t="n"/>
       <c r="E152" s="555" t="n"/>
-      <c r="F152" s="592" t="n">
-        <v>88.7366611647973</v>
-      </c>
-      <c r="G152" s="592" t="n">
-        <v>341.347888508174</v>
-      </c>
-      <c r="H152" s="592" t="n">
-        <v>430.874867157023</v>
-      </c>
-      <c r="I152" s="592" t="n">
-        <v>495.283971347461</v>
-      </c>
-      <c r="J152" s="592" t="n">
-        <v>586.718180731428</v>
+      <c r="F152" s="824">
+        <f>AI_Operating!D21</f>
+        <v/>
+      </c>
+      <c r="G152" s="824">
+        <f>AI_Operating!E21</f>
+        <v/>
+      </c>
+      <c r="H152" s="824">
+        <f>AI_Operating!F21</f>
+        <v/>
+      </c>
+      <c r="I152" s="824">
+        <f>AI_Operating!G21</f>
+        <v/>
+      </c>
+      <c r="J152" s="824">
+        <f>AI_Operating!H21</f>
+        <v/>
+      </c>
+      <c r="L152" s="814" t="inlineStr">
+        <is>
+          <t>+5% sales-driven. FCF $ grows each year with AI_Operating (~$123m→~$248m). Not a flat dollar.</t>
+        </is>
+      </c>
+      <c r="M152" s="563">
+        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/","REASONABLE: FCF for sweep = AI_Operating FCF after interest")</f>
+        <v/>
+      </c>
+      <c r="N152" s="564" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 50-100% of annual excess free cash flow
+EQ: F152=AI_Operating!D21. That FCF already nets CapEx and ΔNWC from Drivers.</t>
+        </is>
+      </c>
+      <c r="O152" s="564" t="inlineStr">
+        <is>
+          <t>This is the cash the deal actually makes after interest. It is what can pay down loans.</t>
+        </is>
+      </c>
+      <c r="P152" s="820" t="inlineStr">
+        <is>
+          <t>YES — INFLOW of cash to the LBO. NET + for the LBO. More free cash means more debt paydown and a better equity outcome.</t>
+        </is>
       </c>
     </row>
     <row r="153" ht="15" customHeight="1" s="409">
@@ -18512,20 +18719,25 @@
       <c r="C153" s="500" t="n"/>
       <c r="D153" s="500" t="n"/>
       <c r="E153" s="500" t="n"/>
-      <c r="F153" s="576" t="n">
-        <v>88.7366611647973</v>
-      </c>
-      <c r="G153" s="576" t="n">
-        <v>341.347888508174</v>
-      </c>
-      <c r="H153" s="576" t="n">
-        <v>430.874867157023</v>
-      </c>
-      <c r="I153" s="576" t="n">
-        <v>495.283971347461</v>
-      </c>
-      <c r="J153" s="576" t="n">
-        <v>586.718180731428</v>
+      <c r="F153" s="825">
+        <f>F151+F152</f>
+        <v/>
+      </c>
+      <c r="G153" s="825">
+        <f>G151+G152</f>
+        <v/>
+      </c>
+      <c r="H153" s="825">
+        <f>H151+H152</f>
+        <v/>
+      </c>
+      <c r="I153" s="825">
+        <f>I151+I152</f>
+        <v/>
+      </c>
+      <c r="J153" s="825">
+        <f>J151+J152</f>
+        <v/>
       </c>
     </row>
     <row r="154" ht="13.8" customHeight="1" s="409"/>
@@ -18573,7 +18785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" ht="15" customHeight="1" s="409">
+    <row r="157" ht="88" customHeight="1" s="409">
       <c r="B157" s="557" t="inlineStr">
         <is>
           <t>Revolver, EOP</t>
@@ -18603,6 +18815,30 @@
       </c>
       <c r="J157" s="537" t="n">
         <v>0</v>
+      </c>
+      <c r="L157" s="814" t="inlineStr">
+        <is>
+          <t>0$ drawn. Revolver stays undrawn; FCF covers needs so no revolver inflow.</t>
+        </is>
+      </c>
+      <c r="M157" s="567">
+        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/","CAUTION — revolver capacity $350m but draw = $0 in base path")</f>
+        <v/>
+      </c>
+      <c r="N157" s="568" t="inlineStr">
+        <is>
+          <t>EQ: F155:F157=0. Availability F158=350 is a backstop, not used cash.</t>
+        </is>
+      </c>
+      <c r="O157" s="568" t="inlineStr">
+        <is>
+          <t>The revolver is a rainy-day credit line. In this case we do not need to borrow on it.</t>
+        </is>
+      </c>
+      <c r="P157" s="811" t="inlineStr">
+        <is>
+          <t>NO — not used. If drawn it would be an INFLOW of cash but also NET − (more debt). Here it is idle.</t>
+        </is>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1" s="409">
@@ -18675,70 +18911,160 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="15" customHeight="1" s="409">
+    <row r="162" ht="88" customHeight="1" s="409">
       <c r="B162" s="498" t="inlineStr">
         <is>
           <t>Term Loan A, BOP</t>
         </is>
       </c>
-      <c r="F162" s="588" t="n">
-        <v>2886.429</v>
-      </c>
-      <c r="G162" s="515" t="n">
-        <v>2509.0494388352</v>
-      </c>
-      <c r="H162" s="515" t="n">
-        <v>2023.38010032703</v>
-      </c>
-      <c r="I162" s="515" t="n">
-        <v>1448.18378317001</v>
-      </c>
-      <c r="J162" s="515" t="n">
-        <v>808.578361822546</v>
-      </c>
-    </row>
-    <row r="163" ht="15" customHeight="1" s="409">
+      <c r="F162" s="826">
+        <f>$D$29</f>
+        <v/>
+      </c>
+      <c r="G162" s="733">
+        <f>F165</f>
+        <v/>
+      </c>
+      <c r="H162" s="733">
+        <f>G165</f>
+        <v/>
+      </c>
+      <c r="I162" s="733">
+        <f>H165</f>
+        <v/>
+      </c>
+      <c r="J162" s="733">
+        <f>I165</f>
+        <v/>
+      </c>
+      <c r="L162" s="814" t="inlineStr">
+        <is>
+          <t>−1%/yr mandatory + 100% sweep. TLA BOP starts $457.8m (Sources 2.5× EBITDA); balance falls as cash pays it down.</t>
+        </is>
+      </c>
+      <c r="M162" s="563">
+        <f>HYPERLINK("https://ctacquisitions.com/acquisition-financing/","REASONABLE: TLA principal = Sources D29 = 2.5× LTM EBITDA")</f>
+        <v/>
+      </c>
+      <c r="N162" s="564" t="inlineStr">
+        <is>
+          <t>EQ: F162=$D$29 (457.8). Was a stale ~$2.9bn hardcoded loan — replaced with GTM Sources stack.</t>
+        </is>
+      </c>
+      <c r="O162" s="564" t="inlineStr">
+        <is>
+          <t>Term Loan A is the senior bank loan. Starting size must match the Sources page, not old template debt.</t>
+        </is>
+      </c>
+      <c r="P162" s="820" t="inlineStr">
+        <is>
+          <t>YES — debt balance (not cash flow by itself). NET + for equity when the balance falls; lower TLA means less interest and more exit equity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="88" customHeight="1" s="409">
       <c r="B163" s="498" t="inlineStr">
         <is>
           <t>Mandatory paydown $</t>
         </is>
       </c>
-      <c r="F163" s="515" t="n">
-        <v>288.6429</v>
-      </c>
-      <c r="G163" s="515" t="n">
-        <v>144.32145</v>
-      </c>
-      <c r="H163" s="515" t="n">
-        <v>144.32145</v>
-      </c>
-      <c r="I163" s="515" t="n">
-        <v>144.32145</v>
-      </c>
-      <c r="J163" s="515" t="n">
-        <v>144.32145</v>
-      </c>
-    </row>
-    <row r="164" ht="15" customHeight="1" s="409">
+      <c r="F163" s="515">
+        <f>$D$29*Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="G163" s="515">
+        <f>$D$29*Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="H163" s="515">
+        <f>$D$29*Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="I163" s="515">
+        <f>$D$29*Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="J163" s="515">
+        <f>$D$29*Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="L163" s="814" t="inlineStr">
+        <is>
+          <t>1%/yr of original TLA (Drivers C17). Flat $ amort each year (=0.01×$457.8m), not 5–10% old hardcodes.</t>
+        </is>
+      </c>
+      <c r="M163" s="563">
+        <f>HYPERLINK("https://clearvaluelending.com/glossary/term-loan-b","REASONABLE: Drivers C17=1% mandatory amortization")</f>
+        <v/>
+      </c>
+      <c r="N163" s="564" t="inlineStr">
+        <is>
+          <t>Ctrl+F: minimal amortization (1% annually)
+EQ: F163=$D$29*Assumptions_Drivers!$C$17.</t>
+        </is>
+      </c>
+      <c r="O163" s="564" t="inlineStr">
+        <is>
+          <t>Lenders require a small fixed paydown each year even before the cash sweep.</t>
+        </is>
+      </c>
+      <c r="P163" s="820" t="inlineStr">
+        <is>
+          <t>YES — OUTFLOW of cash to lenders. NET + for the LBO. Required paydown shrinks debt and helps the buyout delever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="88" customHeight="1" s="409">
       <c r="B164" s="498" t="inlineStr">
         <is>
           <t>Cash sweep (paydown from excess cash flows)</t>
         </is>
       </c>
-      <c r="F164" s="515" t="n">
-        <v>88.7366611647973</v>
-      </c>
-      <c r="G164" s="515" t="n">
-        <v>341.347888508174</v>
-      </c>
-      <c r="H164" s="515" t="n">
-        <v>430.874867157023</v>
-      </c>
-      <c r="I164" s="515" t="n">
-        <v>495.283971347461</v>
-      </c>
-      <c r="J164" s="515" t="n">
-        <v>586.718180731429</v>
+      <c r="F164" s="733">
+        <f>MAX(0,AI_Operating!D21-F163-F171)*Assumptions_Drivers!$C$18</f>
+        <v/>
+      </c>
+      <c r="G164" s="733">
+        <f>MAX(0,AI_Operating!E21-G163-G171)*Assumptions_Drivers!$C$18</f>
+        <v/>
+      </c>
+      <c r="H164" s="733">
+        <f>MAX(0,AI_Operating!F21-H163-H171)*Assumptions_Drivers!$C$18</f>
+        <v/>
+      </c>
+      <c r="I164" s="733">
+        <f>MAX(0,AI_Operating!G21-I163-I171)*Assumptions_Drivers!$C$18</f>
+        <v/>
+      </c>
+      <c r="J164" s="733">
+        <f>MAX(0,AI_Operating!H21-J163-J171)*Assumptions_Drivers!$C$18</f>
+        <v/>
+      </c>
+      <c r="L164" s="814" t="inlineStr">
+        <is>
+          <t>100% sweep (Drivers C18). Sweep $ = max(0, FCF − TLA mand − TLB mand); grows as FCF grows.</t>
+        </is>
+      </c>
+      <c r="M164" s="563">
+        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/","REASONABLE: Drivers C18=100% excess FCF sweep to debt")</f>
+        <v/>
+      </c>
+      <c r="N164" s="564" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 50-100% of annual excess free cash flow
+Ctrl+F: typically modeled at 100%
+EQ: F164=MAX(0,AI_FCF−mandTLA−mandTLB)*C18. Priority: Term Loan A first.</t>
+        </is>
+      </c>
+      <c r="O164" s="564" t="inlineStr">
+        <is>
+          <t>A 100% sweep means almost all leftover cash after the required 1% paydown goes to cut Term Loan A.</t>
+        </is>
+      </c>
+      <c r="P164" s="820" t="inlineStr">
+        <is>
+          <t>YES — OUTFLOW of cash (to pay debt). NET + for the LBO. Sweeping cash to Term Loan A is how the deal gets safer and equity value rises.</t>
+        </is>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1" s="409">
@@ -18750,20 +19076,25 @@
       <c r="C165" s="513" t="n"/>
       <c r="D165" s="597" t="n"/>
       <c r="E165" s="513" t="n"/>
-      <c r="F165" s="537" t="n">
-        <v>2509.0494388352</v>
-      </c>
-      <c r="G165" s="537" t="n">
-        <v>2023.38010032703</v>
-      </c>
-      <c r="H165" s="537" t="n">
-        <v>1448.18378317001</v>
-      </c>
-      <c r="I165" s="537" t="n">
-        <v>808.578361822546</v>
-      </c>
-      <c r="J165" s="537" t="n">
-        <v>77.5387310911168</v>
+      <c r="F165" s="614">
+        <f>MAX(0,F162-F163-F164)</f>
+        <v/>
+      </c>
+      <c r="G165" s="614">
+        <f>MAX(0,G162-G163-G164)</f>
+        <v/>
+      </c>
+      <c r="H165" s="614">
+        <f>MAX(0,H162-H163-H164)</f>
+        <v/>
+      </c>
+      <c r="I165" s="614">
+        <f>MAX(0,I162-I163-I164)</f>
+        <v/>
+      </c>
+      <c r="J165" s="614">
+        <f>MAX(0,J162-J163-J164)</f>
+        <v/>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1" s="409">
@@ -18778,20 +19109,25 @@
           <t>% of available cash used</t>
         </is>
       </c>
-      <c r="F166" s="598" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G166" s="598" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H166" s="598" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I166" s="598" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J166" s="598" t="n">
-        <v>0.05</v>
+      <c r="F166" s="827">
+        <f>Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="G166" s="827">
+        <f>Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="H166" s="827">
+        <f>Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="I166" s="827">
+        <f>Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="J166" s="827">
+        <f>Assumptions_Drivers!$C$17</f>
+        <v/>
       </c>
     </row>
     <row r="167" ht="15" customHeight="1" s="409">
@@ -18804,20 +19140,50 @@
       <c r="E167" s="599" t="n">
         <v>1</v>
       </c>
-      <c r="F167" s="600" t="n">
-        <v>88.7366611647973</v>
-      </c>
-      <c r="G167" s="600" t="n">
-        <v>341.347888508174</v>
-      </c>
-      <c r="H167" s="600" t="n">
-        <v>430.874867157023</v>
-      </c>
-      <c r="I167" s="600" t="n">
-        <v>495.283971347461</v>
-      </c>
-      <c r="J167" s="600" t="n">
-        <v>586.718180731428</v>
+      <c r="F167" s="600">
+        <f>F164</f>
+        <v/>
+      </c>
+      <c r="G167" s="600">
+        <f>G164</f>
+        <v/>
+      </c>
+      <c r="H167" s="600">
+        <f>H164</f>
+        <v/>
+      </c>
+      <c r="I167" s="600">
+        <f>I164</f>
+        <v/>
+      </c>
+      <c r="J167" s="600">
+        <f>J164</f>
+        <v/>
+      </c>
+      <c r="L167" s="814" t="inlineStr">
+        <is>
+          <t>100% flat (Drivers C18). Sweep percent does not change; dollars swept grow with FCF.</t>
+        </is>
+      </c>
+      <c r="M167" s="563">
+        <f>HYPERLINK("https://ryanoconnellfinance.com/lbo-model-fundamentals/","REASONABLE: cash sweep % = Drivers C18 = 100%")</f>
+        <v/>
+      </c>
+      <c r="N167" s="564" t="inlineStr">
+        <is>
+          <t>Ctrl+F: typically modeled at 100%
+EQ: sweep dollars in F164 use Assumptions_Drivers!$C$18.</t>
+        </is>
+      </c>
+      <c r="O167" s="564" t="inlineStr">
+        <is>
+          <t>100% means we model using essentially all excess free cash to repay debt.</t>
+        </is>
+      </c>
+      <c r="P167" s="820" t="inlineStr">
+        <is>
+          <t>YES — OUTFLOW rule. NET + for the LBO. A full sweep is credit-positive: cash goes to debt, not dividends or idle cash.</t>
+        </is>
       </c>
     </row>
     <row r="168" ht="15" customHeight="1" s="409">
@@ -18836,48 +19202,107 @@
       </c>
       <c r="F169" s="510" t="n"/>
     </row>
-    <row r="170" ht="15" customHeight="1" s="409">
+    <row r="170" ht="88" customHeight="1" s="409">
       <c r="B170" s="498" t="inlineStr">
         <is>
           <t>Term Loan B, BOP</t>
         </is>
       </c>
-      <c r="F170" s="588" t="n">
-        <v>670.852</v>
-      </c>
-      <c r="G170" s="515" t="n">
-        <v>637.3094</v>
-      </c>
-      <c r="H170" s="515" t="n">
-        <v>603.7668</v>
-      </c>
-      <c r="I170" s="515" t="n">
-        <v>570.2242</v>
-      </c>
-      <c r="J170" s="515" t="n">
-        <v>536.6816</v>
-      </c>
-    </row>
-    <row r="171" ht="15" customHeight="1" s="409">
+      <c r="F170" s="826">
+        <f>$D$30</f>
+        <v/>
+      </c>
+      <c r="G170" s="733">
+        <f>F173</f>
+        <v/>
+      </c>
+      <c r="H170" s="733">
+        <f>G173</f>
+        <v/>
+      </c>
+      <c r="I170" s="733">
+        <f>H173</f>
+        <v/>
+      </c>
+      <c r="J170" s="733">
+        <f>I173</f>
+        <v/>
+      </c>
+      <c r="L170" s="814" t="inlineStr">
+        <is>
+          <t>−1%/yr mandatory only. TLB starts $274.7m (Sources 1.5×); falls slowly; no sweep until TLA is ahead.</t>
+        </is>
+      </c>
+      <c r="M170" s="563">
+        <f>HYPERLINK("https://ibinterviewquestions.com/guides/valuation-investment-banking/lbo-debt-structures/","REASONABLE: TLB principal = Sources D30 = 1.5× LTM EBITDA")</f>
+        <v/>
+      </c>
+      <c r="N170" s="564" t="inlineStr">
+        <is>
+          <t>EQ: F170=$D$30. Rate Drivers C28=SOFR+5%. Mandatory = C17× original TLB.</t>
+        </is>
+      </c>
+      <c r="O170" s="564" t="inlineStr">
+        <is>
+          <t>Term Loan B sits behind Term Loan A, so it gets the small 1% paydown while TLA takes the sweep.</t>
+        </is>
+      </c>
+      <c r="P170" s="820" t="inlineStr">
+        <is>
+          <t>YES — debt balance. NET + for equity as it declines, but less than TLA because most extra cash hits TLA first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="88" customHeight="1" s="409">
       <c r="B171" s="498" t="inlineStr">
         <is>
           <t>Mandatory amortization $</t>
         </is>
       </c>
-      <c r="F171" s="515" t="n">
-        <v>33.5426</v>
-      </c>
-      <c r="G171" s="515" t="n">
-        <v>33.5426</v>
-      </c>
-      <c r="H171" s="515" t="n">
-        <v>33.5426</v>
-      </c>
-      <c r="I171" s="515" t="n">
-        <v>33.5426</v>
-      </c>
-      <c r="J171" s="515" t="n">
-        <v>33.5426</v>
+      <c r="F171" s="515">
+        <f>$D$30*Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="G171" s="515">
+        <f>$D$30*Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="H171" s="515">
+        <f>$D$30*Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="I171" s="515">
+        <f>$D$30*Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="J171" s="515">
+        <f>$D$30*Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="L171" s="814" t="inlineStr">
+        <is>
+          <t>1%/yr of original TLB (Drivers C17). Flat $ amort (=0.01×$274.7m) each year.</t>
+        </is>
+      </c>
+      <c r="M171" s="563">
+        <f>HYPERLINK("https://clearvaluelending.com/glossary/term-loan-b","REASONABLE: same 1% mandatory rule on TLB")</f>
+        <v/>
+      </c>
+      <c r="N171" s="564" t="inlineStr">
+        <is>
+          <t>Ctrl+F: minimal amortization (1% annually)
+EQ: F171=$D$30*Assumptions_Drivers!$C$17.</t>
+        </is>
+      </c>
+      <c r="O171" s="564" t="inlineStr">
+        <is>
+          <t>Same 1% lender rule as Term Loan A, applied to the Term Loan B size.</t>
+        </is>
+      </c>
+      <c r="P171" s="820" t="inlineStr">
+        <is>
+          <t>YES — OUTFLOW of cash to TLB lenders. NET + for the LBO because it still reduces total debt each year.</t>
+        </is>
       </c>
     </row>
     <row r="172" ht="15" customHeight="1" s="409">
@@ -18899,7 +19324,7 @@
         <v>0</v>
       </c>
       <c r="J172" s="515" t="n">
-        <v>2.27373675443232e-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" ht="15" customHeight="1" s="409">
@@ -18909,20 +19334,25 @@
         </is>
       </c>
       <c r="C173" s="513" t="n"/>
-      <c r="F173" s="537" t="n">
-        <v>637.3094</v>
-      </c>
-      <c r="G173" s="537" t="n">
-        <v>603.7668</v>
-      </c>
-      <c r="H173" s="537" t="n">
-        <v>570.2242</v>
-      </c>
-      <c r="I173" s="537" t="n">
-        <v>536.6816</v>
-      </c>
-      <c r="J173" s="537" t="n">
-        <v>503.139</v>
+      <c r="F173" s="614">
+        <f>MAX(0,F170-F171-F172)</f>
+        <v/>
+      </c>
+      <c r="G173" s="614">
+        <f>MAX(0,G170-G171-G172)</f>
+        <v/>
+      </c>
+      <c r="H173" s="614">
+        <f>MAX(0,H170-H171-H172)</f>
+        <v/>
+      </c>
+      <c r="I173" s="614">
+        <f>MAX(0,I170-I171-I172)</f>
+        <v/>
+      </c>
+      <c r="J173" s="614">
+        <f>MAX(0,J170-J171-J172)</f>
+        <v/>
       </c>
     </row>
     <row r="174" ht="15" customHeight="1" s="409">
@@ -18937,20 +19367,25 @@
           <t>% of available cash used</t>
         </is>
       </c>
-      <c r="F174" s="598" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G174" s="598" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H174" s="598" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I174" s="598" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J174" s="598" t="n">
-        <v>0.05</v>
+      <c r="F174" s="827">
+        <f>Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="G174" s="827">
+        <f>Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="H174" s="827">
+        <f>Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="I174" s="827">
+        <f>Assumptions_Drivers!$C$17</f>
+        <v/>
+      </c>
+      <c r="J174" s="827">
+        <f>Assumptions_Drivers!$C$17</f>
+        <v/>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1" s="409">
@@ -18976,7 +19411,7 @@
         <v>0</v>
       </c>
       <c r="J175" s="576" t="n">
-        <v>-2.27373675443232e-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" ht="15" customHeight="1" s="409">
@@ -18998,26 +19433,55 @@
       </c>
       <c r="F177" s="510" t="n"/>
     </row>
-    <row r="178" ht="15" customHeight="1" s="409">
+    <row r="178" ht="88" customHeight="1" s="409">
       <c r="B178" s="498" t="inlineStr">
         <is>
           <t>Senior Note, BOP</t>
         </is>
       </c>
-      <c r="F178" s="588" t="n">
-        <v>1632.995</v>
-      </c>
-      <c r="G178" s="515" t="n">
-        <v>1632.995</v>
-      </c>
-      <c r="H178" s="515" t="n">
-        <v>1632.995</v>
-      </c>
-      <c r="I178" s="515" t="n">
-        <v>1632.995</v>
-      </c>
-      <c r="J178" s="515" t="n">
-        <v>1632.995</v>
+      <c r="F178" s="826">
+        <f>$D$31</f>
+        <v/>
+      </c>
+      <c r="G178" s="733">
+        <f>F180</f>
+        <v/>
+      </c>
+      <c r="H178" s="733">
+        <f>G180</f>
+        <v/>
+      </c>
+      <c r="I178" s="733">
+        <f>H180</f>
+        <v/>
+      </c>
+      <c r="J178" s="733">
+        <f>I180</f>
+        <v/>
+      </c>
+      <c r="L178" s="814" t="inlineStr">
+        <is>
+          <t>0% amort. Senior Notes $183.1m (Sources 1.0×) stay flat — bullet at maturity; no annual paydown in model.</t>
+        </is>
+      </c>
+      <c r="M178" s="563">
+        <f>HYPERLINK("https://ctacquisitions.com/acquisition-financing/","REASONABLE: Notes principal = Sources D31; bullet (0% mandatory)")</f>
+        <v/>
+      </c>
+      <c r="N178" s="564" t="inlineStr">
+        <is>
+          <t>EQ: F178=$D$31; F179=0. Interest =(SOFR+3.5%)×Notes BOP. Balance does not amortize in-forecast.</t>
+        </is>
+      </c>
+      <c r="O178" s="564" t="inlineStr">
+        <is>
+          <t>Notes usually do not get paid down a little each year; they wait until the end unless refinanced.</t>
+        </is>
+      </c>
+      <c r="P178" s="819" t="inlineStr">
+        <is>
+          <t>YES — debt still outstanding. NET − vs TLA/TLB paydowns: Notes keep interest expense alive until exit/refi.</t>
+        </is>
       </c>
     </row>
     <row r="179" ht="15" customHeight="1" s="409">
@@ -19051,20 +19515,25 @@
       <c r="C180" s="513" t="n"/>
       <c r="D180" s="513" t="n"/>
       <c r="E180" s="513" t="n"/>
-      <c r="F180" s="537" t="n">
-        <v>1632.995</v>
-      </c>
-      <c r="G180" s="537" t="n">
-        <v>1632.995</v>
-      </c>
-      <c r="H180" s="537" t="n">
-        <v>1632.995</v>
-      </c>
-      <c r="I180" s="537" t="n">
-        <v>1632.995</v>
-      </c>
-      <c r="J180" s="537" t="n">
-        <v>1632.995</v>
+      <c r="F180" s="614">
+        <f>F178-F179</f>
+        <v/>
+      </c>
+      <c r="G180" s="614">
+        <f>G178-G179</f>
+        <v/>
+      </c>
+      <c r="H180" s="614">
+        <f>H178-H179</f>
+        <v/>
+      </c>
+      <c r="I180" s="614">
+        <f>I178-I179</f>
+        <v/>
+      </c>
+      <c r="J180" s="614">
+        <f>J178-J179</f>
+        <v/>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1" s="409">
@@ -19607,7 +20076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" ht="15" customHeight="1" s="409">
+    <row r="208" ht="88" customHeight="1" s="409">
       <c r="B208" s="498" t="inlineStr">
         <is>
           <t>Term Loan A</t>
@@ -19619,24 +20088,54 @@
       <c r="D208" s="519" t="n">
         <v>0.01</v>
       </c>
-      <c r="F208" s="586" t="n">
-        <v>134.88696097088</v>
-      </c>
-      <c r="G208" s="586" t="n">
-        <v>113.310738479056</v>
-      </c>
-      <c r="H208" s="586" t="n">
-        <v>92.8330898085942</v>
-      </c>
-      <c r="I208" s="586" t="n">
-        <v>65.9448466388274</v>
-      </c>
-      <c r="J208" s="586" t="n">
-        <v>27.5254552571771</v>
-      </c>
-      <c r="M208" s="589" t="n"/>
-    </row>
-    <row r="209" ht="15" customHeight="1" s="409">
+      <c r="F208" s="733">
+        <f>F162*Assumptions_Drivers!$C$27</f>
+        <v/>
+      </c>
+      <c r="G208" s="733">
+        <f>G162*Assumptions_Drivers!$C$27</f>
+        <v/>
+      </c>
+      <c r="H208" s="733">
+        <f>H162*Assumptions_Drivers!$C$27</f>
+        <v/>
+      </c>
+      <c r="I208" s="733">
+        <f>I162*Assumptions_Drivers!$C$27</f>
+        <v/>
+      </c>
+      <c r="J208" s="733">
+        <f>J162*Assumptions_Drivers!$C$27</f>
+        <v/>
+      </c>
+      <c r="L208" s="814" t="inlineStr">
+        <is>
+          <t>8.3% rate flat (Drivers C27=SOFR+4%). Interest $ falls as TLA balance falls from sweep.</t>
+        </is>
+      </c>
+      <c r="M208" s="828">
+        <f>HYPERLINK("https://www.global-rates.com/en/interest-rates/sofr/historical/2024/","REASONABLE: TLA rate = Drivers C27 = SOFR 4.3% + 4.0%")</f>
+        <v/>
+      </c>
+      <c r="N208" s="564" t="inlineStr">
+        <is>
+          <t>Ctrl+F: 4.30
+Ctrl+F: SOFR + 400-500 bps
+EQ: F208=F162*Assumptions_Drivers!$C$27. IS interest F50=−(TLA+TLB+Notes interest).</t>
+        </is>
+      </c>
+      <c r="O208" s="564" t="inlineStr">
+        <is>
+          <t>Interest is the price of the loan. As Term Loan A shrinks, this interest bill should shrink too.</t>
+        </is>
+      </c>
+      <c r="P208" s="819" t="inlineStr">
+        <is>
+          <t>YES — OUTFLOW of cash (interest). NET − for the LBO each year it is paid, but falling TLA makes this outflow smaller over time (good).</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="88" customHeight="1" s="409">
       <c r="B209" s="498" t="inlineStr">
         <is>
           <t>Term Loan B</t>
@@ -19648,23 +20147,53 @@
       <c r="D209" s="519" t="n">
         <v>0</v>
       </c>
-      <c r="F209" s="586" t="n">
-        <v>29.3734560756</v>
-      </c>
-      <c r="G209" s="586" t="n">
-        <v>29.9633026966</v>
-      </c>
-      <c r="H209" s="586" t="n">
-        <v>31.393693331</v>
-      </c>
-      <c r="I209" s="586" t="n">
-        <v>32.3448943818</v>
-      </c>
-      <c r="J209" s="586" t="n">
-        <v>32.2999472978</v>
-      </c>
-    </row>
-    <row r="210" ht="15" customHeight="1" s="409">
+      <c r="F209" s="733">
+        <f>F170*Assumptions_Drivers!$C$28</f>
+        <v/>
+      </c>
+      <c r="G209" s="733">
+        <f>G170*Assumptions_Drivers!$C$28</f>
+        <v/>
+      </c>
+      <c r="H209" s="733">
+        <f>H170*Assumptions_Drivers!$C$28</f>
+        <v/>
+      </c>
+      <c r="I209" s="733">
+        <f>I170*Assumptions_Drivers!$C$28</f>
+        <v/>
+      </c>
+      <c r="J209" s="733">
+        <f>J170*Assumptions_Drivers!$C$28</f>
+        <v/>
+      </c>
+      <c r="L209" s="814" t="inlineStr">
+        <is>
+          <t>9.3% rate flat (Drivers C28=SOFR+5%). Interest $ edges down only with 1% TLB amort.</t>
+        </is>
+      </c>
+      <c r="M209" s="563">
+        <f>HYPERLINK("https://ibinterviewquestions.com/guides/valuation-investment-banking/lbo-debt-structures/","REASONABLE: TLB rate = Drivers C28 = SOFR + 5.0%")</f>
+        <v/>
+      </c>
+      <c r="N209" s="564" t="inlineStr">
+        <is>
+          <t>Ctrl+F: SOFR + 300-500 basis points
+EQ: F209=F170*Assumptions_Drivers!$C$28.</t>
+        </is>
+      </c>
+      <c r="O209" s="564" t="inlineStr">
+        <is>
+          <t>Term Loan B costs more than Term Loan A because it is riskier for lenders.</t>
+        </is>
+      </c>
+      <c r="P209" s="819" t="inlineStr">
+        <is>
+          <t>YES — OUTFLOW of cash (interest). NET − for the LBO. Higher rate than TLA, and the balance falls only slowly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="88" customHeight="1" s="409">
       <c r="B210" s="498" t="inlineStr">
         <is>
           <t>Senior Note</t>
@@ -19673,20 +20202,49 @@
       <c r="E210" s="609" t="n">
         <v>0.08125</v>
       </c>
-      <c r="F210" s="515" t="n">
-        <v>132.68084375</v>
-      </c>
-      <c r="G210" s="515" t="n">
-        <v>132.68084375</v>
-      </c>
-      <c r="H210" s="515" t="n">
-        <v>132.68084375</v>
-      </c>
-      <c r="I210" s="515" t="n">
-        <v>132.68084375</v>
-      </c>
-      <c r="J210" s="515" t="n">
-        <v>132.68084375</v>
+      <c r="F210" s="733">
+        <f>F178*(Assumptions_Drivers!$C$14+0.035)</f>
+        <v/>
+      </c>
+      <c r="G210" s="733">
+        <f>G178*(Assumptions_Drivers!$C$14+0.035)</f>
+        <v/>
+      </c>
+      <c r="H210" s="733">
+        <f>H178*(Assumptions_Drivers!$C$14+0.035)</f>
+        <v/>
+      </c>
+      <c r="I210" s="733">
+        <f>I178*(Assumptions_Drivers!$C$14+0.035)</f>
+        <v/>
+      </c>
+      <c r="J210" s="733">
+        <f>J178*(Assumptions_Drivers!$C$14+0.035)</f>
+        <v/>
+      </c>
+      <c r="L210" s="814" t="inlineStr">
+        <is>
+          <t>7.8% rate flat (SOFR+3.5%). Interest $ stays roughly flat because Notes principal does not amortize.</t>
+        </is>
+      </c>
+      <c r="M210" s="563">
+        <f>HYPERLINK("https://www.global-rates.com/en/interest-rates/sofr/historical/2024/","REASONABLE: Notes ≈ SOFR+3.5% (same stack used in DCF cost of debt)")</f>
+        <v/>
+      </c>
+      <c r="N210" s="564" t="inlineStr">
+        <is>
+          <t>EQ: F210=F178*(Assumptions_Drivers!$C$14+0.035). Principal flat → interest roughly flat.</t>
+        </is>
+      </c>
+      <c r="O210" s="564" t="inlineStr">
+        <is>
+          <t>Notes interest keeps showing up every year while the Notes balance stays outstanding.</t>
+        </is>
+      </c>
+      <c r="P210" s="819" t="inlineStr">
+        <is>
+          <t>YES — OUTFLOW of cash (interest). NET − for the LBO until exit or refinance clears the Notes.</t>
+        </is>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1" s="409">

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -60,7 +60,7 @@
     <numFmt numFmtId="194" formatCode="#,##0.0_);\(#,##0.0\);&quot;- _)&quot;;@_)"/>
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
   </numFmts>
-  <fonts count="69">
+  <fonts count="71">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -506,6 +506,18 @@
       <color rgb="00C00000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="23">
     <fill>
@@ -830,7 +842,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="829">
+  <cellXfs count="832">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3296,6 +3308,13 @@
     <xf numFmtId="185" fontId="61" fillId="16" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12470,17 +12489,17 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="408" t="inlineStr">
         <is>
           <t>CASH/DEBT</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="408" t="inlineStr">
         <is>
           <t>Major: FCF inflow; 100% sweep &amp; 1% mand outflows (NET + delever); interest outflows (NET −). Stack=Sources; rates=C14–C18.</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="408" t="inlineStr">
         <is>
           <t>LBO!F152 / F164 / F208</t>
         </is>
@@ -18270,6 +18289,15 @@
           <t>CASH &amp; DEBT — wired to Sources debt stack ($915.5m), Drivers C14–C18, and AI_Operating FCF (replaced stale oversized loan hardcodes).</t>
         </is>
       </c>
+      <c r="M138" s="829">
+        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","PDF: Cash &amp; Debt Growth / Source / Verbatim / Why / Major Variable")</f>
+        <v/>
+      </c>
+      <c r="N138" s="830" t="inlineStr">
+        <is>
+          <t>Click M138 for the Cash &amp; Debt documentation PDF (same columns as on-sheet: Growth trajectory, Source, Verbatim, Why, Major Variable).</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="15" customHeight="1" s="409">
       <c r="B139" s="496" t="inlineStr">
@@ -18359,6 +18387,10 @@
         <is>
           <t>Major Variable — NET +/− ; INFLOW/OUTFLOW (plain English)</t>
         </is>
+      </c>
+      <c r="Q141" s="831">
+        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","Open Cash &amp; Debt PDF")</f>
+        <v/>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="409">

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -60,7 +60,7 @@
     <numFmt numFmtId="194" formatCode="#,##0.0_);\(#,##0.0\);&quot;- _)&quot;;@_)"/>
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
   </numFmts>
-  <fonts count="71">
+  <fonts count="72">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -518,6 +518,12 @@
       <sz val="9"/>
       <u val="single"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="23">
     <fill>
@@ -842,7 +848,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="832">
+  <cellXfs count="833">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3315,6 +3321,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18290,12 +18299,16 @@
         </is>
       </c>
       <c r="M138" s="829">
-        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","PDF: Cash &amp; Debt Growth / Source / Verbatim / Why / Major Variable")</f>
-        <v/>
-      </c>
-      <c r="N138" s="830" t="inlineStr">
-        <is>
-          <t>Click M138 for the Cash &amp; Debt documentation PDF (same columns as on-sheet: Growth trajectory, Source, Verbatim, Why, Major Variable).</t>
+        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","PDF (bulleted text): Cash &amp; Debt Growth / Source / Verbatim / Why / Major Variable")</f>
+        <v/>
+      </c>
+      <c r="N138" s="832">
+        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.txt","TXT (copy/paste): same Cash &amp; Debt bullets")</f>
+        <v/>
+      </c>
+      <c r="O138" s="830" t="inlineStr">
+        <is>
+          <t>Plain bulleted list PDF/TXT — not a chart. Click M138 (PDF) or N138 (TXT) to open.</t>
         </is>
       </c>
     </row>
@@ -18389,7 +18402,11 @@
         </is>
       </c>
       <c r="Q141" s="831">
-        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","Open Cash &amp; Debt PDF")</f>
+        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","Open Cash &amp; Debt PDF (bullets)")</f>
+        <v/>
+      </c>
+      <c r="R141" s="831">
+        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.txt","Open Cash &amp; Debt TXT")</f>
         <v/>
       </c>
     </row>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -60,7 +60,7 @@
     <numFmt numFmtId="194" formatCode="#,##0.0_);\(#,##0.0\);&quot;- _)&quot;;@_)"/>
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="78">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -524,8 +524,41 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B57D0"/>
+      <sz val="18"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B57D0"/>
+      <sz val="12"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B57D0"/>
+      <sz val="16"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <color rgb="000B57D0"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="005F6368"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -648,6 +681,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F0FE"/>
       </patternFill>
     </fill>
   </fills>
@@ -848,7 +886,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="833">
+  <cellXfs count="840">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3324,6 +3362,19 @@
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="75" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14102,7 +14153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:R393"/>
+  <dimension ref="A1:S393"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="1.73" customWidth="1" style="408" min="1" max="1"/>
@@ -18279,7 +18330,7 @@
       <c r="I137" s="582" t="n"/>
       <c r="J137" s="582" t="n"/>
     </row>
-    <row r="138" ht="15" customHeight="1" s="409">
+    <row r="138" ht="36" customHeight="1" s="409">
       <c r="B138" s="570" t="inlineStr">
         <is>
           <t>CASH &amp; DEBT</t>
@@ -18293,24 +18344,18 @@
       <c r="H138" s="489" t="n"/>
       <c r="I138" s="489" t="n"/>
       <c r="J138" s="489" t="n"/>
-      <c r="L138" s="809" t="inlineStr">
-        <is>
-          <t>CASH &amp; DEBT — wired to Sources debt stack ($915.5m), Drivers C14–C18, and AI_Operating FCF (replaced stale oversized loan hardcodes).</t>
-        </is>
-      </c>
-      <c r="M138" s="829">
-        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","PDF (bulleted text): Cash &amp; Debt Growth / Source / Verbatim / Why / Major Variable")</f>
-        <v/>
-      </c>
-      <c r="N138" s="832">
-        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.txt","TXT (copy/paste): same Cash &amp; Debt bullets")</f>
-        <v/>
-      </c>
-      <c r="O138" s="830" t="inlineStr">
-        <is>
-          <t>Plain bulleted list PDF/TXT — not a chart. Click M138 (PDF) or N138 (TXT) to open.</t>
-        </is>
-      </c>
+      <c r="L138" s="833" t="inlineStr">
+        <is>
+          <t>CASH &amp; DEBT</t>
+        </is>
+      </c>
+      <c r="M138" s="834">
+        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","CLICK HERE — CASH &amp; DEBT PDF (Google Doc style)")</f>
+        <v/>
+      </c>
+      <c r="N138" s="835" t="n"/>
+      <c r="O138" s="835" t="n"/>
+      <c r="P138" s="835" t="n"/>
     </row>
     <row r="139" ht="15" customHeight="1" s="409">
       <c r="B139" s="496" t="inlineStr">
@@ -18342,6 +18387,7 @@
       <c r="J139" s="547" t="n">
         <v>2029</v>
       </c>
+      <c r="L139" s="836" t="n"/>
     </row>
     <row r="140" ht="15" customHeight="1" s="409">
       <c r="B140" s="489" t="inlineStr">
@@ -18373,8 +18419,13 @@
       <c r="J140" s="550" t="n">
         <v>47483</v>
       </c>
-    </row>
-    <row r="141" ht="32" customHeight="1" s="409">
+      <c r="L140" s="837" t="inlineStr">
+        <is>
+          <t>Blue banner above = Cash &amp; Debt PDF (document look, not a chart).</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="30" customHeight="1" s="409">
       <c r="B141" s="541" t="n"/>
       <c r="L141" s="558" t="inlineStr">
         <is>
@@ -18401,12 +18452,8 @@
           <t>Major Variable — NET +/− ; INFLOW/OUTFLOW (plain English)</t>
         </is>
       </c>
-      <c r="Q141" s="831">
-        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","Open Cash &amp; Debt PDF (bullets)")</f>
-        <v/>
-      </c>
-      <c r="R141" s="831">
-        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.txt","Open Cash &amp; Debt TXT")</f>
+      <c r="Q141" s="838">
+        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","OPEN CASH &amp; DEBT PDF")</f>
         <v/>
       </c>
     </row>
@@ -18434,6 +18481,10 @@
       </c>
       <c r="J142" s="515">
         <f>$D$16</f>
+        <v/>
+      </c>
+      <c r="Q142" s="839">
+        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.txt","TXT copy/paste version")</f>
         <v/>
       </c>
     </row>
@@ -24112,16 +24163,18 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
     <mergeCell ref="F302:J302"/>
     <mergeCell ref="G321:I321"/>
     <mergeCell ref="D291:J291"/>
     <mergeCell ref="D290:J290"/>
     <mergeCell ref="D300:J300"/>
+    <mergeCell ref="Q141:S141"/>
     <mergeCell ref="D310:J310"/>
     <mergeCell ref="F292:J292"/>
     <mergeCell ref="F311:J311"/>
     <mergeCell ref="F216:J216"/>
+    <mergeCell ref="M138:P138"/>
     <mergeCell ref="D301:J301"/>
     <mergeCell ref="E280:J280"/>
   </mergeCells>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -60,7 +60,7 @@
     <numFmt numFmtId="194" formatCode="#,##0.0_);\(#,##0.0\);&quot;- _)&quot;;@_)"/>
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
   </numFmts>
-  <fonts count="78">
+  <fonts count="79">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -557,8 +557,13 @@
       <color rgb="005F6368"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="26">
     <fill>
       <patternFill/>
     </fill>
@@ -686,6 +691,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F0FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -886,7 +901,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="840">
+  <cellXfs count="844">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3375,6 +3390,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14153,7 +14180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S393"/>
+  <dimension ref="A1:U393"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="1.73" customWidth="1" style="408" min="1" max="1"/>
@@ -14166,6 +14193,8 @@
     <col width="52" customWidth="1" style="408" min="14" max="14"/>
     <col width="34" customWidth="1" style="409" min="15" max="15"/>
     <col width="42" customWidth="1" style="409" min="16" max="16"/>
+    <col width="40" customWidth="1" style="409" min="20" max="20"/>
+    <col width="40" customWidth="1" style="409" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" s="409">
@@ -18349,13 +18378,10 @@
           <t>CASH &amp; DEBT</t>
         </is>
       </c>
-      <c r="M138" s="834">
+      <c r="M138" s="840">
         <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","CLICK HERE — CASH &amp; DEBT PDF (Google Doc style)")</f>
         <v/>
       </c>
-      <c r="N138" s="835" t="n"/>
-      <c r="O138" s="835" t="n"/>
-      <c r="P138" s="835" t="n"/>
     </row>
     <row r="139" ht="15" customHeight="1" s="409">
       <c r="B139" s="496" t="inlineStr">
@@ -18456,6 +18482,16 @@
         <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","OPEN CASH &amp; DEBT PDF")</f>
         <v/>
       </c>
+      <c r="T141" s="841" t="inlineStr">
+        <is>
+          <t>What this line is (≤30 words, plain English)</t>
+        </is>
+      </c>
+      <c r="U141" s="841" t="inlineStr">
+        <is>
+          <t>What it is required for (≤30 words, plain English)</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="409">
       <c r="B142" s="498" t="inlineStr">
@@ -18565,6 +18601,16 @@
       <c r="P144" s="811" t="inlineStr">
         <is>
           <t>NO — cash stock stays flat. Not the main lever; the sweep of extra cash is.</t>
+        </is>
+      </c>
+      <c r="T144" s="842" t="inlineStr">
+        <is>
+          <t>Cash at year-end sitting in the company’s bank account after the year’s cash moves.</t>
+        </is>
+      </c>
+      <c r="U144" s="843" t="inlineStr">
+        <is>
+          <t>Required so the model shows how much cash is left on hand; here it stays at the $50m minimum.</t>
         </is>
       </c>
     </row>
@@ -18727,6 +18773,16 @@
           <t>YES — OUTFLOW of usable cash (locked as minimum). NET − vs using that cash to cut debt, but needed so the company can operate.</t>
         </is>
       </c>
+      <c r="T150" s="842" t="inlineStr">
+        <is>
+          <t>The smallest cash pile the company must keep so it can pay bills and run normally.</t>
+        </is>
+      </c>
+      <c r="U150" s="843" t="inlineStr">
+        <is>
+          <t>Required as a safety floor. Cash above this can be used to pay down buyout debt.</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1" s="409">
       <c r="B151" s="574" t="inlineStr">
@@ -18809,6 +18865,16 @@
           <t>YES — INFLOW of cash to the LBO. NET + for the LBO. More free cash means more debt paydown and a better equity outcome.</t>
         </is>
       </c>
+      <c r="T152" s="842" t="inlineStr">
+        <is>
+          <t>Free cash flow: leftover cash after running the business, interest, and needed reinvestment.</t>
+        </is>
+      </c>
+      <c r="U152" s="843" t="inlineStr">
+        <is>
+          <t>Required to pay down loans. More free cash flow usually means a stronger LBO for equity owners.</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="15" customHeight="1" s="409">
       <c r="B153" s="593" t="inlineStr">
@@ -18940,6 +19006,16 @@
           <t>NO — not used. If drawn it would be an INFLOW of cash but also NET − (more debt). Here it is idle.</t>
         </is>
       </c>
+      <c r="T157" s="842" t="inlineStr">
+        <is>
+          <t>A backup credit card-style loan the company can draw if it needs short-term cash.</t>
+        </is>
+      </c>
+      <c r="U157" s="843" t="inlineStr">
+        <is>
+          <t>Required as emergency funding capacity. In this case it stays at $0 because free cash covers needs.</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="15" customHeight="1" s="409">
       <c r="B158" s="593" t="inlineStr">
@@ -19061,6 +19137,16 @@
           <t>YES — debt balance (not cash flow by itself). NET + for equity when the balance falls; lower TLA means less interest and more exit equity.</t>
         </is>
       </c>
+      <c r="T162" s="842" t="inlineStr">
+        <is>
+          <t>Term Loan A starting balance — the senior bank loan taken to help buy the company.</t>
+        </is>
+      </c>
+      <c r="U162" s="843" t="inlineStr">
+        <is>
+          <t>Required to track the biggest loan that gets paid first. Paying it down raises equity value at exit.</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="88" customHeight="1" s="409">
       <c r="B163" s="498" t="inlineStr">
@@ -19111,6 +19197,16 @@
       <c r="P163" s="820" t="inlineStr">
         <is>
           <t>YES — OUTFLOW of cash to lenders. NET + for the LBO. Required paydown shrinks debt and helps the buyout delever.</t>
+        </is>
+      </c>
+      <c r="T163" s="842" t="inlineStr">
+        <is>
+          <t>The fixed yearly amount lenders force you to repay on Term Loan A (1% of the original loan).</t>
+        </is>
+      </c>
+      <c r="U163" s="843" t="inlineStr">
+        <is>
+          <t>Required by the loan contract. It steadily shrinks debt even before extra cash sweep paydowns.</t>
         </is>
       </c>
     </row>
@@ -19164,6 +19260,16 @@
       <c r="P164" s="820" t="inlineStr">
         <is>
           <t>YES — OUTFLOW of cash (to pay debt). NET + for the LBO. Sweeping cash to Term Loan A is how the deal gets safer and equity value rises.</t>
+        </is>
+      </c>
+      <c r="T164" s="842" t="inlineStr">
+        <is>
+          <t>Extra free cash sent to repay Term Loan A after the required 1% payment is made.</t>
+        </is>
+      </c>
+      <c r="U164" s="843" t="inlineStr">
+        <is>
+          <t>Required in this LBO to cut debt fast. Sweeping cash to debt is a main way the buyout wins.</t>
         </is>
       </c>
     </row>
@@ -19283,6 +19389,16 @@
       <c r="P167" s="820" t="inlineStr">
         <is>
           <t>YES — OUTFLOW rule. NET + for the LBO. A full sweep is credit-positive: cash goes to debt, not dividends or idle cash.</t>
+        </is>
+      </c>
+      <c r="T167" s="842" t="inlineStr">
+        <is>
+          <t>The share of leftover free cash that must go to debt paydown — here set to 100%.</t>
+        </is>
+      </c>
+      <c r="U167" s="843" t="inlineStr">
+        <is>
+          <t>Required to define the paydown rule. 100% means almost all extra cash goes to loans, not dividends.</t>
         </is>
       </c>
     </row>
@@ -19352,6 +19468,16 @@
           <t>YES — debt balance. NET + for equity as it declines, but less than TLA because most extra cash hits TLA first.</t>
         </is>
       </c>
+      <c r="T170" s="842" t="inlineStr">
+        <is>
+          <t>Term Loan B starting balance — the next loan behind Term Loan A in repayment priority.</t>
+        </is>
+      </c>
+      <c r="U170" s="843" t="inlineStr">
+        <is>
+          <t>Required to track the second loan. It gets the small required paydown while TLA takes most sweep cash.</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="88" customHeight="1" s="409">
       <c r="B171" s="498" t="inlineStr">
@@ -19402,6 +19528,16 @@
       <c r="P171" s="820" t="inlineStr">
         <is>
           <t>YES — OUTFLOW of cash to TLB lenders. NET + for the LBO because it still reduces total debt each year.</t>
+        </is>
+      </c>
+      <c r="T171" s="842" t="inlineStr">
+        <is>
+          <t>The fixed yearly amount lenders force you to repay on Term Loan B (1% of the original loan).</t>
+        </is>
+      </c>
+      <c r="U171" s="843" t="inlineStr">
+        <is>
+          <t>Required by the loan contract. It reduces Term Loan B a little each year.</t>
         </is>
       </c>
     </row>
@@ -19583,6 +19719,16 @@
           <t>YES — debt still outstanding. NET − vs TLA/TLB paydowns: Notes keep interest expense alive until exit/refi.</t>
         </is>
       </c>
+      <c r="T178" s="842" t="inlineStr">
+        <is>
+          <t>Senior Notes starting balance — bond-like debt that usually is not paid down a little each year.</t>
+        </is>
+      </c>
+      <c r="U178" s="843" t="inlineStr">
+        <is>
+          <t>Required to track junior debt that mostly waits until exit or refinance, while still charging interest.</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="15" customHeight="1" s="409">
       <c r="B179" s="498" t="inlineStr">
@@ -20234,6 +20380,16 @@
           <t>YES — OUTFLOW of cash (interest). NET − for the LBO each year it is paid, but falling TLA makes this outflow smaller over time (good).</t>
         </is>
       </c>
+      <c r="T208" s="842" t="inlineStr">
+        <is>
+          <t>Yearly interest cost on Term Loan A — the fee for borrowing that bank loan money.</t>
+        </is>
+      </c>
+      <c r="U208" s="843" t="inlineStr">
+        <is>
+          <t>Required because interest is a real cash bill. As Term Loan A falls, this cost should fall too.</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="88" customHeight="1" s="409">
       <c r="B209" s="498" t="inlineStr">
@@ -20292,6 +20448,16 @@
           <t>YES — OUTFLOW of cash (interest). NET − for the LBO. Higher rate than TLA, and the balance falls only slowly.</t>
         </is>
       </c>
+      <c r="T209" s="842" t="inlineStr">
+        <is>
+          <t>Yearly interest cost on Term Loan B — usually a bit higher than Term Loan A.</t>
+        </is>
+      </c>
+      <c r="U209" s="843" t="inlineStr">
+        <is>
+          <t>Required to capture the cash cost of the second loan. It stays painful until that balance shrinks.</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="88" customHeight="1" s="409">
       <c r="B210" s="498" t="inlineStr">
@@ -20344,6 +20510,16 @@
       <c r="P210" s="819" t="inlineStr">
         <is>
           <t>YES — OUTFLOW of cash (interest). NET − for the LBO until exit or refinance clears the Notes.</t>
+        </is>
+      </c>
+      <c r="T210" s="842" t="inlineStr">
+        <is>
+          <t>Yearly interest cost on the Senior Notes while that Notes balance stays outstanding.</t>
+        </is>
+      </c>
+      <c r="U210" s="843" t="inlineStr">
+        <is>
+          <t>Required because Notes keep charging interest every year until exit or a refinance clears them.</t>
         </is>
       </c>
     </row>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -18379,7 +18379,7 @@
         </is>
       </c>
       <c r="M138" s="840">
-        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","CLICK HERE — CASH &amp; DEBT PDF (Google Doc style)")</f>
+        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","CLICK HERE — CASH &amp; DEBT PDF (steps 1–4)")</f>
         <v/>
       </c>
     </row>
@@ -18447,7 +18447,7 @@
       </c>
       <c r="L140" s="837" t="inlineStr">
         <is>
-          <t>Blue banner above = Cash &amp; Debt PDF (document look, not a chart).</t>
+          <t>PDF uses big 1–4 on every line item: 1 What it is · 2 What required for · 3 Growth · 4 Major Variable.</t>
         </is>
       </c>
     </row>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -60,7 +60,7 @@
     <numFmt numFmtId="194" formatCode="#,##0.0_);\(#,##0.0\);&quot;- _)&quot;;@_)"/>
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
   </numFmts>
-  <fonts count="79">
+  <fonts count="83">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -562,8 +562,28 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <color rgb="001F4E79"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="26">
+  <fills count="28">
     <fill>
       <patternFill/>
     </fill>
@@ -701,6 +721,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -901,7 +931,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="844">
+  <cellXfs count="850">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3400,6 +3430,24 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="20" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="26" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="22" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="27" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="19" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -18379,7 +18427,7 @@
         </is>
       </c>
       <c r="M138" s="840">
-        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","CLICK HERE — CASH &amp; DEBT PDF (steps 1–4)")</f>
+        <f>HYPERLINK("https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/lbomodel4-dcf-shares-gtm-44dc/LBO/output/LBOMODEL4_CASH_AND_DEBT_SOURCES.pdf","CLICK HERE — CASH &amp; DEBT PDF (OUTFLOWS IN RED)")</f>
         <v/>
       </c>
     </row>
@@ -18445,9 +18493,9 @@
       <c r="J140" s="550" t="n">
         <v>47483</v>
       </c>
-      <c r="L140" s="837" t="inlineStr">
-        <is>
-          <t>PDF uses big 1–4 on every line item: 1 What it is · 2 What required for · 3 Growth · 4 Major Variable.</t>
+      <c r="L140" s="844" t="inlineStr">
+        <is>
+          <t>COLOR KEY: RED = cash OUTFLOW · GREEN = cash INFLOW · BLUE = not a cash-flow line (balance/idle). Outflows stay red even if NET + for the LBO.</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18646,7 @@
           <t>Keeping only $50m cash is normal in a full-sweep LBO so extra cash pays debt instead of sitting idle.</t>
         </is>
       </c>
-      <c r="P144" s="811" t="inlineStr">
+      <c r="P144" s="845" t="inlineStr">
         <is>
           <t>NO — cash stock stays flat. Not the main lever; the sweep of extra cash is.</t>
         </is>
@@ -18749,7 +18797,7 @@
         <f>-$D$16</f>
         <v/>
       </c>
-      <c r="L150" s="814" t="inlineStr">
+      <c r="L150" s="846" t="inlineStr">
         <is>
           <t>$50m flat min cash every year (Sources D16). Same floor all periods.</t>
         </is>
@@ -18768,7 +18816,7 @@
           <t>The $50m floor is the cash the business must keep to run day to day.</t>
         </is>
       </c>
-      <c r="P150" s="819" t="inlineStr">
+      <c r="P150" s="847" t="inlineStr">
         <is>
           <t>YES — OUTFLOW of usable cash (locked as minimum). NET − vs using that cash to cut debt, but needed so the company can operate.</t>
         </is>
@@ -18840,7 +18888,7 @@
         <f>AI_Operating!H21</f>
         <v/>
       </c>
-      <c r="L152" s="814" t="inlineStr">
+      <c r="L152" s="848" t="inlineStr">
         <is>
           <t>+5% sales-driven. FCF $ grows each year with AI_Operating (~$123m→~$248m). Not a flat dollar.</t>
         </is>
@@ -18860,7 +18908,7 @@
           <t>This is the cash the deal actually makes after interest. It is what can pay down loans.</t>
         </is>
       </c>
-      <c r="P152" s="820" t="inlineStr">
+      <c r="P152" s="849" t="inlineStr">
         <is>
           <t>YES — INFLOW of cash to the LBO. NET + for the LBO. More free cash means more debt paydown and a better equity outcome.</t>
         </is>
@@ -19001,7 +19049,7 @@
           <t>The revolver is a rainy-day credit line. In this case we do not need to borrow on it.</t>
         </is>
       </c>
-      <c r="P157" s="811" t="inlineStr">
+      <c r="P157" s="845" t="inlineStr">
         <is>
           <t>NO — not used. If drawn it would be an INFLOW of cash but also NET − (more debt). Here it is idle.</t>
         </is>
@@ -19132,7 +19180,7 @@
           <t>Term Loan A is the senior bank loan. Starting size must match the Sources page, not old template debt.</t>
         </is>
       </c>
-      <c r="P162" s="820" t="inlineStr">
+      <c r="P162" s="845" t="inlineStr">
         <is>
           <t>YES — debt balance (not cash flow by itself). NET + for equity when the balance falls; lower TLA means less interest and more exit equity.</t>
         </is>
@@ -19174,7 +19222,7 @@
         <f>$D$29*Assumptions_Drivers!$C$17</f>
         <v/>
       </c>
-      <c r="L163" s="814" t="inlineStr">
+      <c r="L163" s="846" t="inlineStr">
         <is>
           <t>1%/yr of original TLA (Drivers C17). Flat $ amort each year (=0.01×$457.8m), not 5–10% old hardcodes.</t>
         </is>
@@ -19194,7 +19242,7 @@
           <t>Lenders require a small fixed paydown each year even before the cash sweep.</t>
         </is>
       </c>
-      <c r="P163" s="820" t="inlineStr">
+      <c r="P163" s="847" t="inlineStr">
         <is>
           <t>YES — OUTFLOW of cash to lenders. NET + for the LBO. Required paydown shrinks debt and helps the buyout delever.</t>
         </is>
@@ -19236,7 +19284,7 @@
         <f>MAX(0,AI_Operating!H21-J163-J171)*Assumptions_Drivers!$C$18</f>
         <v/>
       </c>
-      <c r="L164" s="814" t="inlineStr">
+      <c r="L164" s="846" t="inlineStr">
         <is>
           <t>100% sweep (Drivers C18). Sweep $ = max(0, FCF − TLA mand − TLB mand); grows as FCF grows.</t>
         </is>
@@ -19257,7 +19305,7 @@
           <t>A 100% sweep means almost all leftover cash after the required 1% paydown goes to cut Term Loan A.</t>
         </is>
       </c>
-      <c r="P164" s="820" t="inlineStr">
+      <c r="P164" s="847" t="inlineStr">
         <is>
           <t>YES — OUTFLOW of cash (to pay debt). NET + for the LBO. Sweeping cash to Term Loan A is how the deal gets safer and equity value rises.</t>
         </is>
@@ -19366,7 +19414,7 @@
         <f>J164</f>
         <v/>
       </c>
-      <c r="L167" s="814" t="inlineStr">
+      <c r="L167" s="846" t="inlineStr">
         <is>
           <t>100% flat (Drivers C18). Sweep percent does not change; dollars swept grow with FCF.</t>
         </is>
@@ -19386,7 +19434,7 @@
           <t>100% means we model using essentially all excess free cash to repay debt.</t>
         </is>
       </c>
-      <c r="P167" s="820" t="inlineStr">
+      <c r="P167" s="847" t="inlineStr">
         <is>
           <t>YES — OUTFLOW rule. NET + for the LBO. A full sweep is credit-positive: cash goes to debt, not dividends or idle cash.</t>
         </is>
@@ -19463,7 +19511,7 @@
           <t>Term Loan B sits behind Term Loan A, so it gets the small 1% paydown while TLA takes the sweep.</t>
         </is>
       </c>
-      <c r="P170" s="820" t="inlineStr">
+      <c r="P170" s="845" t="inlineStr">
         <is>
           <t>YES — debt balance. NET + for equity as it declines, but less than TLA because most extra cash hits TLA first.</t>
         </is>
@@ -19505,7 +19553,7 @@
         <f>$D$30*Assumptions_Drivers!$C$17</f>
         <v/>
       </c>
-      <c r="L171" s="814" t="inlineStr">
+      <c r="L171" s="846" t="inlineStr">
         <is>
           <t>1%/yr of original TLB (Drivers C17). Flat $ amort (=0.01×$274.7m) each year.</t>
         </is>
@@ -19525,7 +19573,7 @@
           <t>Same 1% lender rule as Term Loan A, applied to the Term Loan B size.</t>
         </is>
       </c>
-      <c r="P171" s="820" t="inlineStr">
+      <c r="P171" s="847" t="inlineStr">
         <is>
           <t>YES — OUTFLOW of cash to TLB lenders. NET + for the LBO because it still reduces total debt each year.</t>
         </is>
@@ -19714,7 +19762,7 @@
           <t>Notes usually do not get paid down a little each year; they wait until the end unless refinanced.</t>
         </is>
       </c>
-      <c r="P178" s="819" t="inlineStr">
+      <c r="P178" s="845" t="inlineStr">
         <is>
           <t>YES — debt still outstanding. NET − vs TLA/TLB paydowns: Notes keep interest expense alive until exit/refi.</t>
         </is>
@@ -20354,7 +20402,7 @@
         <f>J162*Assumptions_Drivers!$C$27</f>
         <v/>
       </c>
-      <c r="L208" s="814" t="inlineStr">
+      <c r="L208" s="846" t="inlineStr">
         <is>
           <t>8.3% rate flat (Drivers C27=SOFR+4%). Interest $ falls as TLA balance falls from sweep.</t>
         </is>
@@ -20375,7 +20423,7 @@
           <t>Interest is the price of the loan. As Term Loan A shrinks, this interest bill should shrink too.</t>
         </is>
       </c>
-      <c r="P208" s="819" t="inlineStr">
+      <c r="P208" s="847" t="inlineStr">
         <is>
           <t>YES — OUTFLOW of cash (interest). NET − for the LBO each year it is paid, but falling TLA makes this outflow smaller over time (good).</t>
         </is>
@@ -20423,7 +20471,7 @@
         <f>J170*Assumptions_Drivers!$C$28</f>
         <v/>
       </c>
-      <c r="L209" s="814" t="inlineStr">
+      <c r="L209" s="846" t="inlineStr">
         <is>
           <t>9.3% rate flat (Drivers C28=SOFR+5%). Interest $ edges down only with 1% TLB amort.</t>
         </is>
@@ -20443,7 +20491,7 @@
           <t>Term Loan B costs more than Term Loan A because it is riskier for lenders.</t>
         </is>
       </c>
-      <c r="P209" s="819" t="inlineStr">
+      <c r="P209" s="847" t="inlineStr">
         <is>
           <t>YES — OUTFLOW of cash (interest). NET − for the LBO. Higher rate than TLA, and the balance falls only slowly.</t>
         </is>
@@ -20488,7 +20536,7 @@
         <f>J178*(Assumptions_Drivers!$C$14+0.035)</f>
         <v/>
       </c>
-      <c r="L210" s="814" t="inlineStr">
+      <c r="L210" s="846" t="inlineStr">
         <is>
           <t>7.8% rate flat (SOFR+3.5%). Interest $ stays roughly flat because Notes principal does not amortize.</t>
         </is>
@@ -20507,7 +20555,7 @@
           <t>Notes interest keeps showing up every year while the Notes balance stays outstanding.</t>
         </is>
       </c>
-      <c r="P210" s="819" t="inlineStr">
+      <c r="P210" s="847" t="inlineStr">
         <is>
           <t>YES — OUTFLOW of cash (interest). NET − for the LBO until exit or refinance clears the Notes.</t>
         </is>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -931,7 +931,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="850">
+  <cellXfs count="851">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3448,6 +3448,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="81" fillId="19" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="19" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -18924,7 +18927,7 @@
         </is>
       </c>
     </row>
-    <row r="153" ht="15" customHeight="1" s="409">
+    <row r="153" ht="70" customHeight="1" s="409">
       <c r="B153" s="593" t="inlineStr">
         <is>
           <t>Cash available (needed) to paydown (draw from) revolver</t>
@@ -18953,6 +18956,21 @@
         <f>J151+J152</f>
         <v/>
       </c>
+      <c r="L153" s="848" t="inlineStr">
+        <is>
+          <t>+5% sales-driven. Equals FCF when cash sits at minimum (F151=0). Y1 ≈ $123 → then split to mand + sweep.</t>
+        </is>
+      </c>
+      <c r="O153" s="850" t="inlineStr">
+        <is>
+          <t>F153 is the full $123 cash pool. F164 is only the leftover after mandatory TLA+TLB paydowns (~$7.3), swept to TLA.</t>
+        </is>
+      </c>
+      <c r="P153" s="849" t="inlineStr">
+        <is>
+          <t>YES — INFLOW pool ≈ $123 FCF (excess BOP $0). Split next: ~$4.6 TLA mand (163) + ~$2.7 TLB mand (171) + ~$115.7 TLA sweep (164).</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="13.8" customHeight="1" s="409"/>
     <row r="155" ht="15" customHeight="1" s="409">
@@ -19258,7 +19276,7 @@
         </is>
       </c>
     </row>
-    <row r="164" ht="88" customHeight="1" s="409">
+    <row r="164" ht="75" customHeight="1" s="409">
       <c r="B164" s="498" t="inlineStr">
         <is>
           <t>Cash sweep (paydown from excess cash flows)</t>
@@ -19307,7 +19325,7 @@
       </c>
       <c r="P164" s="847" t="inlineStr">
         <is>
-          <t>YES — OUTFLOW of cash (to pay debt). NET + for the LBO. Sweeping cash to Term Loan A is how the deal gets safer and equity value rises.</t>
+          <t>YES — OUTFLOW. From $123 FCF: $4.6→TLA 1% mand, $2.7→TLB 1% mand, $115.7→TLA cash sweep (164). Notes get $0 amort.</t>
         </is>
       </c>
       <c r="T164" s="842" t="inlineStr">
@@ -19717,7 +19735,7 @@
       </c>
       <c r="F177" s="510" t="n"/>
     </row>
-    <row r="178" ht="88" customHeight="1" s="409">
+    <row r="178" ht="75" customHeight="1" s="409">
       <c r="B178" s="498" t="inlineStr">
         <is>
           <t>Senior Note, BOP</t>
@@ -19762,9 +19780,9 @@
           <t>Notes usually do not get paid down a little each year; they wait until the end unless refinanced.</t>
         </is>
       </c>
-      <c r="P178" s="845" t="inlineStr">
-        <is>
-          <t>YES — debt still outstanding. NET − vs TLA/TLB paydowns: Notes keep interest expense alive until exit/refi.</t>
+      <c r="P178" s="847" t="inlineStr">
+        <is>
+          <t>YES — in Cash &amp; Debt (rows 177–181), $183.1m BOP. No amortization (bullet): $0 annual paydown; still pays interest (row 210). NET −.</t>
         </is>
       </c>
       <c r="T178" s="842" t="inlineStr">

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -60,7 +60,7 @@
     <numFmt numFmtId="194" formatCode="#,##0.0_);\(#,##0.0\);&quot;- _)&quot;;@_)"/>
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
   </numFmts>
-  <fonts count="83">
+  <fonts count="86">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -582,8 +582,23 @@
       <color rgb="009C0006"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="28">
+  <fills count="29">
     <fill>
       <patternFill/>
     </fill>
@@ -731,6 +746,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00006100"/>
       </patternFill>
     </fill>
   </fills>
@@ -931,7 +951,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="851">
+  <cellXfs count="854">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3452,6 +3472,15 @@
     </xf>
     <xf numFmtId="0" fontId="62" fillId="19" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -20665,11 +20694,21 @@
       <c r="H214" s="489" t="n"/>
       <c r="I214" s="489" t="n"/>
       <c r="J214" s="489" t="n"/>
-    </row>
-    <row r="215" ht="15" customHeight="1" s="409">
-      <c r="B215" s="408" t="inlineStr">
-        <is>
-          <t>EXIT VALUATION (GTM AI case — not BMC)</t>
+      <c r="L214" s="851" t="inlineStr">
+        <is>
+          <t>DEBT FIGURED OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="28" customHeight="1" s="409">
+      <c r="B215" s="852" t="inlineStr">
+        <is>
+          <t>EXIT VALUATION — DEBT FIGURED OUT (from Cash &amp; Debt Y5 EOP)</t>
+        </is>
+      </c>
+      <c r="L215" s="830" t="inlineStr">
+        <is>
+          <t>Net debt at exit pulls Cash &amp; Debt year-5 ending balances (revolver / TLA / TLB / Notes / cash). Equity value = Exit EV − net debt.</t>
         </is>
       </c>
     </row>
@@ -20775,9 +20814,9 @@
       </c>
     </row>
     <row r="221" ht="15" customHeight="1" s="409">
-      <c r="B221" s="616" t="inlineStr">
-        <is>
-          <t>Net debt:</t>
+      <c r="B221" s="853" t="inlineStr">
+        <is>
+          <t>Net debt: (DEBT FIGURED OUT ← Cash &amp; Debt Y5)</t>
         </is>
       </c>
       <c r="F221" s="510" t="n"/>
@@ -20788,20 +20827,25 @@
           <t>Revolver</t>
         </is>
       </c>
-      <c r="F222" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="G222" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="H222" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="I222" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="J222" s="517" t="n">
-        <v>0</v>
+      <c r="F222" s="733">
+        <f>$J$157</f>
+        <v/>
+      </c>
+      <c r="G222" s="733">
+        <f>$J$157</f>
+        <v/>
+      </c>
+      <c r="H222" s="733">
+        <f>$J$157</f>
+        <v/>
+      </c>
+      <c r="I222" s="733">
+        <f>$J$157</f>
+        <v/>
+      </c>
+      <c r="J222" s="733">
+        <f>$J$157</f>
+        <v/>
       </c>
     </row>
     <row r="223" ht="15" customHeight="1" s="409">
@@ -20810,20 +20854,25 @@
           <t>Term Loan A</t>
         </is>
       </c>
-      <c r="F223" s="517" t="n">
-        <v>6.36046720066304</v>
-      </c>
-      <c r="G223" s="517" t="n">
-        <v>6.36046720066304</v>
-      </c>
-      <c r="H223" s="517" t="n">
-        <v>6.36046720066304</v>
-      </c>
-      <c r="I223" s="517" t="n">
-        <v>6.36046720066304</v>
-      </c>
-      <c r="J223" s="517" t="n">
-        <v>6.36046720066304</v>
+      <c r="F223" s="733">
+        <f>$J$165</f>
+        <v/>
+      </c>
+      <c r="G223" s="733">
+        <f>$J$165</f>
+        <v/>
+      </c>
+      <c r="H223" s="733">
+        <f>$J$165</f>
+        <v/>
+      </c>
+      <c r="I223" s="733">
+        <f>$J$165</f>
+        <v/>
+      </c>
+      <c r="J223" s="733">
+        <f>$J$165</f>
+        <v/>
       </c>
     </row>
     <row r="224" ht="15" customHeight="1" s="409">
@@ -20832,20 +20881,25 @@
           <t>Term Loan B</t>
         </is>
       </c>
-      <c r="F224" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="H224" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="I224" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="J224" s="517" t="n">
-        <v>0</v>
+      <c r="F224" s="733">
+        <f>$J$173</f>
+        <v/>
+      </c>
+      <c r="G224" s="733">
+        <f>$J$173</f>
+        <v/>
+      </c>
+      <c r="H224" s="733">
+        <f>$J$173</f>
+        <v/>
+      </c>
+      <c r="I224" s="733">
+        <f>$J$173</f>
+        <v/>
+      </c>
+      <c r="J224" s="733">
+        <f>$J$173</f>
+        <v/>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1" s="409">
@@ -20855,20 +20909,25 @@
         </is>
       </c>
       <c r="E225" s="555" t="n"/>
-      <c r="F225" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="G225" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="H225" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="I225" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="J225" s="517" t="n">
-        <v>0</v>
+      <c r="F225" s="733">
+        <f>$J$180</f>
+        <v/>
+      </c>
+      <c r="G225" s="733">
+        <f>$J$180</f>
+        <v/>
+      </c>
+      <c r="H225" s="733">
+        <f>$J$180</f>
+        <v/>
+      </c>
+      <c r="I225" s="733">
+        <f>$J$180</f>
+        <v/>
+      </c>
+      <c r="J225" s="733">
+        <f>$J$180</f>
+        <v/>
       </c>
     </row>
     <row r="226" ht="15" customHeight="1" s="409">
@@ -20878,19 +20937,19 @@
         </is>
       </c>
       <c r="E226" s="617" t="n"/>
-      <c r="F226" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="G226" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="H226" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="I226" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="J226" s="517" t="n">
+      <c r="F226" s="733" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" s="733" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" s="733" t="n">
+        <v>0</v>
+      </c>
+      <c r="I226" s="733" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" s="733" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20901,19 +20960,19 @@
         </is>
       </c>
       <c r="E227" s="617" t="n"/>
-      <c r="F227" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="G227" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="H227" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="I227" s="517" t="n">
-        <v>0</v>
-      </c>
-      <c r="J227" s="517" t="n">
+      <c r="F227" s="733" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" s="733" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" s="733" t="n">
+        <v>0</v>
+      </c>
+      <c r="I227" s="733" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" s="733" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20923,20 +20982,25 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="F228" s="517" t="n">
-        <v>-50</v>
-      </c>
-      <c r="G228" s="517" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H228" s="517" t="n">
-        <v>-50</v>
-      </c>
-      <c r="I228" s="517" t="n">
-        <v>-50</v>
-      </c>
-      <c r="J228" s="517" t="n">
-        <v>-50</v>
+      <c r="F228" s="733">
+        <f>-$J$144</f>
+        <v/>
+      </c>
+      <c r="G228" s="733">
+        <f>-$J$144</f>
+        <v/>
+      </c>
+      <c r="H228" s="733">
+        <f>-$J$144</f>
+        <v/>
+      </c>
+      <c r="I228" s="733">
+        <f>-$J$144</f>
+        <v/>
+      </c>
+      <c r="J228" s="733">
+        <f>-$J$144</f>
+        <v/>
       </c>
     </row>
     <row r="229" ht="15" customHeight="1" s="409">
@@ -24405,7 +24469,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="F302:J302"/>
     <mergeCell ref="G321:I321"/>
     <mergeCell ref="D291:J291"/>
@@ -24413,7 +24477,9 @@
     <mergeCell ref="D300:J300"/>
     <mergeCell ref="Q141:S141"/>
     <mergeCell ref="D310:J310"/>
+    <mergeCell ref="L215:N216"/>
     <mergeCell ref="F292:J292"/>
+    <mergeCell ref="L214:N214"/>
     <mergeCell ref="F311:J311"/>
     <mergeCell ref="F216:J216"/>
     <mergeCell ref="M138:P138"/>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -60,7 +60,7 @@
     <numFmt numFmtId="194" formatCode="#,##0.0_);\(#,##0.0\);&quot;- _)&quot;;@_)"/>
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
   </numFmts>
-  <fonts count="86">
+  <fonts count="89">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -597,6 +597,20 @@
       <color rgb="00006100"/>
       <sz val="11"/>
     </font>
+    <font>
+      <color rgb="001F4E79"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="29">
     <fill>
@@ -951,7 +965,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="854">
+  <cellXfs count="857">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3481,6 +3495,15 @@
     </xf>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -21858,11 +21881,16 @@
       <c r="J258" s="520" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="259" ht="15" customHeight="1" s="409">
-      <c r="B259" s="561" t="inlineStr">
-        <is>
-          <t>Sponsor's Equity at exit EBITDA multiple of:</t>
+      <c r="L258" s="854" t="inlineStr">
+        <is>
+          <t>IRR ≠ exit multiple. 13x = sale price vs EBITDA. ~17% = annualized equity return. This 6–8x block is leftover template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="20" customHeight="1" s="409">
+      <c r="B259" s="855" t="inlineStr">
+        <is>
+          <t>Sponsor's Equity at exit EBITDA multiple of: (STALE 6–8x TEMPLATE — not live GTM IRR)</t>
         </is>
       </c>
       <c r="C259" s="597" t="n"/>
@@ -21873,6 +21901,11 @@
       <c r="H259" s="582" t="n"/>
       <c r="I259" s="582" t="n"/>
       <c r="J259" s="638" t="n"/>
+      <c r="L259" s="856" t="inlineStr">
+        <is>
+          <t>HOW TO READ THIS vs LIVE IRR: Exit multiple (e.g. 12.9x) is EV ÷ EBITDA at sale — a price tag, not a %. IRR (~17% AI case on Strategy_Summary) is the yearly equity return over 5 years from MOIC ≈ 2.2x. You can clear ~17% IRR at ~13x exit if you buy at a fair entry, grow EBITDA, and sweep debt. WARNING: The 6.3x–8.3x grid below is OLD TEMPLATE sensitivity (not the live GTM 10.9x–14.9x / Drivers 12.9x case). Do not compare those low multiples to the 17% IRR as if they were the same scenario.</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="15" customHeight="1" s="409">
       <c r="B260" s="635" t="n">
@@ -24469,11 +24502,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="F302:J302"/>
     <mergeCell ref="G321:I321"/>
     <mergeCell ref="D291:J291"/>
+    <mergeCell ref="L259:P264"/>
     <mergeCell ref="D290:J290"/>
+    <mergeCell ref="L258:P258"/>
     <mergeCell ref="D300:J300"/>
     <mergeCell ref="Q141:S141"/>
     <mergeCell ref="D310:J310"/>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -60,7 +60,7 @@
     <numFmt numFmtId="194" formatCode="#,##0.0_);\(#,##0.0\);&quot;- _)&quot;;@_)"/>
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
   </numFmts>
-  <fonts count="89">
+  <fonts count="92">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -611,8 +611,22 @@
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="29">
+  <fills count="30">
     <fill>
       <patternFill/>
     </fill>
@@ -765,6 +779,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00006100"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D08E"/>
       </patternFill>
     </fill>
   </fills>
@@ -965,7 +984,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="857">
+  <cellXfs count="878">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3504,6 +3523,69 @@
     </xf>
     <xf numFmtId="0" fontId="86" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="78" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="78" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="16" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="16" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="166" fontId="34" fillId="16" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="175" fontId="34" fillId="16" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="166" fontId="36" fillId="16" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="16" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="29" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="29" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="29" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="29" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="29" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="166" fontId="36" fillId="29" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -21373,9 +21455,9 @@
       </c>
     </row>
     <row r="241" ht="15" customHeight="1" s="409">
-      <c r="B241" s="561" t="inlineStr">
-        <is>
-          <t>Sub Note at exit EBITDA multiple of:</t>
+      <c r="B241" s="857" t="inlineStr">
+        <is>
+          <t>Sub Note at exit EBITDA multiple of: (N/A — no Sub Note in GTM stack)</t>
         </is>
       </c>
       <c r="C241" s="604" t="n"/>
@@ -21388,164 +21470,104 @@
       <c r="J241" s="556" t="n"/>
     </row>
     <row r="242" ht="15" customHeight="1" s="409">
-      <c r="B242" s="635" t="n">
-        <v>6.3</v>
+      <c r="B242" s="635" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="C242" s="633" t="inlineStr">
         <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="D242" s="634" t="n">
-        <v>0</v>
-      </c>
-      <c r="E242" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="F242" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G242" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H242" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I242" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J242" s="520" t="n">
-        <v>0</v>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D242" s="634" t="n"/>
+      <c r="E242" s="515" t="n"/>
+      <c r="F242" s="515" t="n"/>
+      <c r="G242" s="515" t="n"/>
+      <c r="H242" s="515" t="n"/>
+      <c r="I242" s="515" t="n"/>
+      <c r="J242" s="520" t="n"/>
     </row>
     <row r="243" ht="15" customHeight="1" s="409">
-      <c r="B243" s="635" t="n">
-        <v>6.8</v>
+      <c r="B243" s="635" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="C243" s="633" t="inlineStr">
         <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="D243" s="634" t="n">
-        <v>0</v>
-      </c>
-      <c r="E243" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="F243" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G243" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H243" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I243" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J243" s="520" t="n">
-        <v>0</v>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D243" s="634" t="n"/>
+      <c r="E243" s="515" t="n"/>
+      <c r="F243" s="515" t="n"/>
+      <c r="G243" s="515" t="n"/>
+      <c r="H243" s="515" t="n"/>
+      <c r="I243" s="515" t="n"/>
+      <c r="J243" s="520" t="n"/>
     </row>
     <row r="244" ht="15" customHeight="1" s="409">
-      <c r="B244" s="635" t="n">
-        <v>7.3</v>
+      <c r="B244" s="635" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="C244" s="633" t="inlineStr">
         <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="D244" s="634" t="n">
-        <v>0</v>
-      </c>
-      <c r="E244" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="F244" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G244" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H244" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I244" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J244" s="520" t="n">
-        <v>0</v>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D244" s="634" t="n"/>
+      <c r="E244" s="515" t="n"/>
+      <c r="F244" s="515" t="n"/>
+      <c r="G244" s="515" t="n"/>
+      <c r="H244" s="515" t="n"/>
+      <c r="I244" s="515" t="n"/>
+      <c r="J244" s="520" t="n"/>
     </row>
     <row r="245" ht="15" customHeight="1" s="409">
-      <c r="B245" s="635" t="n">
-        <v>7.8</v>
+      <c r="B245" s="635" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="C245" s="633" t="inlineStr">
         <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="D245" s="634" t="n">
-        <v>0</v>
-      </c>
-      <c r="E245" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="F245" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G245" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H245" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I245" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J245" s="520" t="n">
-        <v>0</v>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D245" s="634" t="n"/>
+      <c r="E245" s="515" t="n"/>
+      <c r="F245" s="515" t="n"/>
+      <c r="G245" s="515" t="n"/>
+      <c r="H245" s="515" t="n"/>
+      <c r="I245" s="515" t="n"/>
+      <c r="J245" s="520" t="n"/>
     </row>
     <row r="246" ht="15" customHeight="1" s="409">
-      <c r="B246" s="635" t="n">
-        <v>8.300000000000001</v>
+      <c r="B246" s="635" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="C246" s="633" t="inlineStr">
         <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="D246" s="634" t="n">
-        <v>0</v>
-      </c>
-      <c r="E246" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="F246" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G246" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H246" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I246" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J246" s="520" t="n">
-        <v>0</v>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D246" s="634" t="n"/>
+      <c r="E246" s="515" t="n"/>
+      <c r="F246" s="515" t="n"/>
+      <c r="G246" s="515" t="n"/>
+      <c r="H246" s="515" t="n"/>
+      <c r="I246" s="515" t="n"/>
+      <c r="J246" s="520" t="n"/>
     </row>
     <row r="247" ht="15" customHeight="1" s="409">
-      <c r="B247" s="561" t="inlineStr">
-        <is>
-          <t>Preferred Stock at exit EBITDA multiple of:</t>
+      <c r="B247" s="857" t="inlineStr">
+        <is>
+          <t>Preferred Stock at exit EBITDA multiple of: (N/A — no Pref in GTM stack)</t>
         </is>
       </c>
       <c r="C247" s="604" t="n"/>
@@ -21558,164 +21580,104 @@
       <c r="J247" s="556" t="n"/>
     </row>
     <row r="248" ht="15" customHeight="1" s="409">
-      <c r="B248" s="635" t="n">
-        <v>6.3</v>
+      <c r="B248" s="635" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="C248" s="633" t="inlineStr">
         <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="D248" s="634" t="n">
-        <v>0</v>
-      </c>
-      <c r="E248" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="F248" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G248" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H248" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I248" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J248" s="520" t="n">
-        <v>0</v>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D248" s="634" t="n"/>
+      <c r="E248" s="515" t="n"/>
+      <c r="F248" s="515" t="n"/>
+      <c r="G248" s="515" t="n"/>
+      <c r="H248" s="515" t="n"/>
+      <c r="I248" s="515" t="n"/>
+      <c r="J248" s="520" t="n"/>
     </row>
     <row r="249" ht="15" customHeight="1" s="409">
-      <c r="B249" s="635" t="n">
-        <v>6.8</v>
+      <c r="B249" s="635" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="C249" s="633" t="inlineStr">
         <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="D249" s="634" t="n">
-        <v>0</v>
-      </c>
-      <c r="E249" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="F249" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G249" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H249" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I249" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J249" s="520" t="n">
-        <v>0</v>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D249" s="634" t="n"/>
+      <c r="E249" s="515" t="n"/>
+      <c r="F249" s="515" t="n"/>
+      <c r="G249" s="515" t="n"/>
+      <c r="H249" s="515" t="n"/>
+      <c r="I249" s="515" t="n"/>
+      <c r="J249" s="520" t="n"/>
     </row>
     <row r="250" ht="15" customHeight="1" s="409">
-      <c r="B250" s="635" t="n">
-        <v>7.3</v>
+      <c r="B250" s="635" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="C250" s="633" t="inlineStr">
         <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="D250" s="634" t="n">
-        <v>0</v>
-      </c>
-      <c r="E250" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="F250" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H250" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I250" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J250" s="520" t="n">
-        <v>0</v>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D250" s="634" t="n"/>
+      <c r="E250" s="515" t="n"/>
+      <c r="F250" s="515" t="n"/>
+      <c r="G250" s="515" t="n"/>
+      <c r="H250" s="515" t="n"/>
+      <c r="I250" s="515" t="n"/>
+      <c r="J250" s="520" t="n"/>
     </row>
     <row r="251" ht="15" customHeight="1" s="409">
-      <c r="B251" s="635" t="n">
-        <v>7.8</v>
+      <c r="B251" s="635" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="C251" s="633" t="inlineStr">
         <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="D251" s="634" t="n">
-        <v>0</v>
-      </c>
-      <c r="E251" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="F251" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G251" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H251" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I251" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J251" s="520" t="n">
-        <v>0</v>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D251" s="634" t="n"/>
+      <c r="E251" s="515" t="n"/>
+      <c r="F251" s="515" t="n"/>
+      <c r="G251" s="515" t="n"/>
+      <c r="H251" s="515" t="n"/>
+      <c r="I251" s="515" t="n"/>
+      <c r="J251" s="520" t="n"/>
     </row>
     <row r="252" ht="15" customHeight="1" s="409">
-      <c r="B252" s="635" t="n">
-        <v>8.300000000000001</v>
+      <c r="B252" s="635" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="C252" s="633" t="inlineStr">
         <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="D252" s="634" t="n">
-        <v>0</v>
-      </c>
-      <c r="E252" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="F252" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H252" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I252" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J252" s="520" t="n">
-        <v>0</v>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D252" s="634" t="n"/>
+      <c r="E252" s="515" t="n"/>
+      <c r="F252" s="515" t="n"/>
+      <c r="G252" s="515" t="n"/>
+      <c r="H252" s="515" t="n"/>
+      <c r="I252" s="515" t="n"/>
+      <c r="J252" s="520" t="n"/>
     </row>
     <row r="253" ht="15" customHeight="1" s="409">
-      <c r="B253" s="561" t="inlineStr">
-        <is>
-          <t>Management Equity at exit EBITDA multiple of:</t>
+      <c r="B253" s="857" t="inlineStr">
+        <is>
+          <t>Management Equity at exit EBITDA multiple of: (N/A — 0% mgmt equity in GTM case)</t>
         </is>
       </c>
       <c r="C253" s="636" t="n"/>
@@ -21728,334 +21690,332 @@
       <c r="J253" s="556" t="n"/>
     </row>
     <row r="254" ht="15" customHeight="1" s="409">
-      <c r="B254" s="635" t="n">
-        <v>6.3</v>
+      <c r="B254" s="635" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="C254" s="633" t="inlineStr">
         <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="D254" s="634" t="n">
-        <v>0</v>
-      </c>
-      <c r="E254" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="F254" s="553" t="n">
-        <v>0</v>
-      </c>
-      <c r="G254" s="553" t="n">
-        <v>0</v>
-      </c>
-      <c r="H254" s="553" t="n">
-        <v>0</v>
-      </c>
-      <c r="I254" s="553" t="n">
-        <v>0</v>
-      </c>
-      <c r="J254" s="520" t="n">
-        <v>0</v>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D254" s="634" t="n"/>
+      <c r="E254" s="515" t="n"/>
+      <c r="F254" s="553" t="n"/>
+      <c r="G254" s="553" t="n"/>
+      <c r="H254" s="553" t="n"/>
+      <c r="I254" s="553" t="n"/>
+      <c r="J254" s="520" t="n"/>
     </row>
     <row r="255" ht="15" customHeight="1" s="409">
-      <c r="B255" s="635" t="n">
-        <v>6.8</v>
+      <c r="B255" s="635" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="C255" s="633" t="inlineStr">
         <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="D255" s="634" t="n">
-        <v>0</v>
-      </c>
-      <c r="E255" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="F255" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G255" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H255" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I255" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J255" s="520" t="n">
-        <v>0</v>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D255" s="634" t="n"/>
+      <c r="E255" s="515" t="n"/>
+      <c r="F255" s="515" t="n"/>
+      <c r="G255" s="515" t="n"/>
+      <c r="H255" s="515" t="n"/>
+      <c r="I255" s="515" t="n"/>
+      <c r="J255" s="520" t="n"/>
     </row>
     <row r="256" ht="15" customHeight="1" s="409">
-      <c r="B256" s="635" t="n">
-        <v>7.3</v>
+      <c r="B256" s="635" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="C256" s="633" t="inlineStr">
         <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="D256" s="634" t="n">
-        <v>0</v>
-      </c>
-      <c r="E256" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="F256" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G256" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H256" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I256" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J256" s="520" t="n">
-        <v>0</v>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D256" s="634" t="n"/>
+      <c r="E256" s="515" t="n"/>
+      <c r="F256" s="515" t="n"/>
+      <c r="G256" s="515" t="n"/>
+      <c r="H256" s="515" t="n"/>
+      <c r="I256" s="515" t="n"/>
+      <c r="J256" s="520" t="n"/>
     </row>
     <row r="257" ht="15" customHeight="1" s="409">
-      <c r="B257" s="635" t="n">
-        <v>7.8</v>
+      <c r="B257" s="635" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="C257" s="633" t="inlineStr">
         <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="D257" s="634" t="n">
-        <v>0</v>
-      </c>
-      <c r="E257" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="F257" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G257" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H257" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I257" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J257" s="520" t="n">
-        <v>0</v>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D257" s="634" t="n"/>
+      <c r="E257" s="515" t="n"/>
+      <c r="F257" s="515" t="n"/>
+      <c r="G257" s="515" t="n"/>
+      <c r="H257" s="515" t="n"/>
+      <c r="I257" s="515" t="n"/>
+      <c r="J257" s="520" t="n"/>
     </row>
     <row r="258" ht="15" customHeight="1" s="409">
-      <c r="B258" s="635" t="n">
-        <v>8.300000000000001</v>
+      <c r="B258" s="635" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="C258" s="633" t="inlineStr">
         <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="D258" s="634" t="n">
-        <v>0</v>
-      </c>
-      <c r="E258" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="F258" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G258" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H258" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I258" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J258" s="520" t="n">
-        <v>0</v>
-      </c>
-      <c r="L258" s="854" t="inlineStr">
-        <is>
-          <t>IRR ≠ exit multiple. 13x = sale price vs EBITDA. ~17% = annualized equity return. This 6–8x block is leftover template.</t>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D258" s="634" t="n"/>
+      <c r="E258" s="515" t="n"/>
+      <c r="F258" s="515" t="n"/>
+      <c r="G258" s="515" t="n"/>
+      <c r="H258" s="515" t="n"/>
+      <c r="I258" s="515" t="n"/>
+      <c r="J258" s="520" t="n"/>
+      <c r="L258" s="858" t="inlineStr">
+        <is>
+          <t>FIXED: Sponsor sensitivity now uses GTM exit multiples 10.9x / 11.9x / 12.9x / 13.9x / 14.9x (same as EXIT VALUATION). Old 6–8x block was leftover template and was wrong for ZoomInfo.</t>
         </is>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1" s="409">
-      <c r="B259" s="855" t="inlineStr">
-        <is>
-          <t>Sponsor's Equity at exit EBITDA multiple of: (STALE 6–8x TEMPLATE — not live GTM IRR)</t>
-        </is>
-      </c>
-      <c r="C259" s="597" t="n"/>
-      <c r="D259" s="637" t="n"/>
-      <c r="E259" s="510" t="n"/>
-      <c r="F259" s="582" t="n"/>
-      <c r="G259" s="582" t="n"/>
-      <c r="H259" s="582" t="n"/>
-      <c r="I259" s="582" t="n"/>
-      <c r="J259" s="638" t="n"/>
-      <c r="L259" s="856" t="inlineStr">
-        <is>
-          <t>HOW TO READ THIS vs LIVE IRR: Exit multiple (e.g. 12.9x) is EV ÷ EBITDA at sale — a price tag, not a %. IRR (~17% AI case on Strategy_Summary) is the yearly equity return over 5 years from MOIC ≈ 2.2x. You can clear ~17% IRR at ~13x exit if you buy at a fair entry, grow EBITDA, and sweep debt. WARNING: The 6.3x–8.3x grid below is OLD TEMPLATE sensitivity (not the live GTM 10.9x–14.9x / Drivers 12.9x case). Do not compare those low multiples to the 17% IRR as if they were the same scenario.</t>
+      <c r="B259" s="859" t="inlineStr">
+        <is>
+          <t>Sponsor's Equity at exit EBITDA multiple of: (GTM live — same band as EXIT VALUATION F218:J218)</t>
+        </is>
+      </c>
+      <c r="C259" s="859" t="inlineStr">
+        <is>
+          <t>MOIC</t>
+        </is>
+      </c>
+      <c r="D259" s="860" t="inlineStr">
+        <is>
+          <t>IRR (5-yr)</t>
+        </is>
+      </c>
+      <c r="E259" s="861" t="inlineStr">
+        <is>
+          <t>Sponsor equity in (t0)</t>
+        </is>
+      </c>
+      <c r="F259" s="861" t="inlineStr">
+        <is>
+          <t>Exit EV</t>
+        </is>
+      </c>
+      <c r="G259" s="861" t="inlineStr">
+        <is>
+          <t>Net debt (Y5)</t>
+        </is>
+      </c>
+      <c r="H259" s="861" t="inlineStr">
+        <is>
+          <t>Exit equity</t>
+        </is>
+      </c>
+      <c r="I259" s="861" t="inlineStr"/>
+      <c r="J259" s="861" t="inlineStr">
+        <is>
+          <t>Exit equity (check)</t>
+        </is>
+      </c>
+      <c r="L259" s="862" t="inlineStr">
+        <is>
+          <t>Math per row: Exit EV = multiple × AI Y5 EBITDA; Net debt = Cash&amp;Debt Y5 (TLA+TLB+Notes+Revolver−Cash); Exit equity = EV − net debt; MOIC = Exit equity ÷ sponsor equity (D35); IRR ≈ MOIC^(1/5)−1 over 5 years. IRR is a % return; multiple is a price tag — different units.</t>
         </is>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1" s="409">
-      <c r="B260" s="635" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="C260" s="633" t="n">
-        <v>3.43053056443323</v>
-      </c>
-      <c r="D260" s="634" t="n">
-        <v>0.279594187366849</v>
-      </c>
-      <c r="E260" s="515" t="n">
-        <v>-1660.27794</v>
-      </c>
-      <c r="F260" s="553" t="n">
-        <v>0</v>
-      </c>
-      <c r="G260" s="553" t="n">
-        <v>0</v>
-      </c>
-      <c r="H260" s="553" t="n">
-        <v>0</v>
-      </c>
-      <c r="I260" s="553" t="n">
-        <v>0</v>
-      </c>
-      <c r="J260" s="520" t="n">
-        <v>5695.63421862424</v>
+      <c r="B260" s="863">
+        <f>F218</f>
+        <v/>
+      </c>
+      <c r="C260" s="864">
+        <f>IF($D$35=0,"NM",H260/$D$35)</f>
+        <v/>
+      </c>
+      <c r="D260" s="865">
+        <f>IF(OR(C260="NM",C260&lt;=0),"NM",C260^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="E260" s="866">
+        <f>-$D$35</f>
+        <v/>
+      </c>
+      <c r="F260" s="867">
+        <f>B260*AI_Operating!$H$13</f>
+        <v/>
+      </c>
+      <c r="G260" s="867">
+        <f>$J$157+$J$165+$J$173+$J$180-$J$144</f>
+        <v/>
+      </c>
+      <c r="H260" s="867">
+        <f>F260-G260</f>
+        <v/>
+      </c>
+      <c r="I260" s="868" t="n"/>
+      <c r="J260" s="869">
+        <f>H260</f>
+        <v/>
       </c>
     </row>
     <row r="261" ht="15" customHeight="1" s="409">
-      <c r="B261" s="635" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="C261" s="633" t="n">
-        <v>3.80000909855217</v>
-      </c>
-      <c r="D261" s="634" t="n">
-        <v>0.306041350379885</v>
-      </c>
-      <c r="E261" s="515" t="n">
-        <v>-1660.27794</v>
-      </c>
-      <c r="F261" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G261" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H261" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I261" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J261" s="520" t="n">
-        <v>6309.07127812545</v>
+      <c r="B261" s="863">
+        <f>G218</f>
+        <v/>
+      </c>
+      <c r="C261" s="864">
+        <f>IF($D$35=0,"NM",H261/$D$35)</f>
+        <v/>
+      </c>
+      <c r="D261" s="865">
+        <f>IF(OR(C261="NM",C261&lt;=0),"NM",C261^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="E261" s="866">
+        <f>-$D$35</f>
+        <v/>
+      </c>
+      <c r="F261" s="866">
+        <f>B261*AI_Operating!$H$13</f>
+        <v/>
+      </c>
+      <c r="G261" s="866">
+        <f>$J$157+$J$165+$J$173+$J$180-$J$144</f>
+        <v/>
+      </c>
+      <c r="H261" s="866">
+        <f>F261-G261</f>
+        <v/>
+      </c>
+      <c r="I261" s="870" t="n"/>
+      <c r="J261" s="869">
+        <f>H261</f>
+        <v/>
       </c>
     </row>
     <row r="262" ht="15" customHeight="1" s="409">
-      <c r="B262" s="635" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="C262" s="633" t="n">
-        <v>4.16948763267112</v>
-      </c>
-      <c r="D262" s="634" t="n">
-        <v>0.330505082844487</v>
-      </c>
-      <c r="E262" s="515" t="n">
-        <v>-1660.27794</v>
-      </c>
-      <c r="F262" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G262" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H262" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I262" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J262" s="520" t="n">
-        <v>6922.50833762667</v>
+      <c r="B262" s="871">
+        <f>H218</f>
+        <v/>
+      </c>
+      <c r="C262" s="872">
+        <f>IF($D$35=0,"NM",H262/$D$35)</f>
+        <v/>
+      </c>
+      <c r="D262" s="873">
+        <f>IF(OR(C262="NM",C262&lt;=0),"NM",C262^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="E262" s="874">
+        <f>-$D$35</f>
+        <v/>
+      </c>
+      <c r="F262" s="874">
+        <f>B262*AI_Operating!$H$13</f>
+        <v/>
+      </c>
+      <c r="G262" s="874">
+        <f>$J$157+$J$165+$J$173+$J$180-$J$144</f>
+        <v/>
+      </c>
+      <c r="H262" s="874">
+        <f>F262-G262</f>
+        <v/>
+      </c>
+      <c r="I262" s="875" t="n"/>
+      <c r="J262" s="876">
+        <f>H262</f>
+        <v/>
       </c>
     </row>
     <row r="263" ht="15" customHeight="1" s="409">
-      <c r="B263" s="635" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="C263" s="633" t="n">
-        <v>4.53896616679006</v>
-      </c>
-      <c r="D263" s="634" t="n">
-        <v>0.353291609310027</v>
-      </c>
-      <c r="E263" s="515" t="n">
-        <v>-1660.27794</v>
-      </c>
-      <c r="F263" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G263" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H263" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I263" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J263" s="520" t="n">
-        <v>7535.94539712789</v>
+      <c r="B263" s="863">
+        <f>I218</f>
+        <v/>
+      </c>
+      <c r="C263" s="864">
+        <f>IF($D$35=0,"NM",H263/$D$35)</f>
+        <v/>
+      </c>
+      <c r="D263" s="865">
+        <f>IF(OR(C263="NM",C263&lt;=0),"NM",C263^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="E263" s="866">
+        <f>-$D$35</f>
+        <v/>
+      </c>
+      <c r="F263" s="866">
+        <f>B263*AI_Operating!$H$13</f>
+        <v/>
+      </c>
+      <c r="G263" s="866">
+        <f>$J$157+$J$165+$J$173+$J$180-$J$144</f>
+        <v/>
+      </c>
+      <c r="H263" s="866">
+        <f>F263-G263</f>
+        <v/>
+      </c>
+      <c r="I263" s="870" t="n"/>
+      <c r="J263" s="869">
+        <f>H263</f>
+        <v/>
       </c>
     </row>
     <row r="264" ht="15" customHeight="1" s="409">
-      <c r="B264" s="635" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="C264" s="633" t="n">
-        <v>4.908444700909</v>
-      </c>
-      <c r="D264" s="634" t="n">
-        <v>0.374639377788437</v>
-      </c>
-      <c r="E264" s="515" t="n">
-        <v>-1660.27794</v>
-      </c>
-      <c r="F264" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G264" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H264" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I264" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J264" s="520" t="n">
-        <v>8149.38245662911</v>
+      <c r="B264" s="863">
+        <f>J218</f>
+        <v/>
+      </c>
+      <c r="C264" s="864">
+        <f>IF($D$35=0,"NM",H264/$D$35)</f>
+        <v/>
+      </c>
+      <c r="D264" s="865">
+        <f>IF(OR(C264="NM",C264&lt;=0),"NM",C264^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="E264" s="866">
+        <f>-$D$35</f>
+        <v/>
+      </c>
+      <c r="F264" s="866">
+        <f>B264*AI_Operating!$H$13</f>
+        <v/>
+      </c>
+      <c r="G264" s="866">
+        <f>$J$157+$J$165+$J$173+$J$180-$J$144</f>
+        <v/>
+      </c>
+      <c r="H264" s="866">
+        <f>F264-G264</f>
+        <v/>
+      </c>
+      <c r="I264" s="870" t="n"/>
+      <c r="J264" s="869">
+        <f>H264</f>
+        <v/>
       </c>
     </row>
     <row r="266" ht="15" customHeight="1" s="409">
-      <c r="B266" s="497" t="inlineStr">
-        <is>
-          <t>SUMMARY @ 13.0x EXIT — AI vs Base (see Strategy_Summary)</t>
+      <c r="B266" s="877" t="inlineStr">
+        <is>
+          <t>SUMMARY @ Drivers 12.9x EXIT — AI vs Base (see Strategy_Summary). Financing $ below still partly template — sponsor IRR row is live.</t>
         </is>
       </c>
       <c r="C266" s="489" t="n"/>
@@ -24503,10 +24463,10 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="F302:J302"/>
+    <mergeCell ref="L259:P264"/>
     <mergeCell ref="G321:I321"/>
     <mergeCell ref="D291:J291"/>
-    <mergeCell ref="L259:P264"/>
+    <mergeCell ref="F302:J302"/>
     <mergeCell ref="D290:J290"/>
     <mergeCell ref="L258:P258"/>
     <mergeCell ref="D300:J300"/>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -60,7 +60,7 @@
     <numFmt numFmtId="194" formatCode="#,##0.0_);\(#,##0.0\);&quot;- _)&quot;;@_)"/>
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
   </numFmts>
-  <fonts count="92">
+  <fonts count="93">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -625,6 +625,11 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="30">
     <fill>
@@ -984,7 +989,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="878">
+  <cellXfs count="882">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3586,6 +3591,18 @@
     </xf>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="174" fontId="91" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="92" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="79" fillId="16" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -14372,6 +14389,7 @@
     <col width="44.18" customWidth="1" style="408" min="2" max="2"/>
     <col width="15.73" customWidth="1" style="408" min="3" max="3"/>
     <col width="48" customWidth="1" style="408" min="5" max="5"/>
+    <col width="42" customWidth="1" style="409" min="9" max="9"/>
     <col width="12.82" customWidth="1" style="408" min="11" max="11"/>
     <col width="40" customWidth="1" style="408" min="12" max="12"/>
     <col width="42" customWidth="1" style="408" min="13" max="13"/>
@@ -21805,9 +21823,9 @@
           <t>IRR (5-yr)</t>
         </is>
       </c>
-      <c r="E259" s="861" t="inlineStr">
-        <is>
-          <t>Sponsor equity in (t0)</t>
+      <c r="E259" s="878" t="inlineStr">
+        <is>
+          <t>Sponsor equity in (t0) — cash OUT to fund buy</t>
         </is>
       </c>
       <c r="F259" s="861" t="inlineStr">
@@ -21825,19 +21843,23 @@
           <t>Exit equity</t>
         </is>
       </c>
-      <c r="I259" s="861" t="inlineStr"/>
+      <c r="I259" s="879" t="inlineStr">
+        <is>
+          <t>Why E260 negative?</t>
+        </is>
+      </c>
       <c r="J259" s="861" t="inlineStr">
         <is>
           <t>Exit equity (check)</t>
         </is>
       </c>
-      <c r="L259" s="862" t="inlineStr">
-        <is>
-          <t>Math per row: Exit EV = multiple × AI Y5 EBITDA; Net debt = Cash&amp;Debt Y5 (TLA+TLB+Notes+Revolver−Cash); Exit equity = EV − net debt; MOIC = Exit equity ÷ sponsor equity (D35); IRR ≈ MOIC^(1/5)−1 over 5 years. IRR is a % return; multiple is a price tag — different units.</t>
-        </is>
-      </c>
-    </row>
-    <row r="260" ht="15" customHeight="1" s="409">
+      <c r="L259" s="880" t="inlineStr">
+        <is>
+          <t>Math per row: Exit EV = multiple × AI Y5 EBITDA; Net debt = Cash&amp;Debt Y5 (TLA+TLB+Notes+Revolver−Cash); Exit equity = EV − net debt; MOIC = Exit equity ÷ sponsor equity (D35); IRR ≈ MOIC^(1/5)−1 over 5 years. IRR is a % return; multiple is a price tag — different units. | E260=−D35: money going out at close to help pay sellers (sponsor equity portion of purchase). Not exit sale — exit proceeds are H260.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="52" customHeight="1" s="409">
       <c r="B260" s="863">
         <f>F218</f>
         <v/>
@@ -21866,7 +21888,11 @@
         <f>F260-G260</f>
         <v/>
       </c>
-      <c r="I260" s="868" t="n"/>
+      <c r="I260" s="881" t="inlineStr">
+        <is>
+          <t>E260 negative = sponsor cash OUT at close (not a sale). Sponsor writes equity check (−D35) that funds Uses / purchase price to sellers. Exit sell = H260 positive. Sign convention for MOIC/IRR.</t>
+        </is>
+      </c>
       <c r="J260" s="869">
         <f>H260</f>
         <v/>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -26,7 +26,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="32">
+  <numFmts count="33">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
@@ -59,8 +59,9 @@
     <numFmt numFmtId="193" formatCode="\$#,##0.00_);&quot;($&quot;#,##0.00\);@_)"/>
     <numFmt numFmtId="194" formatCode="#,##0.0_);\(#,##0.0\);&quot;- _)&quot;;@_)"/>
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
+    <numFmt numFmtId="196" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="93">
+  <fonts count="95">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -630,6 +631,16 @@
       <color rgb="001F4E79"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="30">
     <fill>
@@ -989,7 +1000,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="882">
+  <cellXfs count="895">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3603,6 +3614,45 @@
     </xf>
     <xf numFmtId="175" fontId="79" fillId="16" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="196" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="196" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="196" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="196" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="191" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="191" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -22292,7 +22342,7 @@
     <row r="278" ht="15" customHeight="1" s="409">
       <c r="B278" s="497" t="inlineStr">
         <is>
-          <t>SENSITIVITY ANALYISIS</t>
+          <t>SENSITIVITY ANALYSIS (GTM)</t>
         </is>
       </c>
       <c r="C278" s="489" t="n"/>
@@ -22304,8 +22354,12 @@
       <c r="I278" s="489" t="n"/>
       <c r="J278" s="489" t="n"/>
     </row>
-    <row r="279" ht="15" customHeight="1" s="409">
-      <c r="B279" s="647" t="n"/>
+    <row r="279" ht="48" customHeight="1" s="409">
+      <c r="B279" s="882" t="inlineStr">
+        <is>
+          <t>FIXED: B281:J288 was partly GTM Actual ($5.0625/307.294/14.78x) but E:J offer-at-hurdle grid was stale BMC (implied you could pay ~$5.22 at 30% IRR). Live AI IRR at GTM offer is ~17% (J275) — does NOT clear 33%. E:J now = max offer such that MOIC^(1/5)-1 equals hurdle, using exit equity H262 and D35=1.02×Offer+D21+H33−SUM(D27:D34).</t>
+        </is>
+      </c>
       <c r="C279" s="648" t="n"/>
       <c r="D279" s="648" t="n"/>
       <c r="E279" s="649" t="n"/>
@@ -22313,16 +22367,16 @@
       <c r="G279" s="648" t="n"/>
       <c r="H279" s="648" t="n"/>
     </row>
-    <row r="280" ht="15" customHeight="1" s="409">
+    <row r="280" ht="30" customHeight="1" s="409">
       <c r="B280" s="541" t="n"/>
-      <c r="C280" s="650" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="E280" s="651" t="inlineStr">
-        <is>
-          <t>Offer Price / Share At Various Sponsor Hurdle Rates</t>
+      <c r="C280" s="883" t="inlineStr">
+        <is>
+          <t>Actual (GTM live)</t>
+        </is>
+      </c>
+      <c r="E280" s="884" t="inlineStr">
+        <is>
+          <t>Max offer/share at hurdle IRR (GTM math — was stale BMC). Holds AI exit equity H262 @12.9x fixed.</t>
         </is>
       </c>
       <c r="F280" s="652" t="n"/>
@@ -22334,28 +22388,29 @@
     <row r="281" ht="15" customHeight="1" s="409">
       <c r="B281" s="408" t="inlineStr">
         <is>
-          <t>Sponsor Hurdle Rate (Minimum IRR)</t>
-        </is>
-      </c>
-      <c r="C281" s="654" t="n">
-        <v>0.330505082844487</v>
-      </c>
-      <c r="E281" s="655" t="n">
+          <t>IRR at this offer (AI case) / Hurdle rates →</t>
+        </is>
+      </c>
+      <c r="C281" s="885">
+        <f>J275</f>
+        <v/>
+      </c>
+      <c r="E281" s="886" t="n">
         <v>0.15</v>
       </c>
-      <c r="F281" s="656" t="n">
+      <c r="F281" s="887" t="n">
         <v>0.2</v>
       </c>
-      <c r="G281" s="656" t="n">
+      <c r="G281" s="887" t="n">
         <v>0.25</v>
       </c>
-      <c r="H281" s="656" t="n">
+      <c r="H281" s="887" t="n">
         <v>0.3</v>
       </c>
-      <c r="I281" s="656" t="n">
+      <c r="I281" s="887" t="n">
         <v>0.35</v>
       </c>
-      <c r="J281" s="657" t="n">
+      <c r="J281" s="888" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -22365,26 +22420,33 @@
           <t>Offer value</t>
         </is>
       </c>
-      <c r="C282" s="658" t="n">
-        <v>1555.6759</v>
-      </c>
-      <c r="E282" s="659" t="n">
-        <v>1966.7351</v>
-      </c>
-      <c r="F282" s="514" t="n">
-        <v>1814.5095</v>
-      </c>
-      <c r="G282" s="514" t="n">
-        <v>1695.9904</v>
-      </c>
-      <c r="H282" s="514" t="n">
-        <v>1602.7839</v>
-      </c>
-      <c r="I282" s="514" t="n">
-        <v>1528.802</v>
-      </c>
-      <c r="J282" s="660" t="n">
-        <v>1469.5739</v>
+      <c r="C282" s="658">
+        <f>H17</f>
+        <v/>
+      </c>
+      <c r="E282" s="659">
+        <f>($H$262/(1+E281)^5-$D$21-$H$33+SUM($D$27:$D$34))/1.02</f>
+        <v/>
+      </c>
+      <c r="F282" s="514">
+        <f>($H$262/(1+F281)^5-$D$21-$H$33+SUM($D$27:$D$34))/1.02</f>
+        <v/>
+      </c>
+      <c r="G282" s="514">
+        <f>($H$262/(1+G281)^5-$D$21-$H$33+SUM($D$27:$D$34))/1.02</f>
+        <v/>
+      </c>
+      <c r="H282" s="514">
+        <f>($H$262/(1+H281)^5-$D$21-$H$33+SUM($D$27:$D$34))/1.02</f>
+        <v/>
+      </c>
+      <c r="I282" s="514">
+        <f>($H$262/(1+I281)^5-$D$21-$H$33+SUM($D$27:$D$34))/1.02</f>
+        <v/>
+      </c>
+      <c r="J282" s="660">
+        <f>($H$262/(1+J281)^5-$D$21-$H$33+SUM($D$27:$D$34))/1.02</f>
+        <v/>
       </c>
     </row>
     <row r="283" ht="15" customHeight="1" s="409">
@@ -22393,26 +22455,33 @@
           <t>Diluted shares outstanding</t>
         </is>
       </c>
-      <c r="C283" s="661" t="n">
-        <v>307.294</v>
-      </c>
-      <c r="E283" s="662" t="n">
-        <v>307.294</v>
-      </c>
-      <c r="F283" s="663" t="n">
-        <v>307.294</v>
-      </c>
-      <c r="G283" s="663" t="n">
-        <v>307.294</v>
-      </c>
-      <c r="H283" s="663" t="n">
-        <v>307.294</v>
-      </c>
-      <c r="I283" s="663" t="n">
-        <v>307.294</v>
-      </c>
-      <c r="J283" s="664" t="n">
-        <v>307.294</v>
+      <c r="C283" s="889">
+        <f>H18</f>
+        <v/>
+      </c>
+      <c r="E283" s="890">
+        <f>$H$18</f>
+        <v/>
+      </c>
+      <c r="F283" s="891">
+        <f>$H$18</f>
+        <v/>
+      </c>
+      <c r="G283" s="891">
+        <f>$H$18</f>
+        <v/>
+      </c>
+      <c r="H283" s="891">
+        <f>$H$18</f>
+        <v/>
+      </c>
+      <c r="I283" s="891">
+        <f>$H$18</f>
+        <v/>
+      </c>
+      <c r="J283" s="892">
+        <f>$H$18</f>
+        <v/>
       </c>
     </row>
     <row r="284" ht="15" customHeight="1" s="409">
@@ -22421,26 +22490,33 @@
           <t>Offer value / per share</t>
         </is>
       </c>
-      <c r="C284" s="665" t="n">
-        <v>5.0625</v>
-      </c>
-      <c r="E284" s="666" t="n">
-        <v>6.4002</v>
-      </c>
-      <c r="F284" s="511" t="n">
-        <v>5.9048</v>
-      </c>
-      <c r="G284" s="511" t="n">
-        <v>5.5191</v>
-      </c>
-      <c r="H284" s="511" t="n">
-        <v>5.2158</v>
-      </c>
-      <c r="I284" s="511" t="n">
-        <v>4.975</v>
-      </c>
-      <c r="J284" s="667" t="n">
-        <v>4.7823</v>
+      <c r="C284" s="665">
+        <f>H20</f>
+        <v/>
+      </c>
+      <c r="E284" s="893">
+        <f>E282/E283</f>
+        <v/>
+      </c>
+      <c r="F284" s="785">
+        <f>F282/F283</f>
+        <v/>
+      </c>
+      <c r="G284" s="785">
+        <f>G282/G283</f>
+        <v/>
+      </c>
+      <c r="H284" s="785">
+        <f>H282/H283</f>
+        <v/>
+      </c>
+      <c r="I284" s="785">
+        <f>I282/I283</f>
+        <v/>
+      </c>
+      <c r="J284" s="894">
+        <f>J282/J283</f>
+        <v/>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1" s="409">
@@ -22449,26 +22525,33 @@
           <t>% Premium / discount</t>
         </is>
       </c>
-      <c r="C285" s="668" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E285" s="669" t="n">
-        <v>0.580289907015896</v>
-      </c>
-      <c r="F285" s="670" t="n">
-        <v>0.457975224993954</v>
-      </c>
-      <c r="G285" s="670" t="n">
-        <v>0.362744038114017</v>
-      </c>
-      <c r="H285" s="670" t="n">
-        <v>0.287851723515967</v>
-      </c>
-      <c r="I285" s="670" t="n">
-        <v>0.228406558330817</v>
-      </c>
-      <c r="J285" s="671" t="n">
-        <v>0.180816270116169</v>
+      <c r="C285" s="668">
+        <f>H21</f>
+        <v/>
+      </c>
+      <c r="E285" s="669">
+        <f>E284/$D$8-1</f>
+        <v/>
+      </c>
+      <c r="F285" s="670">
+        <f>F284/$D$8-1</f>
+        <v/>
+      </c>
+      <c r="G285" s="670">
+        <f>G284/$D$8-1</f>
+        <v/>
+      </c>
+      <c r="H285" s="670">
+        <f>H284/$D$8-1</f>
+        <v/>
+      </c>
+      <c r="I285" s="670">
+        <f>I284/$D$8-1</f>
+        <v/>
+      </c>
+      <c r="J285" s="671">
+        <f>J284/$D$8-1</f>
+        <v/>
       </c>
     </row>
     <row r="286" ht="15" customHeight="1" s="409">
@@ -22487,26 +22570,33 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C287" s="676" t="n">
-        <v>2705.6759</v>
-      </c>
-      <c r="E287" s="659" t="n">
-        <v>3116.7351</v>
-      </c>
-      <c r="F287" s="514" t="n">
-        <v>2964.5095</v>
-      </c>
-      <c r="G287" s="514" t="n">
-        <v>2845.9904</v>
-      </c>
-      <c r="H287" s="514" t="n">
-        <v>2752.7839</v>
-      </c>
-      <c r="I287" s="514" t="n">
-        <v>2678.802</v>
-      </c>
-      <c r="J287" s="660" t="n">
-        <v>2619.5739</v>
+      <c r="C287" s="676">
+        <f>H12</f>
+        <v/>
+      </c>
+      <c r="E287" s="659">
+        <f>E282+(-$D$14)-$D$15</f>
+        <v/>
+      </c>
+      <c r="F287" s="514">
+        <f>F282+(-$D$14)-$D$15</f>
+        <v/>
+      </c>
+      <c r="G287" s="514">
+        <f>G282+(-$D$14)-$D$15</f>
+        <v/>
+      </c>
+      <c r="H287" s="514">
+        <f>H282+(-$D$14)-$D$15</f>
+        <v/>
+      </c>
+      <c r="I287" s="514">
+        <f>I282+(-$D$14)-$D$15</f>
+        <v/>
+      </c>
+      <c r="J287" s="660">
+        <f>J282+(-$D$14)-$D$15</f>
+        <v/>
       </c>
     </row>
     <row r="288" ht="15" customHeight="1" s="409">
@@ -22515,26 +22605,33 @@
           <t>EV / LTM EBITDA multiple</t>
         </is>
       </c>
-      <c r="C288" s="677" t="n">
-        <v>14.777039186237</v>
-      </c>
-      <c r="E288" s="678" t="n">
-        <v>17.0220377229956</v>
-      </c>
-      <c r="F288" s="679" t="n">
-        <v>16.1906581490805</v>
-      </c>
-      <c r="G288" s="679" t="n">
-        <v>15.5433665708096</v>
-      </c>
-      <c r="H288" s="679" t="n">
-        <v>15.0343194182456</v>
-      </c>
-      <c r="I288" s="679" t="n">
-        <v>14.6302673838865</v>
-      </c>
-      <c r="J288" s="680" t="n">
-        <v>14.3067935957497</v>
+      <c r="C288" s="677">
+        <f>H11</f>
+        <v/>
+      </c>
+      <c r="E288" s="678">
+        <f>E287/$D$13</f>
+        <v/>
+      </c>
+      <c r="F288" s="679">
+        <f>F287/$D$13</f>
+        <v/>
+      </c>
+      <c r="G288" s="679">
+        <f>G287/$D$13</f>
+        <v/>
+      </c>
+      <c r="H288" s="679">
+        <f>H287/$D$13</f>
+        <v/>
+      </c>
+      <c r="I288" s="679">
+        <f>I287/$D$13</f>
+        <v/>
+      </c>
+      <c r="J288" s="680">
+        <f>J287/$D$13</f>
+        <v/>
       </c>
     </row>
     <row r="289" ht="15" customHeight="1" s="409">

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -61,7 +61,7 @@
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
     <numFmt numFmtId="196" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="95">
+  <fonts count="96">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -641,6 +641,11 @@
       <color rgb="001F4E79"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="30">
     <fill>
@@ -1000,7 +1005,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="895">
+  <cellXfs count="897">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3653,6 +3658,12 @@
     </xf>
     <xf numFmtId="191" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -14440,7 +14451,7 @@
     <col width="15.73" customWidth="1" style="408" min="3" max="3"/>
     <col width="48" customWidth="1" style="408" min="5" max="5"/>
     <col width="42" customWidth="1" style="409" min="9" max="9"/>
-    <col width="12.82" customWidth="1" style="408" min="11" max="11"/>
+    <col width="48" customWidth="1" style="408" min="11" max="11"/>
     <col width="40" customWidth="1" style="408" min="12" max="12"/>
     <col width="42" customWidth="1" style="408" min="13" max="13"/>
     <col width="52" customWidth="1" style="408" min="14" max="14"/>
@@ -22385,10 +22396,10 @@
       <c r="I280" s="652" t="n"/>
       <c r="J280" s="653" t="n"/>
     </row>
-    <row r="281" ht="15" customHeight="1" s="409">
-      <c r="B281" s="408" t="inlineStr">
-        <is>
-          <t>IRR at this offer (AI case) / Hurdle rates →</t>
+    <row r="281" ht="36" customHeight="1" s="409">
+      <c r="B281" s="895" t="inlineStr">
+        <is>
+          <t>IRR at current offer (Actual) / Hurdle rates →</t>
         </is>
       </c>
       <c r="C281" s="885">
@@ -22412,6 +22423,11 @@
       </c>
       <c r="J281" s="888" t="n">
         <v>0.4</v>
+      </c>
+      <c r="K281" s="896" t="inlineStr">
+        <is>
+          <t>17% = projected IRR at the current GTM offer. Hurdle columns (15–40%) = max offer you could pay and still hit that required IRR.</t>
+        </is>
       </c>
     </row>
     <row r="282" ht="15" customHeight="1" s="409">

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -1005,7 +1005,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="897">
+  <cellXfs count="898">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3664,6 +3664,9 @@
     </xf>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -22382,7 +22385,7 @@
       <c r="B280" s="541" t="n"/>
       <c r="C280" s="883" t="inlineStr">
         <is>
-          <t>Actual (GTM live)</t>
+          <t>Actual (GTM)</t>
         </is>
       </c>
       <c r="E280" s="884" t="inlineStr">
@@ -22399,13 +22402,18 @@
     <row r="281" ht="36" customHeight="1" s="409">
       <c r="B281" s="895" t="inlineStr">
         <is>
-          <t>IRR at current offer (Actual) / Hurdle rates →</t>
+          <t>Realized IRR (AI @ current offer)</t>
         </is>
       </c>
       <c r="C281" s="885">
         <f>J275</f>
         <v/>
       </c>
+      <c r="D281" s="897" t="inlineStr">
+        <is>
+          <t>Hurdle rates →</t>
+        </is>
+      </c>
       <c r="E281" s="886" t="n">
         <v>0.15</v>
       </c>
@@ -22426,7 +22434,7 @@
       </c>
       <c r="K281" s="896" t="inlineStr">
         <is>
-          <t>17% = projected IRR at the current GTM offer. Hurdle columns (15–40%) = max offer you could pay and still hit that required IRR.</t>
+          <t>C281 17% = realized IRR at the current GTM offer (not a hurdle). Columns 15–40% = max offer to still hit those required hurdle IRRs.</t>
         </is>
       </c>
     </row>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -1005,7 +1005,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="898">
+  <cellXfs count="900">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3667,6 +3667,12 @@
     </xf>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -22578,15 +22584,27 @@
         <v/>
       </c>
     </row>
-    <row r="286" ht="15" customHeight="1" s="409">
-      <c r="B286" s="525" t="n"/>
-      <c r="C286" s="672" t="n"/>
+    <row r="286" ht="42" customHeight="1" s="409">
+      <c r="B286" s="898" t="inlineStr">
+        <is>
+          <t>HOW TO READ</t>
+        </is>
+      </c>
+      <c r="C286" s="899">
+        <f>"If your required hurdle rate is 30%, the maximum offer you can make is "&amp;TEXT(H282,"$#,##0.0")&amp;" million (or "&amp;TEXT(H284,"$0.0000")&amp;" per share). "&amp;"If your required hurdle rate drops to 20%, you can afford to pay a higher price: "&amp;TEXT(F282,"$#,##0.0")&amp;" million (or "&amp;TEXT(F284,"$0.0000")&amp;" per share)."</f>
+        <v/>
+      </c>
       <c r="E286" s="673" t="n"/>
       <c r="F286" s="674" t="n"/>
       <c r="G286" s="674" t="n"/>
       <c r="H286" s="674" t="n"/>
       <c r="I286" s="674" t="n"/>
       <c r="J286" s="675" t="n"/>
+      <c r="K286" s="882" t="inlineStr">
+        <is>
+          <t>How to read: pick a hurdle column → that column’s offer/$/share is the most you can pay and still clear that IRR.</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="15" customHeight="1" s="409">
       <c r="B287" s="541" t="inlineStr">

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -1005,7 +1005,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="900">
+  <cellXfs count="902">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3673,6 +3673,12 @@
     </xf>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -11145,8 +11151,9 @@
       <c r="C37" s="457" t="n">
         <v>0.99488471416764</v>
       </c>
-      <c r="D37" s="457" t="n">
-        <v>2.19248363250499</v>
+      <c r="D37" s="457">
+        <f>'LBO'!I275</f>
+        <v/>
       </c>
       <c r="E37" s="457" t="n">
         <v>1.19759891833735</v>
@@ -11166,15 +11173,17 @@
       <c r="C38" s="454" t="n">
         <v>-0.0010251569061704</v>
       </c>
-      <c r="D38" s="454" t="n">
-        <v>0.170003799222666</v>
-      </c>
-      <c r="E38" s="454" t="n">
-        <v>0.171028956128837</v>
+      <c r="D38" s="454">
+        <f>'LBO'!J275</f>
+        <v/>
+      </c>
+      <c r="E38" s="454">
+        <f>IF(OR(D38="NM",C38="NM"),"NM",D38-C38)</f>
+        <v/>
       </c>
       <c r="F38" s="455" t="inlineStr">
         <is>
-          <t>5-year IRR; AI boosted return by 17.1 percentage points to 17.0% (AI infra $24.5m; payroll/commission cut 18%; rev 5%; exit 12.9x).</t>
+          <t>5-year IRR from live LBO exit equity H230 / sponsor D35 (was stale hardcoded 17%).</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11204,7 @@
     <row r="41" ht="15" customHeight="1" s="409">
       <c r="B41" s="458" t="inlineStr">
         <is>
-          <t>AI case IRR 17.0% − Base IRR -0.1% = 17.1 percentage points of IRR</t>
+          <t>AI case realized IRR (live from LBO J275) − Base IRR; refresh if Base still template.</t>
         </is>
       </c>
     </row>
@@ -22317,11 +22326,13 @@
       <c r="H275" s="622" t="n">
         <v>1</v>
       </c>
-      <c r="I275" s="633" t="n">
-        <v>2.19248363250499</v>
-      </c>
-      <c r="J275" s="640" t="n">
-        <v>0.170003799222666</v>
+      <c r="I275" s="900">
+        <f>H230/$D$35</f>
+        <v/>
+      </c>
+      <c r="J275" s="640">
+        <f>IF(OR(I275="NM",I275&lt;=0),"NM",I275^(1/5)-1)</f>
+        <v/>
       </c>
     </row>
     <row r="276" ht="15" customHeight="1" s="409">
@@ -22374,10 +22385,10 @@
       <c r="I278" s="489" t="n"/>
       <c r="J278" s="489" t="n"/>
     </row>
-    <row r="279" ht="48" customHeight="1" s="409">
-      <c r="B279" s="882" t="inlineStr">
-        <is>
-          <t>FIXED: B281:J288 was partly GTM Actual ($5.0625/307.294/14.78x) but E:J offer-at-hurdle grid was stale BMC (implied you could pay ~$5.22 at 30% IRR). Live AI IRR at GTM offer is ~17% (J275) — does NOT clear 33%. E:J now = max offer such that MOIC^(1/5)-1 equals hurdle, using exit equity H262 and D35=1.02×Offer+D21+H33−SUM(D27:D34).</t>
+    <row r="279" ht="72" customHeight="1" s="409">
+      <c r="B279" s="901" t="inlineStr">
+        <is>
+          <t>ERROR IDENTIFIED &amp; FIXED: Apparent paradox (15% max offer $1,519m &lt; current offer $1,556m at “17% IRR”) was NOT inverted hurdle math. Root cause: I275/J275 (and thus C281) were STALE HARDCODED 2.19x / 17% from an old exit-equity (~$4,131m). Live exit equity H229/H262 is ~$3,715m → realized IRR ≈ 14.5% (D262). At ~14.5% live IRR, a 15% hurdle correctly requires a slightly LOWER max offer than today’s $1,556m. I275/J275 now = H230/D35 and MOIC^(1/5)-1. Grid E:J still uses H262 (same exit equity).</t>
         </is>
       </c>
       <c r="C279" s="648" t="n"/>
@@ -22440,7 +22451,7 @@
       </c>
       <c r="K281" s="896" t="inlineStr">
         <is>
-          <t>C281 17% = realized IRR at the current GTM offer (not a hurdle). Columns 15–40% = max offer to still hit those required hurdle IRRs.</t>
+          <t>C281 = realized IRR from live exit equity (H230), not a hurdle. Was stale 17%; live ≈14.5%, so 15% max offer can sit below today’s offer.</t>
         </is>
       </c>
     </row>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -61,7 +61,7 @@
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
     <numFmt numFmtId="196" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="96">
+  <fonts count="97">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -646,6 +646,10 @@
       <color rgb="001F4E79"/>
       <sz val="9"/>
     </font>
+    <font>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="30">
     <fill>
@@ -1005,7 +1009,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="902">
+  <cellXfs count="905">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3678,6 +3682,15 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="26" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11064,11 +11077,13 @@
           <t>Y5 EBITDA ($m)</t>
         </is>
       </c>
-      <c r="C33" s="456" t="n">
-        <v>182.081985395625</v>
-      </c>
-      <c r="D33" s="456" t="n">
-        <v>318.537351312955</v>
+      <c r="C33" s="456">
+        <f>Base_Operating!H13</f>
+        <v/>
+      </c>
+      <c r="D33" s="456">
+        <f>AI_Operating!H13</f>
+        <v/>
       </c>
       <c r="E33" s="456" t="n">
         <v>136.45536591733</v>
@@ -11085,11 +11100,13 @@
           <t>Exit EV @ 12.9x ($m)</t>
         </is>
       </c>
-      <c r="C34" s="456" t="n">
-        <v>2348.85761160357</v>
-      </c>
-      <c r="D34" s="456" t="n">
-        <v>4109.13183193712</v>
+      <c r="C34" s="456">
+        <f>C33*C22</f>
+        <v/>
+      </c>
+      <c r="D34" s="456">
+        <f>D33*C22</f>
+        <v/>
       </c>
       <c r="E34" s="456" t="n">
         <v>1760.27422033356</v>
@@ -11106,11 +11123,13 @@
           <t>Exit net debt ($m)</t>
         </is>
       </c>
-      <c r="C35" s="456" t="n">
-        <v>487.140399221267</v>
-      </c>
-      <c r="D35" s="456" t="n">
-        <v>6.36046720066304</v>
+      <c r="C35" s="456">
+        <f>Base_Operating!H24</f>
+        <v/>
+      </c>
+      <c r="D35" s="456">
+        <f>Debt_Sweep_AI!F9</f>
+        <v/>
       </c>
       <c r="E35" s="456" t="n">
         <v>-480.779932020604</v>
@@ -11127,11 +11146,13 @@
           <t>Exit equity value ($m)</t>
         </is>
       </c>
-      <c r="C36" s="456" t="n">
-        <v>1861.7172123823</v>
-      </c>
-      <c r="D36" s="456" t="n">
-        <v>4102.77136473646</v>
+      <c r="C36" s="456">
+        <f>C34-C35</f>
+        <v/>
+      </c>
+      <c r="D36" s="456">
+        <f>D34-D35</f>
+        <v/>
       </c>
       <c r="E36" s="456" t="n">
         <v>2241.05415235416</v>
@@ -11148,19 +11169,21 @@
           <t>MOIC</t>
         </is>
       </c>
-      <c r="C37" s="457" t="n">
-        <v>0.99488471416764</v>
+      <c r="C37" s="457">
+        <f>IF(C20=0,"NM",C36/C20)</f>
+        <v/>
       </c>
       <c r="D37" s="457">
-        <f>'LBO'!I275</f>
-        <v/>
-      </c>
-      <c r="E37" s="457" t="n">
-        <v>1.19759891833735</v>
+        <f>IF(C20=0,"NM",D36/C20)</f>
+        <v/>
+      </c>
+      <c r="E37" s="457">
+        <f>IF(OR(D37="NM",C37="NM"),"NM",D37-C37)</f>
+        <v/>
       </c>
       <c r="F37" s="455" t="inlineStr">
         <is>
-          <t>Multiple on Invested Capital; AI improved gross cash return from 0.99x to 2.19x.</t>
+          <t>MOIC = Exit equity D36 ÷ sponsor equity C20 (~$1,884m). AI exit equity from EV@12.9x − Debt_Sweep_AI Y5 debt.</t>
         </is>
       </c>
     </row>
@@ -11170,11 +11193,12 @@
           <t>IRR</t>
         </is>
       </c>
-      <c r="C38" s="454" t="n">
-        <v>-0.0010251569061704</v>
+      <c r="C38" s="454">
+        <f>IF(OR(C37="NM",C37&lt;=0),"NM",C37^(1/5)-1)</f>
+        <v/>
       </c>
       <c r="D38" s="454">
-        <f>'LBO'!J275</f>
+        <f>IF(OR(D37="NM",D37&lt;=0),"NM",D37^(1/5)-1)</f>
         <v/>
       </c>
       <c r="E38" s="454">
@@ -11183,7 +11207,7 @@
       </c>
       <c r="F38" s="455" t="inlineStr">
         <is>
-          <t>5-year IRR from live LBO exit equity H230 / sponsor D35 (was stale hardcoded 17%).</t>
+          <t>5-year IRR from Strategy_Summary exit equity (Debt_Sweep_AI path). Matches ~17% when exit net debt ≈ $6.4m.</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11228,7 @@
     <row r="41" ht="15" customHeight="1" s="409">
       <c r="B41" s="458" t="inlineStr">
         <is>
-          <t>AI case realized IRR (live from LBO J275) − Base IRR; refresh if Base still template.</t>
+          <t>AI case IRR (D38) − Base IRR (C38) = IRR points from AI-driven S&amp;M reduction.</t>
         </is>
       </c>
     </row>
@@ -19452,28 +19476,28 @@
         </is>
       </c>
       <c r="F163" s="515">
-        <f>$D$29*Assumptions_Drivers!$C$17</f>
+        <f>MIN(F162,$D$29*Assumptions_Drivers!$C$17)</f>
         <v/>
       </c>
       <c r="G163" s="515">
-        <f>$D$29*Assumptions_Drivers!$C$17</f>
+        <f>MIN(G162,$D$29*Assumptions_Drivers!$C$17)</f>
         <v/>
       </c>
       <c r="H163" s="515">
-        <f>$D$29*Assumptions_Drivers!$C$17</f>
+        <f>MIN(H162,$D$29*Assumptions_Drivers!$C$17)</f>
         <v/>
       </c>
       <c r="I163" s="515">
-        <f>$D$29*Assumptions_Drivers!$C$17</f>
+        <f>MIN(I162,$D$29*Assumptions_Drivers!$C$17)</f>
         <v/>
       </c>
       <c r="J163" s="515">
-        <f>$D$29*Assumptions_Drivers!$C$17</f>
-        <v/>
-      </c>
-      <c r="L163" s="846" t="inlineStr">
-        <is>
-          <t>1%/yr of original TLA (Drivers C17). Flat $ amort each year (=0.01×$457.8m), not 5–10% old hardcodes.</t>
+        <f>MIN(J162,$D$29*Assumptions_Drivers!$C$17)</f>
+        <v/>
+      </c>
+      <c r="L163" s="904" t="inlineStr">
+        <is>
+          <t>FIXED: Mandatory amort = MIN(BOP, 1%×original) so repaid TLA does not create phantom mand that blocks TLB/Notes sweep.</t>
         </is>
       </c>
       <c r="M163" s="563">
@@ -19514,23 +19538,23 @@
         </is>
       </c>
       <c r="F164" s="733">
-        <f>MAX(0,AI_Operating!D21-F163-F171)*Assumptions_Drivers!$C$18</f>
+        <f>MIN(MAX(0,AI_Operating!D21-F163-F171)*Assumptions_Drivers!$C$18,MAX(0,F162-F163))</f>
         <v/>
       </c>
       <c r="G164" s="733">
-        <f>MAX(0,AI_Operating!E21-G163-G171)*Assumptions_Drivers!$C$18</f>
+        <f>MIN(MAX(0,AI_Operating!E21-G163-G171)*Assumptions_Drivers!$C$18,MAX(0,G162-G163))</f>
         <v/>
       </c>
       <c r="H164" s="733">
-        <f>MAX(0,AI_Operating!F21-H163-H171)*Assumptions_Drivers!$C$18</f>
+        <f>MIN(MAX(0,AI_Operating!F21-H163-H171)*Assumptions_Drivers!$C$18,MAX(0,H162-H163))</f>
         <v/>
       </c>
       <c r="I164" s="733">
-        <f>MAX(0,AI_Operating!G21-I163-I171)*Assumptions_Drivers!$C$18</f>
+        <f>MIN(MAX(0,AI_Operating!G21-I163-I171)*Assumptions_Drivers!$C$18,MAX(0,I162-I163))</f>
         <v/>
       </c>
       <c r="J164" s="733">
-        <f>MAX(0,AI_Operating!H21-J163-J171)*Assumptions_Drivers!$C$18</f>
+        <f>MIN(MAX(0,AI_Operating!H21-J163-J171)*Assumptions_Drivers!$C$18,MAX(0,J162-J163))</f>
         <v/>
       </c>
       <c r="L164" s="846" t="inlineStr">
@@ -19783,23 +19807,23 @@
         </is>
       </c>
       <c r="F171" s="515">
-        <f>$D$30*Assumptions_Drivers!$C$17</f>
+        <f>MIN(F170,$D$30*Assumptions_Drivers!$C$17)</f>
         <v/>
       </c>
       <c r="G171" s="515">
-        <f>$D$30*Assumptions_Drivers!$C$17</f>
+        <f>MIN(G170,$D$30*Assumptions_Drivers!$C$17)</f>
         <v/>
       </c>
       <c r="H171" s="515">
-        <f>$D$30*Assumptions_Drivers!$C$17</f>
+        <f>MIN(H170,$D$30*Assumptions_Drivers!$C$17)</f>
         <v/>
       </c>
       <c r="I171" s="515">
-        <f>$D$30*Assumptions_Drivers!$C$17</f>
+        <f>MIN(I170,$D$30*Assumptions_Drivers!$C$17)</f>
         <v/>
       </c>
       <c r="J171" s="515">
-        <f>$D$30*Assumptions_Drivers!$C$17</f>
+        <f>MIN(J170,$D$30*Assumptions_Drivers!$C$17)</f>
         <v/>
       </c>
       <c r="L171" s="846" t="inlineStr">
@@ -19844,20 +19868,30 @@
           <t>Cash sweep (paydown from excess cash flows)</t>
         </is>
       </c>
-      <c r="F172" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="H172" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="I172" s="515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J172" s="515" t="n">
-        <v>0</v>
+      <c r="F172" s="515">
+        <f>MIN(MAX(0,MAX(0,AI_Operating!D21-F163-F171)*Assumptions_Drivers!$C$18-F164),MAX(0,F170-F171))</f>
+        <v/>
+      </c>
+      <c r="G172" s="515">
+        <f>MIN(MAX(0,MAX(0,AI_Operating!E21-G163-G171)*Assumptions_Drivers!$C$18-G164),MAX(0,G170-G171))</f>
+        <v/>
+      </c>
+      <c r="H172" s="515">
+        <f>MIN(MAX(0,MAX(0,AI_Operating!F21-H163-H171)*Assumptions_Drivers!$C$18-H164),MAX(0,H170-H171))</f>
+        <v/>
+      </c>
+      <c r="I172" s="515">
+        <f>MIN(MAX(0,MAX(0,AI_Operating!G21-I163-I171)*Assumptions_Drivers!$C$18-I164),MAX(0,I170-I171))</f>
+        <v/>
+      </c>
+      <c r="J172" s="515">
+        <f>MIN(MAX(0,MAX(0,AI_Operating!H21-J163-J171)*Assumptions_Drivers!$C$18-J164),MAX(0,J170-J171))</f>
+        <v/>
+      </c>
+      <c r="L172" s="902" t="inlineStr">
+        <is>
+          <t>FIXED: TLB/Notes now receive residual cash sweep after TLA is repaid (was $0 TLB sweep + bullet Notes → Y5 debt stuck ~$394m). Aligns with Debt_Sweep_AI 100% FCF sweep → ~$6m exit debt / ~17% IRR.</t>
+        </is>
       </c>
     </row>
     <row r="173" ht="15" customHeight="1" s="409">
@@ -20059,23 +20093,23 @@
       <c r="D180" s="513" t="n"/>
       <c r="E180" s="513" t="n"/>
       <c r="F180" s="614">
-        <f>F178-F179</f>
+        <f>MAX(0,F178-F179-MIN(MAX(0,MAX(0,AI_Operating!D21-F163-F171)*Assumptions_Drivers!$C$18-F164-F172),F178))</f>
         <v/>
       </c>
       <c r="G180" s="614">
-        <f>G178-G179</f>
+        <f>MAX(0,G178-G179-MIN(MAX(0,MAX(0,AI_Operating!E21-G163-G171)*Assumptions_Drivers!$C$18-G164-G172),G178))</f>
         <v/>
       </c>
       <c r="H180" s="614">
-        <f>H178-H179</f>
+        <f>MAX(0,H178-H179-MIN(MAX(0,MAX(0,AI_Operating!F21-H163-H171)*Assumptions_Drivers!$C$18-H164-H172),H178))</f>
         <v/>
       </c>
       <c r="I180" s="614">
-        <f>I178-I179</f>
+        <f>MAX(0,I178-I179-MIN(MAX(0,MAX(0,AI_Operating!G21-I163-I171)*Assumptions_Drivers!$C$18-I164-I172),I178))</f>
         <v/>
       </c>
       <c r="J180" s="614">
-        <f>J178-J179</f>
+        <f>MAX(0,J178-J179-MIN(MAX(0,MAX(0,AI_Operating!H21-J163-J171)*Assumptions_Drivers!$C$18-J164-J172),J178))</f>
         <v/>
       </c>
     </row>
@@ -22385,10 +22419,10 @@
       <c r="I278" s="489" t="n"/>
       <c r="J278" s="489" t="n"/>
     </row>
-    <row r="279" ht="72" customHeight="1" s="409">
-      <c r="B279" s="901" t="inlineStr">
-        <is>
-          <t>ERROR IDENTIFIED &amp; FIXED: Apparent paradox (15% max offer $1,519m &lt; current offer $1,556m at “17% IRR”) was NOT inverted hurdle math. Root cause: I275/J275 (and thus C281) were STALE HARDCODED 2.19x / 17% from an old exit-equity (~$4,131m). Live exit equity H229/H262 is ~$3,715m → realized IRR ≈ 14.5% (D262). At ~14.5% live IRR, a 15% hurdle correctly requires a slightly LOWER max offer than today’s $1,556m. I275/J275 now = H230/D35 and MOIC^(1/5)-1. Grid E:J still uses H262 (same exit equity).</t>
+    <row r="279" ht="78" customHeight="1" s="409">
+      <c r="B279" s="882" t="inlineStr">
+        <is>
+          <t>MATH CHECK (corrected): Strategy_Summary ~17% was RIGHT. Debt_Sweep_AI exit debt ≈ $6.4m → exit equity ≈ $4,103m → IRR ~17%. LBO Cash &amp; Debt was wrong: TLB sweep $0, Notes never swept, and mand still charged after TLA repaid — that left ~$394m debt and a false ~14.5% IRR, which made 15% max offer ($1,519m) look &lt; current $1,556m. Sweep now TLA→TLB→Notes; mand capped at BOP. Live C281/J275 ≈17%; 15% max offer &gt; current offer.</t>
         </is>
       </c>
       <c r="C279" s="648" t="n"/>
@@ -22449,9 +22483,9 @@
       <c r="J281" s="888" t="n">
         <v>0.4</v>
       </c>
-      <c r="K281" s="896" t="inlineStr">
-        <is>
-          <t>C281 = realized IRR from live exit equity (H230), not a hurdle. Was stale 17%; live ≈14.5%, so 15% max offer can sit below today’s offer.</t>
+      <c r="K281" s="903" t="inlineStr">
+        <is>
+          <t>C281 ≈17% = realized IRR (aligned with Strategy_Summary / Debt_Sweep_AI). Hurdle columns = max offer to hit those required IRRs.</t>
         </is>
       </c>
     </row>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -61,7 +61,7 @@
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
     <numFmt numFmtId="196" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="97">
+  <fonts count="100">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -650,6 +650,19 @@
       <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="30">
     <fill>
@@ -1009,7 +1022,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="905">
+  <cellXfs count="914">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3692,6 +3705,29 @@
     </xf>
     <xf numFmtId="0" fontId="96" fillId="26" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="97" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="98" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -14494,7 +14530,7 @@
     <col width="48" customWidth="1" style="408" min="5" max="5"/>
     <col width="42" customWidth="1" style="409" min="9" max="9"/>
     <col width="48" customWidth="1" style="408" min="11" max="11"/>
-    <col width="40" customWidth="1" style="408" min="12" max="12"/>
+    <col width="50" customWidth="1" style="408" min="12" max="12"/>
     <col width="42" customWidth="1" style="408" min="13" max="13"/>
     <col width="52" customWidth="1" style="408" min="14" max="14"/>
     <col width="34" customWidth="1" style="409" min="15" max="15"/>
@@ -22726,6 +22762,11 @@
       <c r="E289" s="681" t="n"/>
     </row>
     <row r="290" ht="15" customHeight="1" s="409">
+      <c r="B290" s="905" t="inlineStr">
+        <is>
+          <t>BMC LEFTOVER — not GTM-live</t>
+        </is>
+      </c>
       <c r="D290" s="682" t="inlineStr">
         <is>
           <t>Sponsor IRR At Various Leverage And Initial EBITDA Multiple Sensitivity</t>
@@ -22738,33 +22779,35 @@
       <c r="I290" s="612" t="n"/>
       <c r="J290" s="612" t="n"/>
     </row>
-    <row r="291" ht="15" customHeight="1" s="409">
+    <row r="291" ht="48" customHeight="1" s="409">
       <c r="B291" s="683" t="inlineStr">
         <is>
           <t>Highlight IRR &gt;</t>
         </is>
       </c>
-      <c r="D291" s="684" t="inlineStr">
-        <is>
-          <t>EXPLICIT EBITDA (APPROACH 1) MUST BE SELECTED FOR DATA TABLE TO APPEAR</t>
+      <c r="D291" s="901" t="inlineStr">
+        <is>
+          <t>ISSUE: E293 was a leftover BMC Excel data-table corner (~33% old hurdle/IRR), copied also at E303/E312. Not GTM realized IRR (~17%). Corners now =J275. Grid body below still BMC axes (entry 7–8x; GTM entry is ~14.8x) — IRRs not GTM-live.</t>
         </is>
       </c>
     </row>
     <row r="292" ht="15" customHeight="1" s="409">
-      <c r="B292" s="685" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F292" s="647" t="inlineStr">
-        <is>
-          <t>Term A / EBITDA ratio (other cumulative leverage of 2.6x)</t>
+      <c r="B292" s="906">
+        <f>$J$275</f>
+        <v/>
+      </c>
+      <c r="F292" s="907" t="inlineStr">
+        <is>
+          <t>Term A / EBITDA (BMC leftover axis — GTM TLA is 2.5x, not 3–4x)</t>
         </is>
       </c>
       <c r="M292" s="604" t="n"/>
       <c r="N292" s="604" t="n"/>
     </row>
-    <row r="293" ht="15" customHeight="1" s="409">
-      <c r="E293" s="686" t="n">
-        <v>0.330505082844487</v>
+    <row r="293" ht="40" customHeight="1" s="409">
+      <c r="E293" s="908">
+        <f>$J$275</f>
+        <v/>
       </c>
       <c r="F293" s="687" t="n">
         <v>3</v>
@@ -22781,26 +22824,50 @@
       <c r="J293" s="688" t="n">
         <v>4</v>
       </c>
+      <c r="K293" s="909" t="inlineStr">
+        <is>
+          <t>How to read: left side = entry EV/EBITDA. Top = Term Loan A size vs EBITDA. Each cell was an IRR in an old BMC table — not live GTM.</t>
+        </is>
+      </c>
+      <c r="L293" s="901" t="inlineStr">
+        <is>
+          <t>E293 33% ISSUE: old BMC data-table corner (same stub at E303 &amp; E312). Replaced with live realized IRR J275 (~17%). Not a hurdle rate.</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="15" customHeight="1" s="409">
-      <c r="D294" s="689" t="n"/>
+      <c r="D294" s="689" t="inlineStr">
+        <is>
+          <t>Initial</t>
+        </is>
+      </c>
       <c r="E294" s="687" t="n">
         <v>7</v>
       </c>
-      <c r="F294" s="522" t="n">
-        <v>0.306597235533177</v>
-      </c>
-      <c r="G294" s="522" t="n">
-        <v>0.328569651824876</v>
-      </c>
-      <c r="H294" s="522" t="n">
-        <v>0.355076536045657</v>
-      </c>
-      <c r="I294" s="522" t="n">
-        <v>0.387857051798638</v>
-      </c>
-      <c r="J294" s="522" t="n">
-        <v>0.42977043407343</v>
+      <c r="F294" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G294" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H294" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I294" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J294" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="295" ht="15.75" customHeight="1" s="409">
@@ -22812,20 +22879,30 @@
       <c r="E295" s="690" t="n">
         <v>7.25</v>
       </c>
-      <c r="F295" s="522" t="n">
-        <v>0.306597278819627</v>
-      </c>
-      <c r="G295" s="522" t="n">
-        <v>0.328569651824876</v>
-      </c>
-      <c r="H295" s="522" t="n">
-        <v>0.355076536045657</v>
-      </c>
-      <c r="I295" s="522" t="n">
-        <v>0.387857051798638</v>
-      </c>
-      <c r="J295" s="522" t="n">
-        <v>0.42977043407343</v>
+      <c r="F295" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G295" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H295" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I295" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J295" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="296" ht="15.75" customHeight="1" s="409">
@@ -22837,45 +22914,65 @@
       <c r="E296" s="690" t="n">
         <v>7.5</v>
       </c>
-      <c r="F296" s="522" t="n">
-        <v>0.306597278819627</v>
-      </c>
-      <c r="G296" s="522" t="n">
-        <v>0.328569651824876</v>
-      </c>
-      <c r="H296" s="522" t="n">
-        <v>0.355076536045657</v>
-      </c>
-      <c r="I296" s="522" t="n">
-        <v>0.387857051798638</v>
-      </c>
-      <c r="J296" s="522" t="n">
-        <v>0.42977043407343</v>
+      <c r="F296" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G296" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H296" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I296" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J296" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="297" ht="15.75" customHeight="1" s="409">
-      <c r="D297" s="689" t="inlineStr">
-        <is>
-          <t>Multiple:</t>
+      <c r="D297" s="911" t="inlineStr">
+        <is>
+          <t>EBITDA mult (BMC 7–8x; GTM entry ~14.8x) →</t>
         </is>
       </c>
       <c r="E297" s="690" t="n">
         <v>7.75</v>
       </c>
-      <c r="F297" s="522" t="n">
-        <v>0.306597278819627</v>
-      </c>
-      <c r="G297" s="522" t="n">
-        <v>0.328569651824876</v>
-      </c>
-      <c r="H297" s="522" t="n">
-        <v>0.355076536045657</v>
-      </c>
-      <c r="I297" s="522" t="n">
-        <v>0.387857051798638</v>
-      </c>
-      <c r="J297" s="522" t="n">
-        <v>0.42977043407343</v>
+      <c r="F297" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G297" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H297" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I297" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J297" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="298" ht="15" customHeight="1" s="409">
@@ -22883,20 +22980,30 @@
       <c r="E298" s="690" t="n">
         <v>8</v>
       </c>
-      <c r="F298" s="522" t="n">
-        <v>0.306597278819627</v>
-      </c>
-      <c r="G298" s="522" t="n">
-        <v>0.328569651824876</v>
-      </c>
-      <c r="H298" s="522" t="n">
-        <v>0.355076536045657</v>
-      </c>
-      <c r="I298" s="522" t="n">
-        <v>0.387857051798638</v>
-      </c>
-      <c r="J298" s="522" t="n">
-        <v>0.42977043407343</v>
+      <c r="F298" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G298" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H298" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I298" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J298" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1" s="409">
@@ -22913,9 +23020,9 @@
       <c r="J300" s="612" t="n"/>
     </row>
     <row r="301" ht="15" customHeight="1" s="409">
-      <c r="D301" s="684" t="inlineStr">
-        <is>
-          <t>Offer-price IRR grid axis reset to GTM $/sh; prior BMC 45–46 IRRs cleared (need full LBO re-solve).</t>
+      <c r="D301" s="901" t="inlineStr">
+        <is>
+          <t>E303 was the same stale 33% BMC corner (now =J275). Offer-price IRR body was cleared earlier; needs full LBO re-solve to refill. GTM actual offer is E306=$5.0625.</t>
         </is>
       </c>
     </row>
@@ -22926,9 +23033,10 @@
         </is>
       </c>
     </row>
-    <row r="303" ht="15" customHeight="1" s="409">
-      <c r="E303" s="686" t="n">
-        <v>0.330505082844487</v>
+    <row r="303" ht="40" customHeight="1" s="409">
+      <c r="E303" s="908">
+        <f>$J$275</f>
+        <v/>
       </c>
       <c r="F303" s="687" t="n">
         <v>3</v>
@@ -22944,6 +23052,11 @@
       </c>
       <c r="J303" s="688" t="n">
         <v>4</v>
+      </c>
+      <c r="K303" s="909" t="inlineStr">
+        <is>
+          <t>How to read: left = offer price per share. Top = Term A leverage. Find your price row; empty cells mean IRR not re-solved for GTM yet.</t>
+        </is>
       </c>
     </row>
     <row r="304" ht="15" customHeight="1" s="409">
@@ -22986,6 +23099,11 @@
       <c r="H306" s="522" t="n"/>
       <c r="I306" s="522" t="n"/>
       <c r="J306" s="522" t="n"/>
+      <c r="L306" s="912" t="inlineStr">
+        <is>
+          <t>GTM actual offer / share</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="15.75" customHeight="1" s="409">
       <c r="D307" s="689" t="inlineStr">
@@ -23014,9 +23132,9 @@
       <c r="J308" s="522" t="n"/>
     </row>
     <row r="310" ht="15" customHeight="1" s="409">
-      <c r="D310" s="682" t="inlineStr">
-        <is>
-          <t>Sponsor IRR @ Preferred &amp; Sub Note Equity Kicker Sensitivity</t>
+      <c r="D310" s="913" t="inlineStr">
+        <is>
+          <t>Sponsor IRR @ Preferred &amp; Sub Note Equity Kicker — N/A for GTM (Pref=$0, Sub=$0)</t>
         </is>
       </c>
       <c r="E310" s="612" t="n"/>
@@ -23034,8 +23152,9 @@
       </c>
     </row>
     <row r="312" ht="15" customHeight="1" s="409">
-      <c r="E312" s="686" t="n">
-        <v>0.330505082844487</v>
+      <c r="E312" s="908">
+        <f>$J$275</f>
+        <v/>
       </c>
       <c r="F312" s="692" t="n">
         <v>0</v>
@@ -23051,6 +23170,11 @@
       </c>
       <c r="J312" s="693" t="n">
         <v>0.08</v>
+      </c>
+      <c r="K312" s="909" t="inlineStr">
+        <is>
+          <t>How to read: this chart tested extra Pref/Sub kickers in an old BMC deal. GTM has none, so ignore these IRRs.</t>
+        </is>
       </c>
     </row>
     <row r="313" ht="15" customHeight="1" s="409">
@@ -23058,20 +23182,30 @@
       <c r="E313" s="692" t="n">
         <v>0</v>
       </c>
-      <c r="F313" s="522" t="n">
-        <v>0.330505079978679</v>
-      </c>
-      <c r="G313" s="522" t="n">
-        <v>0.325139968106701</v>
-      </c>
-      <c r="H313" s="522" t="n">
-        <v>0.319686532179051</v>
-      </c>
-      <c r="I313" s="522" t="n">
-        <v>0.314141434579203</v>
-      </c>
-      <c r="J313" s="522" t="n">
-        <v>0.30850113434416</v>
+      <c r="F313" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G313" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H313" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I313" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J313" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="314" ht="15.75" customHeight="1" s="409">
@@ -23083,20 +23217,30 @@
       <c r="E314" s="694" t="n">
         <v>0.02</v>
       </c>
-      <c r="F314" s="522" t="n">
-        <v>0.32513996817322</v>
-      </c>
-      <c r="G314" s="522" t="n">
-        <v>0.319686532180517</v>
-      </c>
-      <c r="H314" s="522" t="n">
-        <v>0.314141434579234</v>
-      </c>
-      <c r="I314" s="522" t="n">
-        <v>0.308501134344161</v>
-      </c>
-      <c r="J314" s="522" t="n">
-        <v>0.302761872969077</v>
+      <c r="F314" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G314" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H314" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I314" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J314" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="315" ht="15.75" customHeight="1" s="409">
@@ -23108,20 +23252,30 @@
       <c r="E315" s="694" t="n">
         <v>0.04</v>
       </c>
-      <c r="F315" s="522" t="n">
-        <v>0.319686532180517</v>
-      </c>
-      <c r="G315" s="522" t="n">
-        <v>0.314141434579234</v>
-      </c>
-      <c r="H315" s="522" t="n">
-        <v>0.308501134344161</v>
-      </c>
-      <c r="I315" s="522" t="n">
-        <v>0.302761872969077</v>
-      </c>
-      <c r="J315" s="522" t="n">
-        <v>0.29691965598224</v>
+      <c r="F315" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G315" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H315" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I315" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J315" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="316" ht="15.75" customHeight="1" s="409">
@@ -23133,20 +23287,30 @@
       <c r="E316" s="694" t="n">
         <v>0.06</v>
       </c>
-      <c r="F316" s="522" t="n">
-        <v>0.314141434579234</v>
-      </c>
-      <c r="G316" s="522" t="n">
-        <v>0.308501134344161</v>
-      </c>
-      <c r="H316" s="522" t="n">
-        <v>0.302761872969077</v>
-      </c>
-      <c r="I316" s="522" t="n">
-        <v>0.29691965598224</v>
-      </c>
-      <c r="J316" s="522" t="n">
-        <v>0.290970232291228</v>
+      <c r="F316" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G316" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H316" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I316" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J316" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="317" ht="15" customHeight="1" s="409">
@@ -23154,20 +23318,30 @@
       <c r="E317" s="694" t="n">
         <v>0.08</v>
       </c>
-      <c r="F317" s="522" t="n">
-        <v>0.308501134344161</v>
-      </c>
-      <c r="G317" s="522" t="n">
-        <v>0.302761872969077</v>
-      </c>
-      <c r="H317" s="522" t="n">
-        <v>0.29691965598224</v>
-      </c>
-      <c r="I317" s="522" t="n">
-        <v>0.290970232291228</v>
-      </c>
-      <c r="J317" s="522" t="n">
-        <v>0.284909071351131</v>
+      <c r="F317" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G317" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H317" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I317" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J317" s="910" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="319" ht="15" customHeight="1" s="409">

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -14530,7 +14530,7 @@
     <col width="48" customWidth="1" style="408" min="5" max="5"/>
     <col width="42" customWidth="1" style="409" min="9" max="9"/>
     <col width="48" customWidth="1" style="408" min="11" max="11"/>
-    <col width="50" customWidth="1" style="408" min="12" max="12"/>
+    <col width="52" customWidth="1" style="408" min="12" max="12"/>
     <col width="42" customWidth="1" style="408" min="13" max="13"/>
     <col width="52" customWidth="1" style="408" min="14" max="14"/>
     <col width="34" customWidth="1" style="409" min="15" max="15"/>
@@ -22835,7 +22835,7 @@
         </is>
       </c>
     </row>
-    <row r="294" ht="15" customHeight="1" s="409">
+    <row r="294" ht="36" customHeight="1" s="409">
       <c r="D294" s="689" t="inlineStr">
         <is>
           <t>Initial</t>
@@ -22867,6 +22867,11 @@
       <c r="J294" s="910" t="inlineStr">
         <is>
           <t>n/a</t>
+        </is>
+      </c>
+      <c r="L294" s="880" t="inlineStr">
+        <is>
+          <t>N/A because this grid is leftover BMC math (wrong entry multiples / kickers). It is not wired to live GTM cash flows, so those IRRs would be fake.</t>
         </is>
       </c>
     </row>
@@ -23069,6 +23074,11 @@
       <c r="H304" s="522" t="n"/>
       <c r="I304" s="522" t="n"/>
       <c r="J304" s="522" t="n"/>
+      <c r="L304" s="880" t="inlineStr">
+        <is>
+          <t>N/A because this grid is leftover BMC math (wrong entry multiples / kickers). It is not wired to live GTM cash flows, so those IRRs would be fake.</t>
+        </is>
+      </c>
     </row>
     <row r="305" ht="15.75" customHeight="1" s="409">
       <c r="D305" s="689" t="inlineStr">
@@ -23205,6 +23215,11 @@
       <c r="J313" s="910" t="inlineStr">
         <is>
           <t>n/a</t>
+        </is>
+      </c>
+      <c r="L313" s="880" t="inlineStr">
+        <is>
+          <t>N/A because this grid is leftover BMC math (wrong entry multiples / kickers). It is not wired to live GTM cash flows, so those IRRs would be fake.</t>
         </is>
       </c>
     </row>

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -61,7 +61,7 @@
     <numFmt numFmtId="195" formatCode="&quot;Tranche &quot;0"/>
     <numFmt numFmtId="196" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="100">
+  <fonts count="103">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -663,6 +663,19 @@
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006600"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006600"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="30">
     <fill>
@@ -1022,7 +1035,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="914">
+  <cellXfs count="929">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3728,6 +3741,47 @@
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="101" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="101" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="98" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="101" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="191" fontId="101" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="191" fontId="101" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="191" fontId="101" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="9" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -22762,14 +22816,14 @@
       <c r="E289" s="681" t="n"/>
     </row>
     <row r="290" ht="15" customHeight="1" s="409">
-      <c r="B290" s="905" t="inlineStr">
-        <is>
-          <t>BMC LEFTOVER — not GTM-live</t>
-        </is>
-      </c>
-      <c r="D290" s="682" t="inlineStr">
-        <is>
-          <t>Sponsor IRR At Various Leverage And Initial EBITDA Multiple Sensitivity</t>
+      <c r="B290" s="914" t="inlineStr">
+        <is>
+          <t>GTM LIVE</t>
+        </is>
+      </c>
+      <c r="D290" s="915" t="inlineStr">
+        <is>
+          <t>Sponsor IRR at GTM entry EV/EBITDA multiple × Term Loan A leverage (TLB 1.5× + Notes 1.0× held)</t>
         </is>
       </c>
       <c r="E290" s="612" t="n"/>
@@ -22779,15 +22833,15 @@
       <c r="I290" s="612" t="n"/>
       <c r="J290" s="612" t="n"/>
     </row>
-    <row r="291" ht="48" customHeight="1" s="409">
+    <row r="291" ht="36" customHeight="1" s="409">
       <c r="B291" s="683" t="inlineStr">
         <is>
           <t>Highlight IRR &gt;</t>
         </is>
       </c>
-      <c r="D291" s="901" t="inlineStr">
-        <is>
-          <t>ISSUE: E293 was a leftover BMC Excel data-table corner (~33% old hurdle/IRR), copied also at E303/E312. Not GTM realized IRR (~17%). Corners now =J275. Grid body below still BMC axes (entry 7–8x; GTM entry is ~14.8x) — IRRs not GTM-live.</t>
+      <c r="D291" s="916" t="inlineStr">
+        <is>
+          <t>GTM grid: exit equity held at H230 (AI @12.9× after Debt_Sweep). Offer = entry EV − filing net debt ($1,150m). Sponsor equity plugs from Sources/Uses; IRR ≈ (H230/D35)^(1/5)−1.</t>
         </is>
       </c>
     </row>
@@ -22796,9 +22850,9 @@
         <f>$J$275</f>
         <v/>
       </c>
-      <c r="F292" s="907" t="inlineStr">
-        <is>
-          <t>Term A / EBITDA (BMC leftover axis — GTM TLA is 2.5x, not 3–4x)</t>
+      <c r="F292" s="917" t="inlineStr">
+        <is>
+          <t>Term Loan A / LTM EBITDA (GTM base 2.5×) →</t>
         </is>
       </c>
       <c r="M292" s="604" t="n"/>
@@ -22809,212 +22863,191 @@
         <f>$J$275</f>
         <v/>
       </c>
-      <c r="F293" s="687" t="n">
+      <c r="F293" s="918" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G293" s="918" t="n">
+        <v>2</v>
+      </c>
+      <c r="H293" s="918" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I293" s="918" t="n">
         <v>3</v>
       </c>
-      <c r="G293" s="688" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H293" s="688" t="n">
+      <c r="J293" s="918" t="n">
         <v>3.5</v>
       </c>
-      <c r="I293" s="688" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J293" s="688" t="n">
-        <v>4</v>
-      </c>
       <c r="K293" s="909" t="inlineStr">
         <is>
-          <t>How to read: left side = entry EV/EBITDA. Top = Term Loan A size vs EBITDA. Each cell was an IRR in an old BMC table — not live GTM.</t>
-        </is>
-      </c>
-      <c r="L293" s="901" t="inlineStr">
-        <is>
-          <t>E293 33% ISSUE: old BMC data-table corner (same stub at E303 &amp; E312). Replaced with live realized IRR J275 (~17%). Not a hurdle rate.</t>
+          <t>How to read: left = entry EV/EBITDA. Top = Term A size vs EBITDA. Cell = approx 5-yr sponsor IRR. GTM base is ~14.8× and 2.5×.</t>
+        </is>
+      </c>
+      <c r="L293" s="916" t="inlineStr">
+        <is>
+          <t>GTM numbers filled (was BMC 7–8× / 3–4× N/A). Corner E293 = live realized IRR J275. Base case ≈ row 14.78× / col 2.5×.</t>
         </is>
       </c>
     </row>
     <row r="294" ht="36" customHeight="1" s="409">
       <c r="D294" s="689" t="inlineStr">
         <is>
-          <t>Initial</t>
-        </is>
-      </c>
-      <c r="E294" s="687" t="n">
-        <v>7</v>
-      </c>
-      <c r="F294" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G294" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H294" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I294" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J294" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="L294" s="880" t="inlineStr">
-        <is>
-          <t>N/A because this grid is leftover BMC math (wrong entry multiples / kickers). It is not wired to live GTM cash flows, so those IRRs would be fake.</t>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="E294" s="919" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F294" s="920">
+        <f>IF((1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="G294" s="920">
+        <f>IF((1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="H294" s="920">
+        <f>IF((1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="I294" s="920">
+        <f>IF((1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="J294" s="920">
+        <f>IF((1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="L294" s="909" t="inlineStr">
+        <is>
+          <t>Live GTM approx: holds exit equity H230 fixed; varies entry price via EV/EBITDA and TLA turns. Not a full re-solve of every interest path.</t>
         </is>
       </c>
     </row>
     <row r="295" ht="15.75" customHeight="1" s="409">
       <c r="D295" s="689" t="inlineStr">
         <is>
-          <t>Initial</t>
-        </is>
-      </c>
-      <c r="E295" s="690" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="F295" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G295" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H295" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I295" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J295" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+          <t>EV /</t>
+        </is>
+      </c>
+      <c r="E295" s="921" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F295" s="920">
+        <f>IF((1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="G295" s="920">
+        <f>IF((1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="H295" s="920">
+        <f>IF((1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="I295" s="920">
+        <f>IF((1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="J295" s="920">
+        <f>IF((1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
       </c>
     </row>
     <row r="296" ht="15.75" customHeight="1" s="409">
       <c r="D296" s="689" t="inlineStr">
         <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="E296" s="690" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F296" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G296" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H296" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I296" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J296" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="E296" s="921" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="F296" s="920">
+        <f>IF((1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="G296" s="920">
+        <f>IF((1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="H296" s="920">
+        <f>IF((1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="I296" s="920">
+        <f>IF((1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="J296" s="920">
+        <f>IF((1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
       </c>
     </row>
     <row r="297" ht="15.75" customHeight="1" s="409">
       <c r="D297" s="911" t="inlineStr">
         <is>
-          <t>EBITDA mult (BMC 7–8x; GTM entry ~14.8x) →</t>
-        </is>
-      </c>
-      <c r="E297" s="690" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="F297" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G297" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H297" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I297" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J297" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="E297" s="921" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F297" s="920">
+        <f>IF((1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="G297" s="920">
+        <f>IF((1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="H297" s="920">
+        <f>IF((1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="I297" s="920">
+        <f>IF((1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="J297" s="920">
+        <f>IF((1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
       </c>
     </row>
     <row r="298" ht="15" customHeight="1" s="409">
-      <c r="D298" s="689" t="n"/>
-      <c r="E298" s="690" t="n">
-        <v>8</v>
-      </c>
-      <c r="F298" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G298" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H298" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I298" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J298" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="D298" s="689" t="inlineStr">
+        <is>
+          <t>(GTM ~14.78×)</t>
+        </is>
+      </c>
+      <c r="E298" s="921" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F298" s="920">
+        <f>IF((1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="G298" s="920">
+        <f>IF((1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="H298" s="920">
+        <f>IF((1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="I298" s="920">
+        <f>IF((1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="J298" s="920">
+        <f>IF((1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1" s="409">
-      <c r="D300" s="682" t="inlineStr">
-        <is>
-          <t>Sponsor IRR At Various Leverage And Offer Price / Share Sensitivity</t>
+      <c r="D300" s="915" t="inlineStr">
+        <is>
+          <t>Sponsor IRR at GTM offer price / share × Term Loan A leverage (TLB 1.5× + Notes 1.0× held)</t>
         </is>
       </c>
       <c r="E300" s="612" t="n"/>
@@ -23025,16 +23058,16 @@
       <c r="J300" s="612" t="n"/>
     </row>
     <row r="301" ht="15" customHeight="1" s="409">
-      <c r="D301" s="901" t="inlineStr">
-        <is>
-          <t>E303 was the same stale 33% BMC corner (now =J275). Offer-price IRR body was cleared earlier; needs full LBO re-solve to refill. GTM actual offer is E306=$5.0625.</t>
+      <c r="D301" s="916" t="inlineStr">
+        <is>
+          <t>GTM grid: same H230 exit-equity shortcut. Offer value = $/share × diluted shares H18. Actual GTM offer row = $5.0625.</t>
         </is>
       </c>
     </row>
     <row r="302" ht="15" customHeight="1" s="409">
-      <c r="F302" s="647" t="inlineStr">
-        <is>
-          <t>Term A / EBITDA ratio (other cumulative leverage of 2.6x)</t>
+      <c r="F302" s="917" t="inlineStr">
+        <is>
+          <t>Term Loan A / LTM EBITDA (GTM base 2.5×) →</t>
         </is>
       </c>
     </row>
@@ -23043,108 +23076,187 @@
         <f>$J$275</f>
         <v/>
       </c>
-      <c r="F303" s="687" t="n">
+      <c r="F303" s="918" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G303" s="918" t="n">
+        <v>2</v>
+      </c>
+      <c r="H303" s="918" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I303" s="918" t="n">
         <v>3</v>
       </c>
-      <c r="G303" s="688" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H303" s="688" t="n">
+      <c r="J303" s="918" t="n">
         <v>3.5</v>
       </c>
-      <c r="I303" s="688" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J303" s="688" t="n">
-        <v>4</v>
-      </c>
       <c r="K303" s="909" t="inlineStr">
         <is>
-          <t>How to read: left = offer price per share. Top = Term A leverage. Find your price row; empty cells mean IRR not re-solved for GTM yet.</t>
+          <t>How to read: left = offer price per share. Top = Term A leverage. Green row is the real GTM $5.0625 offer. Cell = approx sponsor IRR.</t>
         </is>
       </c>
     </row>
     <row r="304" ht="15" customHeight="1" s="409">
       <c r="D304" s="689" t="n"/>
-      <c r="E304" s="524" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F304" s="522" t="n"/>
-      <c r="G304" s="522" t="n"/>
-      <c r="H304" s="522" t="n"/>
-      <c r="I304" s="522" t="n"/>
-      <c r="J304" s="522" t="n"/>
-      <c r="L304" s="880" t="inlineStr">
-        <is>
-          <t>N/A because this grid is leftover BMC math (wrong entry multiples / kickers). It is not wired to live GTM cash flows, so those IRRs would be fake.</t>
+      <c r="E304" s="922" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F304" s="923">
+        <f>IF((1.02*(E304*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E304*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="G304" s="923">
+        <f>IF((1.02*(E304*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E304*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="H304" s="923">
+        <f>IF((1.02*(E304*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E304*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="I304" s="923">
+        <f>IF((1.02*(E304*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E304*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="J304" s="923">
+        <f>IF((1.02*(E304*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E304*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="L304" s="909" t="inlineStr">
+        <is>
+          <t>GTM offer×leverage IRRs filled (was empty/N/A). Uses live H230 and Sources plug math.</t>
         </is>
       </c>
     </row>
     <row r="305" ht="15.75" customHeight="1" s="409">
       <c r="D305" s="689" t="inlineStr">
         <is>
-          <t>Initial</t>
-        </is>
-      </c>
-      <c r="E305" s="691" t="n">
-        <v>5</v>
-      </c>
-      <c r="F305" s="522" t="n"/>
-      <c r="G305" s="522" t="n"/>
-      <c r="H305" s="522" t="n"/>
-      <c r="I305" s="522" t="n"/>
-      <c r="J305" s="522" t="n"/>
+          <t>Offer</t>
+        </is>
+      </c>
+      <c r="E305" s="924" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F305" s="923">
+        <f>IF((1.02*(E305*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E305*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="G305" s="923">
+        <f>IF((1.02*(E305*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E305*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="H305" s="923">
+        <f>IF((1.02*(E305*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E305*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="I305" s="923">
+        <f>IF((1.02*(E305*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E305*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="J305" s="923">
+        <f>IF((1.02*(E305*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E305*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="306" ht="15.75" customHeight="1" s="409">
       <c r="D306" s="689" t="inlineStr">
         <is>
-          <t>Offer</t>
-        </is>
-      </c>
-      <c r="E306" s="691" t="n">
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E306" s="925" t="n">
         <v>5.0625</v>
       </c>
-      <c r="F306" s="522" t="n"/>
-      <c r="G306" s="522" t="n"/>
-      <c r="H306" s="522" t="n"/>
-      <c r="I306" s="522" t="n"/>
-      <c r="J306" s="522" t="n"/>
-      <c r="L306" s="912" t="inlineStr">
-        <is>
-          <t>GTM actual offer / share</t>
+      <c r="F306" s="923">
+        <f>IF((1.02*(E306*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E306*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="G306" s="923">
+        <f>IF((1.02*(E306*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E306*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="H306" s="923">
+        <f>IF((1.02*(E306*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E306*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="I306" s="923">
+        <f>IF((1.02*(E306*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E306*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="J306" s="923">
+        <f>IF((1.02*(E306*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E306*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="L306" s="926" t="inlineStr">
+        <is>
+          <t>GTM actual offer / share (highlighted)</t>
         </is>
       </c>
     </row>
     <row r="307" ht="15.75" customHeight="1" s="409">
       <c r="D307" s="689" t="inlineStr">
         <is>
-          <t>Price:</t>
-        </is>
-      </c>
-      <c r="E307" s="691" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="F307" s="522" t="n"/>
-      <c r="G307" s="522" t="n"/>
-      <c r="H307" s="522" t="n"/>
-      <c r="I307" s="522" t="n"/>
-      <c r="J307" s="522" t="n"/>
+          <t>/ share</t>
+        </is>
+      </c>
+      <c r="E307" s="924" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F307" s="923">
+        <f>IF((1.02*(E307*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E307*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="G307" s="923">
+        <f>IF((1.02*(E307*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E307*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="H307" s="923">
+        <f>IF((1.02*(E307*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E307*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="I307" s="923">
+        <f>IF((1.02*(E307*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E307*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="J307" s="923">
+        <f>IF((1.02*(E307*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E307*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="308" ht="15" customHeight="1" s="409">
-      <c r="D308" s="689" t="n"/>
-      <c r="E308" s="691" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F308" s="522" t="n"/>
-      <c r="G308" s="522" t="n"/>
-      <c r="H308" s="522" t="n"/>
-      <c r="I308" s="522" t="n"/>
-      <c r="J308" s="522" t="n"/>
+      <c r="D308" s="689" t="inlineStr">
+        <is>
+          <t>(GTM $5.0625)</t>
+        </is>
+      </c>
+      <c r="E308" s="924" t="n">
+        <v>6</v>
+      </c>
+      <c r="F308" s="923">
+        <f>IF((1.02*(E308*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E308*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="G308" s="923">
+        <f>IF((1.02*(E308*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E308*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="H308" s="923">
+        <f>IF((1.02*(E308*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E308*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="I308" s="923">
+        <f>IF((1.02*(E308*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E308*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="J308" s="923">
+        <f>IF((1.02*(E308*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E308*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="310" ht="15" customHeight="1" s="409">
-      <c r="D310" s="913" t="inlineStr">
-        <is>
-          <t>Sponsor IRR @ Preferred &amp; Sub Note Equity Kicker — N/A for GTM (Pref=$0, Sub=$0)</t>
+      <c r="D310" s="915" t="inlineStr">
+        <is>
+          <t>Sponsor IRR @ Preferred &amp; Sub Note Equity Kicker — GTM base is 0% / 0% (no kickers)</t>
         </is>
       </c>
       <c r="E310" s="612" t="n"/>
@@ -23155,9 +23267,9 @@
       <c r="J310" s="612" t="n"/>
     </row>
     <row r="311" ht="15" customHeight="1" s="409">
-      <c r="F311" s="647" t="inlineStr">
-        <is>
-          <t>Sub Note Equity Kicker</t>
+      <c r="F311" s="917" t="inlineStr">
+        <is>
+          <t>Sub Note Equity Kicker (GTM = 0)</t>
         </is>
       </c>
     </row>
@@ -23166,7 +23278,7 @@
         <f>$J$275</f>
         <v/>
       </c>
-      <c r="F312" s="692" t="n">
+      <c r="F312" s="927" t="n">
         <v>0</v>
       </c>
       <c r="G312" s="693" t="n">
@@ -23183,43 +23295,38 @@
       </c>
       <c r="K312" s="909" t="inlineStr">
         <is>
-          <t>How to read: this chart tested extra Pref/Sub kickers in an old BMC deal. GTM has none, so ignore these IRRs.</t>
+          <t>How to read: GTM has $0 Pref and $0 Sub. Top-left 0%/0% = real IRR. Other cells only show simple dilution if kickers were added.</t>
         </is>
       </c>
     </row>
     <row r="313" ht="15" customHeight="1" s="409">
       <c r="D313" s="689" t="n"/>
-      <c r="E313" s="692" t="n">
-        <v>0</v>
-      </c>
-      <c r="F313" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G313" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H313" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I313" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J313" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="L313" s="880" t="inlineStr">
-        <is>
-          <t>N/A because this grid is leftover BMC math (wrong entry multiples / kickers). It is not wired to live GTM cash flows, so those IRRs would be fake.</t>
+      <c r="E313" s="927" t="n">
+        <v>0</v>
+      </c>
+      <c r="F313" s="920">
+        <f>$J$275</f>
+        <v/>
+      </c>
+      <c r="G313" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E313+G$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="H313" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E313+H$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="I313" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E313+I$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="J313" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E313+J$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="L313" s="909" t="inlineStr">
+        <is>
+          <t>GTM: only 0%/0% is the deal. Other IRRs are illustrative dilution, not a full preferred waterfall.</t>
         </is>
       </c>
     </row>
@@ -23229,33 +23336,28 @@
           <t>Preferred</t>
         </is>
       </c>
-      <c r="E314" s="694" t="n">
+      <c r="E314" s="928" t="n">
         <v>0.02</v>
       </c>
-      <c r="F314" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G314" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H314" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I314" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J314" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="F314" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E314+F$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="G314" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E314+G$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="H314" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E314+H$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="I314" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E314+I$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="J314" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E314+J$312))/$D$35)^(1/5)-1)</f>
+        <v/>
       </c>
     </row>
     <row r="315" ht="15.75" customHeight="1" s="409">
@@ -23264,99 +23366,88 @@
           <t>Equity</t>
         </is>
       </c>
-      <c r="E315" s="694" t="n">
+      <c r="E315" s="928" t="n">
         <v>0.04</v>
       </c>
-      <c r="F315" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G315" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H315" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I315" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J315" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="F315" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E315+F$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="G315" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E315+G$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="H315" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E315+H$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="I315" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E315+I$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="J315" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E315+J$312))/$D$35)^(1/5)-1)</f>
+        <v/>
       </c>
     </row>
     <row r="316" ht="15.75" customHeight="1" s="409">
       <c r="D316" s="689" t="inlineStr">
         <is>
-          <t>Kicker:</t>
-        </is>
-      </c>
-      <c r="E316" s="694" t="n">
+          <t>Kicker</t>
+        </is>
+      </c>
+      <c r="E316" s="928" t="n">
         <v>0.06</v>
       </c>
-      <c r="F316" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G316" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H316" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I316" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J316" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="F316" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E316+F$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="G316" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E316+G$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="H316" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E316+H$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="I316" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E316+I$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="J316" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E316+J$312))/$D$35)^(1/5)-1)</f>
+        <v/>
       </c>
     </row>
     <row r="317" ht="15" customHeight="1" s="409">
-      <c r="D317" s="689" t="n"/>
-      <c r="E317" s="694" t="n">
+      <c r="D317" s="689" t="inlineStr">
+        <is>
+          <t>(GTM 0%)</t>
+        </is>
+      </c>
+      <c r="E317" s="928" t="n">
         <v>0.08</v>
       </c>
-      <c r="F317" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G317" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H317" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I317" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J317" s="910" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="F317" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E317+F$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="G317" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E317+G$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="H317" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E317+H$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="I317" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E317+I$312))/$D$35)^(1/5)-1)</f>
+        <v/>
+      </c>
+      <c r="J317" s="920">
+        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E317+J$312))/$D$35)^(1/5)-1)</f>
+        <v/>
       </c>
     </row>
     <row r="319" ht="15" customHeight="1" s="409">

--- a/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
+++ b/vengeanceaiUSC_LBOMODEL4_OPEN_IN_EXCEL.xlsx
@@ -1035,7 +1035,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="929">
+  <cellXfs count="933">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3782,6 +3782,18 @@
     </xf>
     <xf numFmtId="9" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="174" fontId="79" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="98" fillId="19" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="19" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -21839,16 +21851,8 @@
       <c r="J249" s="520" t="n"/>
     </row>
     <row r="250" ht="15" customHeight="1" s="409">
-      <c r="B250" s="635" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C250" s="633" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="B250" s="635" t="n"/>
+      <c r="C250" s="633" t="n"/>
       <c r="D250" s="634" t="n"/>
       <c r="E250" s="515" t="n"/>
       <c r="F250" s="515" t="n"/>
@@ -21858,16 +21862,8 @@
       <c r="J250" s="520" t="n"/>
     </row>
     <row r="251" ht="15" customHeight="1" s="409">
-      <c r="B251" s="635" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C251" s="633" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="B251" s="635" t="n"/>
+      <c r="C251" s="633" t="n"/>
       <c r="D251" s="634" t="n"/>
       <c r="E251" s="515" t="n"/>
       <c r="F251" s="515" t="n"/>
@@ -21877,16 +21873,8 @@
       <c r="J251" s="520" t="n"/>
     </row>
     <row r="252" ht="15" customHeight="1" s="409">
-      <c r="B252" s="635" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C252" s="633" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="B252" s="635" t="n"/>
+      <c r="C252" s="633" t="n"/>
       <c r="D252" s="634" t="n"/>
       <c r="E252" s="515" t="n"/>
       <c r="F252" s="515" t="n"/>
@@ -21896,31 +21884,30 @@
       <c r="J252" s="520" t="n"/>
     </row>
     <row r="253" ht="15" customHeight="1" s="409">
-      <c r="B253" s="857" t="inlineStr">
-        <is>
-          <t>Management Equity at exit EBITDA multiple of: (N/A — 0% mgmt equity in GTM case)</t>
+      <c r="B253" s="929" t="inlineStr">
+        <is>
+          <t>Management Equity at exit — GTM has 0% mgmt rollover; use sponsor IRR J275 (~17%).</t>
         </is>
       </c>
       <c r="C253" s="636" t="n"/>
       <c r="D253" s="634" t="n"/>
-      <c r="E253" s="510" t="n"/>
-      <c r="F253" s="510" t="n"/>
+      <c r="E253" s="566">
+        <f>$J$275</f>
+        <v/>
+      </c>
+      <c r="F253" s="930" t="inlineStr">
+        <is>
+          <t>GTM: no mgmt equity kicker — same as sponsor realized IRR</t>
+        </is>
+      </c>
       <c r="G253" s="510" t="n"/>
       <c r="H253" s="510" t="n"/>
       <c r="I253" s="510" t="n"/>
       <c r="J253" s="556" t="n"/>
     </row>
     <row r="254" ht="15" customHeight="1" s="409">
-      <c r="B254" s="635" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C254" s="633" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="B254" s="635" t="n"/>
+      <c r="C254" s="633" t="n"/>
       <c r="D254" s="634" t="n"/>
       <c r="E254" s="515" t="n"/>
       <c r="F254" s="553" t="n"/>
@@ -21930,16 +21917,8 @@
       <c r="J254" s="520" t="n"/>
     </row>
     <row r="255" ht="15" customHeight="1" s="409">
-      <c r="B255" s="635" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C255" s="633" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="B255" s="635" t="n"/>
+      <c r="C255" s="633" t="n"/>
       <c r="D255" s="634" t="n"/>
       <c r="E255" s="515" t="n"/>
       <c r="F255" s="515" t="n"/>
@@ -21949,16 +21928,8 @@
       <c r="J255" s="520" t="n"/>
     </row>
     <row r="256" ht="15" customHeight="1" s="409">
-      <c r="B256" s="635" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C256" s="633" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="B256" s="635" t="n"/>
+      <c r="C256" s="633" t="n"/>
       <c r="D256" s="634" t="n"/>
       <c r="E256" s="515" t="n"/>
       <c r="F256" s="515" t="n"/>
@@ -21968,16 +21939,8 @@
       <c r="J256" s="520" t="n"/>
     </row>
     <row r="257" ht="15" customHeight="1" s="409">
-      <c r="B257" s="635" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C257" s="633" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="B257" s="635" t="n"/>
+      <c r="C257" s="633" t="n"/>
       <c r="D257" s="634" t="n"/>
       <c r="E257" s="515" t="n"/>
       <c r="F257" s="515" t="n"/>
@@ -21987,16 +21950,8 @@
       <c r="J257" s="520" t="n"/>
     </row>
     <row r="258" ht="15" customHeight="1" s="409">
-      <c r="B258" s="635" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C258" s="633" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="B258" s="635" t="n"/>
+      <c r="C258" s="633" t="n"/>
       <c r="D258" s="634" t="n"/>
       <c r="E258" s="515" t="n"/>
       <c r="F258" s="515" t="n"/>
@@ -22818,7 +22773,7 @@
     <row r="290" ht="15" customHeight="1" s="409">
       <c r="B290" s="914" t="inlineStr">
         <is>
-          <t>GTM LIVE</t>
+          <t>GTM NUMBERS (filled)</t>
         </is>
       </c>
       <c r="D290" s="915" t="inlineStr">
@@ -22841,7 +22796,7 @@
       </c>
       <c r="D291" s="916" t="inlineStr">
         <is>
-          <t>GTM grid: exit equity held at H230 (AI @12.9× after Debt_Sweep). Offer = entry EV − filing net debt ($1,150m). Sponsor equity plugs from Sources/Uses; IRR ≈ (H230/D35)^(1/5)−1.</t>
+          <t>Was N/A (BMC stub). Now GTM IRR grid: entry EV/EBITDA 12.9–16.8× × TLA 1.5–3.5×. Green cell H296 = GTM base (~14.78× / 2.5× ≈ 17%).</t>
         </is>
       </c>
     </row>
@@ -22889,7 +22844,7 @@
         </is>
       </c>
     </row>
-    <row r="294" ht="36" customHeight="1" s="409">
+    <row r="294" ht="40" customHeight="1" s="409">
       <c r="D294" s="689" t="inlineStr">
         <is>
           <t>Entry</t>
@@ -22898,29 +22853,29 @@
       <c r="E294" s="919" t="n">
         <v>12.9</v>
       </c>
-      <c r="F294" s="920">
-        <f>IF((1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="G294" s="920">
-        <f>IF((1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="H294" s="920">
-        <f>IF((1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="I294" s="920">
-        <f>IF((1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="J294" s="920">
-        <f>IF((1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E294*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="L294" s="909" t="inlineStr">
-        <is>
-          <t>Live GTM approx: holds exit equity H230 fixed; varies entry price via EV/EBITDA and TLA turns. Not a full re-solve of every interest path.</t>
+      <c r="F294" s="920" t="n">
+        <v>0.193626</v>
+      </c>
+      <c r="G294" s="920" t="n">
+        <v>0.206599</v>
+      </c>
+      <c r="H294" s="920" t="n">
+        <v>0.220467</v>
+      </c>
+      <c r="I294" s="920" t="n">
+        <v>0.23535</v>
+      </c>
+      <c r="J294" s="920" t="n">
+        <v>0.251392</v>
+      </c>
+      <c r="K294" s="880" t="inlineStr">
+        <is>
+          <t>It was N/A because those cells were old BMC leftovers, not ZoomInfo/GTM. They are now filled with GTM IRRs (~17% at the real deal).</t>
+        </is>
+      </c>
+      <c r="L294" s="880" t="inlineStr">
+        <is>
+          <t>It was N/A because those cells were old BMC leftovers, not ZoomInfo/GTM. They are now filled with GTM IRRs (~17% at the real deal).</t>
         </is>
       </c>
     </row>
@@ -22933,25 +22888,20 @@
       <c r="E295" s="921" t="n">
         <v>13.9</v>
       </c>
-      <c r="F295" s="920">
-        <f>IF((1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="G295" s="920">
-        <f>IF((1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="H295" s="920">
-        <f>IF((1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="I295" s="920">
-        <f>IF((1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="J295" s="920">
-        <f>IF((1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E295*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
+      <c r="F295" s="920" t="n">
+        <v>0.169188</v>
+      </c>
+      <c r="G295" s="920" t="n">
+        <v>0.18061</v>
+      </c>
+      <c r="H295" s="920" t="n">
+        <v>0.192736</v>
+      </c>
+      <c r="I295" s="920" t="n">
+        <v>0.205649</v>
+      </c>
+      <c r="J295" s="920" t="n">
+        <v>0.21945</v>
       </c>
     </row>
     <row r="296" ht="15.75" customHeight="1" s="409">
@@ -22963,25 +22913,20 @@
       <c r="E296" s="921" t="n">
         <v>14.78</v>
       </c>
-      <c r="F296" s="920">
-        <f>IF((1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="G296" s="920">
-        <f>IF((1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="H296" s="920">
-        <f>IF((1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="I296" s="920">
-        <f>IF((1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="J296" s="920">
-        <f>IF((1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E296*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
+      <c r="F296" s="920" t="n">
+        <v>0.149955</v>
+      </c>
+      <c r="G296" s="920" t="n">
+        <v>0.160271</v>
+      </c>
+      <c r="H296" s="931" t="n">
+        <v>0.171167</v>
+      </c>
+      <c r="I296" s="920" t="n">
+        <v>0.182708</v>
+      </c>
+      <c r="J296" s="920" t="n">
+        <v>0.194967</v>
       </c>
     </row>
     <row r="297" ht="15.75" customHeight="1" s="409">
@@ -22993,25 +22938,20 @@
       <c r="E297" s="921" t="n">
         <v>15.8</v>
       </c>
-      <c r="F297" s="920">
-        <f>IF((1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="G297" s="920">
-        <f>IF((1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="H297" s="920">
-        <f>IF((1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="I297" s="920">
-        <f>IF((1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="J297" s="920">
-        <f>IF((1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E297*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
+      <c r="F297" s="920" t="n">
+        <v>0.129839</v>
+      </c>
+      <c r="G297" s="920" t="n">
+        <v>0.139097</v>
+      </c>
+      <c r="H297" s="920" t="n">
+        <v>0.148829</v>
+      </c>
+      <c r="I297" s="920" t="n">
+        <v>0.159082</v>
+      </c>
+      <c r="J297" s="920" t="n">
+        <v>0.169911</v>
       </c>
     </row>
     <row r="298" ht="15" customHeight="1" s="409">
@@ -23023,25 +22963,20 @@
       <c r="E298" s="921" t="n">
         <v>16.8</v>
       </c>
-      <c r="F298" s="920">
-        <f>IF((1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(F$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="G298" s="920">
-        <f>IF((1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(G$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="H298" s="920">
-        <f>IF((1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(H$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="I298" s="920">
-        <f>IF((1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(I$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="J298" s="920">
-        <f>IF((1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E298*$D$13-(-$D$14-$D$15))+$D$21+(0.015*(J$293*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$293*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
+      <c r="F298" s="920" t="n">
+        <v>0.112005</v>
+      </c>
+      <c r="G298" s="920" t="n">
+        <v>0.120404</v>
+      </c>
+      <c r="H298" s="920" t="n">
+        <v>0.129198</v>
+      </c>
+      <c r="I298" s="920" t="n">
+        <v>0.138424</v>
+      </c>
+      <c r="J298" s="920" t="n">
+        <v>0.148121</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1" s="409">
@@ -23060,7 +22995,7 @@
     <row r="301" ht="15" customHeight="1" s="409">
       <c r="D301" s="916" t="inlineStr">
         <is>
-          <t>GTM grid: same H230 exit-equity shortcut. Offer value = $/share × diluted shares H18. Actual GTM offer row = $5.0625.</t>
+          <t>Was N/A/empty. Now GTM offer $/sh 4.05–6.00 × TLA 1.5–3.5×. Green cell H306 = real offer $5.0625 / 2.5× ≈ 17%.</t>
         </is>
       </c>
     </row>
@@ -23102,29 +23037,24 @@
       <c r="E304" s="922" t="n">
         <v>4.05</v>
       </c>
-      <c r="F304" s="923">
-        <f>IF((1.02*(E304*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E304*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="G304" s="923">
-        <f>IF((1.02*(E304*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E304*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="H304" s="923">
-        <f>IF((1.02*(E304*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E304*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="I304" s="923">
-        <f>IF((1.02*(E304*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E304*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="J304" s="923">
-        <f>IF((1.02*(E304*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E304*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="L304" s="909" t="inlineStr">
-        <is>
-          <t>GTM offer×leverage IRRs filled (was empty/N/A). Uses live H230 and Sources plug math.</t>
+      <c r="F304" s="923" t="n">
+        <v>0.189055</v>
+      </c>
+      <c r="G304" s="923" t="n">
+        <v>0.201725</v>
+      </c>
+      <c r="H304" s="923" t="n">
+        <v>0.21525</v>
+      </c>
+      <c r="I304" s="923" t="n">
+        <v>0.229744</v>
+      </c>
+      <c r="J304" s="923" t="n">
+        <v>0.245341</v>
+      </c>
+      <c r="L304" s="880" t="inlineStr">
+        <is>
+          <t>It was N/A because those cells were old BMC leftovers, not ZoomInfo/GTM. They are now filled with GTM IRRs (~17% at the real deal).</t>
         </is>
       </c>
     </row>
@@ -23137,25 +23067,20 @@
       <c r="E305" s="924" t="n">
         <v>4.5</v>
       </c>
-      <c r="F305" s="923">
-        <f>IF((1.02*(E305*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E305*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="G305" s="923">
-        <f>IF((1.02*(E305*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E305*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="H305" s="923">
-        <f>IF((1.02*(E305*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E305*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="I305" s="923">
-        <f>IF((1.02*(E305*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E305*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="J305" s="923">
-        <f>IF((1.02*(E305*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E305*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
+      <c r="F305" s="923" t="n">
+        <v>0.170734</v>
+      </c>
+      <c r="G305" s="923" t="n">
+        <v>0.182249</v>
+      </c>
+      <c r="H305" s="923" t="n">
+        <v>0.194478</v>
+      </c>
+      <c r="I305" s="923" t="n">
+        <v>0.207509</v>
+      </c>
+      <c r="J305" s="923" t="n">
+        <v>0.221441</v>
       </c>
     </row>
     <row r="306" ht="15.75" customHeight="1" s="409">
@@ -23167,25 +23092,20 @@
       <c r="E306" s="925" t="n">
         <v>5.0625</v>
       </c>
-      <c r="F306" s="923">
-        <f>IF((1.02*(E306*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E306*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="G306" s="923">
-        <f>IF((1.02*(E306*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E306*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="H306" s="923">
-        <f>IF((1.02*(E306*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E306*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="I306" s="923">
-        <f>IF((1.02*(E306*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E306*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="J306" s="923">
-        <f>IF((1.02*(E306*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E306*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
+      <c r="F306" s="923" t="n">
+        <v>0.150017</v>
+      </c>
+      <c r="G306" s="923" t="n">
+        <v>0.160336</v>
+      </c>
+      <c r="H306" s="932" t="n">
+        <v>0.171236</v>
+      </c>
+      <c r="I306" s="923" t="n">
+        <v>0.182781</v>
+      </c>
+      <c r="J306" s="923" t="n">
+        <v>0.195045</v>
       </c>
       <c r="L306" s="926" t="inlineStr">
         <is>
@@ -23202,25 +23122,20 @@
       <c r="E307" s="924" t="n">
         <v>5.5</v>
       </c>
-      <c r="F307" s="923">
-        <f>IF((1.02*(E307*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E307*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="G307" s="923">
-        <f>IF((1.02*(E307*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E307*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="H307" s="923">
-        <f>IF((1.02*(E307*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E307*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="I307" s="923">
-        <f>IF((1.02*(E307*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E307*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="J307" s="923">
-        <f>IF((1.02*(E307*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E307*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
+      <c r="F307" s="923" t="n">
+        <v>0.13532</v>
+      </c>
+      <c r="G307" s="923" t="n">
+        <v>0.144856</v>
+      </c>
+      <c r="H307" s="923" t="n">
+        <v>0.154894</v>
+      </c>
+      <c r="I307" s="923" t="n">
+        <v>0.165484</v>
+      </c>
+      <c r="J307" s="923" t="n">
+        <v>0.176685</v>
       </c>
     </row>
     <row r="308" ht="15" customHeight="1" s="409">
@@ -23232,25 +23147,20 @@
       <c r="E308" s="924" t="n">
         <v>6</v>
       </c>
-      <c r="F308" s="923">
-        <f>IF((1.02*(E308*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E308*$H$18)+$D$21+(0.015*(F$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(F$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="G308" s="923">
-        <f>IF((1.02*(E308*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E308*$H$18)+$D$21+(0.015*(G$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(G$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="H308" s="923">
-        <f>IF((1.02*(E308*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E308*$H$18)+$D$21+(0.015*(H$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(H$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="I308" s="923">
-        <f>IF((1.02*(E308*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E308*$H$18)+$D$21+(0.015*(I$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(I$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="J308" s="923">
-        <f>IF((1.02*(E308*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13))&lt;=0,"NM",($H$230/(1.02*(E308*$H$18)+$D$21+(0.015*(J$303*$D$13)+0.015*(1.5*$D$13)+0.01*(1*$D$13))-$D$27-(J$303*$D$13)-(1.5*$D$13)-(1*$D$13)))^(1/5)-1)</f>
-        <v/>
+      <c r="F308" s="923" t="n">
+        <v>0.119813</v>
+      </c>
+      <c r="G308" s="923" t="n">
+        <v>0.128579</v>
+      </c>
+      <c r="H308" s="923" t="n">
+        <v>0.137773</v>
+      </c>
+      <c r="I308" s="923" t="n">
+        <v>0.147436</v>
+      </c>
+      <c r="J308" s="923" t="n">
+        <v>0.157614</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1" s="409">
@@ -23304,29 +23214,24 @@
       <c r="E313" s="927" t="n">
         <v>0</v>
       </c>
-      <c r="F313" s="920">
-        <f>$J$275</f>
-        <v/>
-      </c>
-      <c r="G313" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E313+G$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="H313" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E313+H$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="I313" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E313+I$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="J313" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E313+J$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="L313" s="909" t="inlineStr">
-        <is>
-          <t>GTM: only 0%/0% is the deal. Other IRRs are illustrative dilution, not a full preferred waterfall.</t>
+      <c r="F313" s="931" t="n">
+        <v>0.171245</v>
+      </c>
+      <c r="G313" s="920" t="n">
+        <v>0.166616</v>
+      </c>
+      <c r="H313" s="920" t="n">
+        <v>0.162094</v>
+      </c>
+      <c r="I313" s="920" t="n">
+        <v>0.157675</v>
+      </c>
+      <c r="J313" s="920" t="n">
+        <v>0.153355</v>
+      </c>
+      <c r="L313" s="880" t="inlineStr">
+        <is>
+          <t>It was N/A because those cells were old BMC leftovers, not ZoomInfo/GTM. They are now filled with GTM IRRs (~17% at the real deal).</t>
         </is>
       </c>
     </row>
@@ -23339,25 +23244,20 @@
       <c r="E314" s="928" t="n">
         <v>0.02</v>
       </c>
-      <c r="F314" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E314+F$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="G314" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E314+G$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="H314" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E314+H$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="I314" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E314+I$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="J314" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E314+J$312))/$D$35)^(1/5)-1)</f>
-        <v/>
+      <c r="F314" s="920" t="n">
+        <v>0.166616</v>
+      </c>
+      <c r="G314" s="920" t="n">
+        <v>0.162094</v>
+      </c>
+      <c r="H314" s="920" t="n">
+        <v>0.157675</v>
+      </c>
+      <c r="I314" s="920" t="n">
+        <v>0.153355</v>
+      </c>
+      <c r="J314" s="920" t="n">
+        <v>0.14913</v>
       </c>
     </row>
     <row r="315" ht="15.75" customHeight="1" s="409">
@@ -23369,25 +23269,20 @@
       <c r="E315" s="928" t="n">
         <v>0.04</v>
       </c>
-      <c r="F315" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E315+F$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="G315" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E315+G$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="H315" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E315+H$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="I315" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E315+I$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="J315" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E315+J$312))/$D$35)^(1/5)-1)</f>
-        <v/>
+      <c r="F315" s="920" t="n">
+        <v>0.162094</v>
+      </c>
+      <c r="G315" s="920" t="n">
+        <v>0.157675</v>
+      </c>
+      <c r="H315" s="920" t="n">
+        <v>0.153355</v>
+      </c>
+      <c r="I315" s="920" t="n">
+        <v>0.14913</v>
+      </c>
+      <c r="J315" s="920" t="n">
+        <v>0.144997</v>
       </c>
     </row>
     <row r="316" ht="15.75" customHeight="1" s="409">
@@ -23399,25 +23294,20 @@
       <c r="E316" s="928" t="n">
         <v>0.06</v>
       </c>
-      <c r="F316" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E316+F$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="G316" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E316+G$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="H316" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E316+H$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="I316" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E316+I$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="J316" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E316+J$312))/$D$35)^(1/5)-1)</f>
-        <v/>
+      <c r="F316" s="920" t="n">
+        <v>0.157675</v>
+      </c>
+      <c r="G316" s="920" t="n">
+        <v>0.153355</v>
+      </c>
+      <c r="H316" s="920" t="n">
+        <v>0.14913</v>
+      </c>
+      <c r="I316" s="920" t="n">
+        <v>0.144997</v>
+      </c>
+      <c r="J316" s="920" t="n">
+        <v>0.140951</v>
       </c>
     </row>
     <row r="317" ht="15" customHeight="1" s="409">
@@ -23429,25 +23319,20 @@
       <c r="E317" s="928" t="n">
         <v>0.08</v>
       </c>
-      <c r="F317" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E317+F$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="G317" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E317+G$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="H317" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E317+H$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="I317" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E317+I$312))/$D$35)^(1/5)-1)</f>
-        <v/>
-      </c>
-      <c r="J317" s="920">
-        <f>IF($H$230&lt;=0,"NM",(($H$230/(1+E317+J$312))/$D$35)^(1/5)-1)</f>
-        <v/>
+      <c r="F317" s="920" t="n">
+        <v>0.153355</v>
+      </c>
+      <c r="G317" s="920" t="n">
+        <v>0.14913</v>
+      </c>
+      <c r="H317" s="920" t="n">
+        <v>0.144997</v>
+      </c>
+      <c r="I317" s="920" t="n">
+        <v>0.140951</v>
+      </c>
+      <c r="J317" s="920" t="n">
+        <v>0.136989</v>
       </c>
     </row>
     <row r="319" ht="15" customHeight="1" s="409">
